--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU373"/>
+  <dimension ref="A1:AU378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G4">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G34">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G36">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G45">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G84">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G95">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G105">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G182">
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-09-05 11:15:00</t>
+          <t>2026-09-05 11:00:00</t>
         </is>
       </c>
     </row>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G184">
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-09-05 11:30:00</t>
+          <t>2026-09-05 11:15:00</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G194">
@@ -32047,12 +32047,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fanja</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G195">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>2026-09-05 11:45:00</t>
+          <t>2026-09-05 11:30:00</t>
         </is>
       </c>
     </row>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Fanja</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G196">
@@ -32373,27 +32373,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-09-05 12:00:00</t>
+          <t>2026-09-05 11:45:00</t>
         </is>
       </c>
     </row>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,22 +32704,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G202">
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G203">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-09-05 12:15:00</t>
+          <t>2026-09-05 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G205">
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-09-05 12:30:00</t>
+          <t>2026-09-05 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,22 +34497,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G210">
@@ -34655,27 +34655,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G211">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-09-05 12:50:00</t>
+          <t>2026-09-05 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34818,7 +34818,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G212">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-09-05 12:55:00</t>
+          <t>2026-09-05 12:50:00</t>
         </is>
       </c>
     </row>
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-05 13:00:00</t>
+          <t>2026-09-05 12:55:00</t>
         </is>
       </c>
     </row>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,22 +35475,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G216">
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,22 +36290,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,22 +36453,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,22 +36942,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,22 +37105,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G233">
@@ -38404,12 +38404,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G234">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:00</t>
+          <t>2026-09-05 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-09-05 13:15:00</t>
+          <t>2026-09-05 13:10:00</t>
         </is>
       </c>
     </row>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G237">
@@ -39056,27 +39056,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-05 13:30:00</t>
+          <t>2026-09-05 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39224,22 +39224,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G240">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G245">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G246">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-09-05 13:45:00</t>
+          <t>2026-09-05 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G247">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G251">
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-09-05 14:00:00</t>
+          <t>2026-09-05 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G253">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G259">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G260">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G265">
@@ -43620,12 +43620,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-05 14:15:00</t>
+          <t>2026-09-05 14:00:00</t>
         </is>
       </c>
     </row>
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-05 14:30:00</t>
+          <t>2026-09-05 14:15:00</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G268">
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G270">
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G271">
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-05 15:00:00</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q272">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R272">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S272">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T272">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U272">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V272">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W272">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X272">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y272">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z272">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA272">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB272">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC272">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD272">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF272">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG272">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK272">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G280">
@@ -46070,22 +46070,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G281">
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G283">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46554,27 +46554,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G288">
@@ -47369,27 +47369,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -47858,27 +47858,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G293">
@@ -48184,27 +48184,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48510,27 +48510,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48673,27 +48673,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48841,22 +48841,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G298">
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G299">
@@ -49167,22 +49167,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G300">
@@ -49330,22 +49330,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G301">
@@ -49493,22 +49493,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G304">
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G305">
@@ -50145,22 +50145,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G306">
@@ -50308,22 +50308,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G307">
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G308">
@@ -50509,68 +50509,68 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N308">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="O308">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P308">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q308">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R308">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S308">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T308">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U308">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V308">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W308">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X308">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y308">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z308">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA308">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB308">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC308">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD308">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE308">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF308">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG308">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK308">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -50629,27 +50629,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -50792,27 +50792,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -50955,12 +50955,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-05 18:15:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51118,12 +51118,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51281,27 +51281,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G313">
@@ -51324,68 +51324,68 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X313">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -51607,12 +51607,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G315">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -51770,12 +51770,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G316">
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30:00</t>
+          <t>2026-09-05 18:00:00</t>
         </is>
       </c>
     </row>
@@ -51933,12 +51933,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G317">
@@ -52084,7 +52084,7 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:15:00</t>
         </is>
       </c>
     </row>
@@ -52096,12 +52096,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G318">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -52259,12 +52259,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -52748,12 +52748,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 19:30:00</t>
         </is>
       </c>
     </row>
@@ -52911,7 +52911,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53074,12 +53074,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G324">
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G325">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53400,12 +53400,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G326">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53563,12 +53563,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G327">
@@ -53714,7 +53714,7 @@
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53731,7 +53731,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,7 +53894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G329">
@@ -54057,7 +54057,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G331">
@@ -54378,12 +54378,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -54541,27 +54541,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -54704,27 +54704,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -54867,27 +54867,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55030,27 +55030,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G336">
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55193,27 +55193,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G337">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55361,22 +55361,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G341">
@@ -56013,7 +56013,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G342">
@@ -56176,22 +56176,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G343">
@@ -56339,22 +56339,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G344">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G345">
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G347">
@@ -56991,22 +56991,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G348">
@@ -57154,22 +57154,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G349">
@@ -57317,22 +57317,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G350">
@@ -57480,22 +57480,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G351">
@@ -57643,22 +57643,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G352">
@@ -57806,22 +57806,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G353">
@@ -57969,22 +57969,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G354">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G355">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G356">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G357">
@@ -58621,22 +58621,22 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G358">
@@ -58784,22 +58784,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G359">
@@ -58947,22 +58947,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G360">
@@ -59110,22 +59110,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G361">
@@ -59273,22 +59273,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G362">
@@ -59431,27 +59431,27 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="G363">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -59594,27 +59594,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -59757,27 +59757,27 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -59920,27 +59920,27 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G366">
@@ -60071,7 +60071,7 @@
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -60083,27 +60083,27 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G367">
@@ -60234,7 +60234,7 @@
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -60246,12 +60246,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G368">
@@ -60397,7 +60397,7 @@
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60409,12 +60409,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G369">
@@ -60560,7 +60560,7 @@
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60572,12 +60572,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G370">
@@ -60723,7 +60723,7 @@
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60735,12 +60735,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G371">
@@ -60886,7 +60886,7 @@
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60898,7 +60898,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G372">
@@ -61049,7 +61049,7 @@
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -61061,156 +61061,971 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="G373">
+        <v>0</v>
+      </c>
+      <c r="H373">
+        <v>0</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N373">
+        <v>0</v>
+      </c>
+      <c r="O373">
+        <v>0</v>
+      </c>
+      <c r="P373">
+        <v>0</v>
+      </c>
+      <c r="Q373">
+        <v>0</v>
+      </c>
+      <c r="R373">
+        <v>0</v>
+      </c>
+      <c r="S373">
+        <v>0</v>
+      </c>
+      <c r="T373">
+        <v>0</v>
+      </c>
+      <c r="U373">
+        <v>0</v>
+      </c>
+      <c r="V373">
+        <v>0</v>
+      </c>
+      <c r="W373">
+        <v>0</v>
+      </c>
+      <c r="X373">
+        <v>0</v>
+      </c>
+      <c r="Y373">
+        <v>0</v>
+      </c>
+      <c r="Z373">
+        <v>0</v>
+      </c>
+      <c r="AA373">
+        <v>0</v>
+      </c>
+      <c r="AB373">
+        <v>0</v>
+      </c>
+      <c r="AC373">
+        <v>0</v>
+      </c>
+      <c r="AD373">
+        <v>0</v>
+      </c>
+      <c r="AE373">
+        <v>0</v>
+      </c>
+      <c r="AF373">
+        <v>0</v>
+      </c>
+      <c r="AG373">
+        <v>0</v>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ373">
+        <v>0</v>
+      </c>
+      <c r="AK373">
+        <v>0</v>
+      </c>
+      <c r="AL373">
+        <v>0</v>
+      </c>
+      <c r="AM373">
+        <v>-1</v>
+      </c>
+      <c r="AN373">
+        <v>-1</v>
+      </c>
+      <c r="AO373">
+        <v>-1</v>
+      </c>
+      <c r="AP373">
+        <v>-1</v>
+      </c>
+      <c r="AQ373">
+        <v>0</v>
+      </c>
+      <c r="AR373">
+        <v>0</v>
+      </c>
+      <c r="AS373">
+        <v>0</v>
+      </c>
+      <c r="AT373">
+        <v>0</v>
+      </c>
+      <c r="AU373" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G374">
+        <v>0</v>
+      </c>
+      <c r="H374">
+        <v>0</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N374">
+        <v>0</v>
+      </c>
+      <c r="O374">
+        <v>0</v>
+      </c>
+      <c r="P374">
+        <v>0</v>
+      </c>
+      <c r="Q374">
+        <v>0</v>
+      </c>
+      <c r="R374">
+        <v>0</v>
+      </c>
+      <c r="S374">
+        <v>0</v>
+      </c>
+      <c r="T374">
+        <v>0</v>
+      </c>
+      <c r="U374">
+        <v>0</v>
+      </c>
+      <c r="V374">
+        <v>0</v>
+      </c>
+      <c r="W374">
+        <v>0</v>
+      </c>
+      <c r="X374">
+        <v>0</v>
+      </c>
+      <c r="Y374">
+        <v>0</v>
+      </c>
+      <c r="Z374">
+        <v>0</v>
+      </c>
+      <c r="AA374">
+        <v>0</v>
+      </c>
+      <c r="AB374">
+        <v>0</v>
+      </c>
+      <c r="AC374">
+        <v>0</v>
+      </c>
+      <c r="AD374">
+        <v>0</v>
+      </c>
+      <c r="AE374">
+        <v>0</v>
+      </c>
+      <c r="AF374">
+        <v>0</v>
+      </c>
+      <c r="AG374">
+        <v>0</v>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ374">
+        <v>0</v>
+      </c>
+      <c r="AK374">
+        <v>0</v>
+      </c>
+      <c r="AL374">
+        <v>0</v>
+      </c>
+      <c r="AM374">
+        <v>-1</v>
+      </c>
+      <c r="AN374">
+        <v>-1</v>
+      </c>
+      <c r="AO374">
+        <v>-1</v>
+      </c>
+      <c r="AP374">
+        <v>-1</v>
+      </c>
+      <c r="AQ374">
+        <v>0</v>
+      </c>
+      <c r="AR374">
+        <v>0</v>
+      </c>
+      <c r="AS374">
+        <v>0</v>
+      </c>
+      <c r="AT374">
+        <v>0</v>
+      </c>
+      <c r="AU374" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G375">
+        <v>0</v>
+      </c>
+      <c r="H375">
+        <v>0</v>
+      </c>
+      <c r="I375">
+        <v>0</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N375">
+        <v>0</v>
+      </c>
+      <c r="O375">
+        <v>0</v>
+      </c>
+      <c r="P375">
+        <v>0</v>
+      </c>
+      <c r="Q375">
+        <v>0</v>
+      </c>
+      <c r="R375">
+        <v>0</v>
+      </c>
+      <c r="S375">
+        <v>0</v>
+      </c>
+      <c r="T375">
+        <v>0</v>
+      </c>
+      <c r="U375">
+        <v>0</v>
+      </c>
+      <c r="V375">
+        <v>0</v>
+      </c>
+      <c r="W375">
+        <v>0</v>
+      </c>
+      <c r="X375">
+        <v>0</v>
+      </c>
+      <c r="Y375">
+        <v>0</v>
+      </c>
+      <c r="Z375">
+        <v>0</v>
+      </c>
+      <c r="AA375">
+        <v>0</v>
+      </c>
+      <c r="AB375">
+        <v>0</v>
+      </c>
+      <c r="AC375">
+        <v>0</v>
+      </c>
+      <c r="AD375">
+        <v>0</v>
+      </c>
+      <c r="AE375">
+        <v>0</v>
+      </c>
+      <c r="AF375">
+        <v>0</v>
+      </c>
+      <c r="AG375">
+        <v>0</v>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ375">
+        <v>0</v>
+      </c>
+      <c r="AK375">
+        <v>0</v>
+      </c>
+      <c r="AL375">
+        <v>0</v>
+      </c>
+      <c r="AM375">
+        <v>-1</v>
+      </c>
+      <c r="AN375">
+        <v>-1</v>
+      </c>
+      <c r="AO375">
+        <v>-1</v>
+      </c>
+      <c r="AP375">
+        <v>-1</v>
+      </c>
+      <c r="AQ375">
+        <v>0</v>
+      </c>
+      <c r="AR375">
+        <v>0</v>
+      </c>
+      <c r="AS375">
+        <v>0</v>
+      </c>
+      <c r="AT375">
+        <v>0</v>
+      </c>
+      <c r="AU375" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G376">
+        <v>0</v>
+      </c>
+      <c r="H376">
+        <v>0</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>0</v>
+      </c>
+      <c r="L376">
+        <v>0</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N376">
+        <v>0</v>
+      </c>
+      <c r="O376">
+        <v>0</v>
+      </c>
+      <c r="P376">
+        <v>0</v>
+      </c>
+      <c r="Q376">
+        <v>0</v>
+      </c>
+      <c r="R376">
+        <v>0</v>
+      </c>
+      <c r="S376">
+        <v>0</v>
+      </c>
+      <c r="T376">
+        <v>0</v>
+      </c>
+      <c r="U376">
+        <v>0</v>
+      </c>
+      <c r="V376">
+        <v>0</v>
+      </c>
+      <c r="W376">
+        <v>0</v>
+      </c>
+      <c r="X376">
+        <v>0</v>
+      </c>
+      <c r="Y376">
+        <v>0</v>
+      </c>
+      <c r="Z376">
+        <v>0</v>
+      </c>
+      <c r="AA376">
+        <v>0</v>
+      </c>
+      <c r="AB376">
+        <v>0</v>
+      </c>
+      <c r="AC376">
+        <v>0</v>
+      </c>
+      <c r="AD376">
+        <v>0</v>
+      </c>
+      <c r="AE376">
+        <v>0</v>
+      </c>
+      <c r="AF376">
+        <v>0</v>
+      </c>
+      <c r="AG376">
+        <v>0</v>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ376">
+        <v>0</v>
+      </c>
+      <c r="AK376">
+        <v>0</v>
+      </c>
+      <c r="AL376">
+        <v>0</v>
+      </c>
+      <c r="AM376">
+        <v>-1</v>
+      </c>
+      <c r="AN376">
+        <v>-1</v>
+      </c>
+      <c r="AO376">
+        <v>-1</v>
+      </c>
+      <c r="AP376">
+        <v>-1</v>
+      </c>
+      <c r="AQ376">
+        <v>0</v>
+      </c>
+      <c r="AR376">
+        <v>0</v>
+      </c>
+      <c r="AS376">
+        <v>0</v>
+      </c>
+      <c r="AT376">
+        <v>0</v>
+      </c>
+      <c r="AU376" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D377" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G377">
+        <v>0</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N377">
+        <v>0</v>
+      </c>
+      <c r="O377">
+        <v>0</v>
+      </c>
+      <c r="P377">
+        <v>0</v>
+      </c>
+      <c r="Q377">
+        <v>0</v>
+      </c>
+      <c r="R377">
+        <v>0</v>
+      </c>
+      <c r="S377">
+        <v>0</v>
+      </c>
+      <c r="T377">
+        <v>0</v>
+      </c>
+      <c r="U377">
+        <v>0</v>
+      </c>
+      <c r="V377">
+        <v>0</v>
+      </c>
+      <c r="W377">
+        <v>0</v>
+      </c>
+      <c r="X377">
+        <v>0</v>
+      </c>
+      <c r="Y377">
+        <v>0</v>
+      </c>
+      <c r="Z377">
+        <v>0</v>
+      </c>
+      <c r="AA377">
+        <v>0</v>
+      </c>
+      <c r="AB377">
+        <v>0</v>
+      </c>
+      <c r="AC377">
+        <v>0</v>
+      </c>
+      <c r="AD377">
+        <v>0</v>
+      </c>
+      <c r="AE377">
+        <v>0</v>
+      </c>
+      <c r="AF377">
+        <v>0</v>
+      </c>
+      <c r="AG377">
+        <v>0</v>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ377">
+        <v>0</v>
+      </c>
+      <c r="AK377">
+        <v>0</v>
+      </c>
+      <c r="AL377">
+        <v>0</v>
+      </c>
+      <c r="AM377">
+        <v>-1</v>
+      </c>
+      <c r="AN377">
+        <v>-1</v>
+      </c>
+      <c r="AO377">
+        <v>-1</v>
+      </c>
+      <c r="AP377">
+        <v>-1</v>
+      </c>
+      <c r="AQ377">
+        <v>0</v>
+      </c>
+      <c r="AR377">
+        <v>0</v>
+      </c>
+      <c r="AS377">
+        <v>0</v>
+      </c>
+      <c r="AT377">
+        <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>St. Louis City</t>
         </is>
       </c>
-      <c r="G373">
-        <v>0</v>
-      </c>
-      <c r="H373">
-        <v>0</v>
-      </c>
-      <c r="I373">
-        <v>0</v>
-      </c>
-      <c r="J373">
-        <v>0</v>
-      </c>
-      <c r="K373">
-        <v>0</v>
-      </c>
-      <c r="L373">
-        <v>0</v>
-      </c>
-      <c r="M373" t="inlineStr">
+      <c r="G378">
+        <v>0</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+      <c r="M378" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N373">
-        <v>0</v>
-      </c>
-      <c r="O373">
-        <v>0</v>
-      </c>
-      <c r="P373">
-        <v>0</v>
-      </c>
-      <c r="Q373">
-        <v>0</v>
-      </c>
-      <c r="R373">
-        <v>0</v>
-      </c>
-      <c r="S373">
-        <v>0</v>
-      </c>
-      <c r="T373">
-        <v>0</v>
-      </c>
-      <c r="U373">
-        <v>0</v>
-      </c>
-      <c r="V373">
-        <v>0</v>
-      </c>
-      <c r="W373">
-        <v>0</v>
-      </c>
-      <c r="X373">
-        <v>0</v>
-      </c>
-      <c r="Y373">
-        <v>0</v>
-      </c>
-      <c r="Z373">
-        <v>0</v>
-      </c>
-      <c r="AA373">
-        <v>0</v>
-      </c>
-      <c r="AB373">
-        <v>0</v>
-      </c>
-      <c r="AC373">
-        <v>0</v>
-      </c>
-      <c r="AD373">
-        <v>0</v>
-      </c>
-      <c r="AE373">
-        <v>0</v>
-      </c>
-      <c r="AF373">
-        <v>0</v>
-      </c>
-      <c r="AG373">
-        <v>0</v>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ373">
-        <v>0</v>
-      </c>
-      <c r="AK373">
-        <v>0</v>
-      </c>
-      <c r="AL373">
-        <v>0</v>
-      </c>
-      <c r="AM373">
-        <v>-1</v>
-      </c>
-      <c r="AN373">
-        <v>-1</v>
-      </c>
-      <c r="AO373">
-        <v>-1</v>
-      </c>
-      <c r="AP373">
-        <v>-1</v>
-      </c>
-      <c r="AQ373">
-        <v>0</v>
-      </c>
-      <c r="AR373">
-        <v>0</v>
-      </c>
-      <c r="AS373">
-        <v>0</v>
-      </c>
-      <c r="AT373">
-        <v>0</v>
-      </c>
-      <c r="AU373" t="inlineStr">
+      <c r="N378">
+        <v>0</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
+      </c>
+      <c r="P378">
+        <v>0</v>
+      </c>
+      <c r="Q378">
+        <v>0</v>
+      </c>
+      <c r="R378">
+        <v>0</v>
+      </c>
+      <c r="S378">
+        <v>0</v>
+      </c>
+      <c r="T378">
+        <v>0</v>
+      </c>
+      <c r="U378">
+        <v>0</v>
+      </c>
+      <c r="V378">
+        <v>0</v>
+      </c>
+      <c r="W378">
+        <v>0</v>
+      </c>
+      <c r="X378">
+        <v>0</v>
+      </c>
+      <c r="Y378">
+        <v>0</v>
+      </c>
+      <c r="Z378">
+        <v>0</v>
+      </c>
+      <c r="AA378">
+        <v>0</v>
+      </c>
+      <c r="AB378">
+        <v>0</v>
+      </c>
+      <c r="AC378">
+        <v>0</v>
+      </c>
+      <c r="AD378">
+        <v>0</v>
+      </c>
+      <c r="AE378">
+        <v>0</v>
+      </c>
+      <c r="AF378">
+        <v>0</v>
+      </c>
+      <c r="AG378">
+        <v>0</v>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ378">
+        <v>0</v>
+      </c>
+      <c r="AK378">
+        <v>0</v>
+      </c>
+      <c r="AL378">
+        <v>0</v>
+      </c>
+      <c r="AM378">
+        <v>-1</v>
+      </c>
+      <c r="AN378">
+        <v>-1</v>
+      </c>
+      <c r="AO378">
+        <v>-1</v>
+      </c>
+      <c r="AP378">
+        <v>-1</v>
+      </c>
+      <c r="AQ378">
+        <v>0</v>
+      </c>
+      <c r="AR378">
+        <v>0</v>
+      </c>
+      <c r="AS378">
+        <v>0</v>
+      </c>
+      <c r="AT378">
+        <v>0</v>
+      </c>
+      <c r="AU378" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G14">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G18">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G69">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G249">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G32">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G36">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G45">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G69">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G93">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G95">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G120">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G123">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G126">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G129">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G146">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G169">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G179">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G247">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G249">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G257">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G17">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G53">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G67">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G82">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G136">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G145">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU378"/>
+  <dimension ref="A1:AU374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G36">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G45">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G168">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G297">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G333">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G334">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G335">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G336">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G363">
@@ -59594,27 +59594,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59757,27 +59757,27 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59920,27 +59920,27 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G366">
@@ -60071,7 +60071,7 @@
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60083,27 +60083,27 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G367">
@@ -60234,7 +60234,7 @@
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -60246,12 +60246,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G368">
@@ -60397,7 +60397,7 @@
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -60409,7 +60409,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G369">
@@ -60560,7 +60560,7 @@
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -60572,12 +60572,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G370">
@@ -60723,7 +60723,7 @@
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -60735,12 +60735,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G371">
@@ -60886,7 +60886,7 @@
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -60898,12 +60898,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G372">
@@ -61049,7 +61049,7 @@
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -61061,7 +61061,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G373">
@@ -61212,7 +61212,7 @@
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -61224,12 +61224,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G374">
@@ -61374,658 +61374,6 @@
         <v>0</v>
       </c>
       <c r="AU374" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="G375">
-        <v>0</v>
-      </c>
-      <c r="H375">
-        <v>0</v>
-      </c>
-      <c r="I375">
-        <v>0</v>
-      </c>
-      <c r="J375">
-        <v>0</v>
-      </c>
-      <c r="K375">
-        <v>0</v>
-      </c>
-      <c r="L375">
-        <v>0</v>
-      </c>
-      <c r="M375" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N375">
-        <v>0</v>
-      </c>
-      <c r="O375">
-        <v>0</v>
-      </c>
-      <c r="P375">
-        <v>0</v>
-      </c>
-      <c r="Q375">
-        <v>0</v>
-      </c>
-      <c r="R375">
-        <v>0</v>
-      </c>
-      <c r="S375">
-        <v>0</v>
-      </c>
-      <c r="T375">
-        <v>0</v>
-      </c>
-      <c r="U375">
-        <v>0</v>
-      </c>
-      <c r="V375">
-        <v>0</v>
-      </c>
-      <c r="W375">
-        <v>0</v>
-      </c>
-      <c r="X375">
-        <v>0</v>
-      </c>
-      <c r="Y375">
-        <v>0</v>
-      </c>
-      <c r="Z375">
-        <v>0</v>
-      </c>
-      <c r="AA375">
-        <v>0</v>
-      </c>
-      <c r="AB375">
-        <v>0</v>
-      </c>
-      <c r="AC375">
-        <v>0</v>
-      </c>
-      <c r="AD375">
-        <v>0</v>
-      </c>
-      <c r="AE375">
-        <v>0</v>
-      </c>
-      <c r="AF375">
-        <v>0</v>
-      </c>
-      <c r="AG375">
-        <v>0</v>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ375">
-        <v>0</v>
-      </c>
-      <c r="AK375">
-        <v>0</v>
-      </c>
-      <c r="AL375">
-        <v>0</v>
-      </c>
-      <c r="AM375">
-        <v>-1</v>
-      </c>
-      <c r="AN375">
-        <v>-1</v>
-      </c>
-      <c r="AO375">
-        <v>-1</v>
-      </c>
-      <c r="AP375">
-        <v>-1</v>
-      </c>
-      <c r="AQ375">
-        <v>0</v>
-      </c>
-      <c r="AR375">
-        <v>0</v>
-      </c>
-      <c r="AS375">
-        <v>0</v>
-      </c>
-      <c r="AT375">
-        <v>0</v>
-      </c>
-      <c r="AU375" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="G376">
-        <v>0</v>
-      </c>
-      <c r="H376">
-        <v>0</v>
-      </c>
-      <c r="I376">
-        <v>0</v>
-      </c>
-      <c r="J376">
-        <v>0</v>
-      </c>
-      <c r="K376">
-        <v>0</v>
-      </c>
-      <c r="L376">
-        <v>0</v>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N376">
-        <v>0</v>
-      </c>
-      <c r="O376">
-        <v>0</v>
-      </c>
-      <c r="P376">
-        <v>0</v>
-      </c>
-      <c r="Q376">
-        <v>0</v>
-      </c>
-      <c r="R376">
-        <v>0</v>
-      </c>
-      <c r="S376">
-        <v>0</v>
-      </c>
-      <c r="T376">
-        <v>0</v>
-      </c>
-      <c r="U376">
-        <v>0</v>
-      </c>
-      <c r="V376">
-        <v>0</v>
-      </c>
-      <c r="W376">
-        <v>0</v>
-      </c>
-      <c r="X376">
-        <v>0</v>
-      </c>
-      <c r="Y376">
-        <v>0</v>
-      </c>
-      <c r="Z376">
-        <v>0</v>
-      </c>
-      <c r="AA376">
-        <v>0</v>
-      </c>
-      <c r="AB376">
-        <v>0</v>
-      </c>
-      <c r="AC376">
-        <v>0</v>
-      </c>
-      <c r="AD376">
-        <v>0</v>
-      </c>
-      <c r="AE376">
-        <v>0</v>
-      </c>
-      <c r="AF376">
-        <v>0</v>
-      </c>
-      <c r="AG376">
-        <v>0</v>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ376">
-        <v>0</v>
-      </c>
-      <c r="AK376">
-        <v>0</v>
-      </c>
-      <c r="AL376">
-        <v>0</v>
-      </c>
-      <c r="AM376">
-        <v>-1</v>
-      </c>
-      <c r="AN376">
-        <v>-1</v>
-      </c>
-      <c r="AO376">
-        <v>-1</v>
-      </c>
-      <c r="AP376">
-        <v>-1</v>
-      </c>
-      <c r="AQ376">
-        <v>0</v>
-      </c>
-      <c r="AR376">
-        <v>0</v>
-      </c>
-      <c r="AS376">
-        <v>0</v>
-      </c>
-      <c r="AT376">
-        <v>0</v>
-      </c>
-      <c r="AU376" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="G377">
-        <v>0</v>
-      </c>
-      <c r="H377">
-        <v>0</v>
-      </c>
-      <c r="I377">
-        <v>0</v>
-      </c>
-      <c r="J377">
-        <v>0</v>
-      </c>
-      <c r="K377">
-        <v>0</v>
-      </c>
-      <c r="L377">
-        <v>0</v>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N377">
-        <v>0</v>
-      </c>
-      <c r="O377">
-        <v>0</v>
-      </c>
-      <c r="P377">
-        <v>0</v>
-      </c>
-      <c r="Q377">
-        <v>0</v>
-      </c>
-      <c r="R377">
-        <v>0</v>
-      </c>
-      <c r="S377">
-        <v>0</v>
-      </c>
-      <c r="T377">
-        <v>0</v>
-      </c>
-      <c r="U377">
-        <v>0</v>
-      </c>
-      <c r="V377">
-        <v>0</v>
-      </c>
-      <c r="W377">
-        <v>0</v>
-      </c>
-      <c r="X377">
-        <v>0</v>
-      </c>
-      <c r="Y377">
-        <v>0</v>
-      </c>
-      <c r="Z377">
-        <v>0</v>
-      </c>
-      <c r="AA377">
-        <v>0</v>
-      </c>
-      <c r="AB377">
-        <v>0</v>
-      </c>
-      <c r="AC377">
-        <v>0</v>
-      </c>
-      <c r="AD377">
-        <v>0</v>
-      </c>
-      <c r="AE377">
-        <v>0</v>
-      </c>
-      <c r="AF377">
-        <v>0</v>
-      </c>
-      <c r="AG377">
-        <v>0</v>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ377">
-        <v>0</v>
-      </c>
-      <c r="AK377">
-        <v>0</v>
-      </c>
-      <c r="AL377">
-        <v>0</v>
-      </c>
-      <c r="AM377">
-        <v>-1</v>
-      </c>
-      <c r="AN377">
-        <v>-1</v>
-      </c>
-      <c r="AO377">
-        <v>-1</v>
-      </c>
-      <c r="AP377">
-        <v>-1</v>
-      </c>
-      <c r="AQ377">
-        <v>0</v>
-      </c>
-      <c r="AR377">
-        <v>0</v>
-      </c>
-      <c r="AS377">
-        <v>0</v>
-      </c>
-      <c r="AT377">
-        <v>0</v>
-      </c>
-      <c r="AU377" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="G378">
-        <v>0</v>
-      </c>
-      <c r="H378">
-        <v>0</v>
-      </c>
-      <c r="I378">
-        <v>0</v>
-      </c>
-      <c r="J378">
-        <v>0</v>
-      </c>
-      <c r="K378">
-        <v>0</v>
-      </c>
-      <c r="L378">
-        <v>0</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N378">
-        <v>0</v>
-      </c>
-      <c r="O378">
-        <v>0</v>
-      </c>
-      <c r="P378">
-        <v>0</v>
-      </c>
-      <c r="Q378">
-        <v>0</v>
-      </c>
-      <c r="R378">
-        <v>0</v>
-      </c>
-      <c r="S378">
-        <v>0</v>
-      </c>
-      <c r="T378">
-        <v>0</v>
-      </c>
-      <c r="U378">
-        <v>0</v>
-      </c>
-      <c r="V378">
-        <v>0</v>
-      </c>
-      <c r="W378">
-        <v>0</v>
-      </c>
-      <c r="X378">
-        <v>0</v>
-      </c>
-      <c r="Y378">
-        <v>0</v>
-      </c>
-      <c r="Z378">
-        <v>0</v>
-      </c>
-      <c r="AA378">
-        <v>0</v>
-      </c>
-      <c r="AB378">
-        <v>0</v>
-      </c>
-      <c r="AC378">
-        <v>0</v>
-      </c>
-      <c r="AD378">
-        <v>0</v>
-      </c>
-      <c r="AE378">
-        <v>0</v>
-      </c>
-      <c r="AF378">
-        <v>0</v>
-      </c>
-      <c r="AG378">
-        <v>0</v>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ378">
-        <v>0</v>
-      </c>
-      <c r="AK378">
-        <v>0</v>
-      </c>
-      <c r="AL378">
-        <v>0</v>
-      </c>
-      <c r="AM378">
-        <v>-1</v>
-      </c>
-      <c r="AN378">
-        <v>-1</v>
-      </c>
-      <c r="AO378">
-        <v>-1</v>
-      </c>
-      <c r="AP378">
-        <v>-1</v>
-      </c>
-      <c r="AQ378">
-        <v>0</v>
-      </c>
-      <c r="AR378">
-        <v>0</v>
-      </c>
-      <c r="AS378">
-        <v>0</v>
-      </c>
-      <c r="AT378">
-        <v>0</v>
-      </c>
-      <c r="AU378" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU374"/>
+  <dimension ref="A1:AU366"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="G13">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G17">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G83">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G92">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G145">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G154">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G167">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G219">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G306">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G307">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G308">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G323">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G324">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G325">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G326">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G333">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G334">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G339">
@@ -56176,7 +56176,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G343">
@@ -56339,22 +56339,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G344">
@@ -56502,22 +56502,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G345">
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,22 +56828,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G347">
@@ -56991,7 +56991,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G348">
@@ -57154,7 +57154,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G349">
@@ -57317,22 +57317,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G350">
@@ -57480,22 +57480,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G351">
@@ -57643,22 +57643,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G352">
@@ -57806,22 +57806,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G353">
@@ -57969,22 +57969,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G354">
@@ -58132,22 +58132,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G355">
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58616,12 +58616,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G358">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58779,12 +58779,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G359">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58942,12 +58942,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G360">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59105,12 +59105,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G361">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59268,12 +59268,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G362">
@@ -59419,7 +59419,7 @@
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59431,27 +59431,27 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G363">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -59757,7 +59757,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -59920,7 +59920,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G366">
@@ -60070,1310 +60070,6 @@
         <v>0</v>
       </c>
       <c r="AU366" t="inlineStr">
-        <is>
-          <t>2026-09-05 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>New York RB</t>
-        </is>
-      </c>
-      <c r="G367">
-        <v>0</v>
-      </c>
-      <c r="H367">
-        <v>0</v>
-      </c>
-      <c r="I367">
-        <v>0</v>
-      </c>
-      <c r="J367">
-        <v>0</v>
-      </c>
-      <c r="K367">
-        <v>0</v>
-      </c>
-      <c r="L367">
-        <v>0</v>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N367">
-        <v>0</v>
-      </c>
-      <c r="O367">
-        <v>0</v>
-      </c>
-      <c r="P367">
-        <v>0</v>
-      </c>
-      <c r="Q367">
-        <v>0</v>
-      </c>
-      <c r="R367">
-        <v>0</v>
-      </c>
-      <c r="S367">
-        <v>0</v>
-      </c>
-      <c r="T367">
-        <v>0</v>
-      </c>
-      <c r="U367">
-        <v>0</v>
-      </c>
-      <c r="V367">
-        <v>0</v>
-      </c>
-      <c r="W367">
-        <v>0</v>
-      </c>
-      <c r="X367">
-        <v>0</v>
-      </c>
-      <c r="Y367">
-        <v>0</v>
-      </c>
-      <c r="Z367">
-        <v>0</v>
-      </c>
-      <c r="AA367">
-        <v>0</v>
-      </c>
-      <c r="AB367">
-        <v>0</v>
-      </c>
-      <c r="AC367">
-        <v>0</v>
-      </c>
-      <c r="AD367">
-        <v>0</v>
-      </c>
-      <c r="AE367">
-        <v>0</v>
-      </c>
-      <c r="AF367">
-        <v>0</v>
-      </c>
-      <c r="AG367">
-        <v>0</v>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ367">
-        <v>0</v>
-      </c>
-      <c r="AK367">
-        <v>0</v>
-      </c>
-      <c r="AL367">
-        <v>0</v>
-      </c>
-      <c r="AM367">
-        <v>-1</v>
-      </c>
-      <c r="AN367">
-        <v>-1</v>
-      </c>
-      <c r="AO367">
-        <v>-1</v>
-      </c>
-      <c r="AP367">
-        <v>-1</v>
-      </c>
-      <c r="AQ367">
-        <v>0</v>
-      </c>
-      <c r="AR367">
-        <v>0</v>
-      </c>
-      <c r="AS367">
-        <v>0</v>
-      </c>
-      <c r="AT367">
-        <v>0</v>
-      </c>
-      <c r="AU367" t="inlineStr">
-        <is>
-          <t>2026-09-05 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>New England Revolution</t>
-        </is>
-      </c>
-      <c r="G368">
-        <v>0</v>
-      </c>
-      <c r="H368">
-        <v>0</v>
-      </c>
-      <c r="I368">
-        <v>0</v>
-      </c>
-      <c r="J368">
-        <v>0</v>
-      </c>
-      <c r="K368">
-        <v>0</v>
-      </c>
-      <c r="L368">
-        <v>0</v>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N368">
-        <v>0</v>
-      </c>
-      <c r="O368">
-        <v>0</v>
-      </c>
-      <c r="P368">
-        <v>0</v>
-      </c>
-      <c r="Q368">
-        <v>0</v>
-      </c>
-      <c r="R368">
-        <v>0</v>
-      </c>
-      <c r="S368">
-        <v>0</v>
-      </c>
-      <c r="T368">
-        <v>0</v>
-      </c>
-      <c r="U368">
-        <v>0</v>
-      </c>
-      <c r="V368">
-        <v>0</v>
-      </c>
-      <c r="W368">
-        <v>0</v>
-      </c>
-      <c r="X368">
-        <v>0</v>
-      </c>
-      <c r="Y368">
-        <v>0</v>
-      </c>
-      <c r="Z368">
-        <v>0</v>
-      </c>
-      <c r="AA368">
-        <v>0</v>
-      </c>
-      <c r="AB368">
-        <v>0</v>
-      </c>
-      <c r="AC368">
-        <v>0</v>
-      </c>
-      <c r="AD368">
-        <v>0</v>
-      </c>
-      <c r="AE368">
-        <v>0</v>
-      </c>
-      <c r="AF368">
-        <v>0</v>
-      </c>
-      <c r="AG368">
-        <v>0</v>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ368">
-        <v>0</v>
-      </c>
-      <c r="AK368">
-        <v>0</v>
-      </c>
-      <c r="AL368">
-        <v>0</v>
-      </c>
-      <c r="AM368">
-        <v>-1</v>
-      </c>
-      <c r="AN368">
-        <v>-1</v>
-      </c>
-      <c r="AO368">
-        <v>-1</v>
-      </c>
-      <c r="AP368">
-        <v>-1</v>
-      </c>
-      <c r="AQ368">
-        <v>0</v>
-      </c>
-      <c r="AR368">
-        <v>0</v>
-      </c>
-      <c r="AS368">
-        <v>0</v>
-      </c>
-      <c r="AT368">
-        <v>0</v>
-      </c>
-      <c r="AU368" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G369">
-        <v>0</v>
-      </c>
-      <c r="H369">
-        <v>0</v>
-      </c>
-      <c r="I369">
-        <v>0</v>
-      </c>
-      <c r="J369">
-        <v>0</v>
-      </c>
-      <c r="K369">
-        <v>0</v>
-      </c>
-      <c r="L369">
-        <v>0</v>
-      </c>
-      <c r="M369" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N369">
-        <v>0</v>
-      </c>
-      <c r="O369">
-        <v>0</v>
-      </c>
-      <c r="P369">
-        <v>0</v>
-      </c>
-      <c r="Q369">
-        <v>0</v>
-      </c>
-      <c r="R369">
-        <v>0</v>
-      </c>
-      <c r="S369">
-        <v>0</v>
-      </c>
-      <c r="T369">
-        <v>0</v>
-      </c>
-      <c r="U369">
-        <v>0</v>
-      </c>
-      <c r="V369">
-        <v>0</v>
-      </c>
-      <c r="W369">
-        <v>0</v>
-      </c>
-      <c r="X369">
-        <v>0</v>
-      </c>
-      <c r="Y369">
-        <v>0</v>
-      </c>
-      <c r="Z369">
-        <v>0</v>
-      </c>
-      <c r="AA369">
-        <v>0</v>
-      </c>
-      <c r="AB369">
-        <v>0</v>
-      </c>
-      <c r="AC369">
-        <v>0</v>
-      </c>
-      <c r="AD369">
-        <v>0</v>
-      </c>
-      <c r="AE369">
-        <v>0</v>
-      </c>
-      <c r="AF369">
-        <v>0</v>
-      </c>
-      <c r="AG369">
-        <v>0</v>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ369">
-        <v>0</v>
-      </c>
-      <c r="AK369">
-        <v>0</v>
-      </c>
-      <c r="AL369">
-        <v>0</v>
-      </c>
-      <c r="AM369">
-        <v>-1</v>
-      </c>
-      <c r="AN369">
-        <v>-1</v>
-      </c>
-      <c r="AO369">
-        <v>-1</v>
-      </c>
-      <c r="AP369">
-        <v>-1</v>
-      </c>
-      <c r="AQ369">
-        <v>0</v>
-      </c>
-      <c r="AR369">
-        <v>0</v>
-      </c>
-      <c r="AS369">
-        <v>0</v>
-      </c>
-      <c r="AT369">
-        <v>0</v>
-      </c>
-      <c r="AU369" t="inlineStr">
-        <is>
-          <t>2026-09-05 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>Monterey Bay</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="G370">
-        <v>0</v>
-      </c>
-      <c r="H370">
-        <v>0</v>
-      </c>
-      <c r="I370">
-        <v>0</v>
-      </c>
-      <c r="J370">
-        <v>0</v>
-      </c>
-      <c r="K370">
-        <v>0</v>
-      </c>
-      <c r="L370">
-        <v>0</v>
-      </c>
-      <c r="M370" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N370">
-        <v>0</v>
-      </c>
-      <c r="O370">
-        <v>0</v>
-      </c>
-      <c r="P370">
-        <v>0</v>
-      </c>
-      <c r="Q370">
-        <v>0</v>
-      </c>
-      <c r="R370">
-        <v>0</v>
-      </c>
-      <c r="S370">
-        <v>0</v>
-      </c>
-      <c r="T370">
-        <v>0</v>
-      </c>
-      <c r="U370">
-        <v>0</v>
-      </c>
-      <c r="V370">
-        <v>0</v>
-      </c>
-      <c r="W370">
-        <v>0</v>
-      </c>
-      <c r="X370">
-        <v>0</v>
-      </c>
-      <c r="Y370">
-        <v>0</v>
-      </c>
-      <c r="Z370">
-        <v>0</v>
-      </c>
-      <c r="AA370">
-        <v>0</v>
-      </c>
-      <c r="AB370">
-        <v>0</v>
-      </c>
-      <c r="AC370">
-        <v>0</v>
-      </c>
-      <c r="AD370">
-        <v>0</v>
-      </c>
-      <c r="AE370">
-        <v>0</v>
-      </c>
-      <c r="AF370">
-        <v>0</v>
-      </c>
-      <c r="AG370">
-        <v>0</v>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ370">
-        <v>0</v>
-      </c>
-      <c r="AK370">
-        <v>0</v>
-      </c>
-      <c r="AL370">
-        <v>0</v>
-      </c>
-      <c r="AM370">
-        <v>-1</v>
-      </c>
-      <c r="AN370">
-        <v>-1</v>
-      </c>
-      <c r="AO370">
-        <v>-1</v>
-      </c>
-      <c r="AP370">
-        <v>-1</v>
-      </c>
-      <c r="AQ370">
-        <v>0</v>
-      </c>
-      <c r="AR370">
-        <v>0</v>
-      </c>
-      <c r="AS370">
-        <v>0</v>
-      </c>
-      <c r="AT370">
-        <v>0</v>
-      </c>
-      <c r="AU370" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="G371">
-        <v>0</v>
-      </c>
-      <c r="H371">
-        <v>0</v>
-      </c>
-      <c r="I371">
-        <v>0</v>
-      </c>
-      <c r="J371">
-        <v>0</v>
-      </c>
-      <c r="K371">
-        <v>0</v>
-      </c>
-      <c r="L371">
-        <v>0</v>
-      </c>
-      <c r="M371" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N371">
-        <v>0</v>
-      </c>
-      <c r="O371">
-        <v>0</v>
-      </c>
-      <c r="P371">
-        <v>0</v>
-      </c>
-      <c r="Q371">
-        <v>0</v>
-      </c>
-      <c r="R371">
-        <v>0</v>
-      </c>
-      <c r="S371">
-        <v>0</v>
-      </c>
-      <c r="T371">
-        <v>0</v>
-      </c>
-      <c r="U371">
-        <v>0</v>
-      </c>
-      <c r="V371">
-        <v>0</v>
-      </c>
-      <c r="W371">
-        <v>0</v>
-      </c>
-      <c r="X371">
-        <v>0</v>
-      </c>
-      <c r="Y371">
-        <v>0</v>
-      </c>
-      <c r="Z371">
-        <v>0</v>
-      </c>
-      <c r="AA371">
-        <v>0</v>
-      </c>
-      <c r="AB371">
-        <v>0</v>
-      </c>
-      <c r="AC371">
-        <v>0</v>
-      </c>
-      <c r="AD371">
-        <v>0</v>
-      </c>
-      <c r="AE371">
-        <v>0</v>
-      </c>
-      <c r="AF371">
-        <v>0</v>
-      </c>
-      <c r="AG371">
-        <v>0</v>
-      </c>
-      <c r="AH371" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI371" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ371">
-        <v>0</v>
-      </c>
-      <c r="AK371">
-        <v>0</v>
-      </c>
-      <c r="AL371">
-        <v>0</v>
-      </c>
-      <c r="AM371">
-        <v>-1</v>
-      </c>
-      <c r="AN371">
-        <v>-1</v>
-      </c>
-      <c r="AO371">
-        <v>-1</v>
-      </c>
-      <c r="AP371">
-        <v>-1</v>
-      </c>
-      <c r="AQ371">
-        <v>0</v>
-      </c>
-      <c r="AR371">
-        <v>0</v>
-      </c>
-      <c r="AS371">
-        <v>0</v>
-      </c>
-      <c r="AT371">
-        <v>0</v>
-      </c>
-      <c r="AU371" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="G372">
-        <v>0</v>
-      </c>
-      <c r="H372">
-        <v>0</v>
-      </c>
-      <c r="I372">
-        <v>0</v>
-      </c>
-      <c r="J372">
-        <v>0</v>
-      </c>
-      <c r="K372">
-        <v>0</v>
-      </c>
-      <c r="L372">
-        <v>0</v>
-      </c>
-      <c r="M372" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N372">
-        <v>0</v>
-      </c>
-      <c r="O372">
-        <v>0</v>
-      </c>
-      <c r="P372">
-        <v>0</v>
-      </c>
-      <c r="Q372">
-        <v>0</v>
-      </c>
-      <c r="R372">
-        <v>0</v>
-      </c>
-      <c r="S372">
-        <v>0</v>
-      </c>
-      <c r="T372">
-        <v>0</v>
-      </c>
-      <c r="U372">
-        <v>0</v>
-      </c>
-      <c r="V372">
-        <v>0</v>
-      </c>
-      <c r="W372">
-        <v>0</v>
-      </c>
-      <c r="X372">
-        <v>0</v>
-      </c>
-      <c r="Y372">
-        <v>0</v>
-      </c>
-      <c r="Z372">
-        <v>0</v>
-      </c>
-      <c r="AA372">
-        <v>0</v>
-      </c>
-      <c r="AB372">
-        <v>0</v>
-      </c>
-      <c r="AC372">
-        <v>0</v>
-      </c>
-      <c r="AD372">
-        <v>0</v>
-      </c>
-      <c r="AE372">
-        <v>0</v>
-      </c>
-      <c r="AF372">
-        <v>0</v>
-      </c>
-      <c r="AG372">
-        <v>0</v>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ372">
-        <v>0</v>
-      </c>
-      <c r="AK372">
-        <v>0</v>
-      </c>
-      <c r="AL372">
-        <v>0</v>
-      </c>
-      <c r="AM372">
-        <v>-1</v>
-      </c>
-      <c r="AN372">
-        <v>-1</v>
-      </c>
-      <c r="AO372">
-        <v>-1</v>
-      </c>
-      <c r="AP372">
-        <v>-1</v>
-      </c>
-      <c r="AQ372">
-        <v>0</v>
-      </c>
-      <c r="AR372">
-        <v>0</v>
-      </c>
-      <c r="AS372">
-        <v>0</v>
-      </c>
-      <c r="AT372">
-        <v>0</v>
-      </c>
-      <c r="AU372" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="G373">
-        <v>0</v>
-      </c>
-      <c r="H373">
-        <v>0</v>
-      </c>
-      <c r="I373">
-        <v>0</v>
-      </c>
-      <c r="J373">
-        <v>0</v>
-      </c>
-      <c r="K373">
-        <v>0</v>
-      </c>
-      <c r="L373">
-        <v>0</v>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N373">
-        <v>0</v>
-      </c>
-      <c r="O373">
-        <v>0</v>
-      </c>
-      <c r="P373">
-        <v>0</v>
-      </c>
-      <c r="Q373">
-        <v>0</v>
-      </c>
-      <c r="R373">
-        <v>0</v>
-      </c>
-      <c r="S373">
-        <v>0</v>
-      </c>
-      <c r="T373">
-        <v>0</v>
-      </c>
-      <c r="U373">
-        <v>0</v>
-      </c>
-      <c r="V373">
-        <v>0</v>
-      </c>
-      <c r="W373">
-        <v>0</v>
-      </c>
-      <c r="X373">
-        <v>0</v>
-      </c>
-      <c r="Y373">
-        <v>0</v>
-      </c>
-      <c r="Z373">
-        <v>0</v>
-      </c>
-      <c r="AA373">
-        <v>0</v>
-      </c>
-      <c r="AB373">
-        <v>0</v>
-      </c>
-      <c r="AC373">
-        <v>0</v>
-      </c>
-      <c r="AD373">
-        <v>0</v>
-      </c>
-      <c r="AE373">
-        <v>0</v>
-      </c>
-      <c r="AF373">
-        <v>0</v>
-      </c>
-      <c r="AG373">
-        <v>0</v>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ373">
-        <v>0</v>
-      </c>
-      <c r="AK373">
-        <v>0</v>
-      </c>
-      <c r="AL373">
-        <v>0</v>
-      </c>
-      <c r="AM373">
-        <v>-1</v>
-      </c>
-      <c r="AN373">
-        <v>-1</v>
-      </c>
-      <c r="AO373">
-        <v>-1</v>
-      </c>
-      <c r="AP373">
-        <v>-1</v>
-      </c>
-      <c r="AQ373">
-        <v>0</v>
-      </c>
-      <c r="AR373">
-        <v>0</v>
-      </c>
-      <c r="AS373">
-        <v>0</v>
-      </c>
-      <c r="AT373">
-        <v>0</v>
-      </c>
-      <c r="AU373" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="G374">
-        <v>0</v>
-      </c>
-      <c r="H374">
-        <v>0</v>
-      </c>
-      <c r="I374">
-        <v>0</v>
-      </c>
-      <c r="J374">
-        <v>0</v>
-      </c>
-      <c r="K374">
-        <v>0</v>
-      </c>
-      <c r="L374">
-        <v>0</v>
-      </c>
-      <c r="M374" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N374">
-        <v>0</v>
-      </c>
-      <c r="O374">
-        <v>0</v>
-      </c>
-      <c r="P374">
-        <v>0</v>
-      </c>
-      <c r="Q374">
-        <v>0</v>
-      </c>
-      <c r="R374">
-        <v>0</v>
-      </c>
-      <c r="S374">
-        <v>0</v>
-      </c>
-      <c r="T374">
-        <v>0</v>
-      </c>
-      <c r="U374">
-        <v>0</v>
-      </c>
-      <c r="V374">
-        <v>0</v>
-      </c>
-      <c r="W374">
-        <v>0</v>
-      </c>
-      <c r="X374">
-        <v>0</v>
-      </c>
-      <c r="Y374">
-        <v>0</v>
-      </c>
-      <c r="Z374">
-        <v>0</v>
-      </c>
-      <c r="AA374">
-        <v>0</v>
-      </c>
-      <c r="AB374">
-        <v>0</v>
-      </c>
-      <c r="AC374">
-        <v>0</v>
-      </c>
-      <c r="AD374">
-        <v>0</v>
-      </c>
-      <c r="AE374">
-        <v>0</v>
-      </c>
-      <c r="AF374">
-        <v>0</v>
-      </c>
-      <c r="AG374">
-        <v>0</v>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ374">
-        <v>0</v>
-      </c>
-      <c r="AK374">
-        <v>0</v>
-      </c>
-      <c r="AL374">
-        <v>0</v>
-      </c>
-      <c r="AM374">
-        <v>-1</v>
-      </c>
-      <c r="AN374">
-        <v>-1</v>
-      </c>
-      <c r="AO374">
-        <v>-1</v>
-      </c>
-      <c r="AP374">
-        <v>-1</v>
-      </c>
-      <c r="AQ374">
-        <v>0</v>
-      </c>
-      <c r="AR374">
-        <v>0</v>
-      </c>
-      <c r="AS374">
-        <v>0</v>
-      </c>
-      <c r="AT374">
-        <v>0</v>
-      </c>
-      <c r="AU374" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU366"/>
+  <dimension ref="A1:AU368"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-05 07:00:00</t>
+          <t>2026-09-05 07:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-05 07:30:00</t>
+          <t>2026-09-05 08:00:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-05 08:00:00</t>
+          <t>2026-09-05 08:30:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-05 08:30:00</t>
+          <t>2026-09-05 08:35:00</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G52">
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Rasi Salai United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-05 08:35:00</t>
+          <t>2026-09-05 09:00:00</t>
         </is>
       </c>
     </row>
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rasi Salai United</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-09-05 09:00:00</t>
+          <t>2026-09-05 09:15:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-09-05 09:15:00</t>
+          <t>2026-09-05 09:30:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-09-05 09:30:00</t>
+          <t>2026-09-05 09:45:00</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G81">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-05 09:45:00</t>
+          <t>2026-09-05 10:00:00</t>
         </is>
       </c>
     </row>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G103">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-05 10:00:00</t>
+          <t>2026-09-05 10:30:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-05 10:30:00</t>
+          <t>2026-09-05 10:45:00</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hatta</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-05 10:45:00</t>
+          <t>2026-09-05 11:00:00</t>
         </is>
       </c>
     </row>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,22 +24065,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G182">
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-09-05 11:00:00</t>
+          <t>2026-09-05 11:15:00</t>
         </is>
       </c>
     </row>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G184">
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-09-05 11:15:00</t>
+          <t>2026-09-05 11:30:00</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G186">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G203">
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-09-05 12:15:00</t>
+          <t>2026-09-05 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G206">
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-09-05 12:30:00</t>
+          <t>2026-09-05 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G211">
@@ -34818,27 +34818,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G212">
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-09-05 12:50:00</t>
+          <t>2026-09-05 12:30:00</t>
         </is>
       </c>
     </row>
@@ -34981,7 +34981,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-05 12:55:00</t>
+          <t>2026-09-05 12:50:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-05 13:00:00</t>
+          <t>2026-09-05 12:55:00</t>
         </is>
       </c>
     </row>
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G218">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,22 +36453,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G223">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,22 +37105,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,22 +37268,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G234">
@@ -38567,12 +38567,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G235">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:00</t>
+          <t>2026-09-05 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-05 13:15:00</t>
+          <t>2026-09-05 13:10:00</t>
         </is>
       </c>
     </row>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G238">
@@ -39219,27 +39219,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-09-05 13:30:00</t>
+          <t>2026-09-05 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39387,22 +39387,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G241">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G246">
@@ -40523,12 +40523,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G247">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-09-05 13:45:00</t>
+          <t>2026-09-05 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G248">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G250">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G252">
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-09-05 14:00:00</t>
+          <t>2026-09-05 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G261">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G264">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-05 14:15:00</t>
+          <t>2026-09-05 14:00:00</t>
         </is>
       </c>
     </row>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-05 14:30:00</t>
+          <t>2026-09-05 14:00:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-05 14:30:00</t>
+          <t>2026-09-05 14:15:00</t>
         </is>
       </c>
     </row>
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G271">
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G272">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-05 15:00:00</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q273">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R273">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S273">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T273">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U273">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V273">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W273">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X273">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y273">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z273">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA273">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB273">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC273">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD273">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF273">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG273">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK273">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-05 15:00:00</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45255,22 +45255,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O276">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P276">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45744,22 +45744,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G280">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G281">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,22 +46559,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G284">
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -46880,12 +46880,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47369,27 +47369,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48021,12 +48021,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,27 +48347,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G297">
@@ -48836,27 +48836,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G301">
@@ -49493,22 +49493,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O302">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P302">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49656,22 +49656,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,22 +49819,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G304">
@@ -49982,22 +49982,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G306">
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G308">
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G309">
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,22 +50960,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,22 +51123,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G312">
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G313">
@@ -51324,68 +51324,68 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N313">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="O313">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P313">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q313">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R313">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S313">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T313">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U313">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V313">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W313">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X313">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y313">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z313">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA313">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB313">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC313">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD313">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE313">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF313">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG313">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK313">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51444,12 +51444,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51607,12 +51607,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G315">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51770,27 +51770,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,19 +51817,19 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R316">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S316">
         <v>0</v>
@@ -51838,10 +51838,10 @@
         <v>0</v>
       </c>
       <c r="U316">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V316">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W316">
         <v>0</v>
@@ -51850,31 +51850,31 @@
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z316">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC316">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD316">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE316">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF316">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG316">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK316">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00:00</t>
+          <t>2026-09-05 16:30:00</t>
         </is>
       </c>
     </row>
@@ -51933,27 +51933,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G317">
@@ -51976,68 +51976,68 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O317">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P317">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q317">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R317">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S317">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T317">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U317">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V317">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W317">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X317">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y317">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z317">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA317">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB317">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC317">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD317">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE317">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF317">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG317">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK317">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52084,7 +52084,7 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>2026-09-05 18:15:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52096,12 +52096,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G318">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52259,12 +52259,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:00:00</t>
         </is>
       </c>
     </row>
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:15:00</t>
         </is>
       </c>
     </row>
@@ -52748,12 +52748,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53074,12 +53074,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G324">
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G325">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53400,12 +53400,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G326">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 19:30:00</t>
         </is>
       </c>
     </row>
@@ -53568,7 +53568,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G327">
@@ -53726,7 +53726,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -53889,7 +53889,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54052,12 +54052,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54215,12 +54215,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54383,7 +54383,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G332">
@@ -54546,7 +54546,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G333">
@@ -54709,7 +54709,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G334">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G335">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G336">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G337">
@@ -55356,12 +55356,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G338">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55519,27 +55519,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G339">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55682,27 +55682,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G340">
@@ -55833,7 +55833,7 @@
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -55845,27 +55845,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G341">
@@ -55996,7 +55996,7 @@
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56013,22 +56013,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G342">
@@ -56176,7 +56176,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G343">
@@ -56339,22 +56339,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G344">
@@ -56502,22 +56502,22 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G345">
@@ -56665,22 +56665,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G347">
@@ -56991,22 +56991,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G348">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G350">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G352">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G353">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G354">
@@ -58132,22 +58132,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G355">
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -58453,27 +58453,27 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G359">
@@ -58942,7 +58942,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G360">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G361">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59268,12 +59268,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G362">
@@ -59419,7 +59419,7 @@
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59431,12 +59431,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G363">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59757,12 +59757,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59925,151 +59925,477 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G366">
+        <v>0</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N366">
+        <v>0</v>
+      </c>
+      <c r="O366">
+        <v>0</v>
+      </c>
+      <c r="P366">
+        <v>0</v>
+      </c>
+      <c r="Q366">
+        <v>0</v>
+      </c>
+      <c r="R366">
+        <v>0</v>
+      </c>
+      <c r="S366">
+        <v>0</v>
+      </c>
+      <c r="T366">
+        <v>0</v>
+      </c>
+      <c r="U366">
+        <v>0</v>
+      </c>
+      <c r="V366">
+        <v>0</v>
+      </c>
+      <c r="W366">
+        <v>0</v>
+      </c>
+      <c r="X366">
+        <v>0</v>
+      </c>
+      <c r="Y366">
+        <v>0</v>
+      </c>
+      <c r="Z366">
+        <v>0</v>
+      </c>
+      <c r="AA366">
+        <v>0</v>
+      </c>
+      <c r="AB366">
+        <v>0</v>
+      </c>
+      <c r="AC366">
+        <v>0</v>
+      </c>
+      <c r="AD366">
+        <v>0</v>
+      </c>
+      <c r="AE366">
+        <v>0</v>
+      </c>
+      <c r="AF366">
+        <v>0</v>
+      </c>
+      <c r="AG366">
+        <v>0</v>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ366">
+        <v>0</v>
+      </c>
+      <c r="AK366">
+        <v>0</v>
+      </c>
+      <c r="AL366">
+        <v>0</v>
+      </c>
+      <c r="AM366">
+        <v>-1</v>
+      </c>
+      <c r="AN366">
+        <v>-1</v>
+      </c>
+      <c r="AO366">
+        <v>-1</v>
+      </c>
+      <c r="AP366">
+        <v>-1</v>
+      </c>
+      <c r="AQ366">
+        <v>0</v>
+      </c>
+      <c r="AR366">
+        <v>0</v>
+      </c>
+      <c r="AS366">
+        <v>0</v>
+      </c>
+      <c r="AT366">
+        <v>0</v>
+      </c>
+      <c r="AU366" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G367">
+        <v>0</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N367">
+        <v>0</v>
+      </c>
+      <c r="O367">
+        <v>0</v>
+      </c>
+      <c r="P367">
+        <v>0</v>
+      </c>
+      <c r="Q367">
+        <v>0</v>
+      </c>
+      <c r="R367">
+        <v>0</v>
+      </c>
+      <c r="S367">
+        <v>0</v>
+      </c>
+      <c r="T367">
+        <v>0</v>
+      </c>
+      <c r="U367">
+        <v>0</v>
+      </c>
+      <c r="V367">
+        <v>0</v>
+      </c>
+      <c r="W367">
+        <v>0</v>
+      </c>
+      <c r="X367">
+        <v>0</v>
+      </c>
+      <c r="Y367">
+        <v>0</v>
+      </c>
+      <c r="Z367">
+        <v>0</v>
+      </c>
+      <c r="AA367">
+        <v>0</v>
+      </c>
+      <c r="AB367">
+        <v>0</v>
+      </c>
+      <c r="AC367">
+        <v>0</v>
+      </c>
+      <c r="AD367">
+        <v>0</v>
+      </c>
+      <c r="AE367">
+        <v>0</v>
+      </c>
+      <c r="AF367">
+        <v>0</v>
+      </c>
+      <c r="AG367">
+        <v>0</v>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ367">
+        <v>0</v>
+      </c>
+      <c r="AK367">
+        <v>0</v>
+      </c>
+      <c r="AL367">
+        <v>0</v>
+      </c>
+      <c r="AM367">
+        <v>-1</v>
+      </c>
+      <c r="AN367">
+        <v>-1</v>
+      </c>
+      <c r="AO367">
+        <v>-1</v>
+      </c>
+      <c r="AP367">
+        <v>-1</v>
+      </c>
+      <c r="AQ367">
+        <v>0</v>
+      </c>
+      <c r="AR367">
+        <v>0</v>
+      </c>
+      <c r="AS367">
+        <v>0</v>
+      </c>
+      <c r="AT367">
+        <v>0</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F368" t="inlineStr">
         <is>
           <t>St. Louis City</t>
         </is>
       </c>
-      <c r="G366">
-        <v>0</v>
-      </c>
-      <c r="H366">
-        <v>0</v>
-      </c>
-      <c r="I366">
-        <v>0</v>
-      </c>
-      <c r="J366">
-        <v>0</v>
-      </c>
-      <c r="K366">
-        <v>0</v>
-      </c>
-      <c r="L366">
-        <v>0</v>
-      </c>
-      <c r="M366" t="inlineStr">
+      <c r="G368">
+        <v>0</v>
+      </c>
+      <c r="H368">
+        <v>0</v>
+      </c>
+      <c r="I368">
+        <v>0</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>0</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+      <c r="M368" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N366">
-        <v>0</v>
-      </c>
-      <c r="O366">
-        <v>0</v>
-      </c>
-      <c r="P366">
-        <v>0</v>
-      </c>
-      <c r="Q366">
-        <v>0</v>
-      </c>
-      <c r="R366">
-        <v>0</v>
-      </c>
-      <c r="S366">
-        <v>0</v>
-      </c>
-      <c r="T366">
-        <v>0</v>
-      </c>
-      <c r="U366">
-        <v>0</v>
-      </c>
-      <c r="V366">
-        <v>0</v>
-      </c>
-      <c r="W366">
-        <v>0</v>
-      </c>
-      <c r="X366">
-        <v>0</v>
-      </c>
-      <c r="Y366">
-        <v>0</v>
-      </c>
-      <c r="Z366">
-        <v>0</v>
-      </c>
-      <c r="AA366">
-        <v>0</v>
-      </c>
-      <c r="AB366">
-        <v>0</v>
-      </c>
-      <c r="AC366">
-        <v>0</v>
-      </c>
-      <c r="AD366">
-        <v>0</v>
-      </c>
-      <c r="AE366">
-        <v>0</v>
-      </c>
-      <c r="AF366">
-        <v>0</v>
-      </c>
-      <c r="AG366">
-        <v>0</v>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ366">
-        <v>0</v>
-      </c>
-      <c r="AK366">
-        <v>0</v>
-      </c>
-      <c r="AL366">
-        <v>0</v>
-      </c>
-      <c r="AM366">
-        <v>-1</v>
-      </c>
-      <c r="AN366">
-        <v>-1</v>
-      </c>
-      <c r="AO366">
-        <v>-1</v>
-      </c>
-      <c r="AP366">
-        <v>-1</v>
-      </c>
-      <c r="AQ366">
-        <v>0</v>
-      </c>
-      <c r="AR366">
-        <v>0</v>
-      </c>
-      <c r="AS366">
-        <v>0</v>
-      </c>
-      <c r="AT366">
-        <v>0</v>
-      </c>
-      <c r="AU366" t="inlineStr">
+      <c r="N368">
+        <v>0</v>
+      </c>
+      <c r="O368">
+        <v>0</v>
+      </c>
+      <c r="P368">
+        <v>0</v>
+      </c>
+      <c r="Q368">
+        <v>0</v>
+      </c>
+      <c r="R368">
+        <v>0</v>
+      </c>
+      <c r="S368">
+        <v>0</v>
+      </c>
+      <c r="T368">
+        <v>0</v>
+      </c>
+      <c r="U368">
+        <v>0</v>
+      </c>
+      <c r="V368">
+        <v>0</v>
+      </c>
+      <c r="W368">
+        <v>0</v>
+      </c>
+      <c r="X368">
+        <v>0</v>
+      </c>
+      <c r="Y368">
+        <v>0</v>
+      </c>
+      <c r="Z368">
+        <v>0</v>
+      </c>
+      <c r="AA368">
+        <v>0</v>
+      </c>
+      <c r="AB368">
+        <v>0</v>
+      </c>
+      <c r="AC368">
+        <v>0</v>
+      </c>
+      <c r="AD368">
+        <v>0</v>
+      </c>
+      <c r="AE368">
+        <v>0</v>
+      </c>
+      <c r="AF368">
+        <v>0</v>
+      </c>
+      <c r="AG368">
+        <v>0</v>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ368">
+        <v>0</v>
+      </c>
+      <c r="AK368">
+        <v>0</v>
+      </c>
+      <c r="AL368">
+        <v>0</v>
+      </c>
+      <c r="AM368">
+        <v>-1</v>
+      </c>
+      <c r="AN368">
+        <v>-1</v>
+      </c>
+      <c r="AO368">
+        <v>-1</v>
+      </c>
+      <c r="AP368">
+        <v>-1</v>
+      </c>
+      <c r="AQ368">
+        <v>0</v>
+      </c>
+      <c r="AR368">
+        <v>0</v>
+      </c>
+      <c r="AS368">
+        <v>0</v>
+      </c>
+      <c r="AT368">
+        <v>0</v>
+      </c>
+      <c r="AU368" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G113">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G133">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G142">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G153">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G167">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G168">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G169">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G265">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G267">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G333">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G360">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G361">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G365">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G107">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G328">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G335">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G336">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G338">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G368">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G167">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU368"/>
+  <dimension ref="A1:AU366"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,22 +48352,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G295">
@@ -48510,27 +48510,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G298">
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G300">
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -49493,22 +49493,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,22 +49656,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G304">
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O305">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P305">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50145,22 +50145,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G308">
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G310">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G312">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G313">
@@ -51449,22 +51449,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,22 +51612,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G315">
@@ -51770,27 +51770,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,19 +51817,19 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O316">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P316">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q316">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R316">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S316">
         <v>0</v>
@@ -51838,10 +51838,10 @@
         <v>0</v>
       </c>
       <c r="U316">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V316">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W316">
         <v>0</v>
@@ -51850,31 +51850,31 @@
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z316">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA316">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB316">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC316">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD316">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE316">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF316">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG316">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK316">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -51933,27 +51933,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G317">
@@ -51976,68 +51976,68 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N317">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="O317">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P317">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q317">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R317">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S317">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T317">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U317">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V317">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W317">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X317">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y317">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z317">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA317">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB317">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC317">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD317">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE317">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF317">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG317">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK317">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52084,7 +52084,7 @@
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -52096,27 +52096,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,19 +52143,19 @@
         </is>
       </c>
       <c r="N318">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O318">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P318">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S318">
         <v>0</v>
@@ -52164,10 +52164,10 @@
         <v>0</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W318">
         <v>0</v>
@@ -52176,31 +52176,31 @@
         <v>0</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:30:00</t>
         </is>
       </c>
     </row>
@@ -52264,22 +52264,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G319">
@@ -52302,68 +52302,68 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N319">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O319">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P319">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q319">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R319">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S319">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T319">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U319">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V319">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W319">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X319">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y319">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z319">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA319">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB319">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC319">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD319">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE319">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF319">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG319">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK319">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-09-05 18:15:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52748,12 +52748,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:00:00</t>
         </is>
       </c>
     </row>
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:15:00</t>
         </is>
       </c>
     </row>
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G324">
@@ -53242,7 +53242,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G325">
@@ -53400,12 +53400,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G326">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53563,12 +53563,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G327">
@@ -53714,7 +53714,7 @@
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53726,12 +53726,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 19:30:00</t>
         </is>
       </c>
     </row>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G330">
@@ -54220,7 +54220,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G331">
@@ -54378,7 +54378,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54541,12 +54541,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54709,7 +54709,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G334">
@@ -54872,7 +54872,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G335">
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G336">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G341">
@@ -56008,12 +56008,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G342">
@@ -56159,7 +56159,7 @@
       </c>
       <c r="AU342" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56171,27 +56171,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G343">
@@ -56322,7 +56322,7 @@
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56339,22 +56339,22 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G344">
@@ -56991,22 +56991,22 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G348">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G350">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G352">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G353">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G354">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G355">
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58453,27 +58453,27 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G359">
@@ -58942,7 +58942,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G360">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G361">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59268,12 +59268,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G362">
@@ -59419,7 +59419,7 @@
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59431,12 +59431,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G363">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -59757,12 +59757,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 23:30:00</t>
         </is>
       </c>
     </row>
@@ -59925,7 +59925,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G366">
@@ -60070,332 +60070,6 @@
         <v>0</v>
       </c>
       <c r="AU366" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="G367">
-        <v>0</v>
-      </c>
-      <c r="H367">
-        <v>0</v>
-      </c>
-      <c r="I367">
-        <v>0</v>
-      </c>
-      <c r="J367">
-        <v>0</v>
-      </c>
-      <c r="K367">
-        <v>0</v>
-      </c>
-      <c r="L367">
-        <v>0</v>
-      </c>
-      <c r="M367" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N367">
-        <v>0</v>
-      </c>
-      <c r="O367">
-        <v>0</v>
-      </c>
-      <c r="P367">
-        <v>0</v>
-      </c>
-      <c r="Q367">
-        <v>0</v>
-      </c>
-      <c r="R367">
-        <v>0</v>
-      </c>
-      <c r="S367">
-        <v>0</v>
-      </c>
-      <c r="T367">
-        <v>0</v>
-      </c>
-      <c r="U367">
-        <v>0</v>
-      </c>
-      <c r="V367">
-        <v>0</v>
-      </c>
-      <c r="W367">
-        <v>0</v>
-      </c>
-      <c r="X367">
-        <v>0</v>
-      </c>
-      <c r="Y367">
-        <v>0</v>
-      </c>
-      <c r="Z367">
-        <v>0</v>
-      </c>
-      <c r="AA367">
-        <v>0</v>
-      </c>
-      <c r="AB367">
-        <v>0</v>
-      </c>
-      <c r="AC367">
-        <v>0</v>
-      </c>
-      <c r="AD367">
-        <v>0</v>
-      </c>
-      <c r="AE367">
-        <v>0</v>
-      </c>
-      <c r="AF367">
-        <v>0</v>
-      </c>
-      <c r="AG367">
-        <v>0</v>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ367">
-        <v>0</v>
-      </c>
-      <c r="AK367">
-        <v>0</v>
-      </c>
-      <c r="AL367">
-        <v>0</v>
-      </c>
-      <c r="AM367">
-        <v>-1</v>
-      </c>
-      <c r="AN367">
-        <v>-1</v>
-      </c>
-      <c r="AO367">
-        <v>-1</v>
-      </c>
-      <c r="AP367">
-        <v>-1</v>
-      </c>
-      <c r="AQ367">
-        <v>0</v>
-      </c>
-      <c r="AR367">
-        <v>0</v>
-      </c>
-      <c r="AS367">
-        <v>0</v>
-      </c>
-      <c r="AT367">
-        <v>0</v>
-      </c>
-      <c r="AU367" t="inlineStr">
-        <is>
-          <t>2026-09-05 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="G368">
-        <v>0</v>
-      </c>
-      <c r="H368">
-        <v>0</v>
-      </c>
-      <c r="I368">
-        <v>0</v>
-      </c>
-      <c r="J368">
-        <v>0</v>
-      </c>
-      <c r="K368">
-        <v>0</v>
-      </c>
-      <c r="L368">
-        <v>0</v>
-      </c>
-      <c r="M368" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N368">
-        <v>0</v>
-      </c>
-      <c r="O368">
-        <v>0</v>
-      </c>
-      <c r="P368">
-        <v>0</v>
-      </c>
-      <c r="Q368">
-        <v>0</v>
-      </c>
-      <c r="R368">
-        <v>0</v>
-      </c>
-      <c r="S368">
-        <v>0</v>
-      </c>
-      <c r="T368">
-        <v>0</v>
-      </c>
-      <c r="U368">
-        <v>0</v>
-      </c>
-      <c r="V368">
-        <v>0</v>
-      </c>
-      <c r="W368">
-        <v>0</v>
-      </c>
-      <c r="X368">
-        <v>0</v>
-      </c>
-      <c r="Y368">
-        <v>0</v>
-      </c>
-      <c r="Z368">
-        <v>0</v>
-      </c>
-      <c r="AA368">
-        <v>0</v>
-      </c>
-      <c r="AB368">
-        <v>0</v>
-      </c>
-      <c r="AC368">
-        <v>0</v>
-      </c>
-      <c r="AD368">
-        <v>0</v>
-      </c>
-      <c r="AE368">
-        <v>0</v>
-      </c>
-      <c r="AF368">
-        <v>0</v>
-      </c>
-      <c r="AG368">
-        <v>0</v>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ368">
-        <v>0</v>
-      </c>
-      <c r="AK368">
-        <v>0</v>
-      </c>
-      <c r="AL368">
-        <v>0</v>
-      </c>
-      <c r="AM368">
-        <v>-1</v>
-      </c>
-      <c r="AN368">
-        <v>-1</v>
-      </c>
-      <c r="AO368">
-        <v>-1</v>
-      </c>
-      <c r="AP368">
-        <v>-1</v>
-      </c>
-      <c r="AQ368">
-        <v>0</v>
-      </c>
-      <c r="AR368">
-        <v>0</v>
-      </c>
-      <c r="AS368">
-        <v>0</v>
-      </c>
-      <c r="AT368">
-        <v>0</v>
-      </c>
-      <c r="AU368" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G116">
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-09-05 12:15:00</t>
+          <t>2026-09-05 12:00:00</t>
         </is>
       </c>
     </row>
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,22 +34008,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G207">
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G208">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-09-05 12:30:00</t>
+          <t>2026-09-05 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,22 +34823,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G212">
@@ -34981,27 +34981,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G213">
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-09-05 12:50:00</t>
+          <t>2026-09-05 12:30:00</t>
         </is>
       </c>
     </row>
@@ -35144,7 +35144,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-05 12:55:00</t>
+          <t>2026-09-05 12:50:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-09-05 13:00:00</t>
+          <t>2026-09-05 12:55:00</t>
         </is>
       </c>
     </row>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G225">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,22 +37268,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,22 +37431,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G235">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:00</t>
+          <t>2026-09-05 13:00:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-05 13:15:00</t>
+          <t>2026-09-05 13:10:00</t>
         </is>
       </c>
     </row>
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G239">
@@ -39382,27 +39382,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-09-05 13:30:00</t>
+          <t>2026-09-05 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39550,22 +39550,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G243">
@@ -40039,22 +40039,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G247">
@@ -40686,12 +40686,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G248">
@@ -40837,7 +40837,7 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>2026-09-05 13:45:00</t>
+          <t>2026-09-05 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G251">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G252">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G253">
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-09-05 14:00:00</t>
+          <t>2026-09-05 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G258">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G262">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G264">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU366"/>
+  <dimension ref="A1:AU368"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G107">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G205">
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-09-05 12:15:00</t>
+          <t>2026-09-05 12:00:00</t>
         </is>
       </c>
     </row>
@@ -34008,22 +34008,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G208">
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-09-05 12:30:00</t>
+          <t>2026-09-05 12:15:00</t>
         </is>
       </c>
     </row>
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,22 +34986,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G213">
@@ -35144,27 +35144,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-05 12:50:00</t>
+          <t>2026-09-05 12:30:00</t>
         </is>
       </c>
     </row>
@@ -35307,7 +35307,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-09-05 12:55:00</t>
+          <t>2026-09-05 12:50:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G216">
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-09-05 13:00:00</t>
+          <t>2026-09-05 12:55:00</t>
         </is>
       </c>
     </row>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G218">
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,22 +36127,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,22 +36942,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G227">
@@ -37431,22 +37431,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G228">
@@ -37594,22 +37594,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G236">
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-05 13:10:00</t>
+          <t>2026-09-05 13:00:00</t>
         </is>
       </c>
     </row>
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-05 13:15:00</t>
+          <t>2026-09-05 13:10:00</t>
         </is>
       </c>
     </row>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G240">
@@ -39545,27 +39545,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-09-05 13:30:00</t>
+          <t>2026-09-05 13:15:00</t>
         </is>
       </c>
     </row>
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G244">
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G248">
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G249">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-09-05 13:45:00</t>
+          <t>2026-09-05 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G250">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G252">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G254">
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-09-05 14:00:00</t>
+          <t>2026-09-05 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G257">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G259">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G265">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G266">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G267">
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-05 14:15:00</t>
+          <t>2026-09-05 14:00:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-05 14:30:00</t>
+          <t>2026-09-05 14:15:00</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G273">
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-05 15:00:00</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -45087,12 +45087,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O275">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P275">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q275">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R275">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S275">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T275">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U275">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="V275">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W275">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X275">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y275">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z275">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA275">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB275">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC275">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD275">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF275">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG275">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK275">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-05 15:00:00</t>
+          <t>2026-09-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45744,22 +45744,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O279">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P279">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46070,22 +46070,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G287">
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,27 +47369,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-05 15:15:00</t>
+          <t>2026-09-05 15:00:00</t>
         </is>
       </c>
     </row>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G290">
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -47858,27 +47858,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O292">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P292">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-09-05 15:30:00</t>
+          <t>2026-09-05 15:15:00</t>
         </is>
       </c>
     </row>
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,22 +48189,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,22 +48515,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G296">
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -48836,27 +48836,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-05 15:45:00</t>
+          <t>2026-09-05 15:30:00</t>
         </is>
       </c>
     </row>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G299">
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G300">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G301">
@@ -49488,27 +49488,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-05 16:00:00</t>
+          <t>2026-09-05 15:45:00</t>
         </is>
       </c>
     </row>
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G304">
@@ -49982,22 +49982,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G305">
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O306">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P306">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50308,22 +50308,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G307">
@@ -50471,22 +50471,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G309">
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G311">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G312">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G313">
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,22 +51775,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G316">
@@ -51938,22 +51938,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G317">
@@ -52096,27 +52096,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G318">
@@ -52143,19 +52143,19 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O318">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="P318">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q318">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R318">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S318">
         <v>0</v>
@@ -52164,10 +52164,10 @@
         <v>0</v>
       </c>
       <c r="U318">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V318">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W318">
         <v>0</v>
@@ -52176,31 +52176,31 @@
         <v>0</v>
       </c>
       <c r="Y318">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z318">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA318">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB318">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC318">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD318">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE318">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF318">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG318">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK318">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>2026-09-05 16:30:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -52259,27 +52259,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G319">
@@ -52302,68 +52302,68 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N319">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="O319">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P319">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q319">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R319">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S319">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T319">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U319">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V319">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W319">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X319">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y319">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z319">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA319">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB319">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC319">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD319">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE319">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF319">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG319">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK319">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:00:00</t>
         </is>
       </c>
     </row>
@@ -52422,27 +52422,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,19 +52469,19 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S320">
         <v>0</v>
@@ -52490,10 +52490,10 @@
         <v>0</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W320">
         <v>0</v>
@@ -52502,31 +52502,31 @@
         <v>0</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-09-05 17:00:00</t>
+          <t>2026-09-05 16:30:00</t>
         </is>
       </c>
     </row>
@@ -52590,22 +52590,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G321">
@@ -52628,68 +52628,68 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q321">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R321">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S321">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T321">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U321">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V321">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W321">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X321">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y321">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z321">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA321">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB321">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC321">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD321">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE321">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF321">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG321">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK321">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52748,12 +52748,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-09-05 18:00:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G323">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-09-05 18:15:00</t>
+          <t>2026-09-05 17:00:00</t>
         </is>
       </c>
     </row>
@@ -53074,12 +53074,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G324">
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:00:00</t>
         </is>
       </c>
     </row>
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G325">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-09-05 18:30:00</t>
+          <t>2026-09-05 18:15:00</t>
         </is>
       </c>
     </row>
@@ -53405,7 +53405,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G326">
@@ -53568,7 +53568,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G327">
@@ -53726,12 +53726,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-05 19:30:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -53889,12 +53889,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 18:30:00</t>
         </is>
       </c>
     </row>
@@ -54052,12 +54052,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-09-05 20:00:00</t>
+          <t>2026-09-05 19:30:00</t>
         </is>
       </c>
     </row>
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G332">
@@ -54546,7 +54546,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G333">
@@ -54704,7 +54704,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-05 20:30:00</t>
+          <t>2026-09-05 20:00:00</t>
         </is>
       </c>
     </row>
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G336">
@@ -55198,7 +55198,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G337">
@@ -55361,7 +55361,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G341">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G342">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G343">
@@ -56334,12 +56334,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G344">
@@ -56485,7 +56485,7 @@
       </c>
       <c r="AU344" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56497,27 +56497,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G345">
@@ -56648,7 +56648,7 @@
       </c>
       <c r="AU345" t="inlineStr">
         <is>
-          <t>2026-09-05 21:00:00</t>
+          <t>2026-09-05 20:30:00</t>
         </is>
       </c>
     </row>
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,22 +56828,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G347">
@@ -56991,7 +56991,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G348">
@@ -57154,7 +57154,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G350">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G351">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G352">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G353">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G354">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G355">
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-09-05 21:30:00</t>
+          <t>2026-09-05 21:00:00</t>
         </is>
       </c>
     </row>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G359">
@@ -58942,7 +58942,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G360">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G361">
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-09-05 22:30:00</t>
+          <t>2026-09-05 21:30:00</t>
         </is>
       </c>
     </row>
@@ -59268,12 +59268,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G362">
@@ -59419,7 +59419,7 @@
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59431,12 +59431,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G363">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-09-05 23:00:00</t>
+          <t>2026-09-05 22:30:00</t>
         </is>
       </c>
     </row>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G364">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59757,12 +59757,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G365">
@@ -59908,7 +59908,7 @@
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>2026-09-05 23:30:00</t>
+          <t>2026-09-05 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59925,151 +59925,477 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G366">
+        <v>0</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N366">
+        <v>0</v>
+      </c>
+      <c r="O366">
+        <v>0</v>
+      </c>
+      <c r="P366">
+        <v>0</v>
+      </c>
+      <c r="Q366">
+        <v>0</v>
+      </c>
+      <c r="R366">
+        <v>0</v>
+      </c>
+      <c r="S366">
+        <v>0</v>
+      </c>
+      <c r="T366">
+        <v>0</v>
+      </c>
+      <c r="U366">
+        <v>0</v>
+      </c>
+      <c r="V366">
+        <v>0</v>
+      </c>
+      <c r="W366">
+        <v>0</v>
+      </c>
+      <c r="X366">
+        <v>0</v>
+      </c>
+      <c r="Y366">
+        <v>0</v>
+      </c>
+      <c r="Z366">
+        <v>0</v>
+      </c>
+      <c r="AA366">
+        <v>0</v>
+      </c>
+      <c r="AB366">
+        <v>0</v>
+      </c>
+      <c r="AC366">
+        <v>0</v>
+      </c>
+      <c r="AD366">
+        <v>0</v>
+      </c>
+      <c r="AE366">
+        <v>0</v>
+      </c>
+      <c r="AF366">
+        <v>0</v>
+      </c>
+      <c r="AG366">
+        <v>0</v>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ366">
+        <v>0</v>
+      </c>
+      <c r="AK366">
+        <v>0</v>
+      </c>
+      <c r="AL366">
+        <v>0</v>
+      </c>
+      <c r="AM366">
+        <v>-1</v>
+      </c>
+      <c r="AN366">
+        <v>-1</v>
+      </c>
+      <c r="AO366">
+        <v>-1</v>
+      </c>
+      <c r="AP366">
+        <v>-1</v>
+      </c>
+      <c r="AQ366">
+        <v>0</v>
+      </c>
+      <c r="AR366">
+        <v>0</v>
+      </c>
+      <c r="AS366">
+        <v>0</v>
+      </c>
+      <c r="AT366">
+        <v>0</v>
+      </c>
+      <c r="AU366" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="G367">
+        <v>0</v>
+      </c>
+      <c r="H367">
+        <v>0</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>0</v>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N367">
+        <v>0</v>
+      </c>
+      <c r="O367">
+        <v>0</v>
+      </c>
+      <c r="P367">
+        <v>0</v>
+      </c>
+      <c r="Q367">
+        <v>0</v>
+      </c>
+      <c r="R367">
+        <v>0</v>
+      </c>
+      <c r="S367">
+        <v>0</v>
+      </c>
+      <c r="T367">
+        <v>0</v>
+      </c>
+      <c r="U367">
+        <v>0</v>
+      </c>
+      <c r="V367">
+        <v>0</v>
+      </c>
+      <c r="W367">
+        <v>0</v>
+      </c>
+      <c r="X367">
+        <v>0</v>
+      </c>
+      <c r="Y367">
+        <v>0</v>
+      </c>
+      <c r="Z367">
+        <v>0</v>
+      </c>
+      <c r="AA367">
+        <v>0</v>
+      </c>
+      <c r="AB367">
+        <v>0</v>
+      </c>
+      <c r="AC367">
+        <v>0</v>
+      </c>
+      <c r="AD367">
+        <v>0</v>
+      </c>
+      <c r="AE367">
+        <v>0</v>
+      </c>
+      <c r="AF367">
+        <v>0</v>
+      </c>
+      <c r="AG367">
+        <v>0</v>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ367">
+        <v>0</v>
+      </c>
+      <c r="AK367">
+        <v>0</v>
+      </c>
+      <c r="AL367">
+        <v>0</v>
+      </c>
+      <c r="AM367">
+        <v>-1</v>
+      </c>
+      <c r="AN367">
+        <v>-1</v>
+      </c>
+      <c r="AO367">
+        <v>-1</v>
+      </c>
+      <c r="AP367">
+        <v>-1</v>
+      </c>
+      <c r="AQ367">
+        <v>0</v>
+      </c>
+      <c r="AR367">
+        <v>0</v>
+      </c>
+      <c r="AS367">
+        <v>0</v>
+      </c>
+      <c r="AT367">
+        <v>0</v>
+      </c>
+      <c r="AU367" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
         <is>
           <t>Portland Timbers</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F368" t="inlineStr">
         <is>
           <t>Minnesota United</t>
         </is>
       </c>
-      <c r="G366">
-        <v>0</v>
-      </c>
-      <c r="H366">
-        <v>0</v>
-      </c>
-      <c r="I366">
-        <v>0</v>
-      </c>
-      <c r="J366">
-        <v>0</v>
-      </c>
-      <c r="K366">
-        <v>0</v>
-      </c>
-      <c r="L366">
-        <v>0</v>
-      </c>
-      <c r="M366" t="inlineStr">
+      <c r="G368">
+        <v>0</v>
+      </c>
+      <c r="H368">
+        <v>0</v>
+      </c>
+      <c r="I368">
+        <v>0</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>0</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+      <c r="M368" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N366">
-        <v>0</v>
-      </c>
-      <c r="O366">
-        <v>0</v>
-      </c>
-      <c r="P366">
-        <v>0</v>
-      </c>
-      <c r="Q366">
-        <v>0</v>
-      </c>
-      <c r="R366">
-        <v>0</v>
-      </c>
-      <c r="S366">
-        <v>0</v>
-      </c>
-      <c r="T366">
-        <v>0</v>
-      </c>
-      <c r="U366">
-        <v>0</v>
-      </c>
-      <c r="V366">
-        <v>0</v>
-      </c>
-      <c r="W366">
-        <v>0</v>
-      </c>
-      <c r="X366">
-        <v>0</v>
-      </c>
-      <c r="Y366">
-        <v>0</v>
-      </c>
-      <c r="Z366">
-        <v>0</v>
-      </c>
-      <c r="AA366">
-        <v>0</v>
-      </c>
-      <c r="AB366">
-        <v>0</v>
-      </c>
-      <c r="AC366">
-        <v>0</v>
-      </c>
-      <c r="AD366">
-        <v>0</v>
-      </c>
-      <c r="AE366">
-        <v>0</v>
-      </c>
-      <c r="AF366">
-        <v>0</v>
-      </c>
-      <c r="AG366">
-        <v>0</v>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ366">
-        <v>0</v>
-      </c>
-      <c r="AK366">
-        <v>0</v>
-      </c>
-      <c r="AL366">
-        <v>0</v>
-      </c>
-      <c r="AM366">
-        <v>-1</v>
-      </c>
-      <c r="AN366">
-        <v>-1</v>
-      </c>
-      <c r="AO366">
-        <v>-1</v>
-      </c>
-      <c r="AP366">
-        <v>-1</v>
-      </c>
-      <c r="AQ366">
-        <v>0</v>
-      </c>
-      <c r="AR366">
-        <v>0</v>
-      </c>
-      <c r="AS366">
-        <v>0</v>
-      </c>
-      <c r="AT366">
-        <v>0</v>
-      </c>
-      <c r="AU366" t="inlineStr">
+      <c r="N368">
+        <v>0</v>
+      </c>
+      <c r="O368">
+        <v>0</v>
+      </c>
+      <c r="P368">
+        <v>0</v>
+      </c>
+      <c r="Q368">
+        <v>0</v>
+      </c>
+      <c r="R368">
+        <v>0</v>
+      </c>
+      <c r="S368">
+        <v>0</v>
+      </c>
+      <c r="T368">
+        <v>0</v>
+      </c>
+      <c r="U368">
+        <v>0</v>
+      </c>
+      <c r="V368">
+        <v>0</v>
+      </c>
+      <c r="W368">
+        <v>0</v>
+      </c>
+      <c r="X368">
+        <v>0</v>
+      </c>
+      <c r="Y368">
+        <v>0</v>
+      </c>
+      <c r="Z368">
+        <v>0</v>
+      </c>
+      <c r="AA368">
+        <v>0</v>
+      </c>
+      <c r="AB368">
+        <v>0</v>
+      </c>
+      <c r="AC368">
+        <v>0</v>
+      </c>
+      <c r="AD368">
+        <v>0</v>
+      </c>
+      <c r="AE368">
+        <v>0</v>
+      </c>
+      <c r="AF368">
+        <v>0</v>
+      </c>
+      <c r="AG368">
+        <v>0</v>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ368">
+        <v>0</v>
+      </c>
+      <c r="AK368">
+        <v>0</v>
+      </c>
+      <c r="AL368">
+        <v>0</v>
+      </c>
+      <c r="AM368">
+        <v>-1</v>
+      </c>
+      <c r="AN368">
+        <v>-1</v>
+      </c>
+      <c r="AO368">
+        <v>-1</v>
+      </c>
+      <c r="AP368">
+        <v>-1</v>
+      </c>
+      <c r="AQ368">
+        <v>0</v>
+      </c>
+      <c r="AR368">
+        <v>0</v>
+      </c>
+      <c r="AS368">
+        <v>0</v>
+      </c>
+      <c r="AT368">
+        <v>0</v>
+      </c>
+      <c r="AU368" t="inlineStr">
         <is>
           <t>2026-09-05 23:30:00</t>
         </is>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G3">
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G80">
@@ -13358,55 +13358,55 @@
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -24605,10 +24605,10 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S149">
         <v>0</v>
@@ -24617,10 +24617,10 @@
         <v>0</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W149">
         <v>0</v>
@@ -24629,31 +24629,31 @@
         <v>0</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,10 +25909,10 @@
         <v>0</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S157">
         <v>0</v>
@@ -25921,10 +25921,10 @@
         <v>0</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W157">
         <v>0</v>
@@ -25933,31 +25933,31 @@
         <v>0</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE157">
         <v>0</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26917,10 +26917,10 @@
         <v>0</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -28028,55 +28028,55 @@
         <v>0</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X176">
         <v>0</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X179">
         <v>0</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X180">
         <v>0</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,55 +31451,55 @@
         <v>0</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33081,10 +33081,10 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S201">
         <v>0</v>
@@ -33093,10 +33093,10 @@
         <v>0</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W201">
         <v>0</v>
@@ -33105,31 +33105,31 @@
         <v>0</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G203">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G206">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z235">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC235">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD235">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE235">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF235">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG235">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -40416,10 +40416,10 @@
         <v>0</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S246">
         <v>0</v>
@@ -40428,10 +40428,10 @@
         <v>0</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W246">
         <v>0</v>
@@ -40446,19 +40446,19 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF246">
         <v>0</v>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40570,64 +40570,64 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41874,64 +41874,64 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X261">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -46773,10 +46773,10 @@
         <v>0</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S285">
         <v>0</v>
@@ -46785,10 +46785,10 @@
         <v>0</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W285">
         <v>0</v>
@@ -46797,31 +46797,31 @@
         <v>0</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE285">
         <v>0</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,64 +47416,64 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X289">
         <v>0</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q298">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R298">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S298">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T298">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U298">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V298">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W298">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y298">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z298">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA298">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB298">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC298">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD298">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE298">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG298">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK298">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G341">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G342">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G343">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G344">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G345">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="Q2">
-        <v>2.69</v>
+        <v>3.85</v>
       </c>
       <c r="R2">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>3.04</v>
+        <v>2.41</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>2.83</v>
+        <v>3.88</v>
       </c>
       <c r="AA2">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AB2">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="AC2">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
+        <v>1.24</v>
+      </c>
+      <c r="AK2">
         <v>1.27</v>
-      </c>
-      <c r="AK2">
-        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>3.68</v>
+        <v>2.69</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
+        <v>2.47</v>
+      </c>
+      <c r="U3">
+        <v>3.04</v>
+      </c>
+      <c r="V3">
+        <v>1.3</v>
+      </c>
+      <c r="W3">
+        <v>1.02</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.36</v>
+      </c>
+      <c r="Z3">
         <v>2.83</v>
       </c>
-      <c r="U3">
-        <v>2.6</v>
-      </c>
-      <c r="V3">
-        <v>1.4</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1.23</v>
-      </c>
-      <c r="Z3">
-        <v>3.42</v>
-      </c>
       <c r="AA3">
-        <v>1.81</v>
+        <v>2.17</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
+        <v>1.84</v>
+      </c>
+      <c r="AG3">
+        <v>1.83</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.27</v>
+      </c>
+      <c r="AK3">
         <v>1.65</v>
-      </c>
-      <c r="AG3">
-        <v>2.07</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.24</v>
-      </c>
-      <c r="AK3">
-        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="R4">
         <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="U4">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1.23</v>
+      </c>
+      <c r="Z4">
+        <v>3.42</v>
+      </c>
+      <c r="AA4">
+        <v>1.81</v>
+      </c>
+      <c r="AB4">
+        <v>1.88</v>
+      </c>
+      <c r="AC4">
+        <v>3.05</v>
+      </c>
+      <c r="AD4">
+        <v>1.31</v>
+      </c>
+      <c r="AE4">
         <v>1.08</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.18</v>
-      </c>
-      <c r="Z4">
-        <v>3.88</v>
-      </c>
-      <c r="AA4">
-        <v>1.67</v>
-      </c>
-      <c r="AB4">
-        <v>2.06</v>
-      </c>
-      <c r="AC4">
-        <v>2.56</v>
-      </c>
-      <c r="AD4">
-        <v>1.4</v>
-      </c>
-      <c r="AE4">
-        <v>1.13</v>
-      </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>3.68</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="AA8">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="AD8">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q9">
-        <v>3.68</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="AA9">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>4.24</v>
+        <v>3.52</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>3.64</v>
       </c>
       <c r="AA17">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AB17">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AC17">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="AD17">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q18">
-        <v>3.52</v>
+        <v>4.24</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AB18">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AC18">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G39">
@@ -6669,61 +6669,61 @@
         <v>1.91</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q39">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U39">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="V39">
         <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y39">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z39">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC39">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40">
@@ -6832,61 +6832,61 @@
         <v>1.91</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q40">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R40">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U40">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="V40">
         <v>1.4</v>
       </c>
       <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
         <v>1.03</v>
       </c>
-      <c r="X40">
+      <c r="Y40">
+        <v>1.27</v>
+      </c>
+      <c r="Z40">
+        <v>3.35</v>
+      </c>
+      <c r="AA40">
+        <v>2</v>
+      </c>
+      <c r="AB40">
+        <v>1.75</v>
+      </c>
+      <c r="AC40">
+        <v>3.6</v>
+      </c>
+      <c r="AD40">
+        <v>1.24</v>
+      </c>
+      <c r="AE40">
         <v>1.07</v>
       </c>
-      <c r="Y40">
-        <v>1.36</v>
-      </c>
-      <c r="Z40">
-        <v>3.1</v>
-      </c>
-      <c r="AA40">
-        <v>2.01</v>
-      </c>
-      <c r="AB40">
-        <v>1.7</v>
-      </c>
-      <c r="AC40">
-        <v>3.8</v>
-      </c>
-      <c r="AD40">
-        <v>1.25</v>
-      </c>
-      <c r="AE40">
-        <v>1.04</v>
-      </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="S42">
+        <v>1.42</v>
+      </c>
+      <c r="T42">
+        <v>2.65</v>
+      </c>
+      <c r="U42">
+        <v>3.15</v>
+      </c>
+      <c r="V42">
+        <v>1.31</v>
+      </c>
+      <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
+        <v>1.34</v>
+      </c>
+      <c r="Z42">
+        <v>3</v>
+      </c>
+      <c r="AA42">
+        <v>2.18</v>
+      </c>
+      <c r="AB42">
+        <v>1.66</v>
+      </c>
+      <c r="AC42">
+        <v>3.78</v>
+      </c>
+      <c r="AD42">
+        <v>1.19</v>
+      </c>
+      <c r="AE42">
+        <v>1.03</v>
+      </c>
+      <c r="AF42">
+        <v>1.87</v>
+      </c>
+      <c r="AG42">
+        <v>1.83</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.36</v>
       </c>
-      <c r="T42">
-        <v>2.88</v>
-      </c>
-      <c r="U42">
-        <v>2.99</v>
-      </c>
-      <c r="V42">
-        <v>1.33</v>
-      </c>
-      <c r="W42">
-        <v>1.05</v>
-      </c>
-      <c r="X42">
-        <v>1.04</v>
-      </c>
-      <c r="Y42">
-        <v>1.32</v>
-      </c>
-      <c r="Z42">
-        <v>3.15</v>
-      </c>
-      <c r="AA42">
-        <v>2.1</v>
-      </c>
-      <c r="AB42">
-        <v>1.72</v>
-      </c>
-      <c r="AC42">
-        <v>3.7</v>
-      </c>
-      <c r="AD42">
-        <v>1.24</v>
-      </c>
-      <c r="AE42">
-        <v>1.04</v>
-      </c>
-      <c r="AF42">
-        <v>1.8</v>
-      </c>
-      <c r="AG42">
-        <v>1.9</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.44</v>
-      </c>
       <c r="AK42">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="R44">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U44">
+        <v>2.99</v>
+      </c>
+      <c r="V44">
+        <v>1.33</v>
+      </c>
+      <c r="W44">
+        <v>1.05</v>
+      </c>
+      <c r="X44">
+        <v>1.04</v>
+      </c>
+      <c r="Y44">
+        <v>1.32</v>
+      </c>
+      <c r="Z44">
         <v>3.15</v>
       </c>
-      <c r="V44">
-        <v>1.31</v>
-      </c>
-      <c r="W44">
-        <v>1.07</v>
-      </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
-      <c r="Y44">
-        <v>1.34</v>
-      </c>
-      <c r="Z44">
-        <v>3</v>
-      </c>
       <c r="AA44">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC44">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="O77">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.01</v>
+        <v>4.1</v>
       </c>
       <c r="Q77">
-        <v>4.04</v>
+        <v>2.44</v>
       </c>
       <c r="R77">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
+        <v>1.03</v>
+      </c>
+      <c r="X77">
+        <v>1.01</v>
+      </c>
+      <c r="Y77">
+        <v>1.28</v>
+      </c>
+      <c r="Z77">
+        <v>3.08</v>
+      </c>
+      <c r="AA77">
+        <v>1.98</v>
+      </c>
+      <c r="AB77">
+        <v>1.74</v>
+      </c>
+      <c r="AC77">
+        <v>3.34</v>
+      </c>
+      <c r="AD77">
+        <v>1.24</v>
+      </c>
+      <c r="AE77">
         <v>1.05</v>
       </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>1.21</v>
-      </c>
-      <c r="Z77">
-        <v>3.58</v>
-      </c>
-      <c r="AA77">
-        <v>1.8</v>
-      </c>
-      <c r="AB77">
-        <v>1.9</v>
-      </c>
-      <c r="AC77">
-        <v>3.13</v>
-      </c>
-      <c r="AD77">
-        <v>1.33</v>
-      </c>
-      <c r="AE77">
-        <v>1.08</v>
-      </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG77">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,49 +13023,49 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P78">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q78">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="R78">
+        <v>2</v>
+      </c>
+      <c r="S78">
+        <v>1.42</v>
+      </c>
+      <c r="T78">
+        <v>2.56</v>
+      </c>
+      <c r="U78">
+        <v>2.91</v>
+      </c>
+      <c r="V78">
+        <v>1.33</v>
+      </c>
+      <c r="W78">
+        <v>1.04</v>
+      </c>
+      <c r="X78">
+        <v>1.03</v>
+      </c>
+      <c r="Y78">
+        <v>1.3</v>
+      </c>
+      <c r="Z78">
+        <v>2.97</v>
+      </c>
+      <c r="AA78">
         <v>2.02</v>
       </c>
-      <c r="S78">
-        <v>1.4</v>
-      </c>
-      <c r="T78">
-        <v>2.62</v>
-      </c>
-      <c r="U78">
-        <v>2.88</v>
-      </c>
-      <c r="V78">
-        <v>1.34</v>
-      </c>
-      <c r="W78">
-        <v>1.03</v>
-      </c>
-      <c r="X78">
-        <v>1.01</v>
-      </c>
-      <c r="Y78">
-        <v>1.28</v>
-      </c>
-      <c r="Z78">
-        <v>3.08</v>
-      </c>
-      <c r="AA78">
-        <v>1.98</v>
-      </c>
       <c r="AB78">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC78">
         <v>3.34</v>
@@ -13077,10 +13077,10 @@
         <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG78">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.61</v>
+        <v>2.85</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S79">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T79">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="V79">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA79">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AB79">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AC79">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF79">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AG79">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,34 +13349,34 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q80">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
       <c r="R80">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U80">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="V80">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W80">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13388,25 +13388,25 @@
         <v>3.28</v>
       </c>
       <c r="AA80">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AB80">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC80">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="AD80">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG80">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK80">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="R81">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="S81">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T81">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="U81">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="V81">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W81">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z81">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AA81">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB81">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC81">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AD81">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG81">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P82">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="Q82">
-        <v>3.42</v>
+        <v>4.04</v>
       </c>
       <c r="R82">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="S82">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="U82">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="V82">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y82">
+        <v>1.21</v>
+      </c>
+      <c r="Z82">
+        <v>3.58</v>
+      </c>
+      <c r="AA82">
+        <v>1.8</v>
+      </c>
+      <c r="AB82">
+        <v>1.9</v>
+      </c>
+      <c r="AC82">
+        <v>3.13</v>
+      </c>
+      <c r="AD82">
         <v>1.33</v>
       </c>
-      <c r="Z82">
-        <v>2.83</v>
-      </c>
-      <c r="AA82">
-        <v>2.12</v>
-      </c>
-      <c r="AB82">
-        <v>1.64</v>
-      </c>
-      <c r="AC82">
-        <v>3.74</v>
-      </c>
-      <c r="AD82">
-        <v>1.19</v>
-      </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AG82">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="O83">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T83">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U83">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y83">
+        <v>1.27</v>
+      </c>
+      <c r="Z83">
+        <v>3.14</v>
+      </c>
+      <c r="AA83">
+        <v>1.95</v>
+      </c>
+      <c r="AB83">
+        <v>1.76</v>
+      </c>
+      <c r="AC83">
+        <v>3.34</v>
+      </c>
+      <c r="AD83">
+        <v>1.24</v>
+      </c>
+      <c r="AE83">
+        <v>1.05</v>
+      </c>
+      <c r="AF83">
+        <v>1.75</v>
+      </c>
+      <c r="AG83">
+        <v>1.95</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.25</v>
       </c>
-      <c r="Z83">
-        <v>3.28</v>
-      </c>
-      <c r="AA83">
-        <v>1.89</v>
-      </c>
-      <c r="AB83">
-        <v>1.89</v>
-      </c>
-      <c r="AC83">
-        <v>3.18</v>
-      </c>
-      <c r="AD83">
-        <v>1.33</v>
-      </c>
-      <c r="AE83">
-        <v>1.08</v>
-      </c>
-      <c r="AF83">
-        <v>1.73</v>
-      </c>
-      <c r="AG83">
-        <v>1.97</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.24</v>
-      </c>
       <c r="AK83">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="R92">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S92">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T92">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U92">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="V92">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W92">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z92">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA92">
+        <v>1.45</v>
+      </c>
+      <c r="AB92">
+        <v>2.55</v>
+      </c>
+      <c r="AC92">
+        <v>2.25</v>
+      </c>
+      <c r="AD92">
+        <v>1.57</v>
+      </c>
+      <c r="AE92">
+        <v>1.2</v>
+      </c>
+      <c r="AF92">
         <v>1.85</v>
       </c>
-      <c r="AB92">
-        <v>1.82</v>
-      </c>
-      <c r="AC92">
-        <v>3.2</v>
-      </c>
-      <c r="AD92">
-        <v>1.26</v>
-      </c>
-      <c r="AE92">
-        <v>1.05</v>
-      </c>
-      <c r="AF92">
-        <v>1.66</v>
-      </c>
       <c r="AG92">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AK92">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q94">
-        <v>1.64</v>
+        <v>2.88</v>
       </c>
       <c r="R94">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="S94">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="T94">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U94">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="V94">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z94">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA94">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AB94">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="AC94">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
+        <v>1.26</v>
+      </c>
+      <c r="AE94">
+        <v>1.05</v>
+      </c>
+      <c r="AF94">
+        <v>1.66</v>
+      </c>
+      <c r="AG94">
+        <v>2.01</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <v>1.38</v>
+      </c>
+      <c r="AK94">
         <v>1.57</v>
-      </c>
-      <c r="AE94">
-        <v>1.2</v>
-      </c>
-      <c r="AF94">
-        <v>1.85</v>
-      </c>
-      <c r="AG94">
-        <v>1.87</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.1</v>
-      </c>
-      <c r="AK94">
-        <v>3.75</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
+        <v>2.55</v>
+      </c>
+      <c r="O121">
+        <v>3.3</v>
+      </c>
+      <c r="P121">
+        <v>2.75</v>
+      </c>
+      <c r="Q121">
+        <v>3.1</v>
+      </c>
+      <c r="R121">
+        <v>2.1</v>
+      </c>
+      <c r="S121">
+        <v>1.4</v>
+      </c>
+      <c r="T121">
+        <v>2.75</v>
+      </c>
+      <c r="U121">
+        <v>2.9</v>
+      </c>
+      <c r="V121">
+        <v>1.4</v>
+      </c>
+      <c r="W121">
+        <v>1.08</v>
+      </c>
+      <c r="X121">
+        <v>1.06</v>
+      </c>
+      <c r="Y121">
+        <v>1.28</v>
+      </c>
+      <c r="Z121">
+        <v>3.24</v>
+      </c>
+      <c r="AA121">
+        <v>2.01</v>
+      </c>
+      <c r="AB121">
+        <v>1.85</v>
+      </c>
+      <c r="AC121">
+        <v>3.34</v>
+      </c>
+      <c r="AD121">
+        <v>1.27</v>
+      </c>
+      <c r="AE121">
+        <v>1.05</v>
+      </c>
+      <c r="AF121">
         <v>1.8</v>
       </c>
-      <c r="O121">
-        <v>3.6</v>
-      </c>
-      <c r="P121">
-        <v>4</v>
-      </c>
-      <c r="Q121">
-        <v>2.34</v>
-      </c>
-      <c r="R121">
-        <v>2.12</v>
-      </c>
-      <c r="S121">
+      <c r="AG121">
+        <v>2</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.38</v>
       </c>
-      <c r="T121">
-        <v>3.02</v>
-      </c>
-      <c r="U121">
-        <v>2.7</v>
-      </c>
-      <c r="V121">
-        <v>1.46</v>
-      </c>
-      <c r="W121">
-        <v>1.07</v>
-      </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.25</v>
-      </c>
-      <c r="Z121">
-        <v>3.7</v>
-      </c>
-      <c r="AA121">
-        <v>1.83</v>
-      </c>
-      <c r="AB121">
-        <v>2</v>
-      </c>
-      <c r="AC121">
-        <v>2.93</v>
-      </c>
-      <c r="AD121">
-        <v>1.37</v>
-      </c>
-      <c r="AE121">
-        <v>1.13</v>
-      </c>
-      <c r="AF121">
-        <v>1.7</v>
-      </c>
-      <c r="AG121">
-        <v>2.05</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.17</v>
-      </c>
       <c r="AK121">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
+        <v>1.57</v>
+      </c>
+      <c r="O122">
+        <v>3.9</v>
+      </c>
+      <c r="P122">
+        <v>5.9</v>
+      </c>
+      <c r="Q122">
+        <v>2.05</v>
+      </c>
+      <c r="R122">
+        <v>2.08</v>
+      </c>
+      <c r="S122">
+        <v>1.3</v>
+      </c>
+      <c r="T122">
+        <v>3.02</v>
+      </c>
+      <c r="U122">
         <v>2.55</v>
       </c>
-      <c r="O122">
-        <v>3.3</v>
-      </c>
-      <c r="P122">
-        <v>2.75</v>
-      </c>
-      <c r="Q122">
-        <v>3.1</v>
-      </c>
-      <c r="R122">
-        <v>2.1</v>
-      </c>
-      <c r="S122">
-        <v>1.4</v>
-      </c>
-      <c r="T122">
-        <v>2.75</v>
-      </c>
-      <c r="U122">
-        <v>2.9</v>
-      </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z122">
-        <v>3.24</v>
+        <v>3.97</v>
       </c>
       <c r="AA122">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AB122">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC122">
-        <v>3.34</v>
+        <v>2.84</v>
       </c>
       <c r="AD122">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE122">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK122">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,80 +20358,80 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="O123">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="Q123">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="R123">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S123">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T123">
         <v>3.02</v>
       </c>
       <c r="U123">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V123">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W123">
         <v>1.07</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z123">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA123">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB123">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC123">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AD123">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF123">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG123">
+        <v>2.05</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
+        <v>1.17</v>
+      </c>
+      <c r="AK123">
         <v>1.91</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.26</v>
-      </c>
-      <c r="AK123">
-        <v>2.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="O131">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P131">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="Q131">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="R131">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U131">
-        <v>3.34</v>
+        <v>2.91</v>
       </c>
       <c r="V131">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W131">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X131">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y131">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z131">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="AA131">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="AB131">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC131">
-        <v>4.16</v>
+        <v>3.42</v>
       </c>
       <c r="AD131">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE131">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF131">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK131">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="O133">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P133">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q133">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="R133">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S133">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T133">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U133">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="V133">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z133">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="AA133">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AB133">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC133">
-        <v>3.42</v>
+        <v>4.16</v>
       </c>
       <c r="AD133">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG133">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,80 +23618,80 @@
         </is>
       </c>
       <c r="N143">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P143">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q143">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R143">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S143">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T143">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U143">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="V143">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W143">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X143">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y143">
+        <v>1.2</v>
+      </c>
+      <c r="Z143">
+        <v>4.1</v>
+      </c>
+      <c r="AA143">
+        <v>1.73</v>
+      </c>
+      <c r="AB143">
+        <v>2.08</v>
+      </c>
+      <c r="AC143">
+        <v>2.8</v>
+      </c>
+      <c r="AD143">
+        <v>1.38</v>
+      </c>
+      <c r="AE143">
+        <v>1.12</v>
+      </c>
+      <c r="AF143">
+        <v>1.65</v>
+      </c>
+      <c r="AG143">
+        <v>2.04</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
         <v>1.23</v>
       </c>
-      <c r="Z143">
-        <v>3.65</v>
-      </c>
-      <c r="AA143">
-        <v>1.83</v>
-      </c>
-      <c r="AB143">
-        <v>1.95</v>
-      </c>
-      <c r="AC143">
-        <v>3.05</v>
-      </c>
-      <c r="AD143">
-        <v>1.3</v>
-      </c>
-      <c r="AE143">
-        <v>1.08</v>
-      </c>
-      <c r="AF143">
-        <v>1.62</v>
-      </c>
-      <c r="AG143">
-        <v>2.09</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>1.27</v>
-      </c>
       <c r="AK143">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="O144">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q144">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R144">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S144">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T144">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U144">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W144">
+        <v>1.06</v>
+      </c>
+      <c r="X144">
+        <v>1.03</v>
+      </c>
+      <c r="Y144">
+        <v>1.23</v>
+      </c>
+      <c r="Z144">
+        <v>3.65</v>
+      </c>
+      <c r="AA144">
+        <v>1.83</v>
+      </c>
+      <c r="AB144">
+        <v>1.95</v>
+      </c>
+      <c r="AC144">
+        <v>3.05</v>
+      </c>
+      <c r="AD144">
+        <v>1.3</v>
+      </c>
+      <c r="AE144">
         <v>1.08</v>
       </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="Y144">
-        <v>1.2</v>
-      </c>
-      <c r="Z144">
-        <v>4.1</v>
-      </c>
-      <c r="AA144">
-        <v>1.73</v>
-      </c>
-      <c r="AB144">
-        <v>2.08</v>
-      </c>
-      <c r="AC144">
-        <v>2.8</v>
-      </c>
-      <c r="AD144">
-        <v>1.38</v>
-      </c>
-      <c r="AE144">
-        <v>1.12</v>
-      </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK144">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="O153">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P153">
-        <v>2.92</v>
+        <v>3.63</v>
       </c>
       <c r="Q153">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="R153">
         <v>2.15</v>
       </c>
       <c r="S153">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T153">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U153">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V153">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W153">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X153">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y153">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z153">
+        <v>3.25</v>
+      </c>
+      <c r="AA153">
+        <v>1.98</v>
+      </c>
+      <c r="AB153">
+        <v>1.75</v>
+      </c>
+      <c r="AC153">
         <v>3.44</v>
       </c>
-      <c r="AA153">
-        <v>1.89</v>
-      </c>
-      <c r="AB153">
-        <v>1.85</v>
-      </c>
-      <c r="AC153">
-        <v>3.12</v>
-      </c>
       <c r="AD153">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE153">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF153">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG153">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,43 +25411,43 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="O154">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="Q154">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="R154">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S154">
         <v>1.39</v>
       </c>
       <c r="T154">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U154">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W154">
         <v>1.06</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z154">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA154">
         <v>1.89</v>
@@ -25456,19 +25456,19 @@
         <v>1.85</v>
       </c>
       <c r="AC154">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AD154">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE154">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF154">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG154">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O155">
+        <v>3.4</v>
+      </c>
+      <c r="P155">
+        <v>2.1</v>
+      </c>
+      <c r="Q155">
+        <v>4</v>
+      </c>
+      <c r="R155">
+        <v>2.08</v>
+      </c>
+      <c r="S155">
+        <v>1.39</v>
+      </c>
+      <c r="T155">
+        <v>2.69</v>
+      </c>
+      <c r="U155">
+        <v>2.75</v>
+      </c>
+      <c r="V155">
+        <v>1.4</v>
+      </c>
+      <c r="W155">
+        <v>1.06</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.25</v>
+      </c>
+      <c r="Z155">
+        <v>3.3</v>
+      </c>
+      <c r="AA155">
+        <v>1.89</v>
+      </c>
+      <c r="AB155">
+        <v>1.85</v>
+      </c>
+      <c r="AC155">
         <v>3.25</v>
       </c>
-      <c r="P155">
-        <v>2.75</v>
-      </c>
-      <c r="Q155">
-        <v>0</v>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155">
-        <v>0</v>
-      </c>
-      <c r="U155">
-        <v>0</v>
-      </c>
-      <c r="V155">
-        <v>0</v>
-      </c>
-      <c r="W155">
-        <v>0</v>
-      </c>
-      <c r="X155">
-        <v>0</v>
-      </c>
-      <c r="Y155">
-        <v>0</v>
-      </c>
-      <c r="Z155">
-        <v>0</v>
-      </c>
-      <c r="AA155">
-        <v>2</v>
-      </c>
-      <c r="AB155">
-        <v>1.8</v>
-      </c>
-      <c r="AC155">
-        <v>0</v>
-      </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O156">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P156">
-        <v>3.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q156">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R156">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S156">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T156">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U156">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V156">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y156">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z156">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA156">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB156">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC156">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD156">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE156">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF156">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG156">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK156">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O164">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P164">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="Q164">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="R164">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S164">
         <v>1.36</v>
       </c>
       <c r="T164">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U164">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V164">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W164">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X164">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z164">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="AA164">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AB164">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC164">
-        <v>3.45</v>
+        <v>2.73</v>
       </c>
       <c r="AD164">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE164">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF164">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG164">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK164">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O165">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P165">
-        <v>4</v>
+        <v>4.89</v>
       </c>
       <c r="Q165">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R165">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T165">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U165">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V165">
         <v>1.42</v>
       </c>
       <c r="W165">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z165">
         <v>3.3</v>
       </c>
       <c r="AA165">
+        <v>1.85</v>
+      </c>
+      <c r="AB165">
+        <v>1.95</v>
+      </c>
+      <c r="AC165">
+        <v>2.89</v>
+      </c>
+      <c r="AD165">
+        <v>1.32</v>
+      </c>
+      <c r="AE165">
+        <v>1.09</v>
+      </c>
+      <c r="AF165">
         <v>1.78</v>
       </c>
-      <c r="AB165">
-        <v>1.89</v>
-      </c>
-      <c r="AC165">
-        <v>3.1</v>
-      </c>
-      <c r="AD165">
-        <v>1.35</v>
-      </c>
-      <c r="AE165">
-        <v>1.12</v>
-      </c>
-      <c r="AF165">
-        <v>1.7</v>
-      </c>
       <c r="AG165">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK165">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="O166">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="P166">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="Q166">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R166">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S166">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T166">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U166">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V166">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W166">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X166">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y166">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z166">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AA166">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB166">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AC166">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD166">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE166">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF166">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG166">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK166">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O167">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P167">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q167">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="R167">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S167">
         <v>1.36</v>
       </c>
       <c r="T167">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U167">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V167">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W167">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X167">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y167">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z167">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="AA167">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB167">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AC167">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="AD167">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE167">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF167">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG167">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AK167">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="O168">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P168">
-        <v>4.89</v>
+        <v>4</v>
       </c>
       <c r="Q168">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R168">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S168">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T168">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="U168">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V168">
         <v>1.42</v>
       </c>
       <c r="W168">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z168">
         <v>3.3</v>
       </c>
       <c r="AA168">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB168">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC168">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD168">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE168">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF168">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG168">
+        <v>2.01</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.26</v>
+      </c>
+      <c r="AK168">
         <v>1.93</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.22</v>
-      </c>
-      <c r="AK168">
-        <v>2.1</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="O169">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="P169">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA169">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB169">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G319">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>3.68</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="U7">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.18</v>
+        <v>3.65</v>
       </c>
       <c r="AA7">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q8">
-        <v>3.68</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
+        <v>1.03</v>
+      </c>
+      <c r="X8">
         <v>1.06</v>
       </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD8">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1.98</v>
+        <v>3.52</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>4.3</v>
+        <v>3.64</v>
       </c>
       <c r="AA16">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AB16">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC16">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="AD16">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>2.57</v>
+        <v>1.35</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q17">
-        <v>3.52</v>
+        <v>4.24</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AB17">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AC17">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="AD17">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AE17">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>1.38</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="P18">
-        <v>1.84</v>
+        <v>5.2</v>
       </c>
       <c r="Q18">
-        <v>4.24</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S18">
         <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
+        <v>1.15</v>
+      </c>
+      <c r="Z18">
+        <v>4.3</v>
+      </c>
+      <c r="AA18">
+        <v>1.57</v>
+      </c>
+      <c r="AB18">
+        <v>2.25</v>
+      </c>
+      <c r="AC18">
+        <v>2.38</v>
+      </c>
+      <c r="AD18">
+        <v>1.46</v>
+      </c>
+      <c r="AE18">
         <v>1.16</v>
       </c>
-      <c r="Z18">
-        <v>4.1</v>
-      </c>
-      <c r="AA18">
-        <v>1.64</v>
-      </c>
-      <c r="AB18">
-        <v>2.12</v>
-      </c>
-      <c r="AC18">
-        <v>2.52</v>
-      </c>
-      <c r="AD18">
-        <v>1.41</v>
-      </c>
-      <c r="AE18">
+      <c r="AF18">
+        <v>1.74</v>
+      </c>
+      <c r="AG18">
+        <v>1.96</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.13</v>
       </c>
-      <c r="AF18">
-        <v>1.57</v>
-      </c>
-      <c r="AG18">
-        <v>2.23</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.21</v>
-      </c>
       <c r="AK18">
-        <v>1.21</v>
+        <v>2.57</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>4.84</v>
+        <v>3.18</v>
       </c>
       <c r="R43">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z43">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="AA43">
+        <v>2.1</v>
+      </c>
+      <c r="AB43">
+        <v>1.72</v>
+      </c>
+      <c r="AC43">
+        <v>3.7</v>
+      </c>
+      <c r="AD43">
+        <v>1.24</v>
+      </c>
+      <c r="AE43">
+        <v>1.04</v>
+      </c>
+      <c r="AF43">
         <v>1.8</v>
       </c>
-      <c r="AB43">
-        <v>2</v>
-      </c>
-      <c r="AC43">
-        <v>2.76</v>
-      </c>
-      <c r="AD43">
-        <v>1.37</v>
-      </c>
-      <c r="AE43">
-        <v>1.13</v>
-      </c>
-      <c r="AF43">
-        <v>1.68</v>
-      </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK43">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>4.27</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="Q44">
-        <v>3.18</v>
+        <v>4.84</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB44">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC44">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD44">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,52 +13349,52 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="O80">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P80">
-        <v>3.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q80">
-        <v>2.42</v>
+        <v>4.04</v>
       </c>
       <c r="R80">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U80">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V80">
         <v>1.4</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB80">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC80">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="AD80">
         <v>1.33</v>
@@ -13403,10 +13403,10 @@
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.24</v>
       </c>
       <c r="AK80">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="O81">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q81">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="S81">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T81">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="U81">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="V81">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W81">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z81">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AA81">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AB81">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AC81">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD81">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG81">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,52 +13675,52 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.01</v>
+        <v>3.95</v>
       </c>
       <c r="Q82">
-        <v>4.04</v>
+        <v>2.42</v>
       </c>
       <c r="R82">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U82">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V82">
         <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA82">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB82">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC82">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="AD82">
         <v>1.33</v>
@@ -13729,10 +13729,10 @@
         <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q83">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="R83">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="S83">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T83">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="U83">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AA83">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB83">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC83">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AD83">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q92">
         <v>1.64</v>
@@ -15335,7 +15335,7 @@
         <v>1.14</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
         <v>1.11</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.43</v>
+        <v>2.75</v>
       </c>
       <c r="O111">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P111">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="Q111">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="R111">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="S111">
         <v>1.22</v>
       </c>
       <c r="T111">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="U111">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V111">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W111">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
         <v>1.1</v>
       </c>
       <c r="Z111">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA111">
+        <v>1.44</v>
+      </c>
+      <c r="AB111">
+        <v>2.55</v>
+      </c>
+      <c r="AC111">
+        <v>2.21</v>
+      </c>
+      <c r="AD111">
+        <v>1.66</v>
+      </c>
+      <c r="AE111">
+        <v>1.25</v>
+      </c>
+      <c r="AF111">
         <v>1.41</v>
       </c>
-      <c r="AB111">
-        <v>2.88</v>
-      </c>
-      <c r="AC111">
-        <v>2.11</v>
-      </c>
-      <c r="AD111">
-        <v>1.76</v>
-      </c>
-      <c r="AE111">
-        <v>1.29</v>
-      </c>
-      <c r="AF111">
-        <v>1.56</v>
-      </c>
       <c r="AG111">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O112">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P112">
-        <v>2.23</v>
+        <v>3.65</v>
       </c>
       <c r="Q112">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="R112">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="S112">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T112">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U112">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="V112">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z112">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA112">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AB112">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AC112">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="AD112">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AE112">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF112">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AG112">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK112">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="O113">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="P113">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="Q113">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="R113">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="S113">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="U113">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="V113">
+        <v>1.67</v>
+      </c>
+      <c r="W113">
+        <v>1.2</v>
+      </c>
+      <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.1</v>
+      </c>
+      <c r="Z113">
+        <v>6.5</v>
+      </c>
+      <c r="AA113">
+        <v>1.41</v>
+      </c>
+      <c r="AB113">
+        <v>2.88</v>
+      </c>
+      <c r="AC113">
+        <v>2.11</v>
+      </c>
+      <c r="AD113">
+        <v>1.76</v>
+      </c>
+      <c r="AE113">
+        <v>1.29</v>
+      </c>
+      <c r="AF113">
         <v>1.56</v>
       </c>
-      <c r="W113">
-        <v>1.11</v>
-      </c>
-      <c r="X113">
-        <v>1.01</v>
-      </c>
-      <c r="Y113">
-        <v>1.16</v>
-      </c>
-      <c r="Z113">
-        <v>4.8</v>
-      </c>
-      <c r="AA113">
-        <v>1.61</v>
-      </c>
-      <c r="AB113">
-        <v>2.36</v>
-      </c>
-      <c r="AC113">
-        <v>2.62</v>
-      </c>
-      <c r="AD113">
-        <v>1.46</v>
-      </c>
-      <c r="AE113">
-        <v>1.18</v>
-      </c>
-      <c r="AF113">
-        <v>1.6</v>
-      </c>
       <c r="AG113">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK113">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="O120">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="Q120">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="R120">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="S120">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="T120">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="U120">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="V120">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="W120">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z120">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA120">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AB120">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="AC120">
-        <v>1.83</v>
+        <v>2.93</v>
       </c>
       <c r="AD120">
-        <v>1.84</v>
+        <v>1.37</v>
       </c>
       <c r="AE120">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AF120">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG120">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AK120">
-        <v>4.06</v>
+        <v>1.91</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="P123">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="Q123">
-        <v>2.34</v>
+        <v>1.5</v>
       </c>
       <c r="R123">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="S123">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T123">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="U123">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="V123">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="W123">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X123">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z123">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA123">
+        <v>1.3</v>
+      </c>
+      <c r="AB123">
+        <v>2.91</v>
+      </c>
+      <c r="AC123">
         <v>1.83</v>
       </c>
-      <c r="AB123">
-        <v>2</v>
-      </c>
-      <c r="AC123">
-        <v>2.93</v>
-      </c>
       <c r="AD123">
+        <v>1.84</v>
+      </c>
+      <c r="AE123">
         <v>1.37</v>
       </c>
-      <c r="AE123">
-        <v>1.13</v>
-      </c>
       <c r="AF123">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG123">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AK123">
-        <v>1.91</v>
+        <v>4.06</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,19 +21010,19 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O127">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P127">
         <v>4.75</v>
       </c>
       <c r="Q127">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R127">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
         <v>1.31</v>
@@ -21031,59 +21031,59 @@
         <v>3.02</v>
       </c>
       <c r="U127">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V127">
         <v>1.44</v>
       </c>
       <c r="W127">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y127">
+        <v>1.2</v>
+      </c>
+      <c r="Z127">
+        <v>3.7</v>
+      </c>
+      <c r="AA127">
+        <v>1.75</v>
+      </c>
+      <c r="AB127">
+        <v>2</v>
+      </c>
+      <c r="AC127">
+        <v>2.83</v>
+      </c>
+      <c r="AD127">
+        <v>1.4</v>
+      </c>
+      <c r="AE127">
+        <v>1.14</v>
+      </c>
+      <c r="AF127">
+        <v>1.75</v>
+      </c>
+      <c r="AG127">
+        <v>1.95</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
         <v>1.18</v>
       </c>
-      <c r="Z127">
-        <v>3.85</v>
-      </c>
-      <c r="AA127">
-        <v>1.7</v>
-      </c>
-      <c r="AB127">
-        <v>2.03</v>
-      </c>
-      <c r="AC127">
-        <v>2.81</v>
-      </c>
-      <c r="AD127">
-        <v>1.37</v>
-      </c>
-      <c r="AE127">
-        <v>1.15</v>
-      </c>
-      <c r="AF127">
-        <v>1.68</v>
-      </c>
-      <c r="AG127">
-        <v>2.04</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>1.19</v>
-      </c>
       <c r="AK127">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O128">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P128">
         <v>4.75</v>
       </c>
       <c r="Q128">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R128">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S128">
         <v>1.31</v>
@@ -21194,43 +21194,43 @@
         <v>3.02</v>
       </c>
       <c r="U128">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V128">
         <v>1.44</v>
       </c>
       <c r="W128">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X128">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z128">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AA128">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB128">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC128">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD128">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE128">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF128">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK128">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="O131">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P131">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="Q131">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="R131">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S131">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T131">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U131">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="V131">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X131">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z131">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="AA131">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="AB131">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC131">
-        <v>3.42</v>
+        <v>4.16</v>
       </c>
       <c r="AD131">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE131">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF131">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG131">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O132">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P132">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Q132">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="R132">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S132">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T132">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U132">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="V132">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W132">
         <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y132">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z132">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="AA132">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB132">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC132">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD132">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE132">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF132">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG132">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="O133">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P133">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="Q133">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="R133">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="S133">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T133">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U133">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="V133">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W133">
+        <v>1.05</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
+        <v>1.3</v>
+      </c>
+      <c r="Z133">
+        <v>2.97</v>
+      </c>
+      <c r="AA133">
+        <v>1.98</v>
+      </c>
+      <c r="AB133">
+        <v>1.71</v>
+      </c>
+      <c r="AC133">
+        <v>3.8</v>
+      </c>
+      <c r="AD133">
+        <v>1.21</v>
+      </c>
+      <c r="AE133">
         <v>1.03</v>
       </c>
-      <c r="X133">
-        <v>1.03</v>
-      </c>
-      <c r="Y133">
-        <v>1.36</v>
-      </c>
-      <c r="Z133">
-        <v>2.7</v>
-      </c>
-      <c r="AA133">
-        <v>2.21</v>
-      </c>
-      <c r="AB133">
-        <v>1.61</v>
-      </c>
-      <c r="AC133">
-        <v>4.16</v>
-      </c>
-      <c r="AD133">
-        <v>1.17</v>
-      </c>
-      <c r="AE133">
-        <v>1.02</v>
-      </c>
       <c r="AF133">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK133">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="O134">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P134">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="O135">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="P135">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q135">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="R135">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S135">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="T135">
-        <v>3.08</v>
+        <v>2.27</v>
       </c>
       <c r="U135">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="V135">
+        <v>1.24</v>
+      </c>
+      <c r="W135">
+        <v>1.01</v>
+      </c>
+      <c r="X135">
+        <v>1.1</v>
+      </c>
+      <c r="Y135">
+        <v>1.58</v>
+      </c>
+      <c r="Z135">
+        <v>2.41</v>
+      </c>
+      <c r="AA135">
+        <v>2.64</v>
+      </c>
+      <c r="AB135">
         <v>1.42</v>
       </c>
-      <c r="W135">
-        <v>1.05</v>
-      </c>
-      <c r="X135">
-        <v>1.01</v>
-      </c>
-      <c r="Y135">
-        <v>1.26</v>
-      </c>
-      <c r="Z135">
-        <v>3.64</v>
-      </c>
-      <c r="AA135">
-        <v>1.87</v>
-      </c>
-      <c r="AB135">
-        <v>1.92</v>
-      </c>
       <c r="AC135">
-        <v>3.08</v>
+        <v>5.2</v>
       </c>
       <c r="AD135">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AE135">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF135">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AG135">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK135">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="O143">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P143">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q143">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R143">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S143">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T143">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U143">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V143">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W143">
+        <v>1.06</v>
+      </c>
+      <c r="X143">
+        <v>1.03</v>
+      </c>
+      <c r="Y143">
+        <v>1.23</v>
+      </c>
+      <c r="Z143">
+        <v>3.65</v>
+      </c>
+      <c r="AA143">
+        <v>1.83</v>
+      </c>
+      <c r="AB143">
+        <v>1.95</v>
+      </c>
+      <c r="AC143">
+        <v>3.05</v>
+      </c>
+      <c r="AD143">
+        <v>1.3</v>
+      </c>
+      <c r="AE143">
         <v>1.08</v>
       </c>
-      <c r="X143">
-        <v>1</v>
-      </c>
-      <c r="Y143">
-        <v>1.2</v>
-      </c>
-      <c r="Z143">
-        <v>4.1</v>
-      </c>
-      <c r="AA143">
-        <v>1.73</v>
-      </c>
-      <c r="AB143">
-        <v>2.08</v>
-      </c>
-      <c r="AC143">
-        <v>2.8</v>
-      </c>
-      <c r="AD143">
-        <v>1.38</v>
-      </c>
-      <c r="AE143">
-        <v>1.12</v>
-      </c>
       <c r="AF143">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK143">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P144">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q144">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R144">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T144">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U144">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W144">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y144">
+        <v>1.2</v>
+      </c>
+      <c r="Z144">
+        <v>4.1</v>
+      </c>
+      <c r="AA144">
+        <v>1.73</v>
+      </c>
+      <c r="AB144">
+        <v>2.08</v>
+      </c>
+      <c r="AC144">
+        <v>2.8</v>
+      </c>
+      <c r="AD144">
+        <v>1.38</v>
+      </c>
+      <c r="AE144">
+        <v>1.12</v>
+      </c>
+      <c r="AF144">
+        <v>1.65</v>
+      </c>
+      <c r="AG144">
+        <v>2.04</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.23</v>
       </c>
-      <c r="Z144">
-        <v>3.65</v>
-      </c>
-      <c r="AA144">
-        <v>1.83</v>
-      </c>
-      <c r="AB144">
-        <v>1.95</v>
-      </c>
-      <c r="AC144">
-        <v>3.05</v>
-      </c>
-      <c r="AD144">
-        <v>1.3</v>
-      </c>
-      <c r="AE144">
-        <v>1.08</v>
-      </c>
-      <c r="AF144">
-        <v>1.62</v>
-      </c>
-      <c r="AG144">
-        <v>2.09</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.27</v>
-      </c>
       <c r="AK144">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="O167">
+        <v>3.6</v>
+      </c>
+      <c r="P167">
+        <v>4</v>
+      </c>
+      <c r="Q167">
+        <v>2.4</v>
+      </c>
+      <c r="R167">
+        <v>2.18</v>
+      </c>
+      <c r="S167">
+        <v>1.3</v>
+      </c>
+      <c r="T167">
+        <v>3.1</v>
+      </c>
+      <c r="U167">
+        <v>2.65</v>
+      </c>
+      <c r="V167">
+        <v>1.42</v>
+      </c>
+      <c r="W167">
+        <v>1.07</v>
+      </c>
+      <c r="X167">
+        <v>1.02</v>
+      </c>
+      <c r="Y167">
+        <v>1.27</v>
+      </c>
+      <c r="Z167">
         <v>3.3</v>
       </c>
-      <c r="P167">
-        <v>2.78</v>
-      </c>
-      <c r="Q167">
-        <v>3.06</v>
-      </c>
-      <c r="R167">
-        <v>2.06</v>
-      </c>
-      <c r="S167">
-        <v>1.36</v>
-      </c>
-      <c r="T167">
-        <v>2.88</v>
-      </c>
-      <c r="U167">
-        <v>2.88</v>
-      </c>
-      <c r="V167">
-        <v>1.36</v>
-      </c>
-      <c r="W167">
-        <v>1.08</v>
-      </c>
-      <c r="X167">
-        <v>1.06</v>
-      </c>
-      <c r="Y167">
-        <v>1.33</v>
-      </c>
-      <c r="Z167">
-        <v>2.96</v>
-      </c>
       <c r="AA167">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB167">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC167">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD167">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE167">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF167">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK167">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="O168">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P168">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="Q168">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="R168">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S168">
+        <v>1.36</v>
+      </c>
+      <c r="T168">
+        <v>2.88</v>
+      </c>
+      <c r="U168">
+        <v>2.88</v>
+      </c>
+      <c r="V168">
+        <v>1.36</v>
+      </c>
+      <c r="W168">
+        <v>1.08</v>
+      </c>
+      <c r="X168">
+        <v>1.06</v>
+      </c>
+      <c r="Y168">
+        <v>1.33</v>
+      </c>
+      <c r="Z168">
+        <v>2.96</v>
+      </c>
+      <c r="AA168">
+        <v>2</v>
+      </c>
+      <c r="AB168">
+        <v>1.75</v>
+      </c>
+      <c r="AC168">
+        <v>3.45</v>
+      </c>
+      <c r="AD168">
         <v>1.3</v>
       </c>
-      <c r="T168">
-        <v>3.1</v>
-      </c>
-      <c r="U168">
-        <v>2.65</v>
-      </c>
-      <c r="V168">
-        <v>1.42</v>
-      </c>
-      <c r="W168">
-        <v>1.07</v>
-      </c>
-      <c r="X168">
-        <v>1.02</v>
-      </c>
-      <c r="Y168">
-        <v>1.27</v>
-      </c>
-      <c r="Z168">
-        <v>3.3</v>
-      </c>
-      <c r="AA168">
-        <v>1.78</v>
-      </c>
-      <c r="AB168">
-        <v>1.89</v>
-      </c>
-      <c r="AC168">
-        <v>3.1</v>
-      </c>
-      <c r="AD168">
-        <v>1.35</v>
-      </c>
       <c r="AE168">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF168">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG168">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK168">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -30147,34 +30147,34 @@
         <v>2.3</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V183">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X183">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y183">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA183">
         <v>1.95</v>
@@ -30183,19 +30183,19 @@
         <v>1.85</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK183">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30799,55 +30799,55 @@
         <v>2.5</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -38786,55 +38786,55 @@
         <v>6.3</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R236">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S236">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T236">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U236">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V236">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y236">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z236">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC236">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD236">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE236">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF236">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG236">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK236">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -40253,34 +40253,34 @@
         <v>0</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA245">
         <v>1.75</v>
@@ -40289,19 +40289,19 @@
         <v>2.05</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -42372,10 +42372,10 @@
         <v>0</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S258">
         <v>0</v>
@@ -42384,10 +42384,10 @@
         <v>0</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W258">
         <v>0</v>
@@ -42396,31 +42396,31 @@
         <v>0</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE258">
         <v>0</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42535,16 +42535,16 @@
         <v>0</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U259">
         <v>0</v>
@@ -42559,31 +42559,31 @@
         <v>0</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE259">
         <v>0</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G264">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G265">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44980,55 +44980,55 @@
         <v>5.41</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X276">
         <v>0</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -46284,55 +46284,55 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48394,64 +48394,64 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q295">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R295">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S295">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T295">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U295">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V295">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W295">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X295">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC295">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD295">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE295">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF295">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG295">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK295">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50848,55 +50848,55 @@
         <v>0</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P311">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51041,10 +51041,10 @@
         <v>0</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC311">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G314">
@@ -51817,64 +51817,64 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="R316">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S316">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T316">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U316">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V316">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W316">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X316">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y316">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z316">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC316">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD316">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE316">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF316">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG316">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK316">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51980,64 +51980,64 @@
         </is>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O317">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P317">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q317">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R317">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S317">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T317">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U317">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V317">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W317">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X317">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z317">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA317">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB317">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC317">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD317">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE317">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF317">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG317">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK317">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52152,55 +52152,55 @@
         <v>0</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T318">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W318">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X318">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O319">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P319">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q319">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R319">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S319">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T319">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U319">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V319">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W319">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X319">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y319">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z319">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA319">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB319">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC319">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD319">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE319">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF319">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG319">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK319">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52484,10 +52484,10 @@
         <v>2.85</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U320">
         <v>2.1</v>
@@ -52496,10 +52496,10 @@
         <v>1.62</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
         <v>1.12</v>
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q324">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R324">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S324">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T324">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U324">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V324">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W324">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X324">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y324">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z324">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA324">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB324">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC324">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD324">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE324">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF324">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG324">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK324">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL329">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.27</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>1.79</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
-        <v>4.84</v>
+        <v>2.81</v>
       </c>
       <c r="R42">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="U42">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z42">
-        <v>3.54</v>
+        <v>3</v>
       </c>
       <c r="AA42">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC42">
-        <v>2.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.15</v>
+        <v>4.27</v>
       </c>
       <c r="O43">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q43">
-        <v>2.81</v>
+        <v>4.84</v>
       </c>
       <c r="R43">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="S43">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U43">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="V43">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AA43">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AB43">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>3.78</v>
+        <v>2.76</v>
       </c>
       <c r="AD43">
+        <v>1.37</v>
+      </c>
+      <c r="AE43">
+        <v>1.13</v>
+      </c>
+      <c r="AF43">
+        <v>1.68</v>
+      </c>
+      <c r="AG43">
+        <v>2.05</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.26</v>
+      </c>
+      <c r="AK43">
         <v>1.19</v>
-      </c>
-      <c r="AE43">
-        <v>1.03</v>
-      </c>
-      <c r="AF43">
-        <v>1.87</v>
-      </c>
-      <c r="AG43">
-        <v>1.83</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.36</v>
-      </c>
-      <c r="AK43">
-        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q51">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U51">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>4.45</v>
+        <v>5.85</v>
       </c>
       <c r="AA51">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AB51">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AC51">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD51">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AE51">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF51">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK51">
-        <v>2.67</v>
+        <v>1.47</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="R52">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
+        <v>3.6</v>
+      </c>
+      <c r="U52">
+        <v>2.15</v>
+      </c>
+      <c r="V52">
+        <v>1.62</v>
+      </c>
+      <c r="W52">
+        <v>1.15</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.11</v>
+      </c>
+      <c r="Z52">
+        <v>4.45</v>
+      </c>
+      <c r="AA52">
+        <v>1.59</v>
+      </c>
+      <c r="AB52">
+        <v>2.38</v>
+      </c>
+      <c r="AC52">
+        <v>2.4</v>
+      </c>
+      <c r="AD52">
+        <v>1.54</v>
+      </c>
+      <c r="AE52">
         <v>1.2</v>
       </c>
-      <c r="T52">
-        <v>4.2</v>
-      </c>
-      <c r="U52">
-        <v>1.95</v>
-      </c>
-      <c r="V52">
-        <v>1.75</v>
-      </c>
-      <c r="W52">
-        <v>1.2</v>
-      </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
-        <v>1.07</v>
-      </c>
-      <c r="Z52">
-        <v>5.85</v>
-      </c>
-      <c r="AA52">
-        <v>1.37</v>
-      </c>
-      <c r="AB52">
-        <v>2.66</v>
-      </c>
-      <c r="AC52">
-        <v>2.05</v>
-      </c>
-      <c r="AD52">
-        <v>1.77</v>
-      </c>
-      <c r="AE52">
-        <v>1.26</v>
-      </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG52">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>2.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="R81">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U81">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="V81">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA81">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB81">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AC81">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="AD81">
+        <v>1.33</v>
+      </c>
+      <c r="AE81">
+        <v>1.08</v>
+      </c>
+      <c r="AF81">
+        <v>1.73</v>
+      </c>
+      <c r="AG81">
+        <v>1.97</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.24</v>
       </c>
-      <c r="AE81">
-        <v>1.05</v>
-      </c>
-      <c r="AF81">
-        <v>1.75</v>
-      </c>
-      <c r="AG81">
-        <v>1.95</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.25</v>
-      </c>
       <c r="AK81">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="O83">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T83">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U83">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y83">
+        <v>1.27</v>
+      </c>
+      <c r="Z83">
+        <v>3.14</v>
+      </c>
+      <c r="AA83">
+        <v>1.95</v>
+      </c>
+      <c r="AB83">
+        <v>1.76</v>
+      </c>
+      <c r="AC83">
+        <v>3.34</v>
+      </c>
+      <c r="AD83">
+        <v>1.24</v>
+      </c>
+      <c r="AE83">
+        <v>1.05</v>
+      </c>
+      <c r="AF83">
+        <v>1.75</v>
+      </c>
+      <c r="AG83">
+        <v>1.95</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.25</v>
       </c>
-      <c r="Z83">
-        <v>3.28</v>
-      </c>
-      <c r="AA83">
-        <v>1.89</v>
-      </c>
-      <c r="AB83">
-        <v>1.89</v>
-      </c>
-      <c r="AC83">
-        <v>3.18</v>
-      </c>
-      <c r="AD83">
-        <v>1.33</v>
-      </c>
-      <c r="AE83">
-        <v>1.08</v>
-      </c>
-      <c r="AF83">
-        <v>1.73</v>
-      </c>
-      <c r="AG83">
-        <v>1.97</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.24</v>
-      </c>
       <c r="AK83">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,31 +18239,31 @@
         </is>
       </c>
       <c r="N110">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="O110">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P110">
-        <v>2.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q110">
-        <v>3.65</v>
+        <v>2.32</v>
       </c>
       <c r="R110">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="S110">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T110">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="U110">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V110">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W110">
         <v>1.11</v>
@@ -18272,32 +18272,32 @@
         <v>1.01</v>
       </c>
       <c r="Y110">
+        <v>1.16</v>
+      </c>
+      <c r="Z110">
+        <v>4.8</v>
+      </c>
+      <c r="AA110">
+        <v>1.61</v>
+      </c>
+      <c r="AB110">
+        <v>2.36</v>
+      </c>
+      <c r="AC110">
+        <v>2.62</v>
+      </c>
+      <c r="AD110">
+        <v>1.46</v>
+      </c>
+      <c r="AE110">
         <v>1.18</v>
       </c>
-      <c r="Z110">
-        <v>4.25</v>
-      </c>
-      <c r="AA110">
-        <v>1.73</v>
-      </c>
-      <c r="AB110">
+      <c r="AF110">
+        <v>1.6</v>
+      </c>
+      <c r="AG110">
         <v>2.28</v>
       </c>
-      <c r="AC110">
-        <v>2.55</v>
-      </c>
-      <c r="AD110">
-        <v>1.44</v>
-      </c>
-      <c r="AE110">
-        <v>1.13</v>
-      </c>
-      <c r="AF110">
-        <v>1.55</v>
-      </c>
-      <c r="AG110">
-        <v>2.3</v>
-      </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="AK110">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P111">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q111">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="R111">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="S111">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T111">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="U111">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="V111">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W111">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z111">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA111">
+        <v>1.73</v>
+      </c>
+      <c r="AB111">
+        <v>2.28</v>
+      </c>
+      <c r="AC111">
+        <v>2.55</v>
+      </c>
+      <c r="AD111">
         <v>1.44</v>
       </c>
-      <c r="AB111">
-        <v>2.55</v>
-      </c>
-      <c r="AC111">
-        <v>2.21</v>
-      </c>
-      <c r="AD111">
-        <v>1.66</v>
-      </c>
       <c r="AE111">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF111">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG111">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AK111">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O112">
+        <v>3.8</v>
+      </c>
+      <c r="P112">
+        <v>2.23</v>
+      </c>
+      <c r="Q112">
+        <v>3</v>
+      </c>
+      <c r="R112">
+        <v>2.48</v>
+      </c>
+      <c r="S112">
+        <v>1.22</v>
+      </c>
+      <c r="T112">
         <v>3.75</v>
       </c>
-      <c r="P112">
-        <v>3.65</v>
-      </c>
-      <c r="Q112">
-        <v>2.32</v>
-      </c>
-      <c r="R112">
-        <v>2.43</v>
-      </c>
-      <c r="S112">
-        <v>1.31</v>
-      </c>
-      <c r="T112">
-        <v>3.42</v>
-      </c>
       <c r="U112">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="V112">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="W112">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z112">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA112">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB112">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AC112">
-        <v>2.62</v>
+        <v>2.21</v>
       </c>
       <c r="AD112">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AE112">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AG112">
-        <v>2.28</v>
+        <v>2.73</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="O121">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="P121">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q121">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="R121">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="S121">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T121">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="U121">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="V121">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="W121">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z121">
-        <v>6.5</v>
+        <v>3.97</v>
       </c>
       <c r="AA121">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AB121">
-        <v>2.91</v>
+        <v>1.99</v>
       </c>
       <c r="AC121">
-        <v>1.83</v>
+        <v>2.84</v>
       </c>
       <c r="AD121">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AE121">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
         <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AK121">
-        <v>4.06</v>
+        <v>2.3</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="O122">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="P122">
-        <v>5.9</v>
+        <v>12.5</v>
       </c>
       <c r="Q122">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="R122">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="S122">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T122">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="U122">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="V122">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X122">
         <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Z122">
-        <v>3.97</v>
+        <v>6.5</v>
       </c>
       <c r="AA122">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AB122">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="AC122">
-        <v>2.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD122">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="AE122">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AF122">
         <v>1.83</v>
       </c>
       <c r="AG122">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AK122">
-        <v>2.3</v>
+        <v>4.06</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O127">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="P127">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q127">
-        <v>4.67</v>
+        <v>3.81</v>
       </c>
       <c r="R127">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S127">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T127">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U127">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V127">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W127">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y127">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z127">
-        <v>3.72</v>
+        <v>3.94</v>
       </c>
       <c r="AA127">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB127">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC127">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AD127">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE127">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF127">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK127">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O128">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="P128">
-        <v>2.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q128">
-        <v>3.81</v>
+        <v>4.67</v>
       </c>
       <c r="R128">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S128">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T128">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="U128">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V128">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W128">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X128">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
+        <v>1.25</v>
+      </c>
+      <c r="Z128">
+        <v>3.72</v>
+      </c>
+      <c r="AA128">
+        <v>1.8</v>
+      </c>
+      <c r="AB128">
+        <v>2</v>
+      </c>
+      <c r="AC128">
+        <v>2.95</v>
+      </c>
+      <c r="AD128">
+        <v>1.37</v>
+      </c>
+      <c r="AE128">
+        <v>1.08</v>
+      </c>
+      <c r="AF128">
+        <v>1.69</v>
+      </c>
+      <c r="AG128">
+        <v>2.05</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>1.2</v>
+      </c>
+      <c r="AK128">
         <v>1.17</v>
-      </c>
-      <c r="Z128">
-        <v>3.94</v>
-      </c>
-      <c r="AA128">
-        <v>1.75</v>
-      </c>
-      <c r="AB128">
-        <v>2.04</v>
-      </c>
-      <c r="AC128">
-        <v>2.84</v>
-      </c>
-      <c r="AD128">
-        <v>1.4</v>
-      </c>
-      <c r="AE128">
-        <v>1.15</v>
-      </c>
-      <c r="AF128">
-        <v>1.57</v>
-      </c>
-      <c r="AG128">
-        <v>2.23</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.24</v>
-      </c>
-      <c r="AK128">
-        <v>1.28</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="O132">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P132">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="Q132">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="R132">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S132">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T132">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U132">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="V132">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W132">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
+        <v>1.36</v>
+      </c>
+      <c r="Z132">
+        <v>2.7</v>
+      </c>
+      <c r="AA132">
+        <v>2.21</v>
+      </c>
+      <c r="AB132">
+        <v>1.61</v>
+      </c>
+      <c r="AC132">
+        <v>4.16</v>
+      </c>
+      <c r="AD132">
+        <v>1.17</v>
+      </c>
+      <c r="AE132">
+        <v>1.02</v>
+      </c>
+      <c r="AF132">
+        <v>1.87</v>
+      </c>
+      <c r="AG132">
+        <v>1.82</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
         <v>1.3</v>
       </c>
-      <c r="Z132">
-        <v>2.97</v>
-      </c>
-      <c r="AA132">
-        <v>1.98</v>
-      </c>
-      <c r="AB132">
-        <v>1.71</v>
-      </c>
-      <c r="AC132">
-        <v>3.8</v>
-      </c>
-      <c r="AD132">
-        <v>1.21</v>
-      </c>
-      <c r="AE132">
-        <v>1.03</v>
-      </c>
-      <c r="AF132">
-        <v>1.78</v>
-      </c>
-      <c r="AG132">
-        <v>1.91</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.26</v>
-      </c>
       <c r="AK132">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="O133">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P133">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="Q133">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="R133">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="S133">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T133">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U133">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="V133">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W133">
+        <v>1.05</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
+        <v>1.3</v>
+      </c>
+      <c r="Z133">
+        <v>2.97</v>
+      </c>
+      <c r="AA133">
+        <v>1.98</v>
+      </c>
+      <c r="AB133">
+        <v>1.71</v>
+      </c>
+      <c r="AC133">
+        <v>3.8</v>
+      </c>
+      <c r="AD133">
+        <v>1.21</v>
+      </c>
+      <c r="AE133">
         <v>1.03</v>
       </c>
-      <c r="X133">
-        <v>1.03</v>
-      </c>
-      <c r="Y133">
-        <v>1.36</v>
-      </c>
-      <c r="Z133">
-        <v>2.7</v>
-      </c>
-      <c r="AA133">
-        <v>2.21</v>
-      </c>
-      <c r="AB133">
-        <v>1.61</v>
-      </c>
-      <c r="AC133">
-        <v>4.16</v>
-      </c>
-      <c r="AD133">
-        <v>1.17</v>
-      </c>
-      <c r="AE133">
-        <v>1.02</v>
-      </c>
       <c r="AF133">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK133">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O143">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P143">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q143">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="R143">
         <v>2.15</v>
       </c>
       <c r="S143">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T143">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U143">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V143">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W143">
         <v>1.06</v>
       </c>
       <c r="X143">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z143">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA143">
+        <v>1.93</v>
+      </c>
+      <c r="AB143">
         <v>1.83</v>
       </c>
-      <c r="AB143">
-        <v>1.95</v>
-      </c>
       <c r="AC143">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD143">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE143">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF143">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG143">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="O144">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q144">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R144">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S144">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T144">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U144">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W144">
+        <v>1.06</v>
+      </c>
+      <c r="X144">
+        <v>1.03</v>
+      </c>
+      <c r="Y144">
+        <v>1.23</v>
+      </c>
+      <c r="Z144">
+        <v>3.65</v>
+      </c>
+      <c r="AA144">
+        <v>1.83</v>
+      </c>
+      <c r="AB144">
+        <v>1.95</v>
+      </c>
+      <c r="AC144">
+        <v>3.05</v>
+      </c>
+      <c r="AD144">
+        <v>1.3</v>
+      </c>
+      <c r="AE144">
         <v>1.08</v>
       </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="Y144">
-        <v>1.2</v>
-      </c>
-      <c r="Z144">
-        <v>4.1</v>
-      </c>
-      <c r="AA144">
-        <v>1.73</v>
-      </c>
-      <c r="AB144">
-        <v>2.08</v>
-      </c>
-      <c r="AC144">
-        <v>2.8</v>
-      </c>
-      <c r="AD144">
-        <v>1.38</v>
-      </c>
-      <c r="AE144">
-        <v>1.12</v>
-      </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK144">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="O145">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P145">
+        <v>4.5</v>
+      </c>
+      <c r="Q145">
+        <v>2.24</v>
+      </c>
+      <c r="R145">
+        <v>2.26</v>
+      </c>
+      <c r="S145">
+        <v>1.29</v>
+      </c>
+      <c r="T145">
         <v>3.3</v>
       </c>
-      <c r="Q145">
-        <v>2.63</v>
-      </c>
-      <c r="R145">
-        <v>2.15</v>
-      </c>
-      <c r="S145">
-        <v>1.36</v>
-      </c>
-      <c r="T145">
-        <v>2.85</v>
-      </c>
       <c r="U145">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="V145">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z145">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AA145">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB145">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC145">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD145">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF145">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG145">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK145">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="O153">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P153">
-        <v>3.63</v>
+        <v>2.92</v>
       </c>
       <c r="Q153">
-        <v>2.64</v>
+        <v>2.85</v>
       </c>
       <c r="R153">
         <v>2.15</v>
       </c>
       <c r="S153">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T153">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="U153">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V153">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W153">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X153">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z153">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AA153">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB153">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC153">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AD153">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE153">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF153">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AG153">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="O154">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P154">
-        <v>2.92</v>
+        <v>3.63</v>
       </c>
       <c r="Q154">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="R154">
         <v>2.15</v>
       </c>
       <c r="S154">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T154">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U154">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="V154">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W154">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y154">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z154">
+        <v>3.25</v>
+      </c>
+      <c r="AA154">
+        <v>1.98</v>
+      </c>
+      <c r="AB154">
+        <v>1.75</v>
+      </c>
+      <c r="AC154">
         <v>3.44</v>
       </c>
-      <c r="AA154">
-        <v>1.89</v>
-      </c>
-      <c r="AB154">
-        <v>1.85</v>
-      </c>
-      <c r="AC154">
-        <v>3.12</v>
-      </c>
       <c r="AD154">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AG154">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK154">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="O158">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P158">
-        <v>4.33</v>
+        <v>5.67</v>
       </c>
       <c r="Q158">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="R158">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S158">
         <v>1.3</v>
       </c>
       <c r="T158">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U158">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V158">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W158">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X158">
         <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA158">
         <v>1.66</v>
       </c>
       <c r="AB158">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC158">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD158">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AE158">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF158">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG158">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="O159">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P159">
-        <v>5.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q159">
-        <v>2.04</v>
+        <v>2.64</v>
       </c>
       <c r="R159">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S159">
         <v>1.3</v>
       </c>
       <c r="T159">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U159">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V159">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W159">
         <v>1.08</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z159">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA159">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB159">
         <v>2.35</v>
       </c>
       <c r="AC159">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD159">
+        <v>1.52</v>
+      </c>
+      <c r="AE159">
+        <v>1.13</v>
+      </c>
+      <c r="AF159">
         <v>1.55</v>
       </c>
-      <c r="AE159">
-        <v>1.17</v>
-      </c>
-      <c r="AF159">
-        <v>1.71</v>
-      </c>
       <c r="AG159">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK159">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="O160">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P160">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q160">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="R160">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S160">
         <v>1.3</v>
       </c>
       <c r="T160">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U160">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V160">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W160">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X160">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z160">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA160">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB160">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC160">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="AD160">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AE160">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF160">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG160">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK160">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="O164">
+        <v>3.6</v>
+      </c>
+      <c r="P164">
+        <v>4</v>
+      </c>
+      <c r="Q164">
+        <v>2.4</v>
+      </c>
+      <c r="R164">
+        <v>2.18</v>
+      </c>
+      <c r="S164">
+        <v>1.3</v>
+      </c>
+      <c r="T164">
+        <v>3.1</v>
+      </c>
+      <c r="U164">
+        <v>2.65</v>
+      </c>
+      <c r="V164">
+        <v>1.42</v>
+      </c>
+      <c r="W164">
+        <v>1.07</v>
+      </c>
+      <c r="X164">
+        <v>1.02</v>
+      </c>
+      <c r="Y164">
+        <v>1.27</v>
+      </c>
+      <c r="Z164">
         <v>3.3</v>
       </c>
-      <c r="P164">
-        <v>2.78</v>
-      </c>
-      <c r="Q164">
-        <v>3.06</v>
-      </c>
-      <c r="R164">
-        <v>2.06</v>
-      </c>
-      <c r="S164">
-        <v>1.36</v>
-      </c>
-      <c r="T164">
-        <v>2.88</v>
-      </c>
-      <c r="U164">
-        <v>2.88</v>
-      </c>
-      <c r="V164">
-        <v>1.36</v>
-      </c>
-      <c r="W164">
-        <v>1.08</v>
-      </c>
-      <c r="X164">
-        <v>1.06</v>
-      </c>
-      <c r="Y164">
-        <v>1.33</v>
-      </c>
-      <c r="Z164">
-        <v>2.96</v>
-      </c>
       <c r="AA164">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AB164">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AC164">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD164">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE164">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF164">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG164">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK164">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O165">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P165">
-        <v>4</v>
+        <v>4.89</v>
       </c>
       <c r="Q165">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R165">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T165">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U165">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V165">
         <v>1.42</v>
       </c>
       <c r="W165">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z165">
         <v>3.3</v>
       </c>
       <c r="AA165">
+        <v>1.85</v>
+      </c>
+      <c r="AB165">
+        <v>1.95</v>
+      </c>
+      <c r="AC165">
+        <v>2.89</v>
+      </c>
+      <c r="AD165">
+        <v>1.32</v>
+      </c>
+      <c r="AE165">
+        <v>1.09</v>
+      </c>
+      <c r="AF165">
         <v>1.78</v>
       </c>
-      <c r="AB165">
-        <v>1.89</v>
-      </c>
-      <c r="AC165">
-        <v>3.1</v>
-      </c>
-      <c r="AD165">
-        <v>1.35</v>
-      </c>
-      <c r="AE165">
-        <v>1.12</v>
-      </c>
-      <c r="AF165">
-        <v>1.7</v>
-      </c>
       <c r="AG165">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK165">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.46</v>
+        <v>1.63</v>
       </c>
       <c r="O166">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P166">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="Q166">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R166">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S166">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T166">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U166">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V166">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W166">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X166">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y166">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z166">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA166">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AB166">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AC166">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AD166">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE166">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF166">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG166">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK166">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="O167">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="P167">
-        <v>4.89</v>
+        <v>3.95</v>
       </c>
       <c r="Q167">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R167">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S167">
+        <v>1.4</v>
+      </c>
+      <c r="T167">
+        <v>2.9</v>
+      </c>
+      <c r="U167">
+        <v>2.81</v>
+      </c>
+      <c r="V167">
         <v>1.38</v>
       </c>
-      <c r="T167">
-        <v>2.81</v>
-      </c>
-      <c r="U167">
-        <v>2.75</v>
-      </c>
-      <c r="V167">
-        <v>1.42</v>
-      </c>
       <c r="W167">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X167">
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z167">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA167">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB167">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC167">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="AD167">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE167">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF167">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG167">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.22</v>
       </c>
       <c r="AK167">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.63</v>
+        <v>2.46</v>
       </c>
       <c r="O168">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="P168">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA168">
+        <v>1.79</v>
+      </c>
+      <c r="AB168">
+        <v>1.94</v>
+      </c>
+      <c r="AC168">
+        <v>2.73</v>
+      </c>
+      <c r="AD168">
+        <v>1.38</v>
+      </c>
+      <c r="AE168">
+        <v>1.11</v>
+      </c>
+      <c r="AF168">
         <v>1.6</v>
       </c>
-      <c r="AB168">
-        <v>2.3</v>
-      </c>
-      <c r="AC168">
-        <v>0</v>
-      </c>
-      <c r="AD168">
-        <v>0</v>
-      </c>
-      <c r="AE168">
-        <v>0</v>
-      </c>
-      <c r="AF168">
-        <v>0</v>
-      </c>
       <c r="AG168">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="O169">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P169">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="Q169">
-        <v>2.5</v>
+        <v>3.06</v>
       </c>
       <c r="R169">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S169">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T169">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U169">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V169">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W169">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X169">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y169">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z169">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="AA169">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB169">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC169">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD169">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE169">
         <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG169">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK169">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G221">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,80 +36658,80 @@
         </is>
       </c>
       <c r="N223">
+        <v>2.3</v>
+      </c>
+      <c r="O223">
+        <v>3.5</v>
+      </c>
+      <c r="P223">
+        <v>2.5</v>
+      </c>
+      <c r="Q223">
+        <v>2.85</v>
+      </c>
+      <c r="R223">
+        <v>2.38</v>
+      </c>
+      <c r="S223">
+        <v>1.21</v>
+      </c>
+      <c r="T223">
+        <v>3.75</v>
+      </c>
+      <c r="U223">
+        <v>2.06</v>
+      </c>
+      <c r="V223">
+        <v>1.65</v>
+      </c>
+      <c r="W223">
+        <v>1.14</v>
+      </c>
+      <c r="X223">
+        <v>1.02</v>
+      </c>
+      <c r="Y223">
+        <v>1.09</v>
+      </c>
+      <c r="Z223">
+        <v>5.3</v>
+      </c>
+      <c r="AA223">
+        <v>1.43</v>
+      </c>
+      <c r="AB223">
+        <v>2.48</v>
+      </c>
+      <c r="AC223">
+        <v>2.21</v>
+      </c>
+      <c r="AD223">
+        <v>1.64</v>
+      </c>
+      <c r="AE223">
+        <v>1.21</v>
+      </c>
+      <c r="AF223">
+        <v>1.4</v>
+      </c>
+      <c r="AG223">
+        <v>2.73</v>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ223">
         <v>1.48</v>
       </c>
-      <c r="O223">
-        <v>4.5</v>
-      </c>
-      <c r="P223">
-        <v>4.8</v>
-      </c>
-      <c r="Q223">
-        <v>1.83</v>
-      </c>
-      <c r="R223">
-        <v>2.75</v>
-      </c>
-      <c r="S223">
-        <v>1.15</v>
-      </c>
-      <c r="T223">
-        <v>4.75</v>
-      </c>
-      <c r="U223">
-        <v>1.81</v>
-      </c>
-      <c r="V223">
-        <v>1.86</v>
-      </c>
-      <c r="W223">
-        <v>1.25</v>
-      </c>
-      <c r="X223">
-        <v>0</v>
-      </c>
-      <c r="Y223">
-        <v>1.05</v>
-      </c>
-      <c r="Z223">
-        <v>8</v>
-      </c>
-      <c r="AA223">
-        <v>1.25</v>
-      </c>
-      <c r="AB223">
-        <v>3.6</v>
-      </c>
-      <c r="AC223">
-        <v>1.68</v>
-      </c>
-      <c r="AD223">
-        <v>2.02</v>
-      </c>
-      <c r="AE223">
-        <v>1.44</v>
-      </c>
-      <c r="AF223">
-        <v>1.36</v>
-      </c>
-      <c r="AG223">
-        <v>3</v>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ223">
-        <v>1.11</v>
-      </c>
       <c r="AK223">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O224">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P224">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q224">
-        <v>2.85</v>
+        <v>1.83</v>
       </c>
       <c r="R224">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="S224">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="T224">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="U224">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="V224">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="W224">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X224">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y224">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z224">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AA224">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AB224">
-        <v>2.48</v>
+        <v>3.6</v>
       </c>
       <c r="AC224">
-        <v>2.21</v>
+        <v>1.68</v>
       </c>
       <c r="AD224">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AE224">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AF224">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG224">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AK224">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q256">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R256">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S256">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T256">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U256">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="V256">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W256">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X256">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y256">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z256">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA256">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC256">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD256">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE256">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF256">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG256">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK256">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>9.5</v>
+        <v>4.26</v>
       </c>
       <c r="O263">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="P263">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="Q263">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="R263">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="S263">
+        <v>1.41</v>
+      </c>
+      <c r="T263">
+        <v>2.69</v>
+      </c>
+      <c r="U263">
+        <v>2.88</v>
+      </c>
+      <c r="V263">
+        <v>1.36</v>
+      </c>
+      <c r="W263">
+        <v>1.04</v>
+      </c>
+      <c r="X263">
+        <v>1.02</v>
+      </c>
+      <c r="Y263">
         <v>1.28</v>
       </c>
-      <c r="T263">
-        <v>3.3</v>
-      </c>
-      <c r="U263">
-        <v>2.33</v>
-      </c>
-      <c r="V263">
-        <v>1.53</v>
-      </c>
-      <c r="W263">
-        <v>1.1</v>
-      </c>
-      <c r="X263">
-        <v>1.03</v>
-      </c>
-      <c r="Y263">
-        <v>1.15</v>
-      </c>
       <c r="Z263">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA263">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB263">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC263">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD263">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AE263">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF263">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG263">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK263">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>4.26</v>
+        <v>9.5</v>
       </c>
       <c r="O264">
-        <v>3.54</v>
+        <v>5.25</v>
       </c>
       <c r="P264">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="Q264">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="R264">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="S264">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T264">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U264">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="V264">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W264">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X264">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z264">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA264">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB264">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC264">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD264">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE264">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF264">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG264">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK264">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -53443,7 +53443,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N326">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,64 +55892,64 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.31</v>
+        <v>2.2</v>
       </c>
       <c r="O341">
-        <v>5.35</v>
+        <v>3.35</v>
       </c>
       <c r="P341">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="Q341">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="R341">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="S341">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T341">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="U341">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V341">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W341">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X341">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y341">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z341">
-        <v>4.78</v>
+        <v>3.81</v>
       </c>
       <c r="AA341">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB341">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AC341">
-        <v>2.27</v>
+        <v>2.96</v>
       </c>
       <c r="AD341">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AE341">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF341">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AG341">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH341" t="inlineStr">
         <is>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK341">
-        <v>3.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,64 +56055,64 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.2</v>
+        <v>1.31</v>
       </c>
       <c r="O342">
-        <v>3.35</v>
+        <v>5.35</v>
       </c>
       <c r="P342">
-        <v>2.95</v>
+        <v>6.7</v>
       </c>
       <c r="Q342">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="R342">
+        <v>2.66</v>
+      </c>
+      <c r="S342">
+        <v>1.22</v>
+      </c>
+      <c r="T342">
+        <v>3.58</v>
+      </c>
+      <c r="U342">
         <v>2.28</v>
       </c>
-      <c r="S342">
-        <v>1.33</v>
-      </c>
-      <c r="T342">
-        <v>3.17</v>
-      </c>
-      <c r="U342">
-        <v>2.75</v>
-      </c>
       <c r="V342">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W342">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X342">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y342">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z342">
-        <v>3.81</v>
+        <v>4.78</v>
       </c>
       <c r="AA342">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB342">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AC342">
-        <v>2.96</v>
+        <v>2.27</v>
       </c>
       <c r="AD342">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AE342">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF342">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AG342">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK342">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,80 +56381,80 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="O344">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P344">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q344">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="R344">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S344">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="T344">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="U344">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="V344">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="W344">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X344">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y344">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z344">
-        <v>4.32</v>
+        <v>6.36</v>
       </c>
       <c r="AA344">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AB344">
-        <v>2.16</v>
+        <v>2.97</v>
       </c>
       <c r="AC344">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="AD344">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AE344">
+        <v>1.34</v>
+      </c>
+      <c r="AF344">
+        <v>1.43</v>
+      </c>
+      <c r="AG344">
+        <v>2.6</v>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ344">
         <v>1.18</v>
       </c>
-      <c r="AF344">
-        <v>1.53</v>
-      </c>
-      <c r="AG344">
-        <v>2.3</v>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI344" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ344">
-        <v>1.22</v>
-      </c>
       <c r="AK344">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,64 +56707,64 @@
         </is>
       </c>
       <c r="N346">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="O346">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P346">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q346">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R346">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="S346">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T346">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="U346">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V346">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="W346">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X346">
         <v>0</v>
       </c>
       <c r="Y346">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z346">
-        <v>6.36</v>
+        <v>9</v>
       </c>
       <c r="AA346">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AB346">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="AC346">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AD346">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AE346">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="AF346">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AG346">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK346">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,64 +56870,64 @@
         </is>
       </c>
       <c r="N347">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="O347">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P347">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q347">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="R347">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="S347">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T347">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="U347">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="V347">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="W347">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X347">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y347">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z347">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AA347">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB347">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC347">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="AD347">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AE347">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AF347">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG347">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH347" t="inlineStr">
         <is>
@@ -56940,10 +56940,10 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK347">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AL347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,64 +57033,64 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O348">
         <v>3.5</v>
       </c>
       <c r="P348">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q348">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R348">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S348">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T348">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="U348">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="V348">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W348">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X348">
         <v>1.04</v>
       </c>
       <c r="Y348">
+        <v>1.2</v>
+      </c>
+      <c r="Z348">
+        <v>4.32</v>
+      </c>
+      <c r="AA348">
+        <v>1.7</v>
+      </c>
+      <c r="AB348">
+        <v>2.16</v>
+      </c>
+      <c r="AC348">
+        <v>2.73</v>
+      </c>
+      <c r="AD348">
+        <v>1.45</v>
+      </c>
+      <c r="AE348">
         <v>1.18</v>
       </c>
-      <c r="Z348">
-        <v>4.2</v>
-      </c>
-      <c r="AA348">
-        <v>1.6</v>
-      </c>
-      <c r="AB348">
-        <v>2.25</v>
-      </c>
-      <c r="AC348">
-        <v>2.65</v>
-      </c>
-      <c r="AD348">
-        <v>1.5</v>
-      </c>
-      <c r="AE348">
-        <v>1.19</v>
-      </c>
       <c r="AF348">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG348">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>1.22</v>
       </c>
       <c r="AK348">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL348">
         <v>0</v>
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,64 +60456,64 @@
         </is>
       </c>
       <c r="N369">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="O369">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P369">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q369">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="R369">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S369">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T369">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="U369">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="V369">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W369">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X369">
         <v>1.01</v>
       </c>
       <c r="Y369">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z369">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AA369">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AB369">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AC369">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AD369">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE369">
         <v>1.11</v>
       </c>
       <c r="AF369">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG369">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH369" t="inlineStr">
         <is>
@@ -60526,10 +60526,10 @@
         </is>
       </c>
       <c r="AJ369">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK369">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL369">
         <v>0</v>
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G370">
@@ -60619,64 +60619,64 @@
         </is>
       </c>
       <c r="N370">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="O370">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P370">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q370">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="R370">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S370">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T370">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U370">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="V370">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W370">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X370">
         <v>1.01</v>
       </c>
       <c r="Y370">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z370">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AA370">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB370">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC370">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="AD370">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE370">
         <v>1.11</v>
       </c>
       <c r="AF370">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AG370">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AH370" t="inlineStr">
         <is>
@@ -60689,10 +60689,10 @@
         </is>
       </c>
       <c r="AJ370">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK370">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AL370">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,80 +60945,80 @@
         </is>
       </c>
       <c r="N372">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="O372">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P372">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q372">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="R372">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S372">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T372">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U372">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V372">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W372">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X372">
         <v>0</v>
       </c>
       <c r="Y372">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z372">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="AA372">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB372">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="AC372">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AD372">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE372">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF372">
+        <v>1.44</v>
+      </c>
+      <c r="AG372">
+        <v>2.7</v>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ372">
+        <v>1.2</v>
+      </c>
+      <c r="AK372">
         <v>1.62</v>
-      </c>
-      <c r="AG372">
-        <v>2.25</v>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ372">
-        <v>1.11</v>
-      </c>
-      <c r="AK372">
-        <v>2.56</v>
       </c>
       <c r="AL372">
         <v>0</v>
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G373">
@@ -61108,64 +61108,64 @@
         </is>
       </c>
       <c r="N373">
+        <v>1.41</v>
+      </c>
+      <c r="O373">
+        <v>5.05</v>
+      </c>
+      <c r="P373">
+        <v>6.5</v>
+      </c>
+      <c r="Q373">
+        <v>1.87</v>
+      </c>
+      <c r="R373">
+        <v>2.63</v>
+      </c>
+      <c r="S373">
+        <v>1.22</v>
+      </c>
+      <c r="T373">
+        <v>3.9</v>
+      </c>
+      <c r="U373">
         <v>2.1</v>
       </c>
-      <c r="O373">
-        <v>3.5</v>
-      </c>
-      <c r="P373">
-        <v>2.9</v>
-      </c>
-      <c r="Q373">
-        <v>2.55</v>
-      </c>
-      <c r="R373">
-        <v>2.38</v>
-      </c>
-      <c r="S373">
-        <v>1.25</v>
-      </c>
-      <c r="T373">
-        <v>3.75</v>
-      </c>
-      <c r="U373">
-        <v>2.26</v>
-      </c>
       <c r="V373">
+        <v>1.68</v>
+      </c>
+      <c r="W373">
+        <v>1.17</v>
+      </c>
+      <c r="X373">
+        <v>0</v>
+      </c>
+      <c r="Y373">
+        <v>1.11</v>
+      </c>
+      <c r="Z373">
+        <v>5.5</v>
+      </c>
+      <c r="AA373">
+        <v>1.48</v>
+      </c>
+      <c r="AB373">
+        <v>2.76</v>
+      </c>
+      <c r="AC373">
+        <v>2.12</v>
+      </c>
+      <c r="AD373">
+        <v>1.68</v>
+      </c>
+      <c r="AE373">
+        <v>1.24</v>
+      </c>
+      <c r="AF373">
         <v>1.62</v>
       </c>
-      <c r="W373">
-        <v>1.14</v>
-      </c>
-      <c r="X373">
-        <v>0</v>
-      </c>
-      <c r="Y373">
-        <v>1.13</v>
-      </c>
-      <c r="Z373">
-        <v>5.18</v>
-      </c>
-      <c r="AA373">
-        <v>1.55</v>
-      </c>
-      <c r="AB373">
-        <v>2.47</v>
-      </c>
-      <c r="AC373">
-        <v>2.33</v>
-      </c>
-      <c r="AD373">
-        <v>1.61</v>
-      </c>
-      <c r="AE373">
-        <v>1.25</v>
-      </c>
-      <c r="AF373">
-        <v>1.44</v>
-      </c>
       <c r="AG373">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH373" t="inlineStr">
         <is>
@@ -61178,10 +61178,10 @@
         </is>
       </c>
       <c r="AJ373">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK373">
-        <v>1.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL373">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R2">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
         <v>1.32</v>
@@ -671,13 +671,13 @@
         <v>1.18</v>
       </c>
       <c r="Z2">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA2">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
         <v>2.56</v>
@@ -708,7 +708,7 @@
         <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q3">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="R3">
         <v>1.94</v>
@@ -831,19 +831,19 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
         <v>2.83</v>
       </c>
       <c r="AA3">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD3">
         <v>1.2</v>
@@ -852,10 +852,10 @@
         <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
         <v>2.12</v>
@@ -1006,7 +1006,7 @@
         <v>1.88</v>
       </c>
       <c r="AC4">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD4">
         <v>1.31</v>
@@ -1034,7 +1034,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -6195,34 +6195,34 @@
         <v>1.28</v>
       </c>
       <c r="T36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
         <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W36">
         <v>1.1</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="AA36">
         <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC36">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD36">
         <v>1.45</v>
@@ -6231,10 +6231,10 @@
         <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG36">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.15</v>
+        <v>4.27</v>
       </c>
       <c r="O42">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>3.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q42">
-        <v>2.81</v>
+        <v>4.84</v>
       </c>
       <c r="R42">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="U42">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3</v>
+        <v>3.54</v>
       </c>
       <c r="AA42">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>3.78</v>
+        <v>2.76</v>
       </c>
       <c r="AD42">
+        <v>1.37</v>
+      </c>
+      <c r="AE42">
+        <v>1.13</v>
+      </c>
+      <c r="AF42">
+        <v>1.68</v>
+      </c>
+      <c r="AG42">
+        <v>2.05</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.26</v>
+      </c>
+      <c r="AK42">
         <v>1.19</v>
-      </c>
-      <c r="AE42">
-        <v>1.03</v>
-      </c>
-      <c r="AF42">
-        <v>1.87</v>
-      </c>
-      <c r="AG42">
-        <v>1.83</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.36</v>
-      </c>
-      <c r="AK42">
-        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>4.84</v>
+        <v>3.18</v>
       </c>
       <c r="R43">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z43">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="AA43">
+        <v>2.1</v>
+      </c>
+      <c r="AB43">
+        <v>1.72</v>
+      </c>
+      <c r="AC43">
+        <v>3.7</v>
+      </c>
+      <c r="AD43">
+        <v>1.24</v>
+      </c>
+      <c r="AE43">
+        <v>1.04</v>
+      </c>
+      <c r="AF43">
         <v>1.8</v>
       </c>
-      <c r="AB43">
-        <v>2</v>
-      </c>
-      <c r="AC43">
-        <v>2.76</v>
-      </c>
-      <c r="AD43">
-        <v>1.37</v>
-      </c>
-      <c r="AE43">
-        <v>1.13</v>
-      </c>
-      <c r="AF43">
-        <v>1.68</v>
-      </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK43">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q44">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="S44">
+        <v>1.42</v>
+      </c>
+      <c r="T44">
+        <v>2.65</v>
+      </c>
+      <c r="U44">
+        <v>3.15</v>
+      </c>
+      <c r="V44">
+        <v>1.31</v>
+      </c>
+      <c r="W44">
+        <v>1.07</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
+        <v>1.34</v>
+      </c>
+      <c r="Z44">
+        <v>3</v>
+      </c>
+      <c r="AA44">
+        <v>2.18</v>
+      </c>
+      <c r="AB44">
+        <v>1.66</v>
+      </c>
+      <c r="AC44">
+        <v>3.78</v>
+      </c>
+      <c r="AD44">
+        <v>1.19</v>
+      </c>
+      <c r="AE44">
+        <v>1.03</v>
+      </c>
+      <c r="AF44">
+        <v>1.87</v>
+      </c>
+      <c r="AG44">
+        <v>1.83</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.36</v>
       </c>
-      <c r="T44">
-        <v>2.88</v>
-      </c>
-      <c r="U44">
-        <v>2.99</v>
-      </c>
-      <c r="V44">
-        <v>1.33</v>
-      </c>
-      <c r="W44">
-        <v>1.05</v>
-      </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>1.32</v>
-      </c>
-      <c r="Z44">
-        <v>3.15</v>
-      </c>
-      <c r="AA44">
-        <v>2.1</v>
-      </c>
-      <c r="AB44">
-        <v>1.72</v>
-      </c>
-      <c r="AC44">
-        <v>3.7</v>
-      </c>
-      <c r="AD44">
-        <v>1.24</v>
-      </c>
-      <c r="AE44">
-        <v>1.04</v>
-      </c>
-      <c r="AF44">
-        <v>1.8</v>
-      </c>
-      <c r="AG44">
-        <v>1.9</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.44</v>
-      </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="R51">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="S51">
+        <v>1.25</v>
+      </c>
+      <c r="T51">
+        <v>3.6</v>
+      </c>
+      <c r="U51">
+        <v>2.15</v>
+      </c>
+      <c r="V51">
+        <v>1.62</v>
+      </c>
+      <c r="W51">
+        <v>1.15</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.11</v>
+      </c>
+      <c r="Z51">
+        <v>4.45</v>
+      </c>
+      <c r="AA51">
+        <v>1.59</v>
+      </c>
+      <c r="AB51">
+        <v>2.38</v>
+      </c>
+      <c r="AC51">
+        <v>2.4</v>
+      </c>
+      <c r="AD51">
+        <v>1.54</v>
+      </c>
+      <c r="AE51">
         <v>1.2</v>
       </c>
-      <c r="T51">
-        <v>4.2</v>
-      </c>
-      <c r="U51">
-        <v>1.95</v>
-      </c>
-      <c r="V51">
-        <v>1.75</v>
-      </c>
-      <c r="W51">
-        <v>1.2</v>
-      </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.07</v>
-      </c>
-      <c r="Z51">
-        <v>5.85</v>
-      </c>
-      <c r="AA51">
-        <v>1.37</v>
-      </c>
-      <c r="AB51">
-        <v>2.66</v>
-      </c>
-      <c r="AC51">
-        <v>2.05</v>
-      </c>
-      <c r="AD51">
-        <v>1.77</v>
-      </c>
-      <c r="AE51">
-        <v>1.26</v>
-      </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>2.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U52">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>4.45</v>
+        <v>5.85</v>
       </c>
       <c r="AA52">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AC52">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AD52">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF52">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>2.67</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="R69">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T69">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V69">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W69">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z69">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA69">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB69">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD69">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG69">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="O71">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O72">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="P72">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q72">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R72">
         <v>2.5</v>
@@ -12063,7 +12063,7 @@
         <v>1.28</v>
       </c>
       <c r="T72">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U72">
         <v>2.2</v>
@@ -12087,7 +12087,7 @@
         <v>1.62</v>
       </c>
       <c r="AB72">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC72">
         <v>2.4</v>
@@ -12099,10 +12099,10 @@
         <v>1.19</v>
       </c>
       <c r="AF72">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG72">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.81</v>
+        <v>2.65</v>
       </c>
       <c r="O81">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q81">
-        <v>2.42</v>
+        <v>3.42</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T81">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="U81">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z81">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AA81">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="AB81">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AC81">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="AD81">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG81">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.65</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="Q82">
-        <v>3.42</v>
+        <v>2.42</v>
       </c>
       <c r="R82">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="U82">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="V82">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
+        <v>1.25</v>
+      </c>
+      <c r="Z82">
+        <v>3.28</v>
+      </c>
+      <c r="AA82">
+        <v>1.89</v>
+      </c>
+      <c r="AB82">
+        <v>1.89</v>
+      </c>
+      <c r="AC82">
+        <v>3.18</v>
+      </c>
+      <c r="AD82">
         <v>1.33</v>
       </c>
-      <c r="Z82">
-        <v>2.83</v>
-      </c>
-      <c r="AA82">
-        <v>2.12</v>
-      </c>
-      <c r="AB82">
-        <v>1.64</v>
-      </c>
-      <c r="AC82">
-        <v>3.74</v>
-      </c>
-      <c r="AD82">
-        <v>1.19</v>
-      </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
-        <v>7.5</v>
+        <v>4.03</v>
       </c>
       <c r="Q92">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="R92">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
+        <v>1.2</v>
+      </c>
+      <c r="Z92">
+        <v>3.9</v>
+      </c>
+      <c r="AA92">
+        <v>1.72</v>
+      </c>
+      <c r="AB92">
+        <v>1.98</v>
+      </c>
+      <c r="AC92">
+        <v>2.8</v>
+      </c>
+      <c r="AD92">
+        <v>1.37</v>
+      </c>
+      <c r="AE92">
         <v>1.11</v>
       </c>
-      <c r="Z92">
-        <v>5.5</v>
-      </c>
-      <c r="AA92">
-        <v>1.45</v>
-      </c>
-      <c r="AB92">
-        <v>2.55</v>
-      </c>
-      <c r="AC92">
-        <v>2.25</v>
-      </c>
-      <c r="AD92">
-        <v>1.57</v>
-      </c>
-      <c r="AE92">
-        <v>1.2</v>
-      </c>
       <c r="AF92">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG92">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK92">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,61 +15468,61 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="O93">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="P93">
-        <v>4.03</v>
+        <v>2.89</v>
       </c>
       <c r="Q93">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z93">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA93">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB93">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AC93">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF93">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG93">
         <v>2.01</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AK93">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="O94">
-        <v>3.42</v>
+        <v>5.25</v>
       </c>
       <c r="P94">
-        <v>2.89</v>
+        <v>7.5</v>
       </c>
       <c r="Q94">
-        <v>2.88</v>
+        <v>1.64</v>
       </c>
       <c r="R94">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T94">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U94">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="V94">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W94">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z94">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AA94">
+        <v>1.45</v>
+      </c>
+      <c r="AB94">
+        <v>2.55</v>
+      </c>
+      <c r="AC94">
+        <v>2.25</v>
+      </c>
+      <c r="AD94">
+        <v>1.57</v>
+      </c>
+      <c r="AE94">
+        <v>1.2</v>
+      </c>
+      <c r="AF94">
         <v>1.85</v>
       </c>
-      <c r="AB94">
-        <v>1.82</v>
-      </c>
-      <c r="AC94">
-        <v>3.2</v>
-      </c>
-      <c r="AD94">
-        <v>1.26</v>
-      </c>
-      <c r="AE94">
-        <v>1.05</v>
-      </c>
-      <c r="AF94">
-        <v>1.66</v>
-      </c>
       <c r="AG94">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AK94">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17107,7 +17107,7 @@
         <v>3.6</v>
       </c>
       <c r="Q103">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
         <v>2.1</v>
@@ -17119,43 +17119,43 @@
         <v>2.8</v>
       </c>
       <c r="U103">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V103">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
         <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
         <v>1.3</v>
       </c>
       <c r="Z103">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA103">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC103">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD103">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE103">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AG103">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17270,10 +17270,10 @@
         <v>2.44</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="R104">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S104">
         <v>1.37</v>
@@ -17291,13 +17291,13 @@
         <v>1.09</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z104">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA104">
         <v>1.93</v>
@@ -17306,19 +17306,19 @@
         <v>1.83</v>
       </c>
       <c r="AC104">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG104">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,31 +18239,31 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="O110">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P110">
+        <v>2.15</v>
+      </c>
+      <c r="Q110">
         <v>3.65</v>
       </c>
-      <c r="Q110">
-        <v>2.32</v>
-      </c>
       <c r="R110">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="S110">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T110">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="U110">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V110">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W110">
         <v>1.11</v>
@@ -18272,31 +18272,31 @@
         <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z110">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="AA110">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AB110">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AC110">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD110">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG110">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
       <c r="AK110">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="O111">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="P111">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="Q111">
-        <v>3.65</v>
+        <v>1.97</v>
       </c>
       <c r="R111">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="S111">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="U111">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="V111">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W111">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z111">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA111">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="AB111">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="AC111">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="AD111">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AE111">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF111">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG111">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.77</v>
+        <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>1.28</v>
+        <v>2.75</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O112">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P112">
-        <v>2.23</v>
+        <v>3.65</v>
       </c>
       <c r="Q112">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="R112">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="S112">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T112">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U112">
-        <v>2.17</v>
+        <v>2.44</v>
       </c>
       <c r="V112">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z112">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA112">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AB112">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AC112">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="AD112">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AE112">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF112">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AG112">
-        <v>2.73</v>
+        <v>2.28</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK112">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.43</v>
+        <v>2.75</v>
       </c>
       <c r="O113">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P113">
-        <v>6</v>
+        <v>2.23</v>
       </c>
       <c r="Q113">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="R113">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="S113">
         <v>1.22</v>
       </c>
       <c r="T113">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="U113">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V113">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W113">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
         <v>1.1</v>
       </c>
       <c r="Z113">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA113">
+        <v>1.44</v>
+      </c>
+      <c r="AB113">
+        <v>2.55</v>
+      </c>
+      <c r="AC113">
+        <v>2.21</v>
+      </c>
+      <c r="AD113">
+        <v>1.66</v>
+      </c>
+      <c r="AE113">
+        <v>1.25</v>
+      </c>
+      <c r="AF113">
         <v>1.41</v>
       </c>
-      <c r="AB113">
-        <v>2.88</v>
-      </c>
-      <c r="AC113">
-        <v>2.11</v>
-      </c>
-      <c r="AD113">
-        <v>1.76</v>
-      </c>
-      <c r="AE113">
-        <v>1.29</v>
-      </c>
-      <c r="AF113">
-        <v>1.56</v>
-      </c>
       <c r="AG113">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.18</v>
+        <v>2.55</v>
       </c>
       <c r="O122">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>12.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q122">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="R122">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U122">
+        <v>2.9</v>
+      </c>
+      <c r="V122">
+        <v>1.4</v>
+      </c>
+      <c r="W122">
+        <v>1.08</v>
+      </c>
+      <c r="X122">
+        <v>1.06</v>
+      </c>
+      <c r="Y122">
+        <v>1.28</v>
+      </c>
+      <c r="Z122">
+        <v>3.24</v>
+      </c>
+      <c r="AA122">
+        <v>2.01</v>
+      </c>
+      <c r="AB122">
         <v>1.85</v>
       </c>
-      <c r="V122">
-        <v>1.85</v>
-      </c>
-      <c r="W122">
-        <v>1.2</v>
-      </c>
-      <c r="X122">
-        <v>1.01</v>
-      </c>
-      <c r="Y122">
+      <c r="AC122">
+        <v>3.34</v>
+      </c>
+      <c r="AD122">
+        <v>1.27</v>
+      </c>
+      <c r="AE122">
         <v>1.05</v>
       </c>
-      <c r="Z122">
-        <v>6.5</v>
-      </c>
-      <c r="AA122">
-        <v>1.3</v>
-      </c>
-      <c r="AB122">
-        <v>2.91</v>
-      </c>
-      <c r="AC122">
-        <v>1.83</v>
-      </c>
-      <c r="AD122">
-        <v>1.84</v>
-      </c>
-      <c r="AE122">
-        <v>1.37</v>
-      </c>
       <c r="AF122">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG122">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AK122">
-        <v>4.06</v>
+        <v>1.47</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.55</v>
+        <v>1.18</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="P123">
-        <v>2.75</v>
+        <v>12.5</v>
       </c>
       <c r="Q123">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="U123">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X123">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="Z123">
-        <v>3.24</v>
+        <v>6.5</v>
       </c>
       <c r="AA123">
-        <v>2.01</v>
+        <v>1.3</v>
       </c>
       <c r="AB123">
-        <v>1.85</v>
+        <v>2.91</v>
       </c>
       <c r="AC123">
-        <v>3.34</v>
+        <v>1.83</v>
       </c>
       <c r="AD123">
-        <v>1.27</v>
+        <v>1.84</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AF123">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG123">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="AK123">
-        <v>1.47</v>
+        <v>4.06</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,19 +20847,19 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="O126">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P126">
-        <v>4.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q126">
-        <v>2.1</v>
+        <v>4.67</v>
       </c>
       <c r="R126">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S126">
         <v>1.31</v>
@@ -20868,43 +20868,43 @@
         <v>3.02</v>
       </c>
       <c r="U126">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V126">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W126">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X126">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z126">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA126">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB126">
         <v>2</v>
       </c>
       <c r="AC126">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AD126">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE126">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF126">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG126">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK126">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="O127">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="P127">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="Q127">
-        <v>3.81</v>
+        <v>2.1</v>
       </c>
       <c r="R127">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T127">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="U127">
         <v>2.5</v>
       </c>
       <c r="V127">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z127">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AA127">
         <v>1.75</v>
       </c>
       <c r="AB127">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC127">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD127">
         <v>1.4</v>
       </c>
       <c r="AE127">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF127">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG127">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK127">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O128">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="P128">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q128">
-        <v>4.67</v>
+        <v>3.81</v>
       </c>
       <c r="R128">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S128">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T128">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U128">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V128">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W128">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X128">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z128">
-        <v>3.72</v>
+        <v>3.94</v>
       </c>
       <c r="AA128">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB128">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC128">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AD128">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE128">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF128">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG128">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK128">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="O132">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P132">
-        <v>2.47</v>
+        <v>2.74</v>
       </c>
       <c r="Q132">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="R132">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="S132">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T132">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U132">
-        <v>3.34</v>
+        <v>3.02</v>
       </c>
       <c r="V132">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W132">
+        <v>1.05</v>
+      </c>
+      <c r="X132">
+        <v>1.01</v>
+      </c>
+      <c r="Y132">
+        <v>1.3</v>
+      </c>
+      <c r="Z132">
+        <v>2.97</v>
+      </c>
+      <c r="AA132">
+        <v>1.98</v>
+      </c>
+      <c r="AB132">
+        <v>1.71</v>
+      </c>
+      <c r="AC132">
+        <v>3.8</v>
+      </c>
+      <c r="AD132">
+        <v>1.21</v>
+      </c>
+      <c r="AE132">
         <v>1.03</v>
       </c>
-      <c r="X132">
-        <v>1.03</v>
-      </c>
-      <c r="Y132">
-        <v>1.36</v>
-      </c>
-      <c r="Z132">
-        <v>2.7</v>
-      </c>
-      <c r="AA132">
-        <v>2.21</v>
-      </c>
-      <c r="AB132">
-        <v>1.61</v>
-      </c>
-      <c r="AC132">
-        <v>4.16</v>
-      </c>
-      <c r="AD132">
-        <v>1.17</v>
-      </c>
-      <c r="AE132">
-        <v>1.02</v>
-      </c>
       <c r="AF132">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG132">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK132">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,80 +21988,80 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="O133">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P133">
-        <v>2.74</v>
+        <v>2.47</v>
       </c>
       <c r="Q133">
-        <v>3.06</v>
+        <v>3.44</v>
       </c>
       <c r="R133">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S133">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T133">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U133">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="V133">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
+        <v>1.36</v>
+      </c>
+      <c r="Z133">
+        <v>2.7</v>
+      </c>
+      <c r="AA133">
+        <v>2.21</v>
+      </c>
+      <c r="AB133">
+        <v>1.61</v>
+      </c>
+      <c r="AC133">
+        <v>4.16</v>
+      </c>
+      <c r="AD133">
+        <v>1.17</v>
+      </c>
+      <c r="AE133">
+        <v>1.02</v>
+      </c>
+      <c r="AF133">
+        <v>1.87</v>
+      </c>
+      <c r="AG133">
+        <v>1.82</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
         <v>1.3</v>
       </c>
-      <c r="Z133">
-        <v>2.97</v>
-      </c>
-      <c r="AA133">
-        <v>1.98</v>
-      </c>
-      <c r="AB133">
-        <v>1.71</v>
-      </c>
-      <c r="AC133">
-        <v>3.8</v>
-      </c>
-      <c r="AD133">
-        <v>1.21</v>
-      </c>
-      <c r="AE133">
-        <v>1.03</v>
-      </c>
-      <c r="AF133">
-        <v>1.78</v>
-      </c>
-      <c r="AG133">
-        <v>1.91</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>1.26</v>
-      </c>
       <c r="AK133">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="O143">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P143">
+        <v>4.5</v>
+      </c>
+      <c r="Q143">
+        <v>2.24</v>
+      </c>
+      <c r="R143">
+        <v>2.26</v>
+      </c>
+      <c r="S143">
+        <v>1.29</v>
+      </c>
+      <c r="T143">
         <v>3.3</v>
       </c>
-      <c r="Q143">
-        <v>2.63</v>
-      </c>
-      <c r="R143">
-        <v>2.15</v>
-      </c>
-      <c r="S143">
-        <v>1.36</v>
-      </c>
-      <c r="T143">
-        <v>2.85</v>
-      </c>
       <c r="U143">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="V143">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W143">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X143">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y143">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z143">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AA143">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB143">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AC143">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD143">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE143">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF143">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG143">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK143">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q144">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="R144">
         <v>2.15</v>
       </c>
       <c r="S144">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U144">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W144">
         <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA144">
+        <v>1.93</v>
+      </c>
+      <c r="AB144">
         <v>1.83</v>
       </c>
-      <c r="AB144">
-        <v>1.95</v>
-      </c>
       <c r="AC144">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD144">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE144">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG144">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="O145">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q145">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="R145">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S145">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T145">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U145">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V145">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W145">
+        <v>1.06</v>
+      </c>
+      <c r="X145">
+        <v>1.03</v>
+      </c>
+      <c r="Y145">
+        <v>1.23</v>
+      </c>
+      <c r="Z145">
+        <v>3.65</v>
+      </c>
+      <c r="AA145">
+        <v>1.83</v>
+      </c>
+      <c r="AB145">
+        <v>1.95</v>
+      </c>
+      <c r="AC145">
+        <v>3.05</v>
+      </c>
+      <c r="AD145">
+        <v>1.3</v>
+      </c>
+      <c r="AE145">
         <v>1.08</v>
       </c>
-      <c r="X145">
-        <v>1</v>
-      </c>
-      <c r="Y145">
-        <v>1.2</v>
-      </c>
-      <c r="Z145">
-        <v>4.1</v>
-      </c>
-      <c r="AA145">
-        <v>1.73</v>
-      </c>
-      <c r="AB145">
-        <v>2.08</v>
-      </c>
-      <c r="AC145">
-        <v>2.8</v>
-      </c>
-      <c r="AD145">
-        <v>1.38</v>
-      </c>
-      <c r="AE145">
-        <v>1.12</v>
-      </c>
       <c r="AF145">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG145">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK145">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q157">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="R157">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U157">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V157">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z157">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AA157">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB157">
         <v>1.88</v>
       </c>
       <c r="AC157">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD157">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE157">
         <v>0</v>
       </c>
       <c r="AF157">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG157">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -30159,43 +30159,43 @@
         <v>2.75</v>
       </c>
       <c r="U183">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V183">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W183">
         <v>1.06</v>
       </c>
       <c r="X183">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z183">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA183">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB183">
         <v>1.75</v>
       </c>
       <c r="AC183">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD183">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE183">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF183">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG183">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>4.26</v>
+        <v>9.5</v>
       </c>
       <c r="O263">
-        <v>3.54</v>
+        <v>5.25</v>
       </c>
       <c r="P263">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="Q263">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="R263">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="S263">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T263">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U263">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="V263">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W263">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z263">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA263">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB263">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC263">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD263">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE263">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF263">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG263">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK263">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>9.5</v>
+        <v>4.26</v>
       </c>
       <c r="O264">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="P264">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="Q264">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="R264">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="S264">
+        <v>1.41</v>
+      </c>
+      <c r="T264">
+        <v>2.69</v>
+      </c>
+      <c r="U264">
+        <v>2.88</v>
+      </c>
+      <c r="V264">
+        <v>1.36</v>
+      </c>
+      <c r="W264">
+        <v>1.04</v>
+      </c>
+      <c r="X264">
+        <v>1.02</v>
+      </c>
+      <c r="Y264">
         <v>1.28</v>
       </c>
-      <c r="T264">
-        <v>3.3</v>
-      </c>
-      <c r="U264">
-        <v>2.33</v>
-      </c>
-      <c r="V264">
-        <v>1.53</v>
-      </c>
-      <c r="W264">
-        <v>1.1</v>
-      </c>
-      <c r="X264">
-        <v>1.03</v>
-      </c>
-      <c r="Y264">
-        <v>1.15</v>
-      </c>
       <c r="Z264">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA264">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB264">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC264">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD264">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AE264">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF264">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG264">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK264">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O323">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P323">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q323">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="R323">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="S323">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="T323">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="U323">
+        <v>2.8</v>
+      </c>
+      <c r="V323">
+        <v>1.38</v>
+      </c>
+      <c r="W323">
+        <v>1.03</v>
+      </c>
+      <c r="X323">
+        <v>1</v>
+      </c>
+      <c r="Y323">
+        <v>1.25</v>
+      </c>
+      <c r="Z323">
         <v>3.6</v>
       </c>
-      <c r="V323">
-        <v>1.25</v>
-      </c>
-      <c r="W323">
-        <v>1.04</v>
-      </c>
-      <c r="X323">
+      <c r="AA323">
+        <v>2.1</v>
+      </c>
+      <c r="AB323">
+        <v>1.87</v>
+      </c>
+      <c r="AC323">
+        <v>3.28</v>
+      </c>
+      <c r="AD323">
+        <v>1.32</v>
+      </c>
+      <c r="AE323">
         <v>1.06</v>
       </c>
-      <c r="Y323">
-        <v>1.48</v>
-      </c>
-      <c r="Z323">
-        <v>2.75</v>
-      </c>
-      <c r="AA323">
-        <v>2.7</v>
-      </c>
-      <c r="AB323">
-        <v>1.49</v>
-      </c>
-      <c r="AC323">
-        <v>4.25</v>
-      </c>
-      <c r="AD323">
-        <v>1.18</v>
-      </c>
-      <c r="AE323">
-        <v>1.01</v>
-      </c>
       <c r="AF323">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG323">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK323">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q324">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="R324">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="S324">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="T324">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="U324">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="V324">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="W324">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X324">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y324">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Z324">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA324">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB324">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AC324">
-        <v>3.28</v>
+        <v>4.25</v>
       </c>
       <c r="AD324">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AE324">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF324">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG324">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK324">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,64 +56707,64 @@
         </is>
       </c>
       <c r="N346">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="O346">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P346">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q346">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="R346">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="S346">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="T346">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="U346">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="V346">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="W346">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X346">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y346">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z346">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AA346">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AB346">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC346">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="AD346">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AE346">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AF346">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG346">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH346" t="inlineStr">
         <is>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK346">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,64 +56870,64 @@
         </is>
       </c>
       <c r="N347">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="O347">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="P347">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q347">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="R347">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="S347">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="T347">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="U347">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="V347">
+        <v>2</v>
+      </c>
+      <c r="W347">
+        <v>1.29</v>
+      </c>
+      <c r="X347">
+        <v>0</v>
+      </c>
+      <c r="Y347">
+        <v>1.05</v>
+      </c>
+      <c r="Z347">
+        <v>9</v>
+      </c>
+      <c r="AA347">
+        <v>1.25</v>
+      </c>
+      <c r="AB347">
+        <v>3.75</v>
+      </c>
+      <c r="AC347">
+        <v>1.65</v>
+      </c>
+      <c r="AD347">
+        <v>2.07</v>
+      </c>
+      <c r="AE347">
         <v>1.51</v>
       </c>
-      <c r="W347">
-        <v>1.12</v>
-      </c>
-      <c r="X347">
-        <v>1.04</v>
-      </c>
-      <c r="Y347">
-        <v>1.18</v>
-      </c>
-      <c r="Z347">
-        <v>4.2</v>
-      </c>
-      <c r="AA347">
-        <v>1.6</v>
-      </c>
-      <c r="AB347">
-        <v>2.25</v>
-      </c>
-      <c r="AC347">
-        <v>2.65</v>
-      </c>
-      <c r="AD347">
-        <v>1.5</v>
-      </c>
-      <c r="AE347">
-        <v>1.19</v>
-      </c>
       <c r="AF347">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AG347">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH347" t="inlineStr">
         <is>
@@ -56940,10 +56940,10 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK347">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AL347">
         <v>0</v>
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G372">
@@ -60945,64 +60945,64 @@
         </is>
       </c>
       <c r="N372">
+        <v>1.41</v>
+      </c>
+      <c r="O372">
+        <v>5.05</v>
+      </c>
+      <c r="P372">
+        <v>6.5</v>
+      </c>
+      <c r="Q372">
+        <v>1.87</v>
+      </c>
+      <c r="R372">
+        <v>2.63</v>
+      </c>
+      <c r="S372">
+        <v>1.22</v>
+      </c>
+      <c r="T372">
+        <v>3.9</v>
+      </c>
+      <c r="U372">
         <v>2.1</v>
       </c>
-      <c r="O372">
-        <v>3.5</v>
-      </c>
-      <c r="P372">
-        <v>2.9</v>
-      </c>
-      <c r="Q372">
-        <v>2.55</v>
-      </c>
-      <c r="R372">
-        <v>2.38</v>
-      </c>
-      <c r="S372">
-        <v>1.25</v>
-      </c>
-      <c r="T372">
-        <v>3.75</v>
-      </c>
-      <c r="U372">
-        <v>2.26</v>
-      </c>
       <c r="V372">
+        <v>1.68</v>
+      </c>
+      <c r="W372">
+        <v>1.17</v>
+      </c>
+      <c r="X372">
+        <v>0</v>
+      </c>
+      <c r="Y372">
+        <v>1.11</v>
+      </c>
+      <c r="Z372">
+        <v>5.5</v>
+      </c>
+      <c r="AA372">
+        <v>1.48</v>
+      </c>
+      <c r="AB372">
+        <v>2.76</v>
+      </c>
+      <c r="AC372">
+        <v>2.12</v>
+      </c>
+      <c r="AD372">
+        <v>1.68</v>
+      </c>
+      <c r="AE372">
+        <v>1.24</v>
+      </c>
+      <c r="AF372">
         <v>1.62</v>
       </c>
-      <c r="W372">
-        <v>1.14</v>
-      </c>
-      <c r="X372">
-        <v>0</v>
-      </c>
-      <c r="Y372">
-        <v>1.13</v>
-      </c>
-      <c r="Z372">
-        <v>5.18</v>
-      </c>
-      <c r="AA372">
-        <v>1.55</v>
-      </c>
-      <c r="AB372">
-        <v>2.47</v>
-      </c>
-      <c r="AC372">
-        <v>2.33</v>
-      </c>
-      <c r="AD372">
-        <v>1.61</v>
-      </c>
-      <c r="AE372">
-        <v>1.25</v>
-      </c>
-      <c r="AF372">
-        <v>1.44</v>
-      </c>
       <c r="AG372">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH372" t="inlineStr">
         <is>
@@ -61015,10 +61015,10 @@
         </is>
       </c>
       <c r="AJ372">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK372">
-        <v>1.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL372">
         <v>0</v>
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G373">
@@ -61108,80 +61108,80 @@
         </is>
       </c>
       <c r="N373">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="O373">
-        <v>5.05</v>
+        <v>3.5</v>
       </c>
       <c r="P373">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q373">
-        <v>1.87</v>
+        <v>2.55</v>
       </c>
       <c r="R373">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S373">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T373">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U373">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V373">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W373">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X373">
         <v>0</v>
       </c>
       <c r="Y373">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z373">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="AA373">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB373">
-        <v>2.76</v>
+        <v>2.47</v>
       </c>
       <c r="AC373">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AD373">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE373">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF373">
+        <v>1.44</v>
+      </c>
+      <c r="AG373">
+        <v>2.7</v>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ373">
+        <v>1.2</v>
+      </c>
+      <c r="AK373">
         <v>1.62</v>
-      </c>
-      <c r="AG373">
-        <v>2.25</v>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ373">
-        <v>1.11</v>
-      </c>
-      <c r="AK373">
-        <v>2.56</v>
       </c>
       <c r="AL373">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -1465,10 +1465,10 @@
         <v>2.14</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="U7">
         <v>2.65</v>
@@ -1483,10 +1483,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.65</v>
+        <v>3.86</v>
       </c>
       <c r="AA7">
         <v>1.82</v>
@@ -1495,13 +1495,13 @@
         <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD7">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.64</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="R8">
         <v>2.06</v>
@@ -1640,10 +1640,10 @@
         <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
         <v>1.27</v>
@@ -1652,7 +1652,7 @@
         <v>3.18</v>
       </c>
       <c r="AA8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB8">
         <v>1.8</v>
@@ -1661,13 +1661,13 @@
         <v>3.3</v>
       </c>
       <c r="AD8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG8">
         <v>1.9</v>
@@ -1686,7 +1686,7 @@
         <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,16 +1779,16 @@
         <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
         <v>1.43</v>
@@ -1797,10 +1797,10 @@
         <v>2.62</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.02</v>
@@ -1815,13 +1815,13 @@
         <v>2.94</v>
       </c>
       <c r="AA9">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.62</v>
+        <v>3.84</v>
       </c>
       <c r="AD9">
         <v>1.21</v>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,37 +1948,37 @@
         <v>1.82</v>
       </c>
       <c r="Q10">
-        <v>4.2</v>
+        <v>4.68</v>
       </c>
       <c r="R10">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AA10">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
         <v>1.85</v>
@@ -1987,16 +1987,16 @@
         <v>3.08</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
         <v>1.22</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
         <v>3</v>
       </c>
       <c r="U27">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AB27">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AC27">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
         <v>1.32</v>
@@ -4900,22 +4900,22 @@
         <v>1.47</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
         <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AA28">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AC28">
         <v>2.59</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P37">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q37">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
         <v>3.5</v>
       </c>
       <c r="U37">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="V37">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z37">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AC37">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD37">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG37">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,22 +6666,22 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R39">
         <v>2.04</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
         <v>2.62</v>
@@ -6693,7 +6693,7 @@
         <v>1.34</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.02</v>
@@ -6705,13 +6705,13 @@
         <v>2.97</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB39">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC39">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
         <v>1.22</v>
@@ -6720,7 +6720,7 @@
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
         <v>1.83</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R40">
         <v>2.05</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U40">
         <v>2.85</v>
@@ -6859,7 +6859,7 @@
         <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y40">
         <v>1.27</v>
@@ -6868,7 +6868,7 @@
         <v>3.14</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB40">
         <v>1.79</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.4</v>
+      </c>
+      <c r="O41">
+        <v>3.3</v>
+      </c>
+      <c r="P41">
         <v>2.5</v>
       </c>
-      <c r="O41">
-        <v>3.4</v>
-      </c>
-      <c r="P41">
-        <v>2.45</v>
-      </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA41">
         <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,22 +7164,22 @@
         <v>1.8</v>
       </c>
       <c r="Q42">
-        <v>4.6</v>
+        <v>4.84</v>
       </c>
       <c r="R42">
         <v>2.19</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
         <v>2.94</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.07</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7357,16 +7357,16 @@
         <v>2.8</v>
       </c>
       <c r="AA43">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AB43">
         <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE43">
         <v>1.03</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,10 +7490,10 @@
         <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>1.43</v>
@@ -7511,25 +7511,25 @@
         <v>1.03</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
         <v>2.89</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB44">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC44">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE44">
         <v>1.04</v>
@@ -8299,10 +8299,10 @@
         <v>3.25</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P49">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q49">
         <v>3.94</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="O50">
         <v>3.75</v>
       </c>
       <c r="P50">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q50">
         <v>3.63</v>
       </c>
       <c r="R50">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.26</v>
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="S51">
         <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U51">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA51">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB51">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AC51">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD51">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF51">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O52">
         <v>3.7</v>
       </c>
       <c r="P52">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="R52">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="U52">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8830,7 +8830,7 @@
         <v>2.66</v>
       </c>
       <c r="AC52">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD52">
         <v>1.77</v>
@@ -8839,10 +8839,10 @@
         <v>1.26</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG52">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9289,16 +9289,16 @@
         <v>2.56</v>
       </c>
       <c r="S55">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U55">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V55">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W55">
         <v>1.18</v>
@@ -9328,7 +9328,7 @@
         <v>1.28</v>
       </c>
       <c r="AF55">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG55">
         <v>2.5</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O60">
         <v>3.3</v>
@@ -10104,10 +10104,10 @@
         <v>2.17</v>
       </c>
       <c r="S60">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="U60">
         <v>2.44</v>
@@ -10116,7 +10116,7 @@
         <v>1.49</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X60">
         <v>1</v>
@@ -10128,10 +10128,10 @@
         <v>3.95</v>
       </c>
       <c r="AA60">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC60">
         <v>2.51</v>
@@ -10291,10 +10291,10 @@
         <v>4.2</v>
       </c>
       <c r="AA61">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC61">
         <v>2.48</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q82">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="R82">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U82">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="V82">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W82">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA82">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB82">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD82">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG82">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="O83">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q83">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S83">
         <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U83">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="V83">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z83">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA83">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB83">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC83">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD83">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG83">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK83">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15794,25 +15794,25 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="O95">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="P95">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q95">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="R95">
         <v>2.19</v>
       </c>
       <c r="S95">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U95">
         <v>2.39</v>
@@ -15821,7 +15821,7 @@
         <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
         <v>1.02</v>
@@ -15830,28 +15830,28 @@
         <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA95">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB95">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC95">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD95">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE95">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG95">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O96">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="Q96">
         <v>2.72</v>
       </c>
       <c r="R96">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S96">
         <v>1.3</v>
@@ -16008,13 +16008,13 @@
         <v>1.42</v>
       </c>
       <c r="AE96">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P99">
-        <v>4.03</v>
+        <v>3.7</v>
       </c>
       <c r="Q99">
         <v>2.48</v>
@@ -16485,22 +16485,22 @@
         <v>3.18</v>
       </c>
       <c r="AA99">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB99">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD99">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
         <v>1.06</v>
       </c>
       <c r="AF99">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG99">
         <v>1.9</v>
@@ -16618,7 +16618,7 @@
         <v>2.62</v>
       </c>
       <c r="Q100">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R100">
         <v>2.23</v>
@@ -16633,13 +16633,13 @@
         <v>2.32</v>
       </c>
       <c r="V100">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W100">
         <v>1.09</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
         <v>1.13</v>
@@ -16651,13 +16651,13 @@
         <v>1.59</v>
       </c>
       <c r="AB100">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AC100">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AD100">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE100">
         <v>1.15</v>
@@ -16682,7 +16682,7 @@
         <v>1.27</v>
       </c>
       <c r="AK100">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="O111">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P111">
-        <v>4.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q111">
-        <v>2.32</v>
+        <v>3.84</v>
       </c>
       <c r="R111">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S111">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T111">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="U111">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="V111">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W111">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
+        <v>1.17</v>
+      </c>
+      <c r="Z111">
+        <v>4.3</v>
+      </c>
+      <c r="AA111">
+        <v>1.72</v>
+      </c>
+      <c r="AB111">
+        <v>2.3</v>
+      </c>
+      <c r="AC111">
+        <v>2.53</v>
+      </c>
+      <c r="AD111">
+        <v>1.44</v>
+      </c>
+      <c r="AE111">
         <v>1.14</v>
       </c>
-      <c r="Z111">
-        <v>4.7</v>
-      </c>
-      <c r="AA111">
-        <v>1.61</v>
-      </c>
-      <c r="AB111">
-        <v>2.42</v>
-      </c>
-      <c r="AC111">
-        <v>2.4</v>
-      </c>
-      <c r="AD111">
-        <v>1.49</v>
-      </c>
-      <c r="AE111">
-        <v>1.15</v>
-      </c>
       <c r="AF111">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG111">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AK111">
-        <v>2.04</v>
+        <v>1.34</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O112">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P112">
-        <v>2.3</v>
+        <v>4.16</v>
       </c>
       <c r="Q112">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="R112">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S112">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.84</v>
+        <v>3.48</v>
       </c>
       <c r="U112">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="V112">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W112">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AA112">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AB112">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AC112">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD112">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="AE112">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AF112">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AG112">
-        <v>2.77</v>
+        <v>2.35</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>1.43</v>
+        <v>2.04</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="O113">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P113">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
+        <v>3</v>
+      </c>
+      <c r="R113">
+        <v>2.5</v>
+      </c>
+      <c r="S113">
+        <v>1.24</v>
+      </c>
+      <c r="T113">
         <v>3.84</v>
       </c>
-      <c r="R113">
-        <v>2.28</v>
-      </c>
-      <c r="S113">
-        <v>1.32</v>
-      </c>
-      <c r="T113">
-        <v>3.36</v>
-      </c>
       <c r="U113">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="V113">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="W113">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z113">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA113">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB113">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="AC113">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD113">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AF113">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG113">
-        <v>2.32</v>
+        <v>2.77</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AK113">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P136">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q136">
         <v>3.24</v>
@@ -22498,10 +22498,10 @@
         <v>2.81</v>
       </c>
       <c r="U136">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V136">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W136">
         <v>1.05</v>
@@ -22519,22 +22519,22 @@
         <v>1.95</v>
       </c>
       <c r="AB136">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC136">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD136">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
         <v>1.72</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22649,10 +22649,10 @@
         <v>2.9</v>
       </c>
       <c r="Q137">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R137">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S137">
         <v>1.35</v>
@@ -22661,7 +22661,7 @@
         <v>2.9</v>
       </c>
       <c r="U137">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V137">
         <v>1.42</v>
@@ -22673,16 +22673,16 @@
         <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z137">
         <v>3.65</v>
       </c>
       <c r="AA137">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB137">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC137">
         <v>2.92</v>
@@ -22691,13 +22691,13 @@
         <v>1.33</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF137">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG137">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>1.29</v>
       </c>
       <c r="AK137">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22806,10 +22806,10 @@
         <v>2.45</v>
       </c>
       <c r="O138">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P138">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -23129,16 +23129,16 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P140">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q140">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R140">
         <v>2.11</v>
@@ -23168,10 +23168,10 @@
         <v>3.2</v>
       </c>
       <c r="AA140">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB140">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC140">
         <v>3.14</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P141">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23621,16 +23621,16 @@
         <v>1.73</v>
       </c>
       <c r="O143">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P143">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q143">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R143">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S143">
         <v>1.31</v>
@@ -23639,7 +23639,7 @@
         <v>3.1</v>
       </c>
       <c r="U143">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="V143">
         <v>1.48</v>
@@ -23648,7 +23648,7 @@
         <v>1.08</v>
       </c>
       <c r="X143">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y143">
         <v>1.18</v>
@@ -23663,13 +23663,13 @@
         <v>2.08</v>
       </c>
       <c r="AC143">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD143">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE143">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF143">
         <v>1.67</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O144">
         <v>3.5</v>
       </c>
       <c r="P144">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q144">
-        <v>2.7</v>
+        <v>3.72</v>
       </c>
       <c r="R144">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T144">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U144">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V144">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W144">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
         <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA144">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB144">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC144">
         <v>3.2</v>
       </c>
       <c r="AD144">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE144">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF144">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG144">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>1.28</v>
       </c>
       <c r="AK144">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="O145">
         <v>3.5</v>
       </c>
       <c r="P145">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q145">
-        <v>3.72</v>
+        <v>2.69</v>
       </c>
       <c r="R145">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S145">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T145">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U145">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V145">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W145">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X145">
         <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z145">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA145">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB145">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC145">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AD145">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE145">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AG145">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.28</v>
       </c>
       <c r="AK145">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O146">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="P146">
-        <v>5.75</v>
+        <v>6.95</v>
       </c>
       <c r="Q146">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R146">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="S146">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T146">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U146">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="V146">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="W146">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z146">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA146">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AB146">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AC146">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AD146">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE146">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF146">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG146">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK146">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q149">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="R149">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="S149">
         <v>1.18</v>
       </c>
       <c r="T149">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="U149">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="V149">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W149">
         <v>1.16</v>
@@ -24632,19 +24632,19 @@
         <v>1.07</v>
       </c>
       <c r="Z149">
-        <v>6.1</v>
+        <v>5.85</v>
       </c>
       <c r="AA149">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB149">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AC149">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD149">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE149">
         <v>1.28</v>
@@ -24653,7 +24653,7 @@
         <v>1.33</v>
       </c>
       <c r="AG149">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK149">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24768,10 +24768,10 @@
         <v>4.22</v>
       </c>
       <c r="Q150">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="R150">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S150">
         <v>1.38</v>
@@ -24922,10 +24922,10 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O151">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P151">
         <v>10</v>
@@ -25085,16 +25085,16 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O152">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="P152">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
       <c r="Q152">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R152">
         <v>2.13</v>
@@ -25106,7 +25106,7 @@
         <v>2.73</v>
       </c>
       <c r="U152">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="V152">
         <v>1.36</v>
@@ -25136,7 +25136,7 @@
         <v>1.24</v>
       </c>
       <c r="AE152">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF152">
         <v>1.99</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="O153">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="P153">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="Q153">
         <v>2.97</v>
@@ -25269,7 +25269,7 @@
         <v>2.85</v>
       </c>
       <c r="U153">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="V153">
         <v>1.39</v>
@@ -25287,10 +25287,10 @@
         <v>3.44</v>
       </c>
       <c r="AA153">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB153">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC153">
         <v>3.12</v>
@@ -25417,7 +25417,7 @@
         <v>3.4</v>
       </c>
       <c r="P154">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="Q154">
         <v>2.62</v>
@@ -25444,28 +25444,28 @@
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z154">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA154">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB154">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC154">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD154">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE154">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG154">
         <v>1.9</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="O155">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P155">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q155">
         <v>4.16</v>
@@ -25589,16 +25589,16 @@
         <v>2.09</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T155">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U155">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W155">
         <v>1.06</v>
@@ -25607,10 +25607,10 @@
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z155">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA155">
         <v>1.88</v>
@@ -25619,19 +25619,19 @@
         <v>1.89</v>
       </c>
       <c r="AC155">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD155">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE155">
         <v>1.08</v>
       </c>
       <c r="AF155">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG155">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25740,10 +25740,10 @@
         <v>2.37</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P156">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25951,7 +25951,7 @@
         <v>1.36</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF157">
         <v>1.65</v>
@@ -26591,19 +26591,19 @@
         <v>2.89</v>
       </c>
       <c r="AA161">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB161">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC161">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AD161">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE161">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF161">
         <v>1.8</v>
@@ -26715,10 +26715,10 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P162">
         <v>3.25</v>
@@ -27041,49 +27041,49 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O164">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P164">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q164">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R164">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S164">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T164">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U164">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V164">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W164">
         <v>1.06</v>
       </c>
       <c r="X164">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z164">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA164">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB164">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC164">
         <v>2.89</v>
@@ -27095,10 +27095,10 @@
         <v>1.09</v>
       </c>
       <c r="AF164">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG164">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK164">
         <v>1.93</v>
@@ -27213,7 +27213,7 @@
         <v>5</v>
       </c>
       <c r="Q165">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R165">
         <v>2.14</v>
@@ -27222,7 +27222,7 @@
         <v>1.38</v>
       </c>
       <c r="T165">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U165">
         <v>2.65</v>
@@ -27237,19 +27237,19 @@
         <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z165">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA165">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB165">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC165">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="AD165">
         <v>1.32</v>
@@ -27258,10 +27258,10 @@
         <v>1.09</v>
       </c>
       <c r="AF165">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG165">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>1.26</v>
       </c>
       <c r="AK165">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27370,7 +27370,7 @@
         <v>1.65</v>
       </c>
       <c r="O166">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P166">
         <v>4.98</v>
@@ -27539,7 +27539,7 @@
         <v>3.9</v>
       </c>
       <c r="Q167">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R167">
         <v>2.07</v>
@@ -27563,13 +27563,13 @@
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z167">
         <v>3.24</v>
       </c>
       <c r="AA167">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB167">
         <v>1.83</v>
@@ -27603,7 +27603,7 @@
         <v>1.28</v>
       </c>
       <c r="AK167">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27693,10 +27693,10 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O168">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P168">
         <v>2.7</v>
@@ -27735,7 +27735,7 @@
         <v>1.79</v>
       </c>
       <c r="AB168">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC168">
         <v>2.85</v>
@@ -27865,10 +27865,10 @@
         <v>2.78</v>
       </c>
       <c r="Q169">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="R169">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S169">
         <v>1.4</v>
@@ -27877,16 +27877,16 @@
         <v>2.73</v>
       </c>
       <c r="U169">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V169">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W169">
         <v>1.04</v>
       </c>
       <c r="X169">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y169">
         <v>1.27</v>
@@ -27895,7 +27895,7 @@
         <v>3.18</v>
       </c>
       <c r="AA169">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB169">
         <v>1.8</v>
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="O177">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="P177">
+        <v>2.54</v>
+      </c>
+      <c r="Q177">
         <v>2.48</v>
       </c>
-      <c r="Q177">
-        <v>2.5</v>
-      </c>
       <c r="R177">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="S177">
         <v>1.16</v>
@@ -29184,7 +29184,7 @@
         <v>1.87</v>
       </c>
       <c r="V177">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W177">
         <v>1.22</v>
@@ -29196,28 +29196,28 @@
         <v>1.04</v>
       </c>
       <c r="Z177">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="AA177">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AB177">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AC177">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD177">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE177">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF177">
         <v>1.28</v>
       </c>
       <c r="AG177">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK177">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29323,22 +29323,22 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O178">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="P178">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="Q178">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R178">
         <v>2.27</v>
       </c>
       <c r="S178">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T178">
         <v>3.44</v>
@@ -29353,7 +29353,7 @@
         <v>1.13</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y178">
         <v>1.11</v>
@@ -29362,13 +29362,13 @@
         <v>4.95</v>
       </c>
       <c r="AA178">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB178">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AC178">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD178">
         <v>1.62</v>
@@ -29377,10 +29377,10 @@
         <v>1.21</v>
       </c>
       <c r="AF178">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG178">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.26</v>
       </c>
       <c r="AK178">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,25 +29486,25 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="O179">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P179">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q179">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="R179">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S179">
         <v>1.29</v>
       </c>
       <c r="T179">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U179">
         <v>2.36</v>
@@ -29513,28 +29513,28 @@
         <v>1.51</v>
       </c>
       <c r="W179">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z179">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="AA179">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB179">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC179">
-        <v>2.23</v>
+        <v>2.52</v>
       </c>
       <c r="AD179">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE179">
         <v>1.14</v>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK179">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O180">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="P180">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q180">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R180">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="S180">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T180">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U180">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V180">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W180">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X180">
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z180">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="AA180">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AB180">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AC180">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD180">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE180">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF180">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG180">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK180">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29815,10 +29815,10 @@
         <v>1.2</v>
       </c>
       <c r="O181">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="P181">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="Q181">
         <v>1.57</v>
@@ -29857,10 +29857,10 @@
         <v>4.05</v>
       </c>
       <c r="AC181">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AD181">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AE181">
         <v>1.63</v>
@@ -29869,7 +29869,7 @@
         <v>1.47</v>
       </c>
       <c r="AG181">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK181">
-        <v>3.98</v>
+        <v>3.88</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,31 +29975,31 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="O182">
-        <v>5.55</v>
+        <v>5.2</v>
       </c>
       <c r="P182">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Q182">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R182">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="S182">
         <v>1.11</v>
       </c>
       <c r="T182">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="U182">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V182">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="W182">
         <v>1.33</v>
@@ -30011,28 +30011,28 @@
         <v>1.01</v>
       </c>
       <c r="Z182">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA182">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB182">
-        <v>3.98</v>
+        <v>4.38</v>
       </c>
       <c r="AC182">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD182">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AE182">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF182">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG182">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK182">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -32909,25 +32909,25 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O200">
         <v>3.85</v>
       </c>
       <c r="P200">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="Q200">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R200">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S200">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T200">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U200">
         <v>2.44</v>
@@ -32939,7 +32939,7 @@
         <v>1.07</v>
       </c>
       <c r="X200">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y200">
         <v>1.16</v>
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q201">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R201">
+        <v>2.25</v>
+      </c>
+      <c r="S201">
+        <v>1.3</v>
+      </c>
+      <c r="T201">
+        <v>3.3</v>
+      </c>
+      <c r="U201">
+        <v>2.35</v>
+      </c>
+      <c r="V201">
+        <v>1.53</v>
+      </c>
+      <c r="W201">
+        <v>1.13</v>
+      </c>
+      <c r="X201">
+        <v>1.02</v>
+      </c>
+      <c r="Y201">
+        <v>1.18</v>
+      </c>
+      <c r="Z201">
+        <v>4.3</v>
+      </c>
+      <c r="AA201">
+        <v>1.62</v>
+      </c>
+      <c r="AB201">
+        <v>2.15</v>
+      </c>
+      <c r="AC201">
         <v>2.45</v>
       </c>
-      <c r="S201">
-        <v>0</v>
-      </c>
-      <c r="T201">
-        <v>0</v>
-      </c>
-      <c r="U201">
-        <v>2.23</v>
-      </c>
-      <c r="V201">
-        <v>1.56</v>
-      </c>
-      <c r="W201">
-        <v>0</v>
-      </c>
-      <c r="X201">
-        <v>0</v>
-      </c>
-      <c r="Y201">
-        <v>1.14</v>
-      </c>
-      <c r="Z201">
-        <v>4.75</v>
-      </c>
-      <c r="AA201">
+      <c r="AD201">
+        <v>1.48</v>
+      </c>
+      <c r="AE201">
+        <v>1.17</v>
+      </c>
+      <c r="AF201">
         <v>1.53</v>
       </c>
-      <c r="AB201">
-        <v>2.32</v>
-      </c>
-      <c r="AC201">
-        <v>2.33</v>
-      </c>
-      <c r="AD201">
-        <v>1.5</v>
-      </c>
-      <c r="AE201">
-        <v>1.18</v>
-      </c>
-      <c r="AF201">
-        <v>1.47</v>
-      </c>
       <c r="AG201">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>1.22</v>
       </c>
       <c r="AK201">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -35517,19 +35517,19 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O216">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P216">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q216">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="R216">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S216">
         <v>1.25</v>
@@ -35538,43 +35538,43 @@
         <v>3.42</v>
       </c>
       <c r="U216">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V216">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W216">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X216">
         <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z216">
-        <v>4.97</v>
+        <v>4.5</v>
       </c>
       <c r="AA216">
+        <v>1.57</v>
+      </c>
+      <c r="AB216">
+        <v>2.27</v>
+      </c>
+      <c r="AC216">
+        <v>2.42</v>
+      </c>
+      <c r="AD216">
         <v>1.55</v>
       </c>
-      <c r="AB216">
-        <v>2.44</v>
-      </c>
-      <c r="AC216">
-        <v>2.3</v>
-      </c>
-      <c r="AD216">
-        <v>1.54</v>
-      </c>
       <c r="AE216">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF216">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG216">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK216">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O217">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P217">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35719,10 +35719,10 @@
         <v>0</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC217">
         <v>0</v>
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O218">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="P218">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="Q218">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="R218">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S218">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T218">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U218">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="V218">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W218">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X218">
         <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z218">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA218">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB218">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AC218">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AD218">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE218">
         <v>1.14</v>
       </c>
       <c r="AF218">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG218">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36667,22 +36667,22 @@
         <v>2.5</v>
       </c>
       <c r="Q223">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="R223">
         <v>2.38</v>
       </c>
       <c r="S223">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T223">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U223">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="V223">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W223">
         <v>1.14</v>
@@ -36697,25 +36697,25 @@
         <v>5.3</v>
       </c>
       <c r="AA223">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB223">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AC223">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AD223">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE223">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF223">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG223">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AK223">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36830,22 +36830,22 @@
         <v>4.8</v>
       </c>
       <c r="Q224">
+        <v>1.92</v>
+      </c>
+      <c r="R224">
+        <v>2.61</v>
+      </c>
+      <c r="S224">
+        <v>1.16</v>
+      </c>
+      <c r="T224">
+        <v>4.3</v>
+      </c>
+      <c r="U224">
         <v>1.83</v>
       </c>
-      <c r="R224">
-        <v>2.75</v>
-      </c>
-      <c r="S224">
-        <v>1.15</v>
-      </c>
-      <c r="T224">
-        <v>4.75</v>
-      </c>
-      <c r="U224">
-        <v>1.81</v>
-      </c>
       <c r="V224">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="W224">
         <v>1.25</v>
@@ -36860,16 +36860,16 @@
         <v>8</v>
       </c>
       <c r="AA224">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB224">
         <v>3.6</v>
       </c>
       <c r="AC224">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AD224">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AE224">
         <v>1.44</v>
@@ -36878,7 +36878,7 @@
         <v>1.36</v>
       </c>
       <c r="AG224">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK224">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O227">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P227">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q227">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R227">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S227">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T227">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U227">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="V227">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W227">
         <v>1.14</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z227">
         <v>4.95</v>
       </c>
       <c r="AA227">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB227">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC227">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD227">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AE227">
         <v>1.27</v>
       </c>
       <c r="AF227">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG227">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q231">
         <v>3.08</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q249">
         <v>2.63</v>
@@ -40926,7 +40926,7 @@
         <v>1.29</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y249">
         <v>1.03</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>4.26</v>
+        <v>9.5</v>
       </c>
       <c r="O263">
-        <v>3.54</v>
+        <v>5.25</v>
       </c>
       <c r="P263">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="Q263">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="R263">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="S263">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T263">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U263">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="V263">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W263">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z263">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA263">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB263">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC263">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD263">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE263">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF263">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG263">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK263">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>9.5</v>
+        <v>4.26</v>
       </c>
       <c r="O264">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="P264">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="Q264">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="R264">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="S264">
+        <v>1.41</v>
+      </c>
+      <c r="T264">
+        <v>2.69</v>
+      </c>
+      <c r="U264">
+        <v>2.88</v>
+      </c>
+      <c r="V264">
+        <v>1.36</v>
+      </c>
+      <c r="W264">
+        <v>1.04</v>
+      </c>
+      <c r="X264">
+        <v>1.02</v>
+      </c>
+      <c r="Y264">
         <v>1.28</v>
       </c>
-      <c r="T264">
-        <v>3.3</v>
-      </c>
-      <c r="U264">
-        <v>2.33</v>
-      </c>
-      <c r="V264">
-        <v>1.53</v>
-      </c>
-      <c r="W264">
-        <v>1.1</v>
-      </c>
-      <c r="X264">
-        <v>1.03</v>
-      </c>
-      <c r="Y264">
-        <v>1.15</v>
-      </c>
       <c r="Z264">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA264">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB264">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC264">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD264">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AE264">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF264">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG264">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK264">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -45786,28 +45786,28 @@
         </is>
       </c>
       <c r="N279">
-        <v>4.98</v>
+        <v>5.13</v>
       </c>
       <c r="O279">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="P279">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q279">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R279">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S279">
         <v>1.16</v>
       </c>
       <c r="T279">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U279">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V279">
         <v>1.75</v>
@@ -45816,10 +45816,10 @@
         <v>1.18</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y279">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z279">
         <v>5.8</v>
@@ -45837,13 +45837,13 @@
         <v>1.8</v>
       </c>
       <c r="AE279">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF279">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG279">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -48231,31 +48231,31 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O294">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="P294">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="Q294">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R294">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="S294">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T294">
         <v>4.85</v>
       </c>
       <c r="U294">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V294">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="W294">
         <v>1.28</v>
@@ -48273,7 +48273,7 @@
         <v>1.24</v>
       </c>
       <c r="AB294">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AC294">
         <v>1.64</v>
@@ -48883,19 +48883,19 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O298">
         <v>3.4</v>
       </c>
       <c r="P298">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q298">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="R298">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S298">
         <v>1.28</v>
@@ -48904,19 +48904,19 @@
         <v>3.3</v>
       </c>
       <c r="U298">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="V298">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W298">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X298">
         <v>1.03</v>
       </c>
       <c r="Y298">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z298">
         <v>4.1</v>
@@ -48925,16 +48925,16 @@
         <v>1.61</v>
       </c>
       <c r="AB298">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC298">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD298">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE298">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF298">
         <v>1.53</v>
@@ -48956,7 +48956,7 @@
         <v>1.26</v>
       </c>
       <c r="AK298">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49716,13 +49716,13 @@
         <v>1.32</v>
       </c>
       <c r="T303">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U303">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="V303">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W303">
         <v>1.07</v>
@@ -49734,19 +49734,19 @@
         <v>1.25</v>
       </c>
       <c r="Z303">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA303">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB303">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC303">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AD303">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE303">
         <v>1.1</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -51011,55 +51011,55 @@
         <v>0</v>
       </c>
       <c r="Q311">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R311">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S311">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T311">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U311">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V311">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W311">
         <v>1.06</v>
       </c>
       <c r="X311">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y311">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z311">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA311">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB311">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC311">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD311">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE311">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF311">
         <v>1.69</v>
       </c>
       <c r="AG311">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK311">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>3.1</v>
+        <v>2.41</v>
       </c>
       <c r="O316">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P316">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q323">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="R323">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="S323">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="T323">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="U323">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="V323">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="W323">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X323">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y323">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Z323">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA323">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB323">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AC323">
-        <v>3.28</v>
+        <v>4.25</v>
       </c>
       <c r="AD323">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AE323">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF323">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG323">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK323">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O324">
+        <v>0</v>
+      </c>
+      <c r="P324">
+        <v>0</v>
+      </c>
+      <c r="Q324">
+        <v>2.02</v>
+      </c>
+      <c r="R324">
+        <v>2.15</v>
+      </c>
+      <c r="S324">
+        <v>1.39</v>
+      </c>
+      <c r="T324">
+        <v>2.73</v>
+      </c>
+      <c r="U324">
         <v>2.85</v>
       </c>
-      <c r="P324">
-        <v>2.9</v>
-      </c>
-      <c r="Q324">
-        <v>3.05</v>
-      </c>
-      <c r="R324">
-        <v>1.88</v>
-      </c>
-      <c r="S324">
-        <v>1.53</v>
-      </c>
-      <c r="T324">
-        <v>2.4</v>
-      </c>
-      <c r="U324">
-        <v>3.6</v>
-      </c>
       <c r="V324">
+        <v>1.36</v>
+      </c>
+      <c r="W324">
+        <v>1.03</v>
+      </c>
+      <c r="X324">
+        <v>1</v>
+      </c>
+      <c r="Y324">
+        <v>1.26</v>
+      </c>
+      <c r="Z324">
+        <v>3.2</v>
+      </c>
+      <c r="AA324">
+        <v>2</v>
+      </c>
+      <c r="AB324">
+        <v>1.8</v>
+      </c>
+      <c r="AC324">
+        <v>3.28</v>
+      </c>
+      <c r="AD324">
         <v>1.25</v>
       </c>
-      <c r="W324">
-        <v>1.04</v>
-      </c>
-      <c r="X324">
-        <v>1.06</v>
-      </c>
-      <c r="Y324">
-        <v>1.48</v>
-      </c>
-      <c r="Z324">
-        <v>2.75</v>
-      </c>
-      <c r="AA324">
-        <v>2.7</v>
-      </c>
-      <c r="AB324">
-        <v>1.49</v>
-      </c>
-      <c r="AC324">
-        <v>4.25</v>
-      </c>
-      <c r="AD324">
-        <v>1.18</v>
-      </c>
       <c r="AE324">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF324">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG324">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK324">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -54262,13 +54262,13 @@
         </is>
       </c>
       <c r="N331">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O331">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P331">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q331">
         <v>0</v>
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G365">
@@ -59804,64 +59804,64 @@
         </is>
       </c>
       <c r="N365">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="O365">
-        <v>4.22</v>
+        <v>3.75</v>
       </c>
       <c r="P365">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q365">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="R365">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="S365">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T365">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="U365">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="V365">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="W365">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X365">
         <v>0</v>
       </c>
       <c r="Y365">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z365">
-        <v>5.3</v>
+        <v>6.27</v>
       </c>
       <c r="AA365">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB365">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AC365">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AD365">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE365">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF365">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG365">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH365" t="inlineStr">
         <is>
@@ -59874,10 +59874,10 @@
         </is>
       </c>
       <c r="AJ365">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK365">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AL365">
         <v>0</v>
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,80 +59967,80 @@
         </is>
       </c>
       <c r="N366">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="O366">
-        <v>3.75</v>
+        <v>4.22</v>
       </c>
       <c r="P366">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q366">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="R366">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S366">
+        <v>1.25</v>
+      </c>
+      <c r="T366">
+        <v>3.8</v>
+      </c>
+      <c r="U366">
+        <v>2.23</v>
+      </c>
+      <c r="V366">
+        <v>1.63</v>
+      </c>
+      <c r="W366">
+        <v>1.15</v>
+      </c>
+      <c r="X366">
+        <v>0</v>
+      </c>
+      <c r="Y366">
+        <v>1.13</v>
+      </c>
+      <c r="Z366">
+        <v>5.3</v>
+      </c>
+      <c r="AA366">
+        <v>1.5</v>
+      </c>
+      <c r="AB366">
+        <v>2.5</v>
+      </c>
+      <c r="AC366">
+        <v>2.25</v>
+      </c>
+      <c r="AD366">
+        <v>1.63</v>
+      </c>
+      <c r="AE366">
+        <v>1.28</v>
+      </c>
+      <c r="AF366">
+        <v>1.44</v>
+      </c>
+      <c r="AG366">
+        <v>2.63</v>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ366">
         <v>1.2</v>
       </c>
-      <c r="T366">
-        <v>4.33</v>
-      </c>
-      <c r="U366">
-        <v>2.05</v>
-      </c>
-      <c r="V366">
-        <v>1.75</v>
-      </c>
-      <c r="W366">
-        <v>1.18</v>
-      </c>
-      <c r="X366">
-        <v>0</v>
-      </c>
-      <c r="Y366">
-        <v>1.12</v>
-      </c>
-      <c r="Z366">
-        <v>6.27</v>
-      </c>
-      <c r="AA366">
-        <v>1.4</v>
-      </c>
-      <c r="AB366">
-        <v>2.9</v>
-      </c>
-      <c r="AC366">
-        <v>1.99</v>
-      </c>
-      <c r="AD366">
-        <v>1.83</v>
-      </c>
-      <c r="AE366">
-        <v>1.33</v>
-      </c>
-      <c r="AF366">
-        <v>1.38</v>
-      </c>
-      <c r="AG366">
-        <v>2.8</v>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ366">
-        <v>1.24</v>
-      </c>
       <c r="AK366">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AL366">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="Q9">
-        <v>2.45</v>
+        <v>4.68</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U9">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z9">
-        <v>2.94</v>
+        <v>3.38</v>
       </c>
       <c r="AA9">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="AD9">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
+        <v>1.8</v>
+      </c>
+      <c r="O10">
+        <v>3.25</v>
+      </c>
+      <c r="P10">
         <v>4</v>
       </c>
-      <c r="O10">
-        <v>3.55</v>
-      </c>
-      <c r="P10">
-        <v>1.82</v>
-      </c>
       <c r="Q10">
-        <v>4.68</v>
+        <v>2.45</v>
       </c>
       <c r="R10">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="S10">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.38</v>
+        <v>2.94</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="AD10">
+        <v>1.21</v>
+      </c>
+      <c r="AE10">
+        <v>1.03</v>
+      </c>
+      <c r="AF10">
+        <v>1.92</v>
+      </c>
+      <c r="AG10">
+        <v>1.79</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.28</v>
       </c>
-      <c r="AE10">
-        <v>1.07</v>
-      </c>
-      <c r="AF10">
-        <v>1.75</v>
-      </c>
-      <c r="AG10">
-        <v>1.97</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.27</v>
-      </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O43">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="R43">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
+        <v>1.43</v>
+      </c>
+      <c r="T43">
+        <v>2.62</v>
+      </c>
+      <c r="U43">
+        <v>2.99</v>
+      </c>
+      <c r="V43">
+        <v>1.34</v>
+      </c>
+      <c r="W43">
+        <v>1.03</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.36</v>
+      </c>
+      <c r="Z43">
+        <v>2.89</v>
+      </c>
+      <c r="AA43">
+        <v>2.02</v>
+      </c>
+      <c r="AB43">
+        <v>1.68</v>
+      </c>
+      <c r="AC43">
+        <v>3.65</v>
+      </c>
+      <c r="AD43">
+        <v>1.26</v>
+      </c>
+      <c r="AE43">
+        <v>1.04</v>
+      </c>
+      <c r="AF43">
+        <v>1.8</v>
+      </c>
+      <c r="AG43">
+        <v>1.9</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.31</v>
+      </c>
+      <c r="AK43">
         <v>1.47</v>
-      </c>
-      <c r="T43">
-        <v>2.5</v>
-      </c>
-      <c r="U43">
-        <v>3.15</v>
-      </c>
-      <c r="V43">
-        <v>1.31</v>
-      </c>
-      <c r="W43">
-        <v>1.02</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.34</v>
-      </c>
-      <c r="Z43">
-        <v>2.8</v>
-      </c>
-      <c r="AA43">
-        <v>2.08</v>
-      </c>
-      <c r="AB43">
-        <v>1.66</v>
-      </c>
-      <c r="AC43">
-        <v>3.55</v>
-      </c>
-      <c r="AD43">
-        <v>1.24</v>
-      </c>
-      <c r="AE43">
-        <v>1.03</v>
-      </c>
-      <c r="AF43">
-        <v>1.87</v>
-      </c>
-      <c r="AG43">
-        <v>1.83</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.29</v>
-      </c>
-      <c r="AK43">
-        <v>1.76</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q44">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="S44">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T44">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U44">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="V44">
+        <v>1.31</v>
+      </c>
+      <c r="W44">
+        <v>1.02</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
         <v>1.34</v>
       </c>
-      <c r="W44">
+      <c r="Z44">
+        <v>2.8</v>
+      </c>
+      <c r="AA44">
+        <v>2.08</v>
+      </c>
+      <c r="AB44">
+        <v>1.66</v>
+      </c>
+      <c r="AC44">
+        <v>3.55</v>
+      </c>
+      <c r="AD44">
+        <v>1.24</v>
+      </c>
+      <c r="AE44">
         <v>1.03</v>
       </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>1.36</v>
-      </c>
-      <c r="Z44">
-        <v>2.89</v>
-      </c>
-      <c r="AA44">
-        <v>2.02</v>
-      </c>
-      <c r="AB44">
-        <v>1.68</v>
-      </c>
-      <c r="AC44">
-        <v>3.65</v>
-      </c>
-      <c r="AD44">
-        <v>1.26</v>
-      </c>
-      <c r="AE44">
-        <v>1.04</v>
-      </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="O121">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="P121">
-        <v>5.25</v>
+        <v>14</v>
       </c>
       <c r="Q121">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T121">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="U121">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="V121">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="W121">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z121">
-        <v>3.74</v>
+        <v>6.45</v>
       </c>
       <c r="AA121">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AB121">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="AC121">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD121">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="AE121">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AF121">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG121">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK121">
-        <v>2.41</v>
+        <v>5.3</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="O123">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="P123">
-        <v>14</v>
+        <v>5.25</v>
       </c>
       <c r="Q123">
+        <v>2.05</v>
+      </c>
+      <c r="R123">
+        <v>2.3</v>
+      </c>
+      <c r="S123">
+        <v>1.36</v>
+      </c>
+      <c r="T123">
+        <v>3.12</v>
+      </c>
+      <c r="U123">
+        <v>2.63</v>
+      </c>
+      <c r="V123">
         <v>1.48</v>
       </c>
-      <c r="R123">
-        <v>3.2</v>
-      </c>
-      <c r="S123">
-        <v>1.18</v>
-      </c>
-      <c r="T123">
-        <v>4.6</v>
-      </c>
-      <c r="U123">
-        <v>2</v>
-      </c>
-      <c r="V123">
-        <v>1.84</v>
-      </c>
       <c r="W123">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z123">
-        <v>6.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA123">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AB123">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC123">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AD123">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="AE123">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AF123">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG123">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK123">
-        <v>5.3</v>
+        <v>2.41</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O131">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P131">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
       </c>
       <c r="R131">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S131">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T131">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="U131">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="V131">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W131">
         <v>1.02</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
         <v>1.33</v>
       </c>
       <c r="Z131">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AA131">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB131">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC131">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="AD131">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE131">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF131">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG131">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>1.28</v>
       </c>
       <c r="AK131">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O132">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P132">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q132">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R132">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S132">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T132">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U132">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V132">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W132">
         <v>1.02</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z132">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA132">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AB132">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC132">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="AD132">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE132">
         <v>1.03</v>
       </c>
       <c r="AF132">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG132">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.28</v>
       </c>
       <c r="AK132">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,31 +21988,31 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O133">
         <v>3.2</v>
       </c>
       <c r="P133">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q133">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R133">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S133">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T133">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="U133">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V133">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W133">
         <v>1.02</v>
@@ -22021,31 +22021,31 @@
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z133">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA133">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB133">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC133">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="AD133">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE133">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF133">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG133">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.28</v>
       </c>
       <c r="AK133">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,25 +27041,25 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O164">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P164">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="Q164">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R164">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S164">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T164">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U164">
         <v>2.65</v>
@@ -27074,19 +27074,19 @@
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z164">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA164">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB164">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC164">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AD164">
         <v>1.32</v>
@@ -27095,10 +27095,10 @@
         <v>1.09</v>
       </c>
       <c r="AF164">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG164">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK164">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O165">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P165">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="Q165">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R165">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S165">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T165">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U165">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V165">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X165">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y165">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z165">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA165">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AB165">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC165">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD165">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE165">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF165">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG165">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK165">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O166">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P166">
-        <v>4.98</v>
+        <v>3.9</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA166">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AB166">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O167">
         <v>3.5</v>
       </c>
       <c r="P167">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q167">
-        <v>2.51</v>
+        <v>3.13</v>
       </c>
       <c r="R167">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S167">
         <v>1.4</v>
@@ -27551,10 +27551,10 @@
         <v>2.73</v>
       </c>
       <c r="U167">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="V167">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W167">
         <v>1.04</v>
@@ -27563,31 +27563,31 @@
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z167">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA167">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AB167">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC167">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD167">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF167">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG167">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK167">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,58 +27856,58 @@
         </is>
       </c>
       <c r="N169">
+        <v>1.85</v>
+      </c>
+      <c r="O169">
+        <v>3.4</v>
+      </c>
+      <c r="P169">
+        <v>3.85</v>
+      </c>
+      <c r="Q169">
         <v>2.4</v>
       </c>
-      <c r="O169">
-        <v>3.5</v>
-      </c>
-      <c r="P169">
-        <v>2.78</v>
-      </c>
-      <c r="Q169">
-        <v>3.13</v>
-      </c>
       <c r="R169">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S169">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T169">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U169">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="V169">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W169">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X169">
         <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z169">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA169">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB169">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC169">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AD169">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE169">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF169">
         <v>1.73</v>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK169">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,64 +43178,64 @@
         </is>
       </c>
       <c r="N263">
-        <v>9.5</v>
+        <v>4.26</v>
       </c>
       <c r="O263">
-        <v>5.25</v>
+        <v>3.54</v>
       </c>
       <c r="P263">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="Q263">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="R263">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="S263">
+        <v>1.41</v>
+      </c>
+      <c r="T263">
+        <v>2.69</v>
+      </c>
+      <c r="U263">
+        <v>2.88</v>
+      </c>
+      <c r="V263">
+        <v>1.36</v>
+      </c>
+      <c r="W263">
+        <v>1.04</v>
+      </c>
+      <c r="X263">
+        <v>1.02</v>
+      </c>
+      <c r="Y263">
         <v>1.28</v>
       </c>
-      <c r="T263">
-        <v>3.3</v>
-      </c>
-      <c r="U263">
-        <v>2.33</v>
-      </c>
-      <c r="V263">
-        <v>1.53</v>
-      </c>
-      <c r="W263">
-        <v>1.1</v>
-      </c>
-      <c r="X263">
-        <v>1.03</v>
-      </c>
-      <c r="Y263">
-        <v>1.15</v>
-      </c>
       <c r="Z263">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA263">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB263">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC263">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="AD263">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
       <c r="AE263">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF263">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG263">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK263">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>4.26</v>
+        <v>9.5</v>
       </c>
       <c r="O264">
-        <v>3.54</v>
+        <v>5.25</v>
       </c>
       <c r="P264">
-        <v>1.86</v>
+        <v>1.29</v>
       </c>
       <c r="Q264">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="R264">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="S264">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T264">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U264">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="V264">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W264">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X264">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z264">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA264">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB264">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC264">
-        <v>3.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD264">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AE264">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF264">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG264">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK264">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O283">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P283">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q283">
         <v>3.7</v>
@@ -46453,34 +46453,34 @@
         <v>1.85</v>
       </c>
       <c r="S283">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="T283">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U283">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="V283">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W283">
         <v>1.03</v>
       </c>
       <c r="X283">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y283">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z283">
         <v>2.2</v>
       </c>
       <c r="AA283">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AB283">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC283">
         <v>6</v>
@@ -46492,7 +46492,7 @@
         <v>1.03</v>
       </c>
       <c r="AF283">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG283">
         <v>1.62</v>
@@ -46511,7 +46511,7 @@
         <v>1.44</v>
       </c>
       <c r="AK283">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,28 +46601,28 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O284">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P284">
-        <v>3.89</v>
+        <v>3.25</v>
       </c>
       <c r="Q284">
-        <v>3.53</v>
+        <v>3</v>
       </c>
       <c r="R284">
         <v>1.8</v>
       </c>
       <c r="S284">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="T284">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="U284">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="V284">
         <v>1.15</v>
@@ -46631,25 +46631,25 @@
         <v>1.03</v>
       </c>
       <c r="X284">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Y284">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Z284">
         <v>2</v>
       </c>
       <c r="AA284">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AB284">
         <v>1.33</v>
       </c>
       <c r="AC284">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD284">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE284">
         <v>1.02</v>
@@ -49046,25 +49046,25 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O299">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P299">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q299">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="R299">
         <v>1.85</v>
       </c>
       <c r="S299">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T299">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U299">
         <v>4</v>
@@ -49073,10 +49073,10 @@
         <v>1.17</v>
       </c>
       <c r="W299">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X299">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y299">
         <v>1.67</v>
@@ -49088,7 +49088,7 @@
         <v>3</v>
       </c>
       <c r="AB299">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC299">
         <v>6.5</v>
@@ -49097,7 +49097,7 @@
         <v>1.1</v>
       </c>
       <c r="AE299">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF299">
         <v>2.38</v>
@@ -49116,7 +49116,7 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK299">
         <v>1.53</v>
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O313">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P313">
-        <v>4.41</v>
+        <v>3.8</v>
       </c>
       <c r="Q313">
         <v>2.75</v>
       </c>
       <c r="R313">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S313">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="T313">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="U313">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V313">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W313">
         <v>1.03</v>
       </c>
       <c r="X313">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y313">
         <v>1.67</v>
       </c>
       <c r="Z313">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AA313">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AB313">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC313">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="AD313">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE313">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF313">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG313">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O323">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P323">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q323">
-        <v>3.16</v>
+        <v>2.02</v>
       </c>
       <c r="R323">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="S323">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="T323">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="U323">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="V323">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W323">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X323">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y323">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="Z323">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA323">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB323">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC323">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD323">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE323">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF323">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG323">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK323">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,80 +53121,80 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q324">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="R324">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="S324">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="T324">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="U324">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="V324">
+        <v>1.27</v>
+      </c>
+      <c r="W324">
+        <v>1.01</v>
+      </c>
+      <c r="X324">
+        <v>1.06</v>
+      </c>
+      <c r="Y324">
+        <v>1.46</v>
+      </c>
+      <c r="Z324">
+        <v>2.75</v>
+      </c>
+      <c r="AA324">
+        <v>2.3</v>
+      </c>
+      <c r="AB324">
+        <v>1.53</v>
+      </c>
+      <c r="AC324">
+        <v>4.25</v>
+      </c>
+      <c r="AD324">
+        <v>1.15</v>
+      </c>
+      <c r="AE324">
+        <v>1.01</v>
+      </c>
+      <c r="AF324">
+        <v>1.98</v>
+      </c>
+      <c r="AG324">
+        <v>1.74</v>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ324">
         <v>1.36</v>
       </c>
-      <c r="W324">
-        <v>1.03</v>
-      </c>
-      <c r="X324">
-        <v>1</v>
-      </c>
-      <c r="Y324">
-        <v>1.26</v>
-      </c>
-      <c r="Z324">
-        <v>3.2</v>
-      </c>
-      <c r="AA324">
-        <v>2</v>
-      </c>
-      <c r="AB324">
-        <v>1.8</v>
-      </c>
-      <c r="AC324">
-        <v>3.28</v>
-      </c>
-      <c r="AD324">
-        <v>1.25</v>
-      </c>
-      <c r="AE324">
-        <v>1.05</v>
-      </c>
-      <c r="AF324">
-        <v>2.1</v>
-      </c>
-      <c r="AG324">
-        <v>1.66</v>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ324">
-        <v>1.21</v>
-      </c>
       <c r="AK324">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53936,34 +53936,34 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="O329">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P329">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q329">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="R329">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S329">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T329">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U329">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="V329">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W329">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X329">
         <v>1.07</v>
@@ -53975,25 +53975,25 @@
         <v>2.35</v>
       </c>
       <c r="AA329">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AB329">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC329">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="AD329">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE329">
         <v>1.03</v>
       </c>
       <c r="AF329">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG329">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK329">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54751,61 +54751,61 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O334">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P334">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q334">
+        <v>2.87</v>
+      </c>
+      <c r="R334">
+        <v>1.96</v>
+      </c>
+      <c r="S334">
+        <v>1.42</v>
+      </c>
+      <c r="T334">
+        <v>2.54</v>
+      </c>
+      <c r="U334">
+        <v>2.99</v>
+      </c>
+      <c r="V334">
+        <v>1.33</v>
+      </c>
+      <c r="W334">
+        <v>1.05</v>
+      </c>
+      <c r="X334">
+        <v>1.03</v>
+      </c>
+      <c r="Y334">
+        <v>1.32</v>
+      </c>
+      <c r="Z334">
         <v>2.88</v>
       </c>
-      <c r="R334">
-        <v>2</v>
-      </c>
-      <c r="S334">
-        <v>1.44</v>
-      </c>
-      <c r="T334">
-        <v>2.62</v>
-      </c>
-      <c r="U334">
-        <v>3.05</v>
-      </c>
-      <c r="V334">
-        <v>1.32</v>
-      </c>
-      <c r="W334">
-        <v>1.02</v>
-      </c>
-      <c r="X334">
-        <v>1.04</v>
-      </c>
-      <c r="Y334">
-        <v>1.36</v>
-      </c>
-      <c r="Z334">
-        <v>3.11</v>
-      </c>
       <c r="AA334">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB334">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC334">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD334">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE334">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF334">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AG334">
         <v>1.86</v>
@@ -54824,7 +54824,7 @@
         <v>1.32</v>
       </c>
       <c r="AK334">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL334">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -644,7 +644,7 @@
         <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>3.4</v>
+        <v>3.89</v>
       </c>
       <c r="R2">
         <v>2.13</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>2.67</v>
@@ -855,7 +855,7 @@
         <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>3.4</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.34</v>
@@ -982,13 +982,13 @@
         <v>2.83</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V4">
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1003,7 +1003,7 @@
         <v>1.81</v>
       </c>
       <c r="AB4">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
         <v>2.92</v>
@@ -1012,7 +1012,7 @@
         <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
         <v>1.65</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.8</v>
+      </c>
+      <c r="O9">
+        <v>3.25</v>
+      </c>
+      <c r="P9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>3.55</v>
-      </c>
-      <c r="P9">
-        <v>1.82</v>
-      </c>
       <c r="Q9">
-        <v>4.68</v>
+        <v>2.45</v>
       </c>
       <c r="R9">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.38</v>
+        <v>2.94</v>
       </c>
       <c r="AA9">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB9">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="AD9">
+        <v>1.21</v>
+      </c>
+      <c r="AE9">
+        <v>1.03</v>
+      </c>
+      <c r="AF9">
+        <v>1.92</v>
+      </c>
+      <c r="AG9">
+        <v>1.79</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.28</v>
       </c>
-      <c r="AE9">
-        <v>1.07</v>
-      </c>
-      <c r="AF9">
-        <v>1.75</v>
-      </c>
-      <c r="AG9">
-        <v>1.97</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.27</v>
-      </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="Q10">
-        <v>2.45</v>
+        <v>4.68</v>
       </c>
       <c r="R10">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U10">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>2.94</v>
+        <v>3.38</v>
       </c>
       <c r="AA10">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3.84</v>
+        <v>3.08</v>
       </c>
       <c r="AD10">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK10">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="R51">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="U51">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>4.4</v>
+        <v>5.85</v>
       </c>
       <c r="AA51">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AB51">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="AC51">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="AD51">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AE51">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AG51">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>2.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
+        <v>3.36</v>
+      </c>
+      <c r="U52">
+        <v>2.27</v>
+      </c>
+      <c r="V52">
+        <v>1.58</v>
+      </c>
+      <c r="W52">
+        <v>1.12</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.14</v>
+      </c>
+      <c r="Z52">
+        <v>4.4</v>
+      </c>
+      <c r="AA52">
+        <v>1.6</v>
+      </c>
+      <c r="AB52">
+        <v>2.36</v>
+      </c>
+      <c r="AC52">
+        <v>2.42</v>
+      </c>
+      <c r="AD52">
+        <v>1.53</v>
+      </c>
+      <c r="AE52">
+        <v>1.17</v>
+      </c>
+      <c r="AF52">
+        <v>1.71</v>
+      </c>
+      <c r="AG52">
+        <v>2.02</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.19</v>
       </c>
-      <c r="T52">
-        <v>3.85</v>
-      </c>
-      <c r="U52">
-        <v>2.05</v>
-      </c>
-      <c r="V52">
-        <v>1.71</v>
-      </c>
-      <c r="W52">
-        <v>1.15</v>
-      </c>
-      <c r="X52">
-        <v>1.02</v>
-      </c>
-      <c r="Y52">
-        <v>1.07</v>
-      </c>
-      <c r="Z52">
-        <v>5.85</v>
-      </c>
-      <c r="AA52">
-        <v>1.37</v>
-      </c>
-      <c r="AB52">
-        <v>2.66</v>
-      </c>
-      <c r="AC52">
-        <v>2.08</v>
-      </c>
-      <c r="AD52">
-        <v>1.77</v>
-      </c>
-      <c r="AE52">
-        <v>1.26</v>
-      </c>
-      <c r="AF52">
-        <v>1.36</v>
-      </c>
-      <c r="AG52">
-        <v>2.88</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.26</v>
-      </c>
       <c r="AK52">
-        <v>1.63</v>
+        <v>2.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="P71">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="O82">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="Q82">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S82">
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U82">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="V82">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z82">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA82">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB82">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC82">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD82">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE82">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF82">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q83">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="R83">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
         <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U83">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA83">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB83">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD83">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE83">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG83">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="O121">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="P121">
-        <v>14</v>
+        <v>5.25</v>
       </c>
       <c r="Q121">
+        <v>2.05</v>
+      </c>
+      <c r="R121">
+        <v>2.3</v>
+      </c>
+      <c r="S121">
+        <v>1.36</v>
+      </c>
+      <c r="T121">
+        <v>3.12</v>
+      </c>
+      <c r="U121">
+        <v>2.63</v>
+      </c>
+      <c r="V121">
         <v>1.48</v>
       </c>
-      <c r="R121">
-        <v>3.2</v>
-      </c>
-      <c r="S121">
-        <v>1.18</v>
-      </c>
-      <c r="T121">
-        <v>4.6</v>
-      </c>
-      <c r="U121">
-        <v>2</v>
-      </c>
-      <c r="V121">
-        <v>1.84</v>
-      </c>
       <c r="W121">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="X121">
         <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z121">
-        <v>6.45</v>
+        <v>3.74</v>
       </c>
       <c r="AA121">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC121">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AD121">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="AE121">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AF121">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG121">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AK121">
-        <v>5.3</v>
+        <v>2.41</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="O123">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="P123">
-        <v>5.25</v>
+        <v>14</v>
       </c>
       <c r="Q123">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="R123">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="S123">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T123">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="U123">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="V123">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="W123">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z123">
-        <v>3.74</v>
+        <v>6.45</v>
       </c>
       <c r="AA123">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AB123">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="AC123">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD123">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="AE123">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AF123">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AG123">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AK123">
-        <v>2.41</v>
+        <v>5.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O167">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P167">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q167">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="R167">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S167">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T167">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U167">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V167">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W167">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X167">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z167">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="AA167">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AB167">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AC167">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AD167">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE167">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF167">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AG167">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK167">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O168">
+        <v>3.5</v>
+      </c>
+      <c r="P168">
+        <v>2.78</v>
+      </c>
+      <c r="Q168">
+        <v>3.13</v>
+      </c>
+      <c r="R168">
+        <v>2.1</v>
+      </c>
+      <c r="S168">
+        <v>1.4</v>
+      </c>
+      <c r="T168">
+        <v>2.73</v>
+      </c>
+      <c r="U168">
+        <v>2.71</v>
+      </c>
+      <c r="V168">
+        <v>1.39</v>
+      </c>
+      <c r="W168">
+        <v>1.04</v>
+      </c>
+      <c r="X168">
+        <v>1.01</v>
+      </c>
+      <c r="Y168">
+        <v>1.27</v>
+      </c>
+      <c r="Z168">
+        <v>3.18</v>
+      </c>
+      <c r="AA168">
+        <v>2</v>
+      </c>
+      <c r="AB168">
+        <v>1.8</v>
+      </c>
+      <c r="AC168">
         <v>3.3</v>
       </c>
-      <c r="P168">
-        <v>2.7</v>
-      </c>
-      <c r="Q168">
-        <v>3.04</v>
-      </c>
-      <c r="R168">
-        <v>2.14</v>
-      </c>
-      <c r="S168">
-        <v>1.33</v>
-      </c>
-      <c r="T168">
-        <v>3.04</v>
-      </c>
-      <c r="U168">
-        <v>2.62</v>
-      </c>
-      <c r="V168">
-        <v>1.43</v>
-      </c>
-      <c r="W168">
+      <c r="AD168">
+        <v>1.25</v>
+      </c>
+      <c r="AE168">
         <v>1.05</v>
       </c>
-      <c r="X168">
-        <v>1.02</v>
-      </c>
-      <c r="Y168">
-        <v>1.2</v>
-      </c>
-      <c r="Z168">
-        <v>3.74</v>
-      </c>
-      <c r="AA168">
-        <v>1.79</v>
-      </c>
-      <c r="AB168">
-        <v>1.99</v>
-      </c>
-      <c r="AC168">
-        <v>2.85</v>
-      </c>
-      <c r="AD168">
-        <v>1.33</v>
-      </c>
-      <c r="AE168">
-        <v>1.08</v>
-      </c>
       <c r="AF168">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AG168">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK168">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -35043,10 +35043,10 @@
         <v>2.16</v>
       </c>
       <c r="S213">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T213">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U213">
         <v>2.48</v>
@@ -35067,10 +35067,10 @@
         <v>3.86</v>
       </c>
       <c r="AA213">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB213">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC213">
         <v>2.66</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK213">
         <v>1.39</v>
@@ -39287,7 +39287,7 @@
         <v>2.95</v>
       </c>
       <c r="U239">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V239">
         <v>1.44</v>
@@ -39311,7 +39311,7 @@
         <v>2</v>
       </c>
       <c r="AC239">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD239">
         <v>1.33</v>
@@ -39320,10 +39320,10 @@
         <v>1.1</v>
       </c>
       <c r="AF239">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG239">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O283">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P283">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q283">
         <v>3.7</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O284">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P284">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q284">
         <v>3</v>
@@ -46640,7 +46640,7 @@
         <v>2</v>
       </c>
       <c r="AA284">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB284">
         <v>1.33</v>
@@ -48394,64 +48394,64 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="O295">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P295">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="Q295">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R295">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S295">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T295">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U295">
         <v>2.56</v>
       </c>
       <c r="V295">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W295">
         <v>1.08</v>
       </c>
       <c r="X295">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y295">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z295">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA295">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB295">
         <v>1.85</v>
       </c>
       <c r="AC295">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD295">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE295">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF295">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG295">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK295">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -49067,7 +49067,7 @@
         <v>2.11</v>
       </c>
       <c r="U299">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V299">
         <v>1.17</v>
@@ -51331,10 +51331,10 @@
         <v>2.05</v>
       </c>
       <c r="O313">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P313">
-        <v>3.8</v>
+        <v>4.41</v>
       </c>
       <c r="Q313">
         <v>2.75</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,80 +52958,80 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q323">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="R323">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="S323">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="T323">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="U323">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="V323">
+        <v>1.27</v>
+      </c>
+      <c r="W323">
+        <v>1.01</v>
+      </c>
+      <c r="X323">
+        <v>1.06</v>
+      </c>
+      <c r="Y323">
+        <v>1.46</v>
+      </c>
+      <c r="Z323">
+        <v>2.75</v>
+      </c>
+      <c r="AA323">
+        <v>2.3</v>
+      </c>
+      <c r="AB323">
+        <v>1.53</v>
+      </c>
+      <c r="AC323">
+        <v>4.25</v>
+      </c>
+      <c r="AD323">
+        <v>1.15</v>
+      </c>
+      <c r="AE323">
+        <v>1.01</v>
+      </c>
+      <c r="AF323">
+        <v>1.98</v>
+      </c>
+      <c r="AG323">
+        <v>1.74</v>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ323">
         <v>1.36</v>
       </c>
-      <c r="W323">
-        <v>1.03</v>
-      </c>
-      <c r="X323">
-        <v>1</v>
-      </c>
-      <c r="Y323">
-        <v>1.26</v>
-      </c>
-      <c r="Z323">
-        <v>3.2</v>
-      </c>
-      <c r="AA323">
-        <v>1.96</v>
-      </c>
-      <c r="AB323">
-        <v>1.8</v>
-      </c>
-      <c r="AC323">
-        <v>3.28</v>
-      </c>
-      <c r="AD323">
-        <v>1.25</v>
-      </c>
-      <c r="AE323">
-        <v>1.05</v>
-      </c>
-      <c r="AF323">
-        <v>2.1</v>
-      </c>
-      <c r="AG323">
-        <v>1.66</v>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ323">
-        <v>1.21</v>
-      </c>
       <c r="AK323">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O324">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P324">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q324">
-        <v>3.16</v>
+        <v>2.02</v>
       </c>
       <c r="R324">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="S324">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="T324">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="U324">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="V324">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W324">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X324">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y324">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="Z324">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA324">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB324">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC324">
-        <v>4.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD324">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE324">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF324">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG324">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK324">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53619,7 +53619,7 @@
         <v>4</v>
       </c>
       <c r="Q327">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R327">
         <v>1.8</v>
@@ -53640,7 +53640,7 @@
         <v>1.01</v>
       </c>
       <c r="X327">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y327">
         <v>1.59</v>
@@ -53655,7 +53655,7 @@
         <v>1.4</v>
       </c>
       <c r="AC327">
-        <v>5.6</v>
+        <v>5.89</v>
       </c>
       <c r="AD327">
         <v>1.08</v>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK327">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -54588,7 +54588,7 @@
         </is>
       </c>
       <c r="N333">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O333">
         <v>3.25</v>
@@ -54597,55 +54597,55 @@
         <v>2.25</v>
       </c>
       <c r="Q333">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R333">
         <v>2.2</v>
       </c>
       <c r="S333">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T333">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U333">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V333">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W333">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X333">
         <v>1.03</v>
       </c>
       <c r="Y333">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z333">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="AA333">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB333">
         <v>2</v>
       </c>
       <c r="AC333">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD333">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE333">
         <v>1.11</v>
       </c>
       <c r="AF333">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG333">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AK333">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -54953,13 +54953,13 @@
         <v>4.1</v>
       </c>
       <c r="AA335">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB335">
         <v>2.14</v>
       </c>
       <c r="AC335">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AD335">
         <v>1.43</v>
@@ -54968,10 +54968,10 @@
         <v>1.14</v>
       </c>
       <c r="AF335">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG335">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G357">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G360">

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK17">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>3.5</v>
+      </c>
+      <c r="O18">
         <v>3.4</v>
       </c>
-      <c r="O18">
-        <v>3.2</v>
-      </c>
       <c r="P18">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R18">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W18">
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC18">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>3.45</v>
+        <v>2.71</v>
       </c>
       <c r="R65">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="V65">
+        <v>1.67</v>
+      </c>
+      <c r="W65">
+        <v>1.15</v>
+      </c>
+      <c r="X65">
+        <v>1.02</v>
+      </c>
+      <c r="Y65">
+        <v>1.09</v>
+      </c>
+      <c r="Z65">
+        <v>5.3</v>
+      </c>
+      <c r="AA65">
+        <v>1.39</v>
+      </c>
+      <c r="AB65">
+        <v>2.59</v>
+      </c>
+      <c r="AC65">
+        <v>2.1</v>
+      </c>
+      <c r="AD65">
+        <v>1.68</v>
+      </c>
+      <c r="AE65">
+        <v>1.25</v>
+      </c>
+      <c r="AF65">
+        <v>1.38</v>
+      </c>
+      <c r="AG65">
+        <v>2.77</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.19</v>
+      </c>
+      <c r="AK65">
         <v>1.5</v>
-      </c>
-      <c r="W65">
-        <v>1.09</v>
-      </c>
-      <c r="X65">
-        <v>1.01</v>
-      </c>
-      <c r="Y65">
-        <v>1.2</v>
-      </c>
-      <c r="Z65">
-        <v>4.3</v>
-      </c>
-      <c r="AA65">
-        <v>1.56</v>
-      </c>
-      <c r="AB65">
-        <v>2.19</v>
-      </c>
-      <c r="AC65">
-        <v>2.43</v>
-      </c>
-      <c r="AD65">
-        <v>1.44</v>
-      </c>
-      <c r="AE65">
-        <v>1.14</v>
-      </c>
-      <c r="AF65">
-        <v>1.5</v>
-      </c>
-      <c r="AG65">
-        <v>2.38</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.22</v>
-      </c>
-      <c r="AK65">
-        <v>1.34</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P66">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q66">
-        <v>2.71</v>
+        <v>3.45</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S66">
+        <v>1.27</v>
+      </c>
+      <c r="T66">
+        <v>3.25</v>
+      </c>
+      <c r="U66">
+        <v>2.33</v>
+      </c>
+      <c r="V66">
+        <v>1.5</v>
+      </c>
+      <c r="W66">
+        <v>1.09</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
         <v>1.2</v>
       </c>
-      <c r="T66">
-        <v>3.7</v>
-      </c>
-      <c r="U66">
-        <v>2.07</v>
-      </c>
-      <c r="V66">
-        <v>1.67</v>
-      </c>
-      <c r="W66">
-        <v>1.15</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.09</v>
-      </c>
       <c r="Z66">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA66">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AB66">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AC66">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD66">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q82">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T82">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U82">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V82">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z82">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA82">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB82">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC82">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD82">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE82">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
+        <v>1.83</v>
+      </c>
+      <c r="O83">
+        <v>3.4</v>
+      </c>
+      <c r="P83">
+        <v>3.6</v>
+      </c>
+      <c r="Q83">
+        <v>2.4</v>
+      </c>
+      <c r="R83">
+        <v>2.1</v>
+      </c>
+      <c r="S83">
+        <v>1.36</v>
+      </c>
+      <c r="T83">
+        <v>2.77</v>
+      </c>
+      <c r="U83">
+        <v>2.75</v>
+      </c>
+      <c r="V83">
+        <v>1.39</v>
+      </c>
+      <c r="W83">
+        <v>1.06</v>
+      </c>
+      <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
+        <v>1.25</v>
+      </c>
+      <c r="Z83">
+        <v>3.28</v>
+      </c>
+      <c r="AA83">
+        <v>1.95</v>
+      </c>
+      <c r="AB83">
+        <v>1.85</v>
+      </c>
+      <c r="AC83">
+        <v>3.04</v>
+      </c>
+      <c r="AD83">
+        <v>1.29</v>
+      </c>
+      <c r="AE83">
+        <v>1.08</v>
+      </c>
+      <c r="AF83">
+        <v>1.7</v>
+      </c>
+      <c r="AG83">
         <v>1.97</v>
       </c>
-      <c r="O83">
-        <v>3.25</v>
-      </c>
-      <c r="P83">
-        <v>3.25</v>
-      </c>
-      <c r="Q83">
-        <v>2.64</v>
-      </c>
-      <c r="R83">
-        <v>2.19</v>
-      </c>
-      <c r="S83">
-        <v>1.38</v>
-      </c>
-      <c r="T83">
-        <v>2.78</v>
-      </c>
-      <c r="U83">
-        <v>2.82</v>
-      </c>
-      <c r="V83">
-        <v>1.35</v>
-      </c>
-      <c r="W83">
-        <v>1.04</v>
-      </c>
-      <c r="X83">
-        <v>1</v>
-      </c>
-      <c r="Y83">
-        <v>1.27</v>
-      </c>
-      <c r="Z83">
-        <v>3.14</v>
-      </c>
-      <c r="AA83">
-        <v>1.94</v>
-      </c>
-      <c r="AB83">
-        <v>1.77</v>
-      </c>
-      <c r="AC83">
-        <v>3.34</v>
-      </c>
-      <c r="AD83">
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.24</v>
       </c>
-      <c r="AE83">
-        <v>1.1</v>
-      </c>
-      <c r="AF83">
-        <v>1.76</v>
-      </c>
-      <c r="AG83">
-        <v>1.94</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.3</v>
-      </c>
       <c r="AK83">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="O120">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="P120">
-        <v>2.8</v>
+        <v>12.5</v>
       </c>
       <c r="Q120">
-        <v>3.08</v>
+        <v>1.48</v>
       </c>
       <c r="R120">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T120">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="U120">
-        <v>2.88</v>
+        <v>1.89</v>
       </c>
       <c r="V120">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X120">
+        <v>1.01</v>
+      </c>
+      <c r="Y120">
         <v>1.05</v>
       </c>
-      <c r="Y120">
-        <v>1.26</v>
-      </c>
       <c r="Z120">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA120">
-        <v>2.01</v>
+        <v>1.32</v>
       </c>
       <c r="AB120">
+        <v>3.04</v>
+      </c>
+      <c r="AC120">
+        <v>1.91</v>
+      </c>
+      <c r="AD120">
         <v>1.97</v>
       </c>
-      <c r="AC120">
-        <v>3.14</v>
-      </c>
-      <c r="AD120">
-        <v>1.3</v>
-      </c>
       <c r="AE120">
+        <v>1.37</v>
+      </c>
+      <c r="AF120">
+        <v>1.87</v>
+      </c>
+      <c r="AG120">
+        <v>1.85</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
         <v>1.1</v>
       </c>
-      <c r="AF120">
-        <v>1.68</v>
-      </c>
-      <c r="AG120">
-        <v>2</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.34</v>
-      </c>
       <c r="AK120">
-        <v>1.57</v>
+        <v>5.35</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,61 +20032,61 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="O121">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P121">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q121">
-        <v>2.05</v>
+        <v>3.08</v>
       </c>
       <c r="R121">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="S121">
+        <v>1.36</v>
+      </c>
+      <c r="T121">
+        <v>2.75</v>
+      </c>
+      <c r="U121">
+        <v>2.88</v>
+      </c>
+      <c r="V121">
         <v>1.38</v>
       </c>
-      <c r="T121">
-        <v>3.02</v>
-      </c>
-      <c r="U121">
-        <v>2.7</v>
-      </c>
-      <c r="V121">
-        <v>1.46</v>
-      </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y121">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z121">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AA121">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AB121">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AC121">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AD121">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE121">
         <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AG121">
         <v>2</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK121">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="O123">
-        <v>7.4</v>
+        <v>3.78</v>
       </c>
       <c r="P123">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q123">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="R123">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="S123">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="T123">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="U123">
+        <v>2.7</v>
+      </c>
+      <c r="V123">
+        <v>1.46</v>
+      </c>
+      <c r="W123">
+        <v>1.08</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>1.24</v>
+      </c>
+      <c r="Z123">
+        <v>3.56</v>
+      </c>
+      <c r="AA123">
         <v>1.89</v>
       </c>
-      <c r="V123">
-        <v>1.78</v>
-      </c>
-      <c r="W123">
-        <v>1.22</v>
-      </c>
-      <c r="X123">
-        <v>1.01</v>
-      </c>
-      <c r="Y123">
-        <v>1.05</v>
-      </c>
-      <c r="Z123">
-        <v>6.5</v>
-      </c>
-      <c r="AA123">
-        <v>1.32</v>
-      </c>
       <c r="AB123">
-        <v>3.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC123">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AD123">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AE123">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF123">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG123">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AK123">
-        <v>5.35</v>
+        <v>2.35</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,31 +21662,31 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O131">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P131">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q131">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R131">
         <v>1.97</v>
       </c>
       <c r="S131">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U131">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V131">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W131">
         <v>1.02</v>
@@ -21695,31 +21695,31 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z131">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA131">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB131">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC131">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD131">
         <v>1.22</v>
       </c>
       <c r="AE131">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF131">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK131">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,31 +21988,31 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O133">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P133">
-        <v>2.75</v>
+        <v>3.26</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R133">
         <v>1.97</v>
       </c>
       <c r="S133">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T133">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U133">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V133">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W133">
         <v>1.02</v>
@@ -22021,31 +22021,31 @@
         <v>1.01</v>
       </c>
       <c r="Y133">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z133">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA133">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB133">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC133">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD133">
         <v>1.22</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG133">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK133">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,80 +22803,80 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="O138">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P138">
+        <v>3.95</v>
+      </c>
+      <c r="Q138">
+        <v>2.22</v>
+      </c>
+      <c r="R138">
+        <v>2.33</v>
+      </c>
+      <c r="S138">
+        <v>1.28</v>
+      </c>
+      <c r="T138">
+        <v>3.28</v>
+      </c>
+      <c r="U138">
+        <v>2.31</v>
+      </c>
+      <c r="V138">
+        <v>1.53</v>
+      </c>
+      <c r="W138">
+        <v>1.1</v>
+      </c>
+      <c r="X138">
+        <v>1.01</v>
+      </c>
+      <c r="Y138">
+        <v>1.15</v>
+      </c>
+      <c r="Z138">
+        <v>4.2</v>
+      </c>
+      <c r="AA138">
+        <v>1.61</v>
+      </c>
+      <c r="AB138">
         <v>2.25</v>
       </c>
-      <c r="Q138">
-        <v>3.76</v>
-      </c>
-      <c r="R138">
+      <c r="AC138">
+        <v>2.8</v>
+      </c>
+      <c r="AD138">
+        <v>1.45</v>
+      </c>
+      <c r="AE138">
+        <v>1.16</v>
+      </c>
+      <c r="AF138">
+        <v>1.67</v>
+      </c>
+      <c r="AG138">
+        <v>2.21</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>1.17</v>
+      </c>
+      <c r="AK138">
         <v>2.04</v>
-      </c>
-      <c r="S138">
-        <v>1.39</v>
-      </c>
-      <c r="T138">
-        <v>2.73</v>
-      </c>
-      <c r="U138">
-        <v>2.85</v>
-      </c>
-      <c r="V138">
-        <v>1.36</v>
-      </c>
-      <c r="W138">
-        <v>1.03</v>
-      </c>
-      <c r="X138">
-        <v>1</v>
-      </c>
-      <c r="Y138">
-        <v>1.27</v>
-      </c>
-      <c r="Z138">
-        <v>3.14</v>
-      </c>
-      <c r="AA138">
-        <v>2</v>
-      </c>
-      <c r="AB138">
-        <v>1.8</v>
-      </c>
-      <c r="AC138">
-        <v>3.34</v>
-      </c>
-      <c r="AD138">
-        <v>1.24</v>
-      </c>
-      <c r="AE138">
-        <v>1.04</v>
-      </c>
-      <c r="AF138">
-        <v>1.74</v>
-      </c>
-      <c r="AG138">
-        <v>1.98</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>1.3</v>
-      </c>
-      <c r="AK138">
-        <v>1.35</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="O139">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P139">
-        <v>4.33</v>
+        <v>1.96</v>
       </c>
       <c r="Q139">
-        <v>2.37</v>
+        <v>4.07</v>
       </c>
       <c r="R139">
+        <v>2.33</v>
+      </c>
+      <c r="S139">
+        <v>1.32</v>
+      </c>
+      <c r="T139">
+        <v>3.05</v>
+      </c>
+      <c r="U139">
+        <v>2.6</v>
+      </c>
+      <c r="V139">
+        <v>1.46</v>
+      </c>
+      <c r="W139">
+        <v>1.07</v>
+      </c>
+      <c r="X139">
+        <v>1</v>
+      </c>
+      <c r="Y139">
+        <v>1.19</v>
+      </c>
+      <c r="Z139">
+        <v>3.78</v>
+      </c>
+      <c r="AA139">
+        <v>1.8</v>
+      </c>
+      <c r="AB139">
         <v>2.04</v>
       </c>
-      <c r="S139">
-        <v>1.41</v>
-      </c>
-      <c r="T139">
-        <v>2.66</v>
-      </c>
-      <c r="U139">
-        <v>2.9</v>
-      </c>
-      <c r="V139">
-        <v>1.35</v>
-      </c>
-      <c r="W139">
-        <v>1.03</v>
-      </c>
-      <c r="X139">
-        <v>1.01</v>
-      </c>
-      <c r="Y139">
-        <v>1.28</v>
-      </c>
-      <c r="Z139">
-        <v>3.08</v>
-      </c>
-      <c r="AA139">
-        <v>2</v>
-      </c>
-      <c r="AB139">
-        <v>1.8</v>
-      </c>
       <c r="AC139">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE139">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF139">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG139">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.27</v>
       </c>
       <c r="AK139">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="O140">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P140">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q140">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="R140">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="S140">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T140">
-        <v>3.28</v>
+        <v>2.73</v>
       </c>
       <c r="U140">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="V140">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W140">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z140">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA140">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AB140">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC140">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD140">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE140">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF140">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG140">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK140">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O141">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P141">
         <v>3.4</v>
       </c>
       <c r="Q141">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="R141">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S141">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T141">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U141">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V141">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W141">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X141">
         <v>1.02</v>
       </c>
       <c r="Y141">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z141">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA141">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB141">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC141">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD141">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE141">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF141">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG141">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK141">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="O142">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q142">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="R142">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S142">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T142">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U142">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V142">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W142">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X142">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z142">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="AA142">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB142">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC142">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD142">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE142">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF142">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AG142">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK142">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,65 +23618,65 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="O143">
+        <v>3.3</v>
+      </c>
+      <c r="P143">
+        <v>2.7</v>
+      </c>
+      <c r="Q143">
+        <v>3</v>
+      </c>
+      <c r="R143">
+        <v>2.15</v>
+      </c>
+      <c r="S143">
+        <v>1.3</v>
+      </c>
+      <c r="T143">
+        <v>3.2</v>
+      </c>
+      <c r="U143">
+        <v>2.5</v>
+      </c>
+      <c r="V143">
+        <v>1.4</v>
+      </c>
+      <c r="W143">
+        <v>1.07</v>
+      </c>
+      <c r="X143">
+        <v>1</v>
+      </c>
+      <c r="Y143">
+        <v>1.22</v>
+      </c>
+      <c r="Z143">
+        <v>3.5</v>
+      </c>
+      <c r="AA143">
+        <v>1.8</v>
+      </c>
+      <c r="AB143">
+        <v>2</v>
+      </c>
+      <c r="AC143">
         <v>3.4</v>
       </c>
-      <c r="P143">
-        <v>3.4</v>
-      </c>
-      <c r="Q143">
-        <v>2.73</v>
-      </c>
-      <c r="R143">
-        <v>2.06</v>
-      </c>
-      <c r="S143">
-        <v>1.38</v>
-      </c>
-      <c r="T143">
-        <v>2.77</v>
-      </c>
-      <c r="U143">
-        <v>2.85</v>
-      </c>
-      <c r="V143">
-        <v>1.36</v>
-      </c>
-      <c r="W143">
-        <v>1.03</v>
-      </c>
-      <c r="X143">
-        <v>1.02</v>
-      </c>
-      <c r="Y143">
-        <v>1.27</v>
-      </c>
-      <c r="Z143">
-        <v>3.14</v>
-      </c>
-      <c r="AA143">
+      <c r="AD143">
+        <v>1.34</v>
+      </c>
+      <c r="AE143">
+        <v>1.08</v>
+      </c>
+      <c r="AF143">
+        <v>1.61</v>
+      </c>
+      <c r="AG143">
         <v>2</v>
       </c>
-      <c r="AB143">
-        <v>1.8</v>
-      </c>
-      <c r="AC143">
-        <v>3.34</v>
-      </c>
-      <c r="AD143">
-        <v>1.24</v>
-      </c>
-      <c r="AE143">
-        <v>1.04</v>
-      </c>
-      <c r="AF143">
-        <v>1.76</v>
-      </c>
-      <c r="AG143">
-        <v>1.96</v>
-      </c>
       <c r="AH143" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK143">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="O144">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P144">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="Q144">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="R144">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S144">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U144">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="V144">
         <v>1.4</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X144">
         <v>1</v>
       </c>
       <c r="Y144">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z144">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA144">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB144">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC144">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD144">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE144">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF144">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AG144">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P145">
-        <v>1.96</v>
+        <v>4.33</v>
       </c>
       <c r="Q145">
-        <v>4.07</v>
+        <v>2.37</v>
       </c>
       <c r="R145">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="S145">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T145">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="U145">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="V145">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X145">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z145">
-        <v>3.78</v>
+        <v>3.08</v>
       </c>
       <c r="AA145">
+        <v>2</v>
+      </c>
+      <c r="AB145">
         <v>1.8</v>
       </c>
-      <c r="AB145">
-        <v>2.04</v>
-      </c>
       <c r="AC145">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD145">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE145">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF145">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AG145">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.27</v>
       </c>
       <c r="AK145">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="O158">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P158">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="Q158">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R158">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="S158">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T158">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U158">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V158">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W158">
         <v>1.08</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z158">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA158">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB158">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC158">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD158">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE158">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG158">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK158">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="O159">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P159">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="Q159">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R159">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="S159">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T159">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U159">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="V159">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W159">
         <v>1.08</v>
       </c>
       <c r="X159">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z159">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA159">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB159">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC159">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AD159">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE159">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF159">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AG159">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK159">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O165">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P165">
-        <v>4.98</v>
+        <v>4.8</v>
       </c>
       <c r="Q165">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="R165">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T165">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="U165">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="V165">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W165">
+        <v>1.06</v>
+      </c>
+      <c r="X165">
+        <v>1.02</v>
+      </c>
+      <c r="Y165">
+        <v>1.23</v>
+      </c>
+      <c r="Z165">
+        <v>3.44</v>
+      </c>
+      <c r="AA165">
+        <v>1.85</v>
+      </c>
+      <c r="AB165">
+        <v>1.9</v>
+      </c>
+      <c r="AC165">
+        <v>3.1</v>
+      </c>
+      <c r="AD165">
+        <v>1.36</v>
+      </c>
+      <c r="AE165">
         <v>1.09</v>
       </c>
-      <c r="X165">
-        <v>1.03</v>
-      </c>
-      <c r="Y165">
-        <v>1.14</v>
-      </c>
-      <c r="Z165">
-        <v>4.35</v>
-      </c>
-      <c r="AA165">
-        <v>1.6</v>
-      </c>
-      <c r="AB165">
-        <v>2.27</v>
-      </c>
-      <c r="AC165">
-        <v>2.38</v>
-      </c>
-      <c r="AD165">
-        <v>1.47</v>
-      </c>
-      <c r="AE165">
-        <v>1.16</v>
-      </c>
       <c r="AF165">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG165">
-        <v>2.17</v>
+        <v>1.94</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK165">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O166">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P166">
-        <v>4.8</v>
+        <v>4.98</v>
       </c>
       <c r="Q166">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="R166">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S166">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T166">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="U166">
-        <v>2.71</v>
+        <v>2.34</v>
       </c>
       <c r="V166">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W166">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X166">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z166">
-        <v>3.44</v>
+        <v>4.35</v>
       </c>
       <c r="AA166">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB166">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AC166">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD166">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE166">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF166">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG166">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK166">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,43 +27530,43 @@
         </is>
       </c>
       <c r="N167">
+        <v>1.77</v>
+      </c>
+      <c r="O167">
+        <v>3.7</v>
+      </c>
+      <c r="P167">
+        <v>3.95</v>
+      </c>
+      <c r="Q167">
+        <v>2.3</v>
+      </c>
+      <c r="R167">
         <v>2.2</v>
       </c>
-      <c r="O167">
-        <v>3.5</v>
-      </c>
-      <c r="P167">
-        <v>3.1</v>
-      </c>
-      <c r="Q167">
-        <v>2.87</v>
-      </c>
-      <c r="R167">
-        <v>2.07</v>
-      </c>
       <c r="S167">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T167">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="U167">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="V167">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W167">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X167">
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z167">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA167">
         <v>1.95</v>
@@ -27575,19 +27575,19 @@
         <v>1.85</v>
       </c>
       <c r="AC167">
-        <v>3.24</v>
+        <v>2.73</v>
       </c>
       <c r="AD167">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE167">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF167">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK167">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,43 +27693,43 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="O168">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P168">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q168">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="R168">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S168">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T168">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U168">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="V168">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W168">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X168">
         <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z168">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AA168">
         <v>1.95</v>
@@ -27738,19 +27738,19 @@
         <v>1.85</v>
       </c>
       <c r="AC168">
-        <v>2.73</v>
+        <v>3.24</v>
       </c>
       <c r="AD168">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE168">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG168">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK168">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,80 +44156,80 @@
         </is>
       </c>
       <c r="N269">
-        <v>9.699999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="O269">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="P269">
-        <v>1.23</v>
+        <v>1.82</v>
       </c>
       <c r="Q269">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="R269">
-        <v>2.62</v>
+        <v>2.07</v>
       </c>
       <c r="S269">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T269">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="U269">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="V269">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W269">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X269">
         <v>1.02</v>
       </c>
       <c r="Y269">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z269">
-        <v>4.5</v>
+        <v>3.32</v>
       </c>
       <c r="AA269">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AB269">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="AC269">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD269">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AE269">
+        <v>1.06</v>
+      </c>
+      <c r="AF269">
+        <v>1.86</v>
+      </c>
+      <c r="AG269">
+        <v>1.84</v>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ269">
+        <v>1.25</v>
+      </c>
+      <c r="AK269">
         <v>1.18</v>
-      </c>
-      <c r="AF269">
-        <v>1.99</v>
-      </c>
-      <c r="AG269">
-        <v>1.73</v>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ269">
-        <v>3.15</v>
-      </c>
-      <c r="AK269">
-        <v>1.02</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>4.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O270">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="P270">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="Q270">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R270">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="S270">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T270">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="U270">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="V270">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W270">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X270">
         <v>1.02</v>
       </c>
       <c r="Y270">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z270">
-        <v>3.32</v>
+        <v>4.5</v>
       </c>
       <c r="AA270">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AB270">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AC270">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD270">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AE270">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF270">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AG270">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="AK270">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O286">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="P286">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q286">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="R286">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S286">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T286">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U286">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="V286">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W286">
         <v>1.03</v>
       </c>
       <c r="X286">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Y286">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z286">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA286">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB286">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC286">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AD286">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE286">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF286">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AG286">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>1.44</v>
       </c>
       <c r="AK286">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
+        <v>2.87</v>
+      </c>
+      <c r="O287">
+        <v>2.62</v>
+      </c>
+      <c r="P287">
+        <v>2.54</v>
+      </c>
+      <c r="Q287">
+        <v>3.72</v>
+      </c>
+      <c r="R287">
+        <v>1.82</v>
+      </c>
+      <c r="S287">
+        <v>1.57</v>
+      </c>
+      <c r="T287">
         <v>2.25</v>
       </c>
-      <c r="O287">
-        <v>2.7</v>
-      </c>
-      <c r="P287">
-        <v>3.4</v>
-      </c>
-      <c r="Q287">
-        <v>3</v>
-      </c>
-      <c r="R287">
-        <v>1.8</v>
-      </c>
-      <c r="S287">
-        <v>1.68</v>
-      </c>
-      <c r="T287">
-        <v>2.05</v>
-      </c>
       <c r="U287">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V287">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W287">
+        <v>1.04</v>
+      </c>
+      <c r="X287">
+        <v>1.09</v>
+      </c>
+      <c r="Y287">
+        <v>1.62</v>
+      </c>
+      <c r="Z287">
+        <v>2.2</v>
+      </c>
+      <c r="AA287">
+        <v>2.9</v>
+      </c>
+      <c r="AB287">
+        <v>1.34</v>
+      </c>
+      <c r="AC287">
+        <v>6.15</v>
+      </c>
+      <c r="AD287">
+        <v>1.06</v>
+      </c>
+      <c r="AE287">
         <v>1.03</v>
       </c>
-      <c r="X287">
-        <v>1.17</v>
-      </c>
-      <c r="Y287">
-        <v>1.73</v>
-      </c>
-      <c r="Z287">
-        <v>2</v>
-      </c>
-      <c r="AA287">
-        <v>3.2</v>
-      </c>
-      <c r="AB287">
-        <v>1.33</v>
-      </c>
-      <c r="AC287">
-        <v>7.5</v>
-      </c>
-      <c r="AD287">
-        <v>1.08</v>
-      </c>
-      <c r="AE287">
-        <v>1.02</v>
-      </c>
       <c r="AF287">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG287">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK287">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -49538,22 +49538,22 @@
         <v>2.3</v>
       </c>
       <c r="O302">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P302">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q302">
         <v>2.9</v>
       </c>
       <c r="R302">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S302">
         <v>1.64</v>
       </c>
       <c r="T302">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="U302">
         <v>4.05</v>
@@ -49562,28 +49562,28 @@
         <v>1.17</v>
       </c>
       <c r="W302">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X302">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y302">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z302">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AA302">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AB302">
         <v>1.3</v>
       </c>
       <c r="AC302">
-        <v>6.5</v>
+        <v>6.19</v>
       </c>
       <c r="AD302">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE302">
         <v>1.03</v>
@@ -51817,31 +51817,31 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O316">
         <v>2.62</v>
       </c>
       <c r="P316">
-        <v>4.41</v>
+        <v>3.9</v>
       </c>
       <c r="Q316">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="R316">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S316">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T316">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U316">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V316">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W316">
         <v>1.03</v>
@@ -51850,7 +51850,7 @@
         <v>1.15</v>
       </c>
       <c r="Y316">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z316">
         <v>2.1</v>
@@ -51871,10 +51871,10 @@
         <v>1.03</v>
       </c>
       <c r="AF316">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AG316">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK316">
         <v>1.7</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,80 +53610,80 @@
         </is>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q327">
+        <v>3.16</v>
+      </c>
+      <c r="R327">
+        <v>2.02</v>
+      </c>
+      <c r="S327">
+        <v>1.53</v>
+      </c>
+      <c r="T327">
+        <v>2.32</v>
+      </c>
+      <c r="U327">
+        <v>3.35</v>
+      </c>
+      <c r="V327">
+        <v>1.27</v>
+      </c>
+      <c r="W327">
+        <v>1.01</v>
+      </c>
+      <c r="X327">
+        <v>1.06</v>
+      </c>
+      <c r="Y327">
+        <v>1.46</v>
+      </c>
+      <c r="Z327">
+        <v>2.62</v>
+      </c>
+      <c r="AA327">
+        <v>2.4</v>
+      </c>
+      <c r="AB327">
+        <v>1.49</v>
+      </c>
+      <c r="AC327">
+        <v>4.25</v>
+      </c>
+      <c r="AD327">
+        <v>1.15</v>
+      </c>
+      <c r="AE327">
+        <v>1.01</v>
+      </c>
+      <c r="AF327">
         <v>2</v>
       </c>
-      <c r="R327">
-        <v>2.35</v>
-      </c>
-      <c r="S327">
-        <v>1.39</v>
-      </c>
-      <c r="T327">
-        <v>2.73</v>
-      </c>
-      <c r="U327">
-        <v>2.7</v>
-      </c>
-      <c r="V327">
+      <c r="AG327">
+        <v>1.74</v>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ327">
         <v>1.36</v>
       </c>
-      <c r="W327">
-        <v>1.03</v>
-      </c>
-      <c r="X327">
-        <v>1.03</v>
-      </c>
-      <c r="Y327">
-        <v>1.23</v>
-      </c>
-      <c r="Z327">
-        <v>3.85</v>
-      </c>
-      <c r="AA327">
-        <v>2</v>
-      </c>
-      <c r="AB327">
-        <v>1.8</v>
-      </c>
-      <c r="AC327">
-        <v>3.45</v>
-      </c>
-      <c r="AD327">
-        <v>1.25</v>
-      </c>
-      <c r="AE327">
-        <v>1.06</v>
-      </c>
-      <c r="AF327">
-        <v>2.05</v>
-      </c>
-      <c r="AG327">
-        <v>1.66</v>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ327">
-        <v>1.21</v>
-      </c>
       <c r="AK327">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O328">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P328">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q328">
-        <v>3.16</v>
+        <v>2</v>
       </c>
       <c r="R328">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="S328">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="T328">
-        <v>2.32</v>
+        <v>2.73</v>
       </c>
       <c r="U328">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="V328">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W328">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X328">
+        <v>1.03</v>
+      </c>
+      <c r="Y328">
+        <v>1.23</v>
+      </c>
+      <c r="Z328">
+        <v>3.85</v>
+      </c>
+      <c r="AA328">
+        <v>2</v>
+      </c>
+      <c r="AB328">
+        <v>1.8</v>
+      </c>
+      <c r="AC328">
+        <v>3.45</v>
+      </c>
+      <c r="AD328">
+        <v>1.25</v>
+      </c>
+      <c r="AE328">
         <v>1.06</v>
       </c>
-      <c r="Y328">
-        <v>1.46</v>
-      </c>
-      <c r="Z328">
-        <v>2.62</v>
-      </c>
-      <c r="AA328">
-        <v>2.4</v>
-      </c>
-      <c r="AB328">
-        <v>1.49</v>
-      </c>
-      <c r="AC328">
-        <v>4.25</v>
-      </c>
-      <c r="AD328">
-        <v>1.15</v>
-      </c>
-      <c r="AE328">
-        <v>1.01</v>
-      </c>
       <c r="AF328">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG328">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK328">
-        <v>1.5</v>
+        <v>2.58</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54428,7 +54428,7 @@
         <v>1.95</v>
       </c>
       <c r="O332">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P332">
         <v>4</v>
@@ -54452,28 +54452,28 @@
         <v>1.18</v>
       </c>
       <c r="W332">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X332">
         <v>1.08</v>
       </c>
       <c r="Y332">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z332">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AA332">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AB332">
         <v>1.4</v>
       </c>
       <c r="AC332">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="AD332">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE332">
         <v>1.03</v>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AK332">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="O353">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="P353">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q353">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="R353">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="S353">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T353">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="U353">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="V353">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="W353">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="X353">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y353">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="Z353">
-        <v>4.32</v>
+        <v>9</v>
       </c>
       <c r="AA353">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AB353">
-        <v>2.17</v>
+        <v>3.87</v>
       </c>
       <c r="AC353">
-        <v>2.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD353">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="AE353">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AF353">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG353">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57918,10 +57918,10 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK353">
-        <v>1.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="O354">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="P354">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q354">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="R354">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="S354">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T354">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="U354">
-        <v>1.78</v>
+        <v>2.41</v>
       </c>
       <c r="V354">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="W354">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X354">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y354">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z354">
-        <v>9</v>
+        <v>4.32</v>
       </c>
       <c r="AA354">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AB354">
-        <v>3.87</v>
+        <v>2.17</v>
       </c>
       <c r="AC354">
-        <v>1.67</v>
+        <v>2.73</v>
       </c>
       <c r="AD354">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="AE354">
+        <v>1.18</v>
+      </c>
+      <c r="AF354">
         <v>1.53</v>
       </c>
-      <c r="AF354">
-        <v>1.36</v>
-      </c>
       <c r="AG354">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58081,10 +58081,10 @@
         </is>
       </c>
       <c r="AJ354">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK354">
-        <v>2.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL354">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="Q65">
-        <v>2.71</v>
+        <v>3.45</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S65">
+        <v>1.27</v>
+      </c>
+      <c r="T65">
+        <v>3.25</v>
+      </c>
+      <c r="U65">
+        <v>2.33</v>
+      </c>
+      <c r="V65">
+        <v>1.5</v>
+      </c>
+      <c r="W65">
+        <v>1.09</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
         <v>1.2</v>
       </c>
-      <c r="T65">
-        <v>3.7</v>
-      </c>
-      <c r="U65">
-        <v>2.07</v>
-      </c>
-      <c r="V65">
-        <v>1.67</v>
-      </c>
-      <c r="W65">
-        <v>1.15</v>
-      </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
-      <c r="Y65">
-        <v>1.09</v>
-      </c>
       <c r="Z65">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA65">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="AB65">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AC65">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD65">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="O66">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>3.45</v>
+        <v>2.71</v>
       </c>
       <c r="R66">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U66">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="V66">
+        <v>1.67</v>
+      </c>
+      <c r="W66">
+        <v>1.15</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.09</v>
+      </c>
+      <c r="Z66">
+        <v>5.3</v>
+      </c>
+      <c r="AA66">
+        <v>1.39</v>
+      </c>
+      <c r="AB66">
+        <v>2.59</v>
+      </c>
+      <c r="AC66">
+        <v>2.1</v>
+      </c>
+      <c r="AD66">
+        <v>1.68</v>
+      </c>
+      <c r="AE66">
+        <v>1.25</v>
+      </c>
+      <c r="AF66">
+        <v>1.38</v>
+      </c>
+      <c r="AG66">
+        <v>2.77</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.19</v>
+      </c>
+      <c r="AK66">
         <v>1.5</v>
-      </c>
-      <c r="W66">
-        <v>1.09</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.2</v>
-      </c>
-      <c r="Z66">
-        <v>4.3</v>
-      </c>
-      <c r="AA66">
-        <v>1.56</v>
-      </c>
-      <c r="AB66">
-        <v>2.19</v>
-      </c>
-      <c r="AC66">
-        <v>2.43</v>
-      </c>
-      <c r="AD66">
-        <v>1.44</v>
-      </c>
-      <c r="AE66">
-        <v>1.14</v>
-      </c>
-      <c r="AF66">
-        <v>1.5</v>
-      </c>
-      <c r="AG66">
-        <v>2.38</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.22</v>
-      </c>
-      <c r="AK66">
-        <v>1.34</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -16938,61 +16938,61 @@
         <v>1.3</v>
       </c>
       <c r="O102">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="P102">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q102">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="R102">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T102">
-        <v>2.91</v>
+        <v>3.18</v>
       </c>
       <c r="U102">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="V102">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z102">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AA102">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AB102">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AC102">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AG102">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK102">
-        <v>2.79</v>
+        <v>3.24</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.15</v>
+        <v>2.25</v>
       </c>
       <c r="O120">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="P120">
-        <v>12.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q120">
-        <v>1.48</v>
+        <v>3.07</v>
       </c>
       <c r="R120">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="S120">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="T120">
-        <v>4.6</v>
+        <v>2.89</v>
       </c>
       <c r="U120">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="V120">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA120">
+        <v>1.9</v>
+      </c>
+      <c r="AB120">
+        <v>1.9</v>
+      </c>
+      <c r="AC120">
+        <v>3.04</v>
+      </c>
+      <c r="AD120">
         <v>1.32</v>
       </c>
-      <c r="AB120">
-        <v>3.04</v>
-      </c>
-      <c r="AC120">
-        <v>1.91</v>
-      </c>
-      <c r="AD120">
-        <v>1.97</v>
-      </c>
       <c r="AE120">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG120">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK120">
-        <v>5.35</v>
+        <v>1.65</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.25</v>
+        <v>1.15</v>
       </c>
       <c r="O122">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="P122">
-        <v>3.1</v>
+        <v>12.5</v>
       </c>
       <c r="Q122">
-        <v>3.07</v>
+        <v>1.48</v>
       </c>
       <c r="R122">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="T122">
-        <v>2.89</v>
+        <v>4.6</v>
       </c>
       <c r="U122">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X122">
         <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Z122">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA122">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>3.04</v>
       </c>
       <c r="AC122">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="AD122">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AF122">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG122">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AK122">
-        <v>1.65</v>
+        <v>5.35</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,65 +21825,65 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="P132">
-        <v>4.75</v>
+        <v>3.26</v>
       </c>
       <c r="Q132">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R132">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T132">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U132">
-        <v>2.59</v>
+        <v>2.96</v>
       </c>
       <c r="V132">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W132">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X132">
+        <v>1.01</v>
+      </c>
+      <c r="Y132">
+        <v>1.29</v>
+      </c>
+      <c r="Z132">
+        <v>3.04</v>
+      </c>
+      <c r="AA132">
+        <v>2.03</v>
+      </c>
+      <c r="AB132">
+        <v>1.7</v>
+      </c>
+      <c r="AC132">
+        <v>3.5</v>
+      </c>
+      <c r="AD132">
+        <v>1.22</v>
+      </c>
+      <c r="AE132">
         <v>1.03</v>
       </c>
-      <c r="Y132">
-        <v>1.23</v>
-      </c>
-      <c r="Z132">
-        <v>3.42</v>
-      </c>
-      <c r="AA132">
-        <v>1.84</v>
-      </c>
-      <c r="AB132">
+      <c r="AF132">
+        <v>1.8</v>
+      </c>
+      <c r="AG132">
         <v>1.9</v>
       </c>
-      <c r="AC132">
-        <v>3.2</v>
-      </c>
-      <c r="AD132">
-        <v>1.28</v>
-      </c>
-      <c r="AE132">
-        <v>1.07</v>
-      </c>
-      <c r="AF132">
-        <v>1.85</v>
-      </c>
-      <c r="AG132">
-        <v>1.85</v>
-      </c>
       <c r="AH132" t="inlineStr">
         <is>
           <t>[]</t>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>2.19</v>
+        <v>1.59</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="O133">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>3.26</v>
+        <v>4.75</v>
       </c>
       <c r="Q133">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="R133">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="S133">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U133">
-        <v>2.96</v>
+        <v>2.59</v>
       </c>
       <c r="V133">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z133">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
       <c r="AA133">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="AB133">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC133">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE133">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.59</v>
+        <v>2.19</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="O137">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P137">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q137">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="R137">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="S137">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T137">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U137">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="V137">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z137">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA137">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB137">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC137">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD137">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE137">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF137">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK137">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="O138">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P138">
-        <v>3.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q138">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="R138">
-        <v>2.33</v>
+        <v>2.04</v>
       </c>
       <c r="S138">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="T138">
-        <v>3.28</v>
+        <v>2.73</v>
       </c>
       <c r="U138">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="V138">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W138">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z138">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA138">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AB138">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC138">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD138">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE138">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF138">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG138">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK138">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O139">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="Q139">
-        <v>4.07</v>
+        <v>2.55</v>
       </c>
       <c r="R139">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="S139">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T139">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U139">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V139">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W139">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y139">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z139">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AA139">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB139">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC139">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD139">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE139">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF139">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG139">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.27</v>
       </c>
       <c r="AK139">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O140">
         <v>3.3</v>
       </c>
       <c r="P140">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q140">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R140">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S140">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T140">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U140">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V140">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W140">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X140">
         <v>1</v>
       </c>
       <c r="Y140">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z140">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA140">
+        <v>1.8</v>
+      </c>
+      <c r="AB140">
         <v>2</v>
       </c>
-      <c r="AB140">
-        <v>1.8</v>
-      </c>
       <c r="AC140">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD140">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE140">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF140">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AG140">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK140">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,65 +23292,65 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P141">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q141">
-        <v>2.73</v>
+        <v>3.36</v>
       </c>
       <c r="R141">
+        <v>2.08</v>
+      </c>
+      <c r="S141">
+        <v>1.36</v>
+      </c>
+      <c r="T141">
+        <v>2.84</v>
+      </c>
+      <c r="U141">
+        <v>2.69</v>
+      </c>
+      <c r="V141">
+        <v>1.4</v>
+      </c>
+      <c r="W141">
+        <v>1.05</v>
+      </c>
+      <c r="X141">
+        <v>1</v>
+      </c>
+      <c r="Y141">
+        <v>1.24</v>
+      </c>
+      <c r="Z141">
+        <v>3.34</v>
+      </c>
+      <c r="AA141">
+        <v>1.9</v>
+      </c>
+      <c r="AB141">
+        <v>1.9</v>
+      </c>
+      <c r="AC141">
+        <v>3.08</v>
+      </c>
+      <c r="AD141">
+        <v>1.28</v>
+      </c>
+      <c r="AE141">
+        <v>1.07</v>
+      </c>
+      <c r="AF141">
+        <v>1.68</v>
+      </c>
+      <c r="AG141">
         <v>2.06</v>
       </c>
-      <c r="S141">
-        <v>1.38</v>
-      </c>
-      <c r="T141">
-        <v>2.77</v>
-      </c>
-      <c r="U141">
-        <v>2.85</v>
-      </c>
-      <c r="V141">
-        <v>1.36</v>
-      </c>
-      <c r="W141">
-        <v>1.03</v>
-      </c>
-      <c r="X141">
-        <v>1.02</v>
-      </c>
-      <c r="Y141">
-        <v>1.27</v>
-      </c>
-      <c r="Z141">
-        <v>3.14</v>
-      </c>
-      <c r="AA141">
-        <v>2</v>
-      </c>
-      <c r="AB141">
-        <v>1.8</v>
-      </c>
-      <c r="AC141">
-        <v>3.34</v>
-      </c>
-      <c r="AD141">
-        <v>1.24</v>
-      </c>
-      <c r="AE141">
-        <v>1.04</v>
-      </c>
-      <c r="AF141">
-        <v>1.76</v>
-      </c>
-      <c r="AG141">
-        <v>1.96</v>
-      </c>
       <c r="AH141" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK141">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O142">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
         <v>3.4</v>
       </c>
       <c r="Q142">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="R142">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S142">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T142">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U142">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V142">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W142">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X142">
         <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z142">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA142">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AB142">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC142">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD142">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE142">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF142">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AG142">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK142">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,43 +23618,43 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="O143">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P143">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q143">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R143">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S143">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T143">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U143">
         <v>2.5</v>
       </c>
       <c r="V143">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W143">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X143">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y143">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z143">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA143">
         <v>1.8</v>
@@ -23663,19 +23663,19 @@
         <v>2</v>
       </c>
       <c r="AC143">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD143">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE143">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF143">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG143">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.69</v>
+        <v>1.74</v>
       </c>
       <c r="O144">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P144">
-        <v>2.27</v>
+        <v>4.33</v>
       </c>
       <c r="Q144">
-        <v>3.36</v>
+        <v>2.37</v>
       </c>
       <c r="R144">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S144">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T144">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="U144">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="V144">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W144">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X144">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z144">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA144">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB144">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC144">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD144">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE144">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF144">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AG144">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK144">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="O145">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
-        <v>4.33</v>
+        <v>1.96</v>
       </c>
       <c r="Q145">
-        <v>2.37</v>
+        <v>4.07</v>
       </c>
       <c r="R145">
+        <v>2.33</v>
+      </c>
+      <c r="S145">
+        <v>1.32</v>
+      </c>
+      <c r="T145">
+        <v>3.05</v>
+      </c>
+      <c r="U145">
+        <v>2.6</v>
+      </c>
+      <c r="V145">
+        <v>1.46</v>
+      </c>
+      <c r="W145">
+        <v>1.07</v>
+      </c>
+      <c r="X145">
+        <v>1</v>
+      </c>
+      <c r="Y145">
+        <v>1.19</v>
+      </c>
+      <c r="Z145">
+        <v>3.78</v>
+      </c>
+      <c r="AA145">
+        <v>1.8</v>
+      </c>
+      <c r="AB145">
         <v>2.04</v>
       </c>
-      <c r="S145">
-        <v>1.41</v>
-      </c>
-      <c r="T145">
-        <v>2.66</v>
-      </c>
-      <c r="U145">
-        <v>2.9</v>
-      </c>
-      <c r="V145">
-        <v>1.35</v>
-      </c>
-      <c r="W145">
-        <v>1.03</v>
-      </c>
-      <c r="X145">
-        <v>1.01</v>
-      </c>
-      <c r="Y145">
-        <v>1.28</v>
-      </c>
-      <c r="Z145">
-        <v>3.08</v>
-      </c>
-      <c r="AA145">
-        <v>2</v>
-      </c>
-      <c r="AB145">
-        <v>1.8</v>
-      </c>
       <c r="AC145">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD145">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG145">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.27</v>
       </c>
       <c r="AK145">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.35</v>
+        <v>3.4</v>
       </c>
       <c r="O154">
-        <v>4.95</v>
+        <v>3.38</v>
       </c>
       <c r="P154">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q154">
-        <v>1.83</v>
+        <v>4.17</v>
       </c>
       <c r="R154">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="S154">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T154">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="U154">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="V154">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z154">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA154">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB154">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AC154">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="AD154">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF154">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AG154">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK154">
-        <v>3.04</v>
+        <v>1.29</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.4</v>
+        <v>1.35</v>
       </c>
       <c r="O155">
-        <v>3.38</v>
+        <v>4.95</v>
       </c>
       <c r="P155">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="Q155">
-        <v>4.17</v>
+        <v>1.83</v>
       </c>
       <c r="R155">
+        <v>2.42</v>
+      </c>
+      <c r="S155">
+        <v>1.31</v>
+      </c>
+      <c r="T155">
+        <v>3.15</v>
+      </c>
+      <c r="U155">
+        <v>2.5</v>
+      </c>
+      <c r="V155">
+        <v>1.47</v>
+      </c>
+      <c r="W155">
+        <v>1.07</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.18</v>
+      </c>
+      <c r="Z155">
+        <v>3.9</v>
+      </c>
+      <c r="AA155">
+        <v>1.66</v>
+      </c>
+      <c r="AB155">
         <v>2.08</v>
       </c>
-      <c r="S155">
-        <v>1.39</v>
-      </c>
-      <c r="T155">
-        <v>2.77</v>
-      </c>
-      <c r="U155">
-        <v>2.65</v>
-      </c>
-      <c r="V155">
-        <v>1.4</v>
-      </c>
-      <c r="W155">
-        <v>1.06</v>
-      </c>
-      <c r="X155">
-        <v>1.01</v>
-      </c>
-      <c r="Y155">
-        <v>1.25</v>
-      </c>
-      <c r="Z155">
-        <v>3.3</v>
-      </c>
-      <c r="AA155">
-        <v>1.9</v>
-      </c>
-      <c r="AB155">
-        <v>1.9</v>
-      </c>
       <c r="AC155">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="AD155">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AG155">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK155">
-        <v>1.29</v>
+        <v>3.04</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="O158">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="P158">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q158">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="R158">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S158">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T158">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U158">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V158">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W158">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
         <v>1.2</v>
       </c>
       <c r="Z158">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA158">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB158">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC158">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD158">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE158">
         <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG158">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK158">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="O159">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P159">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="Q159">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="R159">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="S159">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T159">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U159">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V159">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W159">
         <v>1.08</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y159">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z159">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AA159">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB159">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC159">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD159">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF159">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG159">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK159">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="O160">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="P160">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="Q160">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="R160">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S160">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T160">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U160">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="V160">
         <v>1.49</v>
       </c>
       <c r="W160">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z160">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA160">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB160">
         <v>2.2</v>
       </c>
       <c r="AC160">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AD160">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE160">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF160">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AG160">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK160">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,80 +26715,80 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O162">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Q162">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="R162">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="S162">
+        <v>1.4</v>
+      </c>
+      <c r="T162">
+        <v>2.73</v>
+      </c>
+      <c r="U162">
+        <v>2.88</v>
+      </c>
+      <c r="V162">
+        <v>1.36</v>
+      </c>
+      <c r="W162">
+        <v>1.04</v>
+      </c>
+      <c r="X162">
+        <v>1.03</v>
+      </c>
+      <c r="Y162">
+        <v>1.32</v>
+      </c>
+      <c r="Z162">
+        <v>3.18</v>
+      </c>
+      <c r="AA162">
+        <v>2</v>
+      </c>
+      <c r="AB162">
+        <v>1.8</v>
+      </c>
+      <c r="AC162">
+        <v>3.3</v>
+      </c>
+      <c r="AD162">
+        <v>1.25</v>
+      </c>
+      <c r="AE162">
+        <v>1.05</v>
+      </c>
+      <c r="AF162">
+        <v>1.73</v>
+      </c>
+      <c r="AG162">
+        <v>2</v>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ162">
         <v>1.33</v>
       </c>
-      <c r="T162">
-        <v>3.02</v>
-      </c>
-      <c r="U162">
-        <v>2.62</v>
-      </c>
-      <c r="V162">
-        <v>1.43</v>
-      </c>
-      <c r="W162">
-        <v>1.06</v>
-      </c>
-      <c r="X162">
-        <v>1</v>
-      </c>
-      <c r="Y162">
-        <v>1.21</v>
-      </c>
-      <c r="Z162">
-        <v>3.62</v>
-      </c>
-      <c r="AA162">
-        <v>1.8</v>
-      </c>
-      <c r="AB162">
-        <v>2</v>
-      </c>
-      <c r="AC162">
-        <v>2.85</v>
-      </c>
-      <c r="AD162">
-        <v>1.33</v>
-      </c>
-      <c r="AE162">
-        <v>1.09</v>
-      </c>
-      <c r="AF162">
-        <v>1.62</v>
-      </c>
-      <c r="AG162">
-        <v>2.17</v>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ162">
-        <v>1.28</v>
-      </c>
       <c r="AK162">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G163">
@@ -26881,61 +26881,61 @@
         <v>2.37</v>
       </c>
       <c r="O163">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P163">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="Q163">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="R163">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S163">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T163">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U163">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="V163">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W163">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X163">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y163">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z163">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="AA163">
+        <v>1.8</v>
+      </c>
+      <c r="AB163">
         <v>2</v>
       </c>
-      <c r="AB163">
-        <v>1.8</v>
-      </c>
       <c r="AC163">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="AD163">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE163">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF163">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG163">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK163">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="O164">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P164">
-        <v>2.79</v>
+        <v>3.9</v>
       </c>
       <c r="Q164">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="R164">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S164">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T164">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="U164">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V164">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W164">
+        <v>1.04</v>
+      </c>
+      <c r="X164">
+        <v>1.01</v>
+      </c>
+      <c r="Y164">
+        <v>1.26</v>
+      </c>
+      <c r="Z164">
+        <v>3.45</v>
+      </c>
+      <c r="AA164">
+        <v>1.95</v>
+      </c>
+      <c r="AB164">
+        <v>1.85</v>
+      </c>
+      <c r="AC164">
+        <v>3.05</v>
+      </c>
+      <c r="AD164">
+        <v>1.31</v>
+      </c>
+      <c r="AE164">
         <v>1.06</v>
       </c>
-      <c r="X164">
-        <v>1.02</v>
-      </c>
-      <c r="Y164">
-        <v>1.25</v>
-      </c>
-      <c r="Z164">
-        <v>3.8</v>
-      </c>
-      <c r="AA164">
-        <v>1.8</v>
-      </c>
-      <c r="AB164">
-        <v>2</v>
-      </c>
-      <c r="AC164">
-        <v>2.76</v>
-      </c>
-      <c r="AD164">
-        <v>1.34</v>
-      </c>
-      <c r="AE164">
-        <v>1.09</v>
-      </c>
       <c r="AF164">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AG164">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>1.28</v>
       </c>
       <c r="AK164">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
+        <v>1.77</v>
+      </c>
+      <c r="O165">
+        <v>3.7</v>
+      </c>
+      <c r="P165">
+        <v>3.95</v>
+      </c>
+      <c r="Q165">
+        <v>2.3</v>
+      </c>
+      <c r="R165">
+        <v>2.2</v>
+      </c>
+      <c r="S165">
+        <v>1.33</v>
+      </c>
+      <c r="T165">
+        <v>3.04</v>
+      </c>
+      <c r="U165">
+        <v>2.47</v>
+      </c>
+      <c r="V165">
+        <v>1.44</v>
+      </c>
+      <c r="W165">
+        <v>1.07</v>
+      </c>
+      <c r="X165">
+        <v>1.01</v>
+      </c>
+      <c r="Y165">
+        <v>1.22</v>
+      </c>
+      <c r="Z165">
+        <v>3.54</v>
+      </c>
+      <c r="AA165">
+        <v>1.95</v>
+      </c>
+      <c r="AB165">
+        <v>1.85</v>
+      </c>
+      <c r="AC165">
+        <v>2.73</v>
+      </c>
+      <c r="AD165">
+        <v>1.33</v>
+      </c>
+      <c r="AE165">
+        <v>1.1</v>
+      </c>
+      <c r="AF165">
         <v>1.7</v>
       </c>
-      <c r="O165">
-        <v>3.8</v>
-      </c>
-      <c r="P165">
-        <v>4.8</v>
-      </c>
-      <c r="Q165">
-        <v>2.25</v>
-      </c>
-      <c r="R165">
-        <v>2.23</v>
-      </c>
-      <c r="S165">
-        <v>1.35</v>
-      </c>
-      <c r="T165">
-        <v>2.94</v>
-      </c>
-      <c r="U165">
-        <v>2.71</v>
-      </c>
-      <c r="V165">
-        <v>1.43</v>
-      </c>
-      <c r="W165">
-        <v>1.06</v>
-      </c>
-      <c r="X165">
-        <v>1.02</v>
-      </c>
-      <c r="Y165">
-        <v>1.23</v>
-      </c>
-      <c r="Z165">
-        <v>3.44</v>
-      </c>
-      <c r="AA165">
-        <v>1.85</v>
-      </c>
-      <c r="AB165">
-        <v>1.9</v>
-      </c>
-      <c r="AC165">
-        <v>3.1</v>
-      </c>
-      <c r="AD165">
-        <v>1.36</v>
-      </c>
-      <c r="AE165">
-        <v>1.09</v>
-      </c>
-      <c r="AF165">
-        <v>1.78</v>
-      </c>
       <c r="AG165">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>1.24</v>
       </c>
       <c r="AK165">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O167">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P167">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q167">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R167">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S167">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T167">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="U167">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="V167">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W167">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z167">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="AA167">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB167">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC167">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="AD167">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE167">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF167">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG167">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.24</v>
       </c>
       <c r="AK167">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O169">
         <v>3.5</v>
       </c>
       <c r="P169">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="Q169">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="R169">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S169">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T169">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="U169">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V169">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W169">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X169">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y169">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z169">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="AA169">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB169">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC169">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AD169">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE169">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF169">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AG169">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>1.28</v>
       </c>
       <c r="AK169">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="O199">
         <v>3.85</v>
       </c>
       <c r="P199">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q199">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="R199">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S199">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T199">
-        <v>3.22</v>
+        <v>3.52</v>
       </c>
       <c r="U199">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V199">
+        <v>1.59</v>
+      </c>
+      <c r="W199">
+        <v>1.12</v>
+      </c>
+      <c r="X199">
+        <v>1.01</v>
+      </c>
+      <c r="Y199">
+        <v>1.14</v>
+      </c>
+      <c r="Z199">
+        <v>4.75</v>
+      </c>
+      <c r="AA199">
+        <v>1.53</v>
+      </c>
+      <c r="AB199">
+        <v>2.32</v>
+      </c>
+      <c r="AC199">
+        <v>2.33</v>
+      </c>
+      <c r="AD199">
         <v>1.5</v>
       </c>
-      <c r="W199">
-        <v>1.11</v>
-      </c>
-      <c r="X199">
-        <v>1.03</v>
-      </c>
-      <c r="Y199">
-        <v>1.16</v>
-      </c>
-      <c r="Z199">
-        <v>4.15</v>
-      </c>
-      <c r="AA199">
-        <v>1.67</v>
-      </c>
-      <c r="AB199">
-        <v>2.15</v>
-      </c>
-      <c r="AC199">
-        <v>2.59</v>
-      </c>
-      <c r="AD199">
-        <v>1.39</v>
-      </c>
       <c r="AE199">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF199">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AG199">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK199">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="O200">
         <v>3.85</v>
       </c>
       <c r="P200">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q200">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="R200">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S200">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T200">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="U200">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V200">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W200">
+        <v>1.11</v>
+      </c>
+      <c r="X200">
+        <v>1.03</v>
+      </c>
+      <c r="Y200">
+        <v>1.16</v>
+      </c>
+      <c r="Z200">
+        <v>4.15</v>
+      </c>
+      <c r="AA200">
+        <v>1.67</v>
+      </c>
+      <c r="AB200">
+        <v>2.15</v>
+      </c>
+      <c r="AC200">
+        <v>2.59</v>
+      </c>
+      <c r="AD200">
+        <v>1.39</v>
+      </c>
+      <c r="AE200">
         <v>1.12</v>
       </c>
-      <c r="X200">
-        <v>1.01</v>
-      </c>
-      <c r="Y200">
-        <v>1.14</v>
-      </c>
-      <c r="Z200">
-        <v>4.75</v>
-      </c>
-      <c r="AA200">
-        <v>1.53</v>
-      </c>
-      <c r="AB200">
-        <v>2.32</v>
-      </c>
-      <c r="AC200">
-        <v>2.33</v>
-      </c>
-      <c r="AD200">
-        <v>1.5</v>
-      </c>
-      <c r="AE200">
-        <v>1.18</v>
-      </c>
       <c r="AF200">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AG200">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O267">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P267">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q267">
         <v>2.12</v>
@@ -43845,16 +43845,16 @@
         <v>2.28</v>
       </c>
       <c r="S267">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T267">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U267">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="V267">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W267">
         <v>1.02</v>
@@ -43863,31 +43863,31 @@
         <v>1.02</v>
       </c>
       <c r="Y267">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z267">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AA267">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB267">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC267">
-        <v>2.88</v>
+        <v>3.61</v>
       </c>
       <c r="AD267">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE267">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF267">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AG267">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O268">
         <v>3.2</v>
       </c>
       <c r="P268">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q268">
         <v>2.79</v>
@@ -44008,10 +44008,10 @@
         <v>2.1</v>
       </c>
       <c r="S268">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T268">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U268">
         <v>2.75</v>
@@ -44032,10 +44032,10 @@
         <v>3.34</v>
       </c>
       <c r="AA268">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB268">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC268">
         <v>2.97</v>
@@ -44047,10 +44047,10 @@
         <v>1.08</v>
       </c>
       <c r="AF268">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG268">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>1.25</v>
       </c>
       <c r="AK268">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL268">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -1486,10 +1486,10 @@
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.54</v>
+        <v>3.89</v>
       </c>
       <c r="AA7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB7">
         <v>1.95</v>
@@ -1501,7 +1501,7 @@
         <v>1.32</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.64</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O8">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P8">
-        <v>4.35</v>
+        <v>3.83</v>
       </c>
       <c r="Q8">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S8">
         <v>1.43</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U8">
         <v>3.04</v>
@@ -1658,7 +1658,7 @@
         <v>1.72</v>
       </c>
       <c r="AC8">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
         <v>1.21</v>
@@ -1782,7 +1782,7 @@
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q9">
         <v>4.68</v>
@@ -1797,7 +1797,7 @@
         <v>2.85</v>
       </c>
       <c r="U9">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V9">
         <v>1.4</v>
@@ -1806,10 +1806,10 @@
         <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z9">
         <v>3.38</v>
@@ -1954,10 +1954,10 @@
         <v>2.06</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.75</v>
@@ -1969,7 +1969,7 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
         <v>1.29</v>
@@ -1984,7 +1984,7 @@
         <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD10">
         <v>1.25</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>1.33</v>
       </c>
       <c r="T15">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
         <v>2.75</v>
@@ -2784,7 +2784,7 @@
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.23</v>
@@ -2793,10 +2793,10 @@
         <v>3.42</v>
       </c>
       <c r="AA15">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
         <v>2.92</v>
@@ -2805,7 +2805,7 @@
         <v>1.31</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
         <v>1.65</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="O16">
         <v>4.2</v>
       </c>
       <c r="P16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q16">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R16">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S16">
         <v>1.26</v>
@@ -2938,10 +2938,10 @@
         <v>3.32</v>
       </c>
       <c r="U16">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W16">
         <v>1.1</v>
@@ -2950,10 +2950,10 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="AA16">
         <v>1.58</v>
@@ -2965,10 +2965,10 @@
         <v>2.38</v>
       </c>
       <c r="AD16">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE16">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF16">
         <v>1.74</v>
@@ -2990,7 +2990,7 @@
         <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="P17">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q17">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
         <v>2.9</v>
@@ -3107,10 +3107,10 @@
         <v>1.38</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
         <v>1.24</v>
@@ -3125,10 +3125,10 @@
         <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q18">
         <v>4</v>
@@ -3297,7 +3297,7 @@
         <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG18">
         <v>2.2</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R27">
         <v>2.12</v>
@@ -4731,40 +4731,40 @@
         <v>2.85</v>
       </c>
       <c r="U27">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27">
         <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB27">
         <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG27">
         <v>2</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O39">
         <v>3.7</v>
@@ -6675,19 +6675,19 @@
         <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R39">
         <v>2.19</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="V39">
         <v>1.44</v>
@@ -6696,28 +6696,28 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA39">
         <v>1.87</v>
       </c>
       <c r="AB39">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC39">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
         <v>1.75</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
         <v>3.8</v>
@@ -6841,7 +6841,7 @@
         <v>2.5</v>
       </c>
       <c r="R40">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
         <v>1.38</v>
@@ -6874,7 +6874,7 @@
         <v>1.76</v>
       </c>
       <c r="AC40">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
         <v>1.22</v>
@@ -6883,10 +6883,10 @@
         <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>4</v>
       </c>
       <c r="O42">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
         <v>1.83</v>
@@ -7185,7 +7185,7 @@
         <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.22</v>
@@ -7194,25 +7194,25 @@
         <v>4.29</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC42">
         <v>2.58</v>
       </c>
       <c r="AD42">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
         <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O43">
         <v>3.18</v>
       </c>
       <c r="P43">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q43">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="R43">
         <v>2</v>
@@ -7339,7 +7339,7 @@
         <v>2.59</v>
       </c>
       <c r="U43">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V43">
         <v>1.35</v>
@@ -7348,25 +7348,25 @@
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
         <v>2.94</v>
       </c>
       <c r="AA43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC43">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="AD43">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
@@ -7375,7 +7375,7 @@
         <v>1.78</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>3.2</v>
       </c>
       <c r="P44">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q44">
         <v>2.81</v>
@@ -7502,10 +7502,10 @@
         <v>2.5</v>
       </c>
       <c r="U44">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="V44">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
         <v>1.02</v>
@@ -7520,7 +7520,7 @@
         <v>2.8</v>
       </c>
       <c r="AA44">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
         <v>1.66</v>
@@ -7529,10 +7529,10 @@
         <v>3.78</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
         <v>1.87</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P48">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="Q48">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S48">
         <v>1.36</v>
@@ -8154,40 +8154,40 @@
         <v>2.89</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA48">
         <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="AD48">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
         <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG48">
         <v>2.09</v>
@@ -8296,28 +8296,28 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P49">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q49">
         <v>3.67</v>
       </c>
       <c r="R49">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
         <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V49">
         <v>1.61</v>
@@ -8326,7 +8326,7 @@
         <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
         <v>1.15</v>
@@ -8335,16 +8335,16 @@
         <v>5.21</v>
       </c>
       <c r="AA49">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB49">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC49">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AD49">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AE49">
         <v>1.2</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R50">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="V50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>5.95</v>
       </c>
       <c r="AA50">
+        <v>1.36</v>
+      </c>
+      <c r="AB50">
+        <v>2.7</v>
+      </c>
+      <c r="AC50">
+        <v>2.01</v>
+      </c>
+      <c r="AD50">
+        <v>1.79</v>
+      </c>
+      <c r="AE50">
+        <v>1.34</v>
+      </c>
+      <c r="AF50">
+        <v>1.4</v>
+      </c>
+      <c r="AG50">
+        <v>2.75</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.22</v>
+      </c>
+      <c r="AK50">
         <v>1.6</v>
-      </c>
-      <c r="AB50">
-        <v>2.36</v>
-      </c>
-      <c r="AC50">
-        <v>2.4</v>
-      </c>
-      <c r="AD50">
-        <v>1.53</v>
-      </c>
-      <c r="AE50">
-        <v>1.17</v>
-      </c>
-      <c r="AF50">
-        <v>1.71</v>
-      </c>
-      <c r="AG50">
-        <v>2</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.19</v>
-      </c>
-      <c r="AK50">
-        <v>2.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,65 +8622,65 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="U51">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="V51">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>5.85</v>
+        <v>4.45</v>
       </c>
       <c r="AA51">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="AB51">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AC51">
+        <v>2.4</v>
+      </c>
+      <c r="AD51">
+        <v>1.54</v>
+      </c>
+      <c r="AE51">
+        <v>1.17</v>
+      </c>
+      <c r="AF51">
+        <v>1.7</v>
+      </c>
+      <c r="AG51">
         <v>2.04</v>
       </c>
-      <c r="AD51">
-        <v>1.77</v>
-      </c>
-      <c r="AE51">
-        <v>1.26</v>
-      </c>
-      <c r="AF51">
-        <v>1.4</v>
-      </c>
-      <c r="AG51">
-        <v>2.75</v>
-      </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.63</v>
+        <v>2.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9283,52 +9283,52 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="R55">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S55">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="U55">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="V55">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W55">
         <v>1.17</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.08</v>
       </c>
       <c r="Z55">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA55">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC55">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AD55">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE55">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF55">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG55">
         <v>2.5</v>
@@ -9347,7 +9347,7 @@
         <v>1.21</v>
       </c>
       <c r="AK55">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O64">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>4.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q64">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="R64">
-        <v>2.61</v>
+        <v>2.36</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="U64">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V64">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z64">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA64">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB64">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="AC64">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AD64">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE64">
+        <v>1.25</v>
+      </c>
+      <c r="AF64">
+        <v>1.37</v>
+      </c>
+      <c r="AG64">
+        <v>2.71</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.19</v>
       </c>
-      <c r="AF64">
-        <v>1.54</v>
-      </c>
-      <c r="AG64">
-        <v>2.29</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.17</v>
-      </c>
       <c r="AK64">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P66">
-        <v>2.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q66">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="R66">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="U66">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W66">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB66">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="AC66">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AD66">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF66">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AG66">
-        <v>2.71</v>
+        <v>2.29</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK66">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>4.1</v>
       </c>
       <c r="AA69">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB69">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC69">
         <v>2.46</v>
@@ -11610,7 +11610,7 @@
         <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG69">
         <v>2.22</v>
@@ -11629,7 +11629,7 @@
         <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q82">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="R82">
         <v>2.1</v>
@@ -13693,46 +13693,46 @@
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U82">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V82">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
+        <v>1.27</v>
+      </c>
+      <c r="Z82">
+        <v>3.14</v>
+      </c>
+      <c r="AA82">
+        <v>1.94</v>
+      </c>
+      <c r="AB82">
+        <v>1.77</v>
+      </c>
+      <c r="AC82">
+        <v>3.45</v>
+      </c>
+      <c r="AD82">
         <v>1.28</v>
       </c>
-      <c r="Z82">
-        <v>3.28</v>
-      </c>
-      <c r="AA82">
-        <v>1.95</v>
-      </c>
-      <c r="AB82">
-        <v>1.85</v>
-      </c>
-      <c r="AC82">
-        <v>3.04</v>
-      </c>
-      <c r="AD82">
-        <v>1.29</v>
-      </c>
       <c r="AE82">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O83">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q83">
-        <v>2.67</v>
+        <v>2.27</v>
       </c>
       <c r="R83">
         <v>2.1</v>
@@ -13856,46 +13856,46 @@
         <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U83">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z83">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA83">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB83">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC83">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AD83">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE83">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="O92">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="P92">
         <v>3.9</v>
@@ -15338,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
         <v>3.8</v>
@@ -15350,7 +15350,7 @@
         <v>1.95</v>
       </c>
       <c r="AC92">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AD92">
         <v>1.38</v>
@@ -15359,7 +15359,7 @@
         <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
         <v>2.11</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O93">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="P93">
-        <v>9.5</v>
+        <v>8.35</v>
       </c>
       <c r="Q93">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R93">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="S93">
         <v>1.25</v>
@@ -15489,13 +15489,13 @@
         <v>4</v>
       </c>
       <c r="U93">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V93">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X93">
         <v>1.02</v>
@@ -15504,28 +15504,28 @@
         <v>1.1</v>
       </c>
       <c r="Z93">
-        <v>5.15</v>
+        <v>4.81</v>
       </c>
       <c r="AA93">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB93">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC93">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AD93">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE93">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF93">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AG93">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK93">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P94">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -15646,13 +15646,13 @@
         <v>2.11</v>
       </c>
       <c r="S94">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T94">
         <v>2.9</v>
       </c>
       <c r="U94">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="V94">
         <v>1.38</v>
@@ -15673,10 +15673,10 @@
         <v>2.02</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC94">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD94">
         <v>1.26</v>
@@ -15685,7 +15685,7 @@
         <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG94">
         <v>1.95</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O99">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P99">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q99">
         <v>2.35</v>
@@ -16461,7 +16461,7 @@
         <v>2.07</v>
       </c>
       <c r="S99">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
         <v>2.73</v>
@@ -16485,7 +16485,7 @@
         <v>3.18</v>
       </c>
       <c r="AA99">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB99">
         <v>1.8</v>
@@ -16494,16 +16494,16 @@
         <v>3.3</v>
       </c>
       <c r="AD99">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF99">
         <v>1.77</v>
       </c>
       <c r="AG99">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O100">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Q100">
         <v>2.8</v>
@@ -16627,7 +16627,7 @@
         <v>1.25</v>
       </c>
       <c r="T100">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U100">
         <v>2.33</v>
@@ -16636,7 +16636,7 @@
         <v>1.53</v>
       </c>
       <c r="W100">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
         <v>1.01</v>
@@ -16651,7 +16651,7 @@
         <v>1.6</v>
       </c>
       <c r="AB100">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC100">
         <v>2.34</v>
@@ -16666,7 +16666,7 @@
         <v>1.47</v>
       </c>
       <c r="AG100">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="O112">
-        <v>3.51</v>
+        <v>4.94</v>
       </c>
       <c r="P112">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="Q112">
+        <v>1.83</v>
+      </c>
+      <c r="R112">
+        <v>2.5</v>
+      </c>
+      <c r="S112">
+        <v>1.22</v>
+      </c>
+      <c r="T112">
+        <v>4.1</v>
+      </c>
+      <c r="U112">
+        <v>2.09</v>
+      </c>
+      <c r="V112">
+        <v>1.77</v>
+      </c>
+      <c r="W112">
+        <v>1.19</v>
+      </c>
+      <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>5.7</v>
+      </c>
+      <c r="AA112">
+        <v>1.44</v>
+      </c>
+      <c r="AB112">
+        <v>2.75</v>
+      </c>
+      <c r="AC112">
+        <v>2.11</v>
+      </c>
+      <c r="AD112">
+        <v>1.84</v>
+      </c>
+      <c r="AE112">
+        <v>1.34</v>
+      </c>
+      <c r="AF112">
+        <v>1.55</v>
+      </c>
+      <c r="AG112">
         <v>2.32</v>
       </c>
-      <c r="R112">
-        <v>2.32</v>
-      </c>
-      <c r="S112">
-        <v>1.28</v>
-      </c>
-      <c r="T112">
-        <v>3.48</v>
-      </c>
-      <c r="U112">
-        <v>2.39</v>
-      </c>
-      <c r="V112">
-        <v>1.6</v>
-      </c>
-      <c r="W112">
-        <v>1.13</v>
-      </c>
-      <c r="X112">
-        <v>1.01</v>
-      </c>
-      <c r="Y112">
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
         <v>1.2</v>
       </c>
-      <c r="Z112">
-        <v>4.7</v>
-      </c>
-      <c r="AA112">
-        <v>1.6</v>
-      </c>
-      <c r="AB112">
-        <v>2.37</v>
-      </c>
-      <c r="AC112">
-        <v>2.38</v>
-      </c>
-      <c r="AD112">
-        <v>1.5</v>
-      </c>
-      <c r="AE112">
-        <v>1.16</v>
-      </c>
-      <c r="AF112">
-        <v>1.54</v>
-      </c>
-      <c r="AG112">
-        <v>2.35</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.29</v>
-      </c>
       <c r="AK112">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="O113">
-        <v>4.94</v>
+        <v>3.51</v>
       </c>
       <c r="P113">
-        <v>6</v>
+        <v>3.51</v>
       </c>
       <c r="Q113">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="U113">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="V113">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="W113">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z113">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="AA113">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB113">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC113">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="AD113">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AE113">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AF113">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG113">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK113">
-        <v>2.84</v>
+        <v>2.02</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P132">
-        <v>4.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q132">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="R132">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T132">
         <v>2.82</v>
       </c>
       <c r="U132">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="V132">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W132">
+        <v>1.02</v>
+      </c>
+      <c r="X132">
+        <v>1.01</v>
+      </c>
+      <c r="Y132">
+        <v>1.33</v>
+      </c>
+      <c r="Z132">
+        <v>3.08</v>
+      </c>
+      <c r="AA132">
+        <v>1.92</v>
+      </c>
+      <c r="AB132">
+        <v>1.72</v>
+      </c>
+      <c r="AC132">
+        <v>3.48</v>
+      </c>
+      <c r="AD132">
+        <v>1.22</v>
+      </c>
+      <c r="AE132">
         <v>1.04</v>
       </c>
-      <c r="X132">
-        <v>1.03</v>
-      </c>
-      <c r="Y132">
-        <v>1.23</v>
-      </c>
-      <c r="Z132">
-        <v>3.42</v>
-      </c>
-      <c r="AA132">
-        <v>1.84</v>
-      </c>
-      <c r="AB132">
-        <v>1.86</v>
-      </c>
-      <c r="AC132">
-        <v>3.2</v>
-      </c>
-      <c r="AD132">
-        <v>1.28</v>
-      </c>
-      <c r="AE132">
-        <v>1.11</v>
-      </c>
       <c r="AF132">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG132">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK132">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O133">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P133">
-        <v>2.8</v>
+        <v>4.65</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R133">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="S133">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
         <v>2.82</v>
       </c>
       <c r="U133">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="V133">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W133">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y133">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z133">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA133">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AB133">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AC133">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AD133">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.46</v>
+        <v>2.18</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22477,16 +22477,16 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O136">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P136">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="Q136">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="R136">
         <v>2.1</v>
@@ -22510,10 +22510,10 @@
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z136">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AA136">
         <v>1.85</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK136">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22661,13 +22661,13 @@
         <v>3.28</v>
       </c>
       <c r="U137">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V137">
         <v>1.54</v>
       </c>
       <c r="W137">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
         <v>1.04</v>
@@ -22685,7 +22685,7 @@
         <v>2.25</v>
       </c>
       <c r="AC137">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AD137">
         <v>1.51</v>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK137">
         <v>2.04</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="O138">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P138">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q138">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R138">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S138">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T138">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U138">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V138">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W138">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z138">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA138">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB138">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC138">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AD138">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AE138">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF138">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="AG138">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK138">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="O139">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P139">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="Q139">
-        <v>3</v>
+        <v>4.23</v>
       </c>
       <c r="R139">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S139">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T139">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U139">
         <v>2.5</v>
       </c>
       <c r="V139">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W139">
         <v>1.07</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z139">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA139">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB139">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC139">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE139">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF139">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG139">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AK139">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O140">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P140">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q140">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="R140">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S140">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T140">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="U140">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V140">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W140">
         <v>1.07</v>
       </c>
       <c r="X140">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y140">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z140">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA140">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB140">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC140">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD140">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE140">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF140">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG140">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK140">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,28 +23292,28 @@
         </is>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O141">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P141">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q141">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="R141">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S141">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T141">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="U141">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V141">
         <v>1.44</v>
@@ -23322,34 +23322,34 @@
         <v>1.07</v>
       </c>
       <c r="X141">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z141">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA141">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB141">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AC141">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="AD141">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE141">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF141">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG141">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AK141">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23476,10 +23476,10 @@
         <v>2.81</v>
       </c>
       <c r="U142">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="V142">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W142">
         <v>1.03</v>
@@ -23494,13 +23494,13 @@
         <v>3.14</v>
       </c>
       <c r="AA142">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB142">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC142">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="AD142">
         <v>1.24</v>
@@ -23624,10 +23624,10 @@
         <v>3.65</v>
       </c>
       <c r="P143">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q143">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R143">
         <v>2.23</v>
@@ -23672,7 +23672,7 @@
         <v>1.1</v>
       </c>
       <c r="AF143">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG143">
         <v>2.15</v>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK143">
         <v>1.69</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="O144">
         <v>3.6</v>
       </c>
       <c r="P144">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q144">
-        <v>4.18</v>
+        <v>2.28</v>
       </c>
       <c r="R144">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S144">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T144">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
       <c r="U144">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V144">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X144">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y144">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z144">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="AA144">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AB144">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AC144">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD144">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE144">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF144">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AG144">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AK144">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,19 +23944,19 @@
         </is>
       </c>
       <c r="N145">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O145">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P145">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q145">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="R145">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S145">
         <v>1.39</v>
@@ -23965,7 +23965,7 @@
         <v>2.73</v>
       </c>
       <c r="U145">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="V145">
         <v>1.36</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="O146">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="P146">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q146">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R146">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S146">
         <v>1.23</v>
@@ -24128,7 +24128,7 @@
         <v>3.58</v>
       </c>
       <c r="U146">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V146">
         <v>1.62</v>
@@ -24146,22 +24146,22 @@
         <v>5.15</v>
       </c>
       <c r="AA146">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB146">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC146">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD146">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE146">
         <v>1.21</v>
       </c>
       <c r="AF146">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG146">
         <v>2.02</v>
@@ -24180,7 +24180,7 @@
         <v>1.16</v>
       </c>
       <c r="AK146">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="O150">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P150">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="Q150">
         <v>2.35</v>
@@ -24789,7 +24789,7 @@
         <v>1.04</v>
       </c>
       <c r="X150">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y150">
         <v>1.23</v>
@@ -24798,10 +24798,10 @@
         <v>3.44</v>
       </c>
       <c r="AA150">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB150">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC150">
         <v>3.1</v>
@@ -24832,7 +24832,7 @@
         <v>1.26</v>
       </c>
       <c r="AK150">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="O151">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="P151">
-        <v>6</v>
+        <v>4.65</v>
       </c>
       <c r="Q151">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="R151">
         <v>2.12</v>
@@ -24940,16 +24940,16 @@
         <v>1.4</v>
       </c>
       <c r="T151">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U151">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="V151">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W151">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X151">
         <v>1</v>
@@ -24964,7 +24964,7 @@
         <v>1.99</v>
       </c>
       <c r="AB151">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC151">
         <v>3.38</v>
@@ -25094,7 +25094,7 @@
         <v>2.55</v>
       </c>
       <c r="Q152">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="R152">
         <v>2.15</v>
@@ -25106,7 +25106,7 @@
         <v>3.04</v>
       </c>
       <c r="U152">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V152">
         <v>1.43</v>
@@ -25115,7 +25115,7 @@
         <v>1.05</v>
       </c>
       <c r="X152">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
         <v>1.19</v>
@@ -25130,7 +25130,7 @@
         <v>2</v>
       </c>
       <c r="AC152">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD152">
         <v>1.33</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK152">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25248,16 +25248,16 @@
         </is>
       </c>
       <c r="N153">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="O153">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P153">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q153">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="R153">
         <v>2.05</v>
@@ -25269,10 +25269,10 @@
         <v>2.69</v>
       </c>
       <c r="U153">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="V153">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W153">
         <v>1.05</v>
@@ -25281,31 +25281,31 @@
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z153">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="AA153">
         <v>1.93</v>
       </c>
       <c r="AB153">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC153">
         <v>3.5</v>
       </c>
       <c r="AD153">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE153">
         <v>1.05</v>
       </c>
       <c r="AF153">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG153">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25411,19 +25411,19 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O154">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P154">
-        <v>7.75</v>
+        <v>8.15</v>
       </c>
       <c r="Q154">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R154">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S154">
         <v>1.31</v>
@@ -25447,28 +25447,28 @@
         <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA154">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB154">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC154">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AD154">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE154">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG154">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK154">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25577,10 +25577,10 @@
         <v>2.37</v>
       </c>
       <c r="O155">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P155">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q155">
         <v>3.04</v>
@@ -25589,13 +25589,13 @@
         <v>2.04</v>
       </c>
       <c r="S155">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T155">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U155">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V155">
         <v>1.39</v>
@@ -25610,28 +25610,28 @@
         <v>1.29</v>
       </c>
       <c r="Z155">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AA155">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB155">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC155">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD155">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE155">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF155">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG155">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25737,28 +25737,28 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="O156">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P156">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q156">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="R156">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S156">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T156">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U156">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V156">
         <v>1.4</v>
@@ -25776,10 +25776,10 @@
         <v>3.3</v>
       </c>
       <c r="AA156">
+        <v>1.88</v>
+      </c>
+      <c r="AB156">
         <v>1.89</v>
-      </c>
-      <c r="AB156">
-        <v>1.9</v>
       </c>
       <c r="AC156">
         <v>2.99</v>
@@ -25791,7 +25791,7 @@
         <v>1.08</v>
       </c>
       <c r="AF156">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG156">
         <v>2</v>
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK156">
         <v>1.29</v>
@@ -25900,25 +25900,25 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O157">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P157">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q157">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="R157">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S157">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T157">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U157">
         <v>2.56</v>
@@ -25927,7 +25927,7 @@
         <v>1.41</v>
       </c>
       <c r="W157">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X157">
         <v>1.01</v>
@@ -25942,7 +25942,7 @@
         <v>1.75</v>
       </c>
       <c r="AB157">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC157">
         <v>2.85</v>
@@ -25954,7 +25954,7 @@
         <v>1.09</v>
       </c>
       <c r="AF157">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG157">
         <v>2.08</v>
@@ -26063,16 +26063,16 @@
         </is>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="O158">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="P158">
-        <v>3.15</v>
+        <v>3.77</v>
       </c>
       <c r="Q158">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="R158">
         <v>2.19</v>
@@ -26093,13 +26093,13 @@
         <v>1.08</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z158">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA158">
         <v>1.7</v>
@@ -26111,10 +26111,10 @@
         <v>2.61</v>
       </c>
       <c r="AD158">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AE158">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF158">
         <v>1.57</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="O159">
-        <v>4</v>
+        <v>4.54</v>
       </c>
       <c r="P159">
-        <v>6</v>
+        <v>6.54</v>
       </c>
       <c r="Q159">
         <v>2</v>
@@ -26247,7 +26247,7 @@
         <v>3.4</v>
       </c>
       <c r="U159">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="V159">
         <v>1.5</v>
@@ -26262,10 +26262,10 @@
         <v>1.15</v>
       </c>
       <c r="Z159">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA159">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB159">
         <v>2.2</v>
@@ -26274,16 +26274,16 @@
         <v>2.4</v>
       </c>
       <c r="AD159">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE159">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF159">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG159">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>1.21</v>
       </c>
       <c r="AK159">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,25 +26389,25 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O160">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P160">
-        <v>4.25</v>
+        <v>4.73</v>
       </c>
       <c r="Q160">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R160">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S160">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T160">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U160">
         <v>2.44</v>
@@ -26419,7 +26419,7 @@
         <v>1.07</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
         <v>1.2</v>
@@ -26443,10 +26443,10 @@
         <v>1.12</v>
       </c>
       <c r="AF160">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG160">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.24</v>
       </c>
       <c r="AK160">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="O161">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P161">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="Q161">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="R161">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S161">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T161">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="U161">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="V161">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W161">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X161">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
         <v>1.32</v>
       </c>
       <c r="Z161">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="AA161">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB161">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC161">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AD161">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE161">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF161">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG161">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK161">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.37</v>
+        <v>2.02</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="P162">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="Q162">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="R162">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S162">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T162">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U162">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V162">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W162">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X162">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z162">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA162">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB162">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC162">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AD162">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE162">
         <v>1.05</v>
       </c>
       <c r="AF162">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG162">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>1.3</v>
       </c>
       <c r="AK162">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="O163">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P163">
+        <v>3.8</v>
+      </c>
+      <c r="Q163">
+        <v>2.51</v>
+      </c>
+      <c r="R163">
+        <v>2.07</v>
+      </c>
+      <c r="S163">
+        <v>1.4</v>
+      </c>
+      <c r="T163">
+        <v>2.73</v>
+      </c>
+      <c r="U163">
         <v>2.75</v>
       </c>
-      <c r="Q163">
-        <v>2.95</v>
-      </c>
-      <c r="R163">
-        <v>2.33</v>
-      </c>
-      <c r="S163">
-        <v>1.33</v>
-      </c>
-      <c r="T163">
-        <v>3.04</v>
-      </c>
-      <c r="U163">
-        <v>2.59</v>
-      </c>
       <c r="V163">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W163">
+        <v>1.04</v>
+      </c>
+      <c r="X163">
+        <v>1.03</v>
+      </c>
+      <c r="Y163">
+        <v>1.26</v>
+      </c>
+      <c r="Z163">
+        <v>3.24</v>
+      </c>
+      <c r="AA163">
+        <v>1.9</v>
+      </c>
+      <c r="AB163">
+        <v>1.83</v>
+      </c>
+      <c r="AC163">
+        <v>3.05</v>
+      </c>
+      <c r="AD163">
+        <v>1.31</v>
+      </c>
+      <c r="AE163">
         <v>1.06</v>
       </c>
-      <c r="X163">
-        <v>1.02</v>
-      </c>
-      <c r="Y163">
-        <v>1.25</v>
-      </c>
-      <c r="Z163">
-        <v>3.82</v>
-      </c>
-      <c r="AA163">
-        <v>1.76</v>
-      </c>
-      <c r="AB163">
-        <v>2.07</v>
-      </c>
-      <c r="AC163">
-        <v>2.76</v>
-      </c>
-      <c r="AD163">
-        <v>1.35</v>
-      </c>
-      <c r="AE163">
-        <v>1.09</v>
-      </c>
       <c r="AF163">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG163">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>1.28</v>
       </c>
       <c r="AK163">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="O164">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P164">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q164">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="R164">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="S164">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T164">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U164">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="V164">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W164">
+        <v>1.06</v>
+      </c>
+      <c r="X164">
+        <v>1.02</v>
+      </c>
+      <c r="Y164">
+        <v>1.19</v>
+      </c>
+      <c r="Z164">
+        <v>3.82</v>
+      </c>
+      <c r="AA164">
+        <v>1.76</v>
+      </c>
+      <c r="AB164">
+        <v>2.03</v>
+      </c>
+      <c r="AC164">
+        <v>2.76</v>
+      </c>
+      <c r="AD164">
+        <v>1.35</v>
+      </c>
+      <c r="AE164">
         <v>1.09</v>
       </c>
-      <c r="X164">
-        <v>1.03</v>
-      </c>
-      <c r="Y164">
-        <v>1.14</v>
-      </c>
-      <c r="Z164">
-        <v>4.35</v>
-      </c>
-      <c r="AA164">
-        <v>1.61</v>
-      </c>
-      <c r="AB164">
-        <v>2.27</v>
-      </c>
-      <c r="AC164">
-        <v>2.36</v>
-      </c>
-      <c r="AD164">
-        <v>1.47</v>
-      </c>
-      <c r="AE164">
-        <v>1.16</v>
-      </c>
       <c r="AF164">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG164">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK164">
-        <v>2.22</v>
+        <v>1.54</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O165">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="P165">
         <v>4.8</v>
       </c>
       <c r="Q165">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="R165">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S165">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T165">
-        <v>2.94</v>
+        <v>3.22</v>
       </c>
       <c r="U165">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="V165">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="W165">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X165">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y165">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z165">
-        <v>3.44</v>
+        <v>4.35</v>
       </c>
       <c r="AA165">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AB165">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AC165">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD165">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE165">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF165">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AG165">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK165">
         <v>2.15</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
+        <v>1.7</v>
+      </c>
+      <c r="O166">
+        <v>3.7</v>
+      </c>
+      <c r="P166">
+        <v>4.8</v>
+      </c>
+      <c r="Q166">
         <v>2.2</v>
       </c>
-      <c r="O166">
-        <v>3.35</v>
-      </c>
-      <c r="P166">
-        <v>3.05</v>
-      </c>
-      <c r="Q166">
-        <v>2.87</v>
-      </c>
       <c r="R166">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S166">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T166">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="U166">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V166">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W166">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X166">
         <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z166">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AA166">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB166">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC166">
-        <v>3.24</v>
+        <v>2.82</v>
       </c>
       <c r="AD166">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE166">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF166">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG166">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK166">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="O167">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P167">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q167">
-        <v>2.98</v>
+        <v>2.2</v>
       </c>
       <c r="R167">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S167">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T167">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U167">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V167">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W167">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X167">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z167">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA167">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB167">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AC167">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AD167">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE167">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF167">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK167">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,37 +27693,37 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="O168">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="P168">
-        <v>4.4</v>
+        <v>2.89</v>
       </c>
       <c r="Q168">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="R168">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S168">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T168">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U168">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V168">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W168">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X168">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y168">
         <v>1.21</v>
@@ -27732,25 +27732,25 @@
         <v>3.62</v>
       </c>
       <c r="AA168">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AB168">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AC168">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AD168">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE168">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF168">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG168">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK168">
-        <v>2.09</v>
+        <v>1.52</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O169">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="P169">
-        <v>3.75</v>
+        <v>3.13</v>
       </c>
       <c r="Q169">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="R169">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S169">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T169">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U169">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V169">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W169">
+        <v>1.05</v>
+      </c>
+      <c r="X169">
+        <v>1.02</v>
+      </c>
+      <c r="Y169">
+        <v>1.32</v>
+      </c>
+      <c r="Z169">
+        <v>2.89</v>
+      </c>
+      <c r="AA169">
+        <v>2.15</v>
+      </c>
+      <c r="AB169">
+        <v>1.72</v>
+      </c>
+      <c r="AC169">
+        <v>3.54</v>
+      </c>
+      <c r="AD169">
+        <v>1.22</v>
+      </c>
+      <c r="AE169">
         <v>1.04</v>
       </c>
-      <c r="X169">
-        <v>1.03</v>
-      </c>
-      <c r="Y169">
-        <v>1.26</v>
-      </c>
-      <c r="Z169">
-        <v>3.24</v>
-      </c>
-      <c r="AA169">
-        <v>1.95</v>
-      </c>
-      <c r="AB169">
-        <v>1.83</v>
-      </c>
-      <c r="AC169">
-        <v>3.18</v>
-      </c>
-      <c r="AD169">
-        <v>1.31</v>
-      </c>
-      <c r="AE169">
-        <v>1.06</v>
-      </c>
       <c r="AF169">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG169">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK169">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O184">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P184">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
+        <v>2.25</v>
+      </c>
+      <c r="O215">
+        <v>3.4</v>
+      </c>
+      <c r="P215">
+        <v>2.8</v>
+      </c>
+      <c r="Q215">
+        <v>2.87</v>
+      </c>
+      <c r="R215">
+        <v>2.29</v>
+      </c>
+      <c r="S215">
+        <v>1.32</v>
+      </c>
+      <c r="T215">
+        <v>2.96</v>
+      </c>
+      <c r="U215">
         <v>2.5</v>
       </c>
-      <c r="O215">
-        <v>3.5</v>
-      </c>
-      <c r="P215">
-        <v>2.4</v>
-      </c>
-      <c r="Q215">
-        <v>3.2</v>
-      </c>
-      <c r="R215">
-        <v>2.17</v>
-      </c>
-      <c r="S215">
-        <v>1.3</v>
-      </c>
-      <c r="T215">
-        <v>3.08</v>
-      </c>
-      <c r="U215">
-        <v>2.47</v>
-      </c>
       <c r="V215">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W215">
         <v>1.09</v>
       </c>
       <c r="X215">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y215">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z215">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA215">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB215">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC215">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD215">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE215">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF215">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG215">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>1.24</v>
       </c>
       <c r="AK215">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35843,28 +35843,28 @@
         </is>
       </c>
       <c r="N218">
+        <v>3.3</v>
+      </c>
+      <c r="O218">
         <v>3.5</v>
       </c>
-      <c r="O218">
-        <v>3.6</v>
-      </c>
       <c r="P218">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q218">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R218">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S218">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T218">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U218">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V218">
         <v>1.58</v>
@@ -35873,7 +35873,7 @@
         <v>1.12</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
         <v>1.13</v>
@@ -35882,19 +35882,19 @@
         <v>4.5</v>
       </c>
       <c r="AA218">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB218">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC218">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD218">
         <v>1.55</v>
       </c>
       <c r="AE218">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF218">
         <v>1.5</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O227">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P227">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q227">
         <v>2.8</v>
@@ -37349,10 +37349,10 @@
         <v>5.3</v>
       </c>
       <c r="AA227">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB227">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AC227">
         <v>2.18</v>
@@ -37367,7 +37367,7 @@
         <v>1.39</v>
       </c>
       <c r="AG227">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O228">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="P228">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="Q228">
         <v>1.92</v>
@@ -37491,13 +37491,13 @@
         <v>1.16</v>
       </c>
       <c r="T228">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="U228">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V228">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W228">
         <v>1.25</v>
@@ -37518,10 +37518,10 @@
         <v>3.6</v>
       </c>
       <c r="AC228">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD228">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AE228">
         <v>1.44</v>
@@ -37817,13 +37817,13 @@
         <v>1.24</v>
       </c>
       <c r="T230">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="U230">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V230">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W230">
         <v>1.11</v>
@@ -37832,10 +37832,10 @@
         <v>1.03</v>
       </c>
       <c r="Y230">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z230">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA230">
         <v>1.57</v>
@@ -37844,10 +37844,10 @@
         <v>2.3</v>
       </c>
       <c r="AC230">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="AD230">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AE230">
         <v>1.18</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O231">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P231">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="Q231">
         <v>2.32</v>
@@ -37983,7 +37983,7 @@
         <v>3.42</v>
       </c>
       <c r="U231">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V231">
         <v>1.64</v>
@@ -37995,7 +37995,7 @@
         <v>1.02</v>
       </c>
       <c r="Y231">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z231">
         <v>4.95</v>
@@ -38007,10 +38007,10 @@
         <v>2.5</v>
       </c>
       <c r="AC231">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AD231">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE231">
         <v>1.23</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O240">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P240">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q240">
         <v>2.02</v>
@@ -39468,10 +39468,10 @@
         <v>5.65</v>
       </c>
       <c r="AA240">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AB240">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC240">
         <v>2.1</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB249">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G259">
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q259">
-        <v>2.73</v>
+        <v>2.27</v>
       </c>
       <c r="R259">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S259">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T259">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U259">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V259">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W259">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X259">
         <v>1.01</v>
       </c>
       <c r="Y259">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z259">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA259">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AB259">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC259">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD259">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE259">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF259">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG259">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK259">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O260">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P260">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Q260">
-        <v>2.27</v>
+        <v>4.27</v>
       </c>
       <c r="R260">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S260">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T260">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U260">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="V260">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W260">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X260">
         <v>1.01</v>
       </c>
       <c r="Y260">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z260">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA260">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AB260">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC260">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD260">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE260">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF260">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG260">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK260">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G261">
@@ -42861,7 +42861,7 @@
         <v>0</v>
       </c>
       <c r="Q261">
-        <v>4.27</v>
+        <v>2.73</v>
       </c>
       <c r="R261">
         <v>1.98</v>
@@ -42925,7 +42925,7 @@
         <v>1.26</v>
       </c>
       <c r="AK261">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -49372,19 +49372,19 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O301">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P301">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q301">
         <v>3</v>
       </c>
       <c r="R301">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S301">
         <v>1.29</v>
@@ -49399,7 +49399,7 @@
         <v>1.52</v>
       </c>
       <c r="W301">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X301">
         <v>1.03</v>
@@ -49417,7 +49417,7 @@
         <v>2.19</v>
       </c>
       <c r="AC301">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD301">
         <v>1.43</v>
@@ -50187,28 +50187,28 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O306">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P306">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="Q306">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="R306">
         <v>2.18</v>
       </c>
       <c r="S306">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T306">
         <v>2.96</v>
       </c>
       <c r="U306">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V306">
         <v>1.44</v>
@@ -50217,28 +50217,28 @@
         <v>1.07</v>
       </c>
       <c r="X306">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y306">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z306">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA306">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB306">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AC306">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AD306">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE306">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF306">
         <v>1.61</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O310">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="P310">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -51235,7 +51235,7 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AK312">
         <v>1.41</v>
@@ -51503,7 +51503,7 @@
         <v>2.5</v>
       </c>
       <c r="R314">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S314">
         <v>1.35</v>
@@ -51521,7 +51521,7 @@
         <v>1.06</v>
       </c>
       <c r="X314">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y314">
         <v>1.23</v>
@@ -51530,25 +51530,25 @@
         <v>3.44</v>
       </c>
       <c r="AA314">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB314">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC314">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="AD314">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE314">
         <v>1.09</v>
       </c>
       <c r="AF314">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG314">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK314">
         <v>1.82</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -52306,16 +52306,16 @@
         </is>
       </c>
       <c r="N319">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="O319">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P319">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="Q319">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R319">
         <v>2.04</v>
@@ -52339,10 +52339,10 @@
         <v>1.01</v>
       </c>
       <c r="Y319">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z319">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AA319">
         <v>1.98</v>
@@ -52379,7 +52379,7 @@
         <v>1.31</v>
       </c>
       <c r="AK319">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>7.75</v>
+        <v>5.75</v>
       </c>
       <c r="O325">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="P325">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q325">
         <v>7</v>
@@ -53299,10 +53299,10 @@
         <v>2.38</v>
       </c>
       <c r="S325">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T325">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="U325">
         <v>2.3</v>
@@ -53320,19 +53320,19 @@
         <v>1.14</v>
       </c>
       <c r="Z325">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA325">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB325">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC325">
         <v>2.35</v>
       </c>
       <c r="AD325">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE325">
         <v>1.19</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="O333">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="P333">
-        <v>4.61</v>
+        <v>4.75</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -55243,10 +55243,10 @@
         <v>2.1</v>
       </c>
       <c r="O337">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P337">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="Q337">
         <v>2.62</v>
@@ -55261,10 +55261,10 @@
         <v>2.59</v>
       </c>
       <c r="U337">
-        <v>2.91</v>
+        <v>3.15</v>
       </c>
       <c r="V337">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W337">
         <v>1.02</v>
@@ -55276,13 +55276,13 @@
         <v>1.36</v>
       </c>
       <c r="Z337">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA337">
         <v>2.23</v>
       </c>
       <c r="AB337">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC337">
         <v>3.85</v>
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="O338">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P338">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q338">
         <v>3.34</v>
@@ -55424,7 +55424,7 @@
         <v>3.1</v>
       </c>
       <c r="U338">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V338">
         <v>1.48</v>
@@ -55436,7 +55436,7 @@
         <v>1</v>
       </c>
       <c r="Y338">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z338">
         <v>3.8</v>
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK338">
         <v>1.35</v>
@@ -55738,19 +55738,19 @@
         <v>0</v>
       </c>
       <c r="Q340">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="R340">
         <v>2.26</v>
       </c>
       <c r="S340">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T340">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="U340">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="V340">
         <v>1.5</v>
@@ -55759,7 +55759,7 @@
         <v>1.11</v>
       </c>
       <c r="X340">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y340">
         <v>1.16</v>
@@ -55768,10 +55768,10 @@
         <v>4.1</v>
       </c>
       <c r="AA340">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB340">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC340">
         <v>2.46</v>
@@ -55783,10 +55783,10 @@
         <v>1.14</v>
       </c>
       <c r="AF340">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG340">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>1.21</v>
       </c>
       <c r="AK340">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55892,25 +55892,25 @@
         </is>
       </c>
       <c r="N341">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="O341">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="P341">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q341">
         <v>3.94</v>
       </c>
       <c r="R341">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S341">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T341">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U341">
         <v>3.11</v>
@@ -55934,7 +55934,7 @@
         <v>1.92</v>
       </c>
       <c r="AB341">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC341">
         <v>3.5</v>
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="O342">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P342">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q342">
         <v>3.5</v>
@@ -56076,10 +56076,10 @@
         <v>3.18</v>
       </c>
       <c r="U342">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V342">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W342">
         <v>1.1</v>
@@ -56109,7 +56109,7 @@
         <v>1.14</v>
       </c>
       <c r="AF342">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG342">
         <v>2.29</v>
@@ -56128,7 +56128,7 @@
         <v>1.22</v>
       </c>
       <c r="AK342">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="O343">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P343">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="Q343">
         <v>2.26</v>
@@ -56254,13 +56254,13 @@
         <v>1.17</v>
       </c>
       <c r="Z343">
-        <v>4.07</v>
+        <v>3.96</v>
       </c>
       <c r="AA343">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB343">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC343">
         <v>2.52</v>
@@ -56390,7 +56390,7 @@
         <v>0</v>
       </c>
       <c r="Q344">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R344">
         <v>2.13</v>
@@ -56423,7 +56423,7 @@
         <v>1.94</v>
       </c>
       <c r="AB344">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC344">
         <v>2.85</v>
@@ -56435,10 +56435,10 @@
         <v>1.06</v>
       </c>
       <c r="AF344">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG344">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK344">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56870,64 +56870,64 @@
         </is>
       </c>
       <c r="N347">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="O347">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P347">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="Q347">
         <v>2.8</v>
       </c>
       <c r="R347">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S347">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T347">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U347">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V347">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W347">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X347">
         <v>1.01</v>
       </c>
       <c r="Y347">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z347">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA347">
         <v>1.85</v>
       </c>
       <c r="AB347">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC347">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="AD347">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE347">
         <v>1.08</v>
       </c>
       <c r="AF347">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG347">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH347" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>5.35</v>
       </c>
       <c r="P348">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q348">
         <v>1.72</v>
@@ -57060,7 +57060,7 @@
         <v>1.6</v>
       </c>
       <c r="W348">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X348">
         <v>1.02</v>
@@ -57072,7 +57072,7 @@
         <v>4.7</v>
       </c>
       <c r="AA348">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB348">
         <v>2.37</v>
@@ -57087,10 +57087,10 @@
         <v>1.19</v>
       </c>
       <c r="AF348">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG348">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>1.1</v>
       </c>
       <c r="AK348">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AL348">
         <v>0</v>
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57359,19 +57359,19 @@
         </is>
       </c>
       <c r="N350">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="O350">
-        <v>5.06</v>
+        <v>4.5</v>
       </c>
       <c r="P350">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="Q350">
         <v>2.05</v>
       </c>
       <c r="R350">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S350">
         <v>1.2</v>
@@ -57380,10 +57380,10 @@
         <v>4.33</v>
       </c>
       <c r="U350">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V350">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="W350">
         <v>1.2</v>
@@ -57401,22 +57401,22 @@
         <v>1.36</v>
       </c>
       <c r="AB350">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AC350">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD350">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AE350">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AF350">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG350">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH350" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>1.13</v>
       </c>
       <c r="AK350">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57522,16 +57522,16 @@
         </is>
       </c>
       <c r="N351">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O351">
-        <v>4.06</v>
+        <v>3.55</v>
       </c>
       <c r="P351">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q351">
-        <v>3.37</v>
+        <v>2.99</v>
       </c>
       <c r="R351">
         <v>2.3</v>
@@ -57567,13 +57567,13 @@
         <v>2.41</v>
       </c>
       <c r="AC351">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AD351">
         <v>1.58</v>
       </c>
       <c r="AE351">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF351">
         <v>1.44</v>
@@ -57595,7 +57595,7 @@
         <v>1.2</v>
       </c>
       <c r="AK351">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -57685,40 +57685,40 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O352">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="P352">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="Q352">
         <v>2.4</v>
       </c>
       <c r="R352">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="S352">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T352">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U352">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="V352">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W352">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X352">
         <v>1.04</v>
       </c>
       <c r="Y352">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z352">
         <v>3.95</v>
@@ -57758,7 +57758,7 @@
         <v>1.25</v>
       </c>
       <c r="AK352">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="O353">
-        <v>5</v>
+        <v>3.32</v>
       </c>
       <c r="P353">
-        <v>5.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q353">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="R353">
-        <v>3.13</v>
+        <v>2.3</v>
       </c>
       <c r="S353">
+        <v>1.3</v>
+      </c>
+      <c r="T353">
+        <v>3.4</v>
+      </c>
+      <c r="U353">
+        <v>2.41</v>
+      </c>
+      <c r="V353">
+        <v>1.51</v>
+      </c>
+      <c r="W353">
+        <v>1.1</v>
+      </c>
+      <c r="X353">
+        <v>1.02</v>
+      </c>
+      <c r="Y353">
+        <v>1.2</v>
+      </c>
+      <c r="Z353">
+        <v>4.2</v>
+      </c>
+      <c r="AA353">
+        <v>1.7</v>
+      </c>
+      <c r="AB353">
+        <v>2.17</v>
+      </c>
+      <c r="AC353">
+        <v>2.73</v>
+      </c>
+      <c r="AD353">
+        <v>1.45</v>
+      </c>
+      <c r="AE353">
         <v>1.14</v>
       </c>
-      <c r="T353">
-        <v>5.25</v>
-      </c>
-      <c r="U353">
-        <v>1.78</v>
-      </c>
-      <c r="V353">
-        <v>2.02</v>
-      </c>
-      <c r="W353">
-        <v>1.29</v>
-      </c>
-      <c r="X353">
-        <v>0</v>
-      </c>
-      <c r="Y353">
-        <v>1.05</v>
-      </c>
-      <c r="Z353">
-        <v>9</v>
-      </c>
-      <c r="AA353">
-        <v>1.25</v>
-      </c>
-      <c r="AB353">
-        <v>3.87</v>
-      </c>
-      <c r="AC353">
-        <v>1.67</v>
-      </c>
-      <c r="AD353">
-        <v>2.24</v>
-      </c>
-      <c r="AE353">
+      <c r="AF353">
         <v>1.53</v>
       </c>
-      <c r="AF353">
-        <v>1.36</v>
-      </c>
       <c r="AG353">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57918,10 +57918,10 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK353">
-        <v>2.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="O354">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="P354">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q354">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="R354">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="S354">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T354">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="U354">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="V354">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="W354">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="X354">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y354">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="Z354">
-        <v>4.32</v>
+        <v>9</v>
       </c>
       <c r="AA354">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AB354">
-        <v>2.17</v>
+        <v>3.87</v>
       </c>
       <c r="AC354">
-        <v>2.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD354">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="AE354">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AF354">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG354">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58081,10 +58081,10 @@
         </is>
       </c>
       <c r="AJ354">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK354">
-        <v>1.62</v>
+        <v>2.61</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58177,7 +58177,7 @@
         <v>2.05</v>
       </c>
       <c r="O355">
-        <v>4.5</v>
+        <v>3.63</v>
       </c>
       <c r="P355">
         <v>2.87</v>
@@ -58189,49 +58189,49 @@
         <v>2.7</v>
       </c>
       <c r="S355">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T355">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U355">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V355">
         <v>1.88</v>
       </c>
       <c r="W355">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X355">
         <v>0</v>
       </c>
       <c r="Y355">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z355">
-        <v>6.8</v>
+        <v>6.87</v>
       </c>
       <c r="AA355">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB355">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AC355">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AD355">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AE355">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF355">
         <v>1.32</v>
       </c>
       <c r="AG355">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH355" t="inlineStr">
         <is>
@@ -58244,10 +58244,10 @@
         </is>
       </c>
       <c r="AJ355">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK355">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -58337,25 +58337,25 @@
         </is>
       </c>
       <c r="N356">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="O356">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="P356">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Q356">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R356">
         <v>2.34</v>
       </c>
       <c r="S356">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T356">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U356">
         <v>2.16</v>
@@ -58388,7 +58388,7 @@
         <v>1.69</v>
       </c>
       <c r="AE356">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF356">
         <v>1.53</v>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK356">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58826,19 +58826,19 @@
         </is>
       </c>
       <c r="N359">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="O359">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P359">
         <v>4.2</v>
       </c>
       <c r="Q359">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="R359">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S359">
         <v>1.41</v>
@@ -58856,13 +58856,13 @@
         <v>1.02</v>
       </c>
       <c r="X359">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y359">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z359">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA359">
         <v>2.05</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="AJ359">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK359">
         <v>1.94</v>
@@ -58995,7 +58995,7 @@
         <v>3.25</v>
       </c>
       <c r="P360">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="Q360">
         <v>2.55</v>
@@ -59034,10 +59034,10 @@
         <v>1.77</v>
       </c>
       <c r="AC360">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD360">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE360">
         <v>1.08</v>
@@ -59046,7 +59046,7 @@
         <v>1.73</v>
       </c>
       <c r="AG360">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -60130,16 +60130,16 @@
         </is>
       </c>
       <c r="N367">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O367">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P367">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="Q367">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R367">
         <v>2.15</v>
@@ -60148,10 +60148,10 @@
         <v>1.38</v>
       </c>
       <c r="T367">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U367">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V367">
         <v>1.36</v>
@@ -60169,25 +60169,25 @@
         <v>3.08</v>
       </c>
       <c r="AA367">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB367">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC367">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="AD367">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE367">
         <v>1.06</v>
       </c>
       <c r="AF367">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG367">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH367" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>1.26</v>
       </c>
       <c r="AK367">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL367">
         <v>0</v>
@@ -60293,13 +60293,13 @@
         </is>
       </c>
       <c r="N368">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O368">
         <v>4.6</v>
       </c>
       <c r="P368">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="Q368">
         <v>1.79</v>
@@ -60317,7 +60317,7 @@
         <v>2.02</v>
       </c>
       <c r="V368">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W368">
         <v>1.17</v>
@@ -60326,10 +60326,10 @@
         <v>0</v>
       </c>
       <c r="Y368">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z368">
-        <v>5.55</v>
+        <v>5.83</v>
       </c>
       <c r="AA368">
         <v>1.44</v>
@@ -60341,16 +60341,16 @@
         <v>2.13</v>
       </c>
       <c r="AD368">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE368">
         <v>1.3</v>
       </c>
       <c r="AF368">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG368">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH368" t="inlineStr">
         <is>
@@ -60363,10 +60363,10 @@
         </is>
       </c>
       <c r="AJ368">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK368">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AL368">
         <v>0</v>
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,80 +60456,80 @@
         </is>
       </c>
       <c r="N369">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O369">
-        <v>4.61</v>
+        <v>3.5</v>
       </c>
       <c r="P369">
-        <v>3.71</v>
+        <v>2.75</v>
       </c>
       <c r="Q369">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="R369">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S369">
+        <v>1.25</v>
+      </c>
+      <c r="T369">
+        <v>3.75</v>
+      </c>
+      <c r="U369">
+        <v>2.26</v>
+      </c>
+      <c r="V369">
+        <v>1.62</v>
+      </c>
+      <c r="W369">
+        <v>1.14</v>
+      </c>
+      <c r="X369">
+        <v>0</v>
+      </c>
+      <c r="Y369">
+        <v>1.16</v>
+      </c>
+      <c r="Z369">
+        <v>5.2</v>
+      </c>
+      <c r="AA369">
+        <v>1.5</v>
+      </c>
+      <c r="AB369">
+        <v>2.46</v>
+      </c>
+      <c r="AC369">
+        <v>2.25</v>
+      </c>
+      <c r="AD369">
+        <v>1.61</v>
+      </c>
+      <c r="AE369">
+        <v>1.25</v>
+      </c>
+      <c r="AF369">
+        <v>1.44</v>
+      </c>
+      <c r="AG369">
+        <v>2.62</v>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ369">
         <v>1.2</v>
       </c>
-      <c r="T369">
-        <v>4.33</v>
-      </c>
-      <c r="U369">
-        <v>2.04</v>
-      </c>
-      <c r="V369">
-        <v>1.78</v>
-      </c>
-      <c r="W369">
-        <v>1.18</v>
-      </c>
-      <c r="X369">
-        <v>0</v>
-      </c>
-      <c r="Y369">
-        <v>1.12</v>
-      </c>
-      <c r="Z369">
-        <v>6.27</v>
-      </c>
-      <c r="AA369">
-        <v>1.4</v>
-      </c>
-      <c r="AB369">
-        <v>2.87</v>
-      </c>
-      <c r="AC369">
-        <v>1.99</v>
-      </c>
-      <c r="AD369">
-        <v>1.83</v>
-      </c>
-      <c r="AE369">
-        <v>1.33</v>
-      </c>
-      <c r="AF369">
-        <v>1.36</v>
-      </c>
-      <c r="AG369">
-        <v>2.9</v>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ369">
-        <v>1.18</v>
-      </c>
       <c r="AK369">
-        <v>1.91</v>
+        <v>1.56</v>
       </c>
       <c r="AL369">
         <v>0</v>
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G370">
@@ -60619,64 +60619,64 @@
         </is>
       </c>
       <c r="N370">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="O370">
+        <v>3.9</v>
+      </c>
+      <c r="P370">
         <v>3.7</v>
       </c>
-      <c r="P370">
-        <v>2.95</v>
-      </c>
       <c r="Q370">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="R370">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S370">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T370">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U370">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="V370">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W370">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X370">
         <v>0</v>
       </c>
       <c r="Y370">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z370">
-        <v>5.2</v>
+        <v>6.27</v>
       </c>
       <c r="AA370">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB370">
-        <v>2.46</v>
+        <v>2.87</v>
       </c>
       <c r="AC370">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD370">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE370">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF370">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG370">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AH370" t="inlineStr">
         <is>
@@ -60689,10 +60689,10 @@
         </is>
       </c>
       <c r="AJ370">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK370">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AL370">
         <v>0</v>
@@ -60785,7 +60785,7 @@
         <v>3.3</v>
       </c>
       <c r="O371">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P371">
         <v>1.9</v>
@@ -60797,7 +60797,7 @@
         <v>2.27</v>
       </c>
       <c r="S371">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T371">
         <v>2.96</v>
@@ -60830,10 +60830,10 @@
         <v>3.15</v>
       </c>
       <c r="AD371">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE371">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF371">
         <v>1.68</v>
@@ -60852,7 +60852,7 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK371">
         <v>1.22</v>
@@ -60945,13 +60945,13 @@
         </is>
       </c>
       <c r="N372">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="O372">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="P372">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Q372">
         <v>2.74</v>
@@ -60966,7 +60966,7 @@
         <v>3.6</v>
       </c>
       <c r="U372">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V372">
         <v>1.57</v>
@@ -60978,16 +60978,16 @@
         <v>1.03</v>
       </c>
       <c r="Y372">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z372">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA372">
         <v>1.57</v>
       </c>
       <c r="AB372">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC372">
         <v>2.49</v>
@@ -60999,10 +60999,10 @@
         <v>1.22</v>
       </c>
       <c r="AF372">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG372">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH372" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>2.3</v>
       </c>
       <c r="O373">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P373">
         <v>2.7</v>
@@ -61274,10 +61274,10 @@
         <v>2.95</v>
       </c>
       <c r="O374">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="P374">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q374">
         <v>3.62</v>
@@ -61292,7 +61292,7 @@
         <v>3.08</v>
       </c>
       <c r="U374">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="V374">
         <v>1.5</v>
@@ -61341,10 +61341,10 @@
         </is>
       </c>
       <c r="AJ374">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK374">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AL374">
         <v>0</v>
@@ -61434,19 +61434,19 @@
         </is>
       </c>
       <c r="N375">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O375">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="P375">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q375">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R375">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S375">
         <v>1.34</v>
@@ -61488,10 +61488,10 @@
         <v>1.07</v>
       </c>
       <c r="AF375">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG375">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH375" t="inlineStr">
         <is>
@@ -61504,7 +61504,7 @@
         </is>
       </c>
       <c r="AJ375">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK375">
         <v>1.53</v>
@@ -61597,13 +61597,13 @@
         </is>
       </c>
       <c r="N376">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O376">
-        <v>5.44</v>
+        <v>4.6</v>
       </c>
       <c r="P376">
-        <v>6.68</v>
+        <v>5.7</v>
       </c>
       <c r="Q376">
         <v>1.87</v>
@@ -61618,13 +61618,13 @@
         <v>4.1</v>
       </c>
       <c r="U376">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V376">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W376">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X376">
         <v>0</v>
@@ -61633,7 +61633,7 @@
         <v>1.14</v>
       </c>
       <c r="Z376">
-        <v>5.79</v>
+        <v>6.25</v>
       </c>
       <c r="AA376">
         <v>1.44</v>
@@ -61645,10 +61645,10 @@
         <v>2.1</v>
       </c>
       <c r="AD376">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE376">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF376">
         <v>1.57</v>
@@ -61667,10 +61667,10 @@
         </is>
       </c>
       <c r="AJ376">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK376">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL376">
         <v>0</v>
@@ -61760,22 +61760,22 @@
         </is>
       </c>
       <c r="N377">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O377">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P377">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="Q377">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="R377">
         <v>2.38</v>
       </c>
       <c r="S377">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T377">
         <v>3.75</v>
@@ -61830,10 +61830,10 @@
         </is>
       </c>
       <c r="AJ377">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK377">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL377">
         <v>0</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.67</v>
+        <v>3.4</v>
       </c>
       <c r="R3">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.83</v>
       </c>
       <c r="U3">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC3">
-        <v>3.72</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
+        <v>2.47</v>
+      </c>
+      <c r="U4">
+        <v>3.04</v>
+      </c>
+      <c r="V4">
+        <v>1.3</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1.06</v>
+      </c>
+      <c r="Y4">
+        <v>1.33</v>
+      </c>
+      <c r="Z4">
         <v>2.83</v>
       </c>
-      <c r="U4">
-        <v>2.74</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
-      <c r="W4">
-        <v>1.06</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.23</v>
-      </c>
-      <c r="Z4">
-        <v>3.42</v>
-      </c>
       <c r="AA4">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>2.92</v>
+        <v>3.72</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U50">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="W50">
+        <v>1.12</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.14</v>
+      </c>
+      <c r="Z50">
+        <v>4.45</v>
+      </c>
+      <c r="AA50">
+        <v>1.6</v>
+      </c>
+      <c r="AB50">
+        <v>2.36</v>
+      </c>
+      <c r="AC50">
+        <v>2.4</v>
+      </c>
+      <c r="AD50">
+        <v>1.54</v>
+      </c>
+      <c r="AE50">
         <v>1.17</v>
       </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>1.07</v>
-      </c>
-      <c r="Z50">
-        <v>5.95</v>
-      </c>
-      <c r="AA50">
-        <v>1.36</v>
-      </c>
-      <c r="AB50">
-        <v>2.7</v>
-      </c>
-      <c r="AC50">
-        <v>2.01</v>
-      </c>
-      <c r="AD50">
-        <v>1.79</v>
-      </c>
-      <c r="AE50">
-        <v>1.34</v>
-      </c>
       <c r="AF50">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="AA51">
+        <v>1.36</v>
+      </c>
+      <c r="AB51">
+        <v>2.7</v>
+      </c>
+      <c r="AC51">
+        <v>2.01</v>
+      </c>
+      <c r="AD51">
+        <v>1.79</v>
+      </c>
+      <c r="AE51">
+        <v>1.34</v>
+      </c>
+      <c r="AF51">
+        <v>1.4</v>
+      </c>
+      <c r="AG51">
+        <v>2.75</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.22</v>
+      </c>
+      <c r="AK51">
         <v>1.6</v>
-      </c>
-      <c r="AB51">
-        <v>2.36</v>
-      </c>
-      <c r="AC51">
-        <v>2.4</v>
-      </c>
-      <c r="AD51">
-        <v>1.54</v>
-      </c>
-      <c r="AE51">
-        <v>1.17</v>
-      </c>
-      <c r="AF51">
-        <v>1.7</v>
-      </c>
-      <c r="AG51">
-        <v>2.04</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.19</v>
-      </c>
-      <c r="AK51">
-        <v>2.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
+        <v>2.8</v>
+      </c>
+      <c r="O64">
+        <v>3.6</v>
+      </c>
+      <c r="P64">
         <v>2.25</v>
       </c>
-      <c r="O64">
-        <v>3.5</v>
-      </c>
-      <c r="P64">
-        <v>2.5</v>
-      </c>
       <c r="Q64">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="R64">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S64">
+        <v>1.27</v>
+      </c>
+      <c r="T64">
+        <v>3.25</v>
+      </c>
+      <c r="U64">
+        <v>2.33</v>
+      </c>
+      <c r="V64">
+        <v>1.5</v>
+      </c>
+      <c r="W64">
+        <v>1.09</v>
+      </c>
+      <c r="X64">
+        <v>1.04</v>
+      </c>
+      <c r="Y64">
         <v>1.2</v>
       </c>
-      <c r="T64">
-        <v>3.7</v>
-      </c>
-      <c r="U64">
-        <v>2.07</v>
-      </c>
-      <c r="V64">
-        <v>1.67</v>
-      </c>
-      <c r="W64">
-        <v>1.15</v>
-      </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.09</v>
-      </c>
       <c r="Z64">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA64">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB64">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.06</v>
+        <v>2.53</v>
       </c>
       <c r="AD64">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AE64">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF64">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>3.02</v>
+        <v>2.56</v>
       </c>
       <c r="R65">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="S65">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="V65">
+        <v>1.67</v>
+      </c>
+      <c r="W65">
+        <v>1.15</v>
+      </c>
+      <c r="X65">
+        <v>1.02</v>
+      </c>
+      <c r="Y65">
+        <v>1.09</v>
+      </c>
+      <c r="Z65">
+        <v>5.3</v>
+      </c>
+      <c r="AA65">
+        <v>1.44</v>
+      </c>
+      <c r="AB65">
+        <v>2.59</v>
+      </c>
+      <c r="AC65">
+        <v>2.06</v>
+      </c>
+      <c r="AD65">
+        <v>1.68</v>
+      </c>
+      <c r="AE65">
+        <v>1.25</v>
+      </c>
+      <c r="AF65">
+        <v>1.37</v>
+      </c>
+      <c r="AG65">
+        <v>2.71</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.19</v>
+      </c>
+      <c r="AK65">
         <v>1.5</v>
-      </c>
-      <c r="W65">
-        <v>1.09</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.2</v>
-      </c>
-      <c r="Z65">
-        <v>4.3</v>
-      </c>
-      <c r="AA65">
-        <v>1.56</v>
-      </c>
-      <c r="AB65">
-        <v>2.25</v>
-      </c>
-      <c r="AC65">
-        <v>2.53</v>
-      </c>
-      <c r="AD65">
-        <v>1.45</v>
-      </c>
-      <c r="AE65">
-        <v>1.19</v>
-      </c>
-      <c r="AF65">
-        <v>1.5</v>
-      </c>
-      <c r="AG65">
-        <v>2.38</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.22</v>
-      </c>
-      <c r="AK65">
-        <v>1.34</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,16 +13675,16 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O82">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q82">
-        <v>2.67</v>
+        <v>2.27</v>
       </c>
       <c r="R82">
         <v>2.1</v>
@@ -13693,46 +13693,46 @@
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="U82">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V82">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W82">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z82">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA82">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB82">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AD82">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG82">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P83">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="R83">
         <v>2.1</v>
@@ -13856,46 +13856,46 @@
         <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U83">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V83">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
+        <v>1.27</v>
+      </c>
+      <c r="Z83">
+        <v>3.14</v>
+      </c>
+      <c r="AA83">
+        <v>1.94</v>
+      </c>
+      <c r="AB83">
+        <v>1.77</v>
+      </c>
+      <c r="AC83">
+        <v>3.45</v>
+      </c>
+      <c r="AD83">
         <v>1.28</v>
       </c>
-      <c r="Z83">
-        <v>3.28</v>
-      </c>
-      <c r="AA83">
-        <v>1.95</v>
-      </c>
-      <c r="AB83">
-        <v>1.85</v>
-      </c>
-      <c r="AC83">
-        <v>3.04</v>
-      </c>
-      <c r="AD83">
-        <v>1.29</v>
-      </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF83">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG83">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK83">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.25</v>
+        <v>1.16</v>
       </c>
       <c r="O120">
-        <v>3.22</v>
+        <v>7.3</v>
       </c>
       <c r="P120">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="Q120">
-        <v>3.07</v>
+        <v>1.48</v>
       </c>
       <c r="R120">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="S120">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="T120">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
       <c r="U120">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X120">
         <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Z120">
+        <v>6.5</v>
+      </c>
+      <c r="AA120">
+        <v>1.33</v>
+      </c>
+      <c r="AB120">
         <v>3.4</v>
       </c>
-      <c r="AA120">
-        <v>1.9</v>
-      </c>
-      <c r="AB120">
-        <v>2.01</v>
-      </c>
       <c r="AC120">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="AD120">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="AE120">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AF120">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AG120">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AK120">
-        <v>1.65</v>
+        <v>5.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O121">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P121">
-        <v>2.9</v>
+        <v>5.2</v>
       </c>
       <c r="Q121">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="R121">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="S121">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T121">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="U121">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V121">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W121">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z121">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AA121">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC121">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD121">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE121">
         <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="O122">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="P122">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="Q122">
-        <v>1.48</v>
+        <v>3.04</v>
       </c>
       <c r="R122">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="S122">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="U122">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="V122">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="W122">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z122">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA122">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AB122">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC122">
-        <v>1.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD122">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF122">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG122">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AK122">
-        <v>5.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,80 +20358,80 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="O123">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="P123">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q123">
-        <v>2.05</v>
+        <v>3.07</v>
       </c>
       <c r="R123">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="S123">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="U123">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V123">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W123">
         <v>1.08</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z123">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AA123">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB123">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC123">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD123">
+        <v>1.32</v>
+      </c>
+      <c r="AE123">
+        <v>1.08</v>
+      </c>
+      <c r="AF123">
+        <v>1.67</v>
+      </c>
+      <c r="AG123">
+        <v>2.1</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
         <v>1.35</v>
       </c>
-      <c r="AE123">
-        <v>1.1</v>
-      </c>
-      <c r="AF123">
-        <v>1.83</v>
-      </c>
-      <c r="AG123">
-        <v>2</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.27</v>
-      </c>
       <c r="AK123">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,31 +21662,31 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="O131">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P131">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q131">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="R131">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S131">
         <v>1.41</v>
       </c>
       <c r="T131">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="U131">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V131">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W131">
         <v>1.02</v>
@@ -21695,31 +21695,31 @@
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z131">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA131">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AB131">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC131">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="AD131">
         <v>1.22</v>
       </c>
       <c r="AE131">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF131">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK131">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,31 +21825,31 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="O132">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P132">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q132">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="R132">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S132">
         <v>1.41</v>
       </c>
       <c r="T132">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="U132">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="V132">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W132">
         <v>1.02</v>
@@ -21858,31 +21858,31 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z132">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA132">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AB132">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC132">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="AD132">
         <v>1.22</v>
       </c>
       <c r="AE132">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF132">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG132">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK132">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,28 +22966,28 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O139">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="Q139">
-        <v>4.23</v>
+        <v>2.53</v>
       </c>
       <c r="R139">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S139">
         <v>1.32</v>
       </c>
       <c r="T139">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="U139">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V139">
         <v>1.46</v>
@@ -22996,34 +22996,34 @@
         <v>1.07</v>
       </c>
       <c r="X139">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z139">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AA139">
         <v>1.73</v>
       </c>
       <c r="AB139">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC139">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD139">
         <v>1.36</v>
       </c>
       <c r="AE139">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF139">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG139">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AK139">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O140">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P140">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q140">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="R140">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S140">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T140">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="U140">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="V140">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W140">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X140">
+        <v>1.02</v>
+      </c>
+      <c r="Y140">
+        <v>1.27</v>
+      </c>
+      <c r="Z140">
+        <v>3.14</v>
+      </c>
+      <c r="AA140">
+        <v>1.98</v>
+      </c>
+      <c r="AB140">
+        <v>1.78</v>
+      </c>
+      <c r="AC140">
+        <v>3.46</v>
+      </c>
+      <c r="AD140">
+        <v>1.24</v>
+      </c>
+      <c r="AE140">
         <v>1.04</v>
       </c>
-      <c r="Y140">
-        <v>1.18</v>
-      </c>
-      <c r="Z140">
-        <v>3.88</v>
-      </c>
-      <c r="AA140">
-        <v>1.73</v>
-      </c>
-      <c r="AB140">
-        <v>2.05</v>
-      </c>
-      <c r="AC140">
-        <v>2.66</v>
-      </c>
-      <c r="AD140">
-        <v>1.36</v>
-      </c>
-      <c r="AE140">
-        <v>1.1</v>
-      </c>
       <c r="AF140">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AG140">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK140">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O142">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P142">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q142">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="R142">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="S142">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T142">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="U142">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="V142">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W142">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X142">
         <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z142">
-        <v>3.14</v>
+        <v>4.01</v>
       </c>
       <c r="AA142">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB142">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AC142">
-        <v>3.46</v>
+        <v>2.74</v>
       </c>
       <c r="AD142">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE142">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF142">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG142">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK142">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="O143">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P143">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q143">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="R143">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S143">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T143">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U143">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V143">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W143">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X143">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y143">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z143">
-        <v>4.01</v>
+        <v>3.14</v>
       </c>
       <c r="AA143">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AB143">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AC143">
-        <v>2.74</v>
+        <v>3.34</v>
       </c>
       <c r="AD143">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE143">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF143">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AG143">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>1.26</v>
       </c>
       <c r="AK143">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,80 +23781,80 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="O144">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P144">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="Q144">
-        <v>2.28</v>
+        <v>4.23</v>
       </c>
       <c r="R144">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S144">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T144">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="U144">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
+        <v>1.46</v>
+      </c>
+      <c r="W144">
+        <v>1.07</v>
+      </c>
+      <c r="X144">
+        <v>1.03</v>
+      </c>
+      <c r="Y144">
+        <v>1.2</v>
+      </c>
+      <c r="Z144">
+        <v>3.8</v>
+      </c>
+      <c r="AA144">
+        <v>1.73</v>
+      </c>
+      <c r="AB144">
+        <v>2.04</v>
+      </c>
+      <c r="AC144">
+        <v>2.7</v>
+      </c>
+      <c r="AD144">
         <v>1.36</v>
       </c>
-      <c r="W144">
-        <v>1.03</v>
-      </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="Y144">
-        <v>1.27</v>
-      </c>
-      <c r="Z144">
-        <v>3.14</v>
-      </c>
-      <c r="AA144">
-        <v>2.05</v>
-      </c>
-      <c r="AB144">
+      <c r="AE144">
+        <v>1.11</v>
+      </c>
+      <c r="AF144">
+        <v>1.62</v>
+      </c>
+      <c r="AG144">
+        <v>2.17</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
         <v>1.79</v>
       </c>
-      <c r="AC144">
-        <v>3.34</v>
-      </c>
-      <c r="AD144">
-        <v>1.24</v>
-      </c>
-      <c r="AE144">
-        <v>1.05</v>
-      </c>
-      <c r="AF144">
-        <v>1.87</v>
-      </c>
-      <c r="AG144">
-        <v>1.83</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>1.26</v>
-      </c>
       <c r="AK144">
-        <v>2.06</v>
+        <v>1.19</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="O151">
-        <v>3.97</v>
+        <v>3.5</v>
       </c>
       <c r="P151">
-        <v>4.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q151">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="R151">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T151">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="U151">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="V151">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W151">
         <v>1.05</v>
       </c>
       <c r="X151">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z151">
-        <v>3.18</v>
+        <v>3.76</v>
       </c>
       <c r="AA151">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AB151">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC151">
-        <v>3.38</v>
+        <v>2.85</v>
       </c>
       <c r="AD151">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF151">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AG151">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK151">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="O152">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P152">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="Q152">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="R152">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S152">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T152">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="U152">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="V152">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W152">
         <v>1.05</v>
       </c>
       <c r="X152">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z152">
-        <v>3.76</v>
+        <v>2.99</v>
       </c>
       <c r="AA152">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB152">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC152">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AD152">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE152">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF152">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AG152">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK152">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="O153">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P153">
-        <v>4.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q153">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="R153">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S153">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T153">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U153">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V153">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W153">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X153">
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z153">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA153">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB153">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC153">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD153">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE153">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF153">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AG153">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK153">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,34 +25574,34 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.37</v>
+        <v>3.21</v>
       </c>
       <c r="O155">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P155">
-        <v>2.87</v>
+        <v>2.13</v>
       </c>
       <c r="Q155">
-        <v>3.04</v>
+        <v>4.16</v>
       </c>
       <c r="R155">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="S155">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T155">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U155">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V155">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
         <v>1.01</v>
@@ -25610,7 +25610,7 @@
         <v>1.29</v>
       </c>
       <c r="Z155">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA155">
         <v>1.88</v>
@@ -25619,35 +25619,35 @@
         <v>1.89</v>
       </c>
       <c r="AC155">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AD155">
+        <v>1.3</v>
+      </c>
+      <c r="AE155">
+        <v>1.08</v>
+      </c>
+      <c r="AF155">
+        <v>1.69</v>
+      </c>
+      <c r="AG155">
+        <v>2</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.29</v>
       </c>
-      <c r="AE155">
-        <v>1.12</v>
-      </c>
-      <c r="AF155">
-        <v>1.66</v>
-      </c>
-      <c r="AG155">
-        <v>2.09</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.31</v>
-      </c>
       <c r="AK155">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.21</v>
+        <v>1.66</v>
       </c>
       <c r="O156">
-        <v>3.55</v>
+        <v>3.97</v>
       </c>
       <c r="P156">
+        <v>4.65</v>
+      </c>
+      <c r="Q156">
         <v>2.13</v>
       </c>
-      <c r="Q156">
-        <v>4.16</v>
-      </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="U156">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V156">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W156">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z156">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA156">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AB156">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AC156">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="AD156">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE156">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF156">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="AG156">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK156">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="O163">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="P163">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="Q163">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="R163">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S163">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T163">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U163">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="V163">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W163">
+        <v>1.05</v>
+      </c>
+      <c r="X163">
+        <v>1.02</v>
+      </c>
+      <c r="Y163">
+        <v>1.32</v>
+      </c>
+      <c r="Z163">
+        <v>2.89</v>
+      </c>
+      <c r="AA163">
+        <v>2.15</v>
+      </c>
+      <c r="AB163">
+        <v>1.72</v>
+      </c>
+      <c r="AC163">
+        <v>3.54</v>
+      </c>
+      <c r="AD163">
+        <v>1.22</v>
+      </c>
+      <c r="AE163">
         <v>1.04</v>
       </c>
-      <c r="X163">
-        <v>1.03</v>
-      </c>
-      <c r="Y163">
-        <v>1.26</v>
-      </c>
-      <c r="Z163">
-        <v>3.24</v>
-      </c>
-      <c r="AA163">
-        <v>1.9</v>
-      </c>
-      <c r="AB163">
-        <v>1.83</v>
-      </c>
-      <c r="AC163">
-        <v>3.05</v>
-      </c>
-      <c r="AD163">
-        <v>1.31</v>
-      </c>
-      <c r="AE163">
-        <v>1.06</v>
-      </c>
       <c r="AF163">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG163">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK163">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="O164">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P164">
-        <v>2.75</v>
+        <v>4.15</v>
       </c>
       <c r="Q164">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="R164">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S164">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T164">
-        <v>3.04</v>
+        <v>3.23</v>
       </c>
       <c r="U164">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="V164">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W164">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X164">
         <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z164">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA164">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AB164">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC164">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="AD164">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE164">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF164">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG164">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK164">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O166">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P166">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q166">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="R166">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S166">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T166">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U166">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V166">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W166">
         <v>1.06</v>
       </c>
       <c r="X166">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y166">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z166">
-        <v>3.52</v>
+        <v>3.82</v>
       </c>
       <c r="AA166">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB166">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC166">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="AD166">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE166">
         <v>1.09</v>
       </c>
       <c r="AF166">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AG166">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK166">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O167">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P167">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="Q167">
         <v>2.2</v>
       </c>
       <c r="R167">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S167">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T167">
-        <v>3.23</v>
+        <v>2.94</v>
       </c>
       <c r="U167">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="V167">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W167">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X167">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z167">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA167">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AB167">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC167">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="AD167">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE167">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF167">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG167">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.23</v>
       </c>
       <c r="AK167">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,80 +27856,80 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="O169">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P169">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="Q169">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="R169">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S169">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T169">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U169">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V169">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W169">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y169">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z169">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="AA169">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB169">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC169">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AD169">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE169">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG169">
+        <v>1.92</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ169">
+        <v>1.28</v>
+      </c>
+      <c r="AK169">
         <v>1.85</v>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ169">
-        <v>1.32</v>
-      </c>
-      <c r="AK169">
-        <v>1.5</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -46939,43 +46939,43 @@
         <v>3</v>
       </c>
       <c r="R286">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="S286">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="T286">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U286">
         <v>4.2</v>
       </c>
       <c r="V286">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W286">
         <v>1.03</v>
       </c>
       <c r="X286">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Y286">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z286">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA286">
         <v>3.4</v>
       </c>
       <c r="AB286">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AC286">
-        <v>7.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD286">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE286">
         <v>1.02</v>
@@ -47096,49 +47096,49 @@
         <v>2.62</v>
       </c>
       <c r="P287">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="Q287">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="R287">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="S287">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T287">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U287">
         <v>4</v>
       </c>
       <c r="V287">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W287">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X287">
         <v>1.09</v>
       </c>
       <c r="Y287">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z287">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AA287">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB287">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC287">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AD287">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE287">
         <v>1.03</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK287">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O302">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P302">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q302">
         <v>2.9</v>
@@ -49553,7 +49553,7 @@
         <v>1.64</v>
       </c>
       <c r="T302">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="U302">
         <v>4.05</v>
@@ -49562,28 +49562,28 @@
         <v>1.17</v>
       </c>
       <c r="W302">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y302">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z302">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AA302">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="AB302">
         <v>1.3</v>
       </c>
       <c r="AC302">
-        <v>6.19</v>
+        <v>6.5</v>
       </c>
       <c r="AD302">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE302">
         <v>1.03</v>
@@ -49605,7 +49605,7 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK302">
         <v>1.53</v>
@@ -51500,55 +51500,55 @@
         <v>0</v>
       </c>
       <c r="Q314">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R314">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S314">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T314">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U314">
         <v>2.75</v>
       </c>
       <c r="V314">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W314">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X314">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y314">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z314">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA314">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB314">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC314">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AD314">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE314">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF314">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG314">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK314">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51823,22 +51823,22 @@
         <v>2.62</v>
       </c>
       <c r="P316">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="Q316">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R316">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S316">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T316">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U316">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="V316">
         <v>1.15</v>
@@ -51850,13 +51850,13 @@
         <v>1.15</v>
       </c>
       <c r="Y316">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z316">
         <v>2.1</v>
       </c>
       <c r="AA316">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB316">
         <v>1.33</v>
@@ -51871,10 +51871,10 @@
         <v>1.03</v>
       </c>
       <c r="AF316">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AG316">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK316">
         <v>1.7</v>
@@ -53610,43 +53610,43 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="O327">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="P327">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q327">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="R327">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S327">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T327">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U327">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="V327">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W327">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X327">
         <v>1.06</v>
       </c>
       <c r="Y327">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z327">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AA327">
         <v>2.4</v>
@@ -53655,19 +53655,19 @@
         <v>1.53</v>
       </c>
       <c r="AC327">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AD327">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE327">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF327">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG327">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>2.73</v>
       </c>
       <c r="U328">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="V328">
         <v>1.36</v>
@@ -53806,10 +53806,10 @@
         <v>1.03</v>
       </c>
       <c r="Y328">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z328">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA328">
         <v>2</v>
@@ -53830,7 +53830,7 @@
         <v>2.05</v>
       </c>
       <c r="AG328">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -54425,19 +54425,19 @@
         </is>
       </c>
       <c r="N332">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="O332">
-        <v>2.87</v>
+        <v>1.85</v>
       </c>
       <c r="P332">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="Q332">
         <v>2.66</v>
       </c>
       <c r="R332">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S332">
         <v>1.62</v>
@@ -54446,43 +54446,43 @@
         <v>2.15</v>
       </c>
       <c r="U332">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="V332">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W332">
         <v>1.03</v>
       </c>
       <c r="X332">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y332">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z332">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AA332">
         <v>2.74</v>
       </c>
       <c r="AB332">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC332">
         <v>5.6</v>
       </c>
       <c r="AD332">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE332">
         <v>1.03</v>
       </c>
       <c r="AF332">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG332">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AK332">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54751,34 +54751,34 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="O334">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="P334">
         <v>3.5</v>
       </c>
       <c r="Q334">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="R334">
         <v>1.91</v>
       </c>
       <c r="S334">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="T334">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="U334">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="V334">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W334">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X334">
         <v>1.08</v>
@@ -54790,7 +54790,7 @@
         <v>2.33</v>
       </c>
       <c r="AA334">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AB334">
         <v>1.47</v>
@@ -54821,10 +54821,10 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK334">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -55246,7 +55246,7 @@
         <v>3.3</v>
       </c>
       <c r="P337">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q337">
         <v>2.62</v>
@@ -55255,43 +55255,43 @@
         <v>2.02</v>
       </c>
       <c r="S337">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T337">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U337">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V337">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W337">
         <v>1.02</v>
       </c>
       <c r="X337">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y337">
         <v>1.36</v>
       </c>
       <c r="Z337">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA337">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AB337">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC337">
         <v>3.85</v>
       </c>
       <c r="AD337">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE337">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF337">
         <v>1.9</v>
@@ -55406,58 +55406,58 @@
         <v>2.65</v>
       </c>
       <c r="O338">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P338">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q338">
         <v>3.34</v>
       </c>
       <c r="R338">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S338">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T338">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U338">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="V338">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W338">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X338">
         <v>1</v>
       </c>
       <c r="Y338">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z338">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA338">
         <v>1.8</v>
       </c>
       <c r="AB338">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC338">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD338">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE338">
         <v>1.11</v>
       </c>
       <c r="AF338">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG338">
         <v>2.16</v>
@@ -55476,7 +55476,7 @@
         <v>1.23</v>
       </c>
       <c r="AK338">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55566,7 +55566,7 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="O339">
         <v>3.2</v>
@@ -55581,7 +55581,7 @@
         <v>1.96</v>
       </c>
       <c r="S339">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T339">
         <v>2.54</v>
@@ -55593,7 +55593,7 @@
         <v>1.33</v>
       </c>
       <c r="W339">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X339">
         <v>1.03</v>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK339">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55898,13 +55898,13 @@
         <v>2.93</v>
       </c>
       <c r="P341">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q341">
         <v>3.94</v>
       </c>
       <c r="R341">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S341">
         <v>1.4</v>
@@ -55931,7 +55931,7 @@
         <v>2.97</v>
       </c>
       <c r="AA341">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AB341">
         <v>1.7</v>
@@ -55949,7 +55949,7 @@
         <v>1.85</v>
       </c>
       <c r="AG341">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH341" t="inlineStr">
         <is>
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="O342">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="P342">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q342">
         <v>3.5</v>
@@ -56070,16 +56070,16 @@
         <v>2.3</v>
       </c>
       <c r="S342">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T342">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U342">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="V342">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W342">
         <v>1.1</v>
@@ -56091,28 +56091,28 @@
         <v>1.16</v>
       </c>
       <c r="Z342">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA342">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB342">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AC342">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD342">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE342">
         <v>1.14</v>
       </c>
       <c r="AF342">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG342">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK342">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56224,19 +56224,19 @@
         <v>3.45</v>
       </c>
       <c r="P343">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="Q343">
         <v>2.26</v>
       </c>
       <c r="R343">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S343">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T343">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U343">
         <v>2.5</v>
@@ -56254,7 +56254,7 @@
         <v>1.17</v>
       </c>
       <c r="Z343">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="AA343">
         <v>1.65</v>
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O344">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P344">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q344">
         <v>2.28</v>
@@ -56423,13 +56423,13 @@
         <v>1.94</v>
       </c>
       <c r="AB344">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC344">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="AD344">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE344">
         <v>1.06</v>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK344">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56876,13 +56876,13 @@
         <v>3</v>
       </c>
       <c r="P347">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q347">
         <v>2.8</v>
       </c>
       <c r="R347">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S347">
         <v>1.33</v>
@@ -56891,10 +56891,10 @@
         <v>2.9</v>
       </c>
       <c r="U347">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V347">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W347">
         <v>1.06</v>
@@ -56912,19 +56912,19 @@
         <v>1.85</v>
       </c>
       <c r="AB347">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC347">
         <v>3.06</v>
       </c>
       <c r="AD347">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE347">
         <v>1.08</v>
       </c>
       <c r="AF347">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG347">
         <v>2.1</v>
@@ -56940,7 +56940,7 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK347">
         <v>1.54</v>
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="O348">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="P348">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="Q348">
         <v>1.72</v>
@@ -57054,13 +57054,13 @@
         <v>3.75</v>
       </c>
       <c r="U348">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="V348">
         <v>1.6</v>
       </c>
       <c r="W348">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X348">
         <v>1.02</v>
@@ -57078,13 +57078,13 @@
         <v>2.37</v>
       </c>
       <c r="AC348">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AD348">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE348">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF348">
         <v>1.78</v>
@@ -57106,7 +57106,7 @@
         <v>1.1</v>
       </c>
       <c r="AK348">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AL348">
         <v>0</v>
@@ -58829,31 +58829,31 @@
         <v>1.91</v>
       </c>
       <c r="O359">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P359">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q359">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R359">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S359">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T359">
         <v>2.69</v>
       </c>
       <c r="U359">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="V359">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W359">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X359">
         <v>1</v>
@@ -58865,10 +58865,10 @@
         <v>2.99</v>
       </c>
       <c r="AA359">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB359">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC359">
         <v>3.62</v>
@@ -58880,10 +58880,10 @@
         <v>1.03</v>
       </c>
       <c r="AF359">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG359">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH359" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>1.16</v>
       </c>
       <c r="AK359">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58989,31 +58989,31 @@
         </is>
       </c>
       <c r="N360">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="O360">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P360">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="Q360">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="R360">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="S360">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T360">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U360">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="V360">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W360">
         <v>1.07</v>
@@ -59022,31 +59022,31 @@
         <v>1.01</v>
       </c>
       <c r="Y360">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z360">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA360">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB360">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC360">
         <v>3.2</v>
       </c>
       <c r="AD360">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE360">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF360">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG360">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -59059,10 +59059,10 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK360">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL360">
         <v>0</v>
@@ -60130,19 +60130,19 @@
         </is>
       </c>
       <c r="N367">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="O367">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P367">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="Q367">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="R367">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S367">
         <v>1.38</v>
@@ -60151,7 +60151,7 @@
         <v>2.7</v>
       </c>
       <c r="U367">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="V367">
         <v>1.36</v>
@@ -60166,13 +60166,13 @@
         <v>1.28</v>
       </c>
       <c r="Z367">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA367">
         <v>2.02</v>
       </c>
       <c r="AB367">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC367">
         <v>3.52</v>
@@ -60184,7 +60184,7 @@
         <v>1.06</v>
       </c>
       <c r="AF367">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG367">
         <v>1.95</v>
@@ -60203,7 +60203,7 @@
         <v>1.26</v>
       </c>
       <c r="AK367">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL367">
         <v>0</v>
@@ -60782,31 +60782,31 @@
         </is>
       </c>
       <c r="N371">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O371">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P371">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q371">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="R371">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="S371">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T371">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U371">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V371">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W371">
         <v>1.06</v>
@@ -60818,22 +60818,22 @@
         <v>1.22</v>
       </c>
       <c r="Z371">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AA371">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB371">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AC371">
         <v>3.15</v>
       </c>
       <c r="AD371">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE371">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF371">
         <v>1.68</v>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK371">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL371">
         <v>0</v>
@@ -61271,13 +61271,13 @@
         </is>
       </c>
       <c r="N374">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="O374">
         <v>3.18</v>
       </c>
       <c r="P374">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q374">
         <v>3.62</v>
@@ -61286,10 +61286,10 @@
         <v>2.2</v>
       </c>
       <c r="S374">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T374">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="U374">
         <v>2.33</v>
@@ -61313,7 +61313,7 @@
         <v>1.68</v>
       </c>
       <c r="AB374">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AC374">
         <v>2.59</v>
@@ -61325,7 +61325,7 @@
         <v>1.12</v>
       </c>
       <c r="AF374">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG374">
         <v>2.25</v>
@@ -61440,10 +61440,10 @@
         <v>3.02</v>
       </c>
       <c r="P375">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="Q375">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="R375">
         <v>2.08</v>
@@ -61467,19 +61467,19 @@
         <v>1</v>
       </c>
       <c r="Y375">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z375">
         <v>3.5</v>
       </c>
       <c r="AA375">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB375">
         <v>1.89</v>
       </c>
       <c r="AC375">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD375">
         <v>1.31</v>

--- a/jogos_2026-09-05.xlsx
+++ b/jogos_2026-09-05.xlsx
@@ -662,10 +662,10 @@
         <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.2</v>
@@ -674,13 +674,13 @@
         <v>3.9</v>
       </c>
       <c r="AA2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AD2">
         <v>1.4</v>
@@ -689,10 +689,10 @@
         <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="R3">
         <v>2.2</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="U3">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.06</v>
@@ -831,13 +831,13 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.42</v>
+        <v>3.64</v>
       </c>
       <c r="AA3">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB3">
         <v>1.92</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="O4">
         <v>3.1</v>
@@ -970,7 +970,7 @@
         <v>3.6</v>
       </c>
       <c r="Q4">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>1.94</v>
@@ -991,7 +991,7 @@
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.33</v>
@@ -1000,7 +1000,7 @@
         <v>2.83</v>
       </c>
       <c r="AA4">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB4">
         <v>1.64</v>
@@ -1018,7 +1018,7 @@
         <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.31</v>
+        <v>2.98</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="P16">
-        <v>5.6</v>
+        <v>1.97</v>
       </c>
       <c r="Q16">
-        <v>1.86</v>
+        <v>3.43</v>
       </c>
       <c r="R16">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="S16">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA16">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AD16">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>2.57</v>
+        <v>1.23</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.98</v>
+        <v>1.31</v>
       </c>
       <c r="O17">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
-        <v>1.97</v>
+        <v>5.6</v>
       </c>
       <c r="Q17">
-        <v>3.43</v>
+        <v>1.86</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="AA17">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC17">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>1.23</v>
+        <v>2.57</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="O43">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P43">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="R43">
         <v>2</v>
       </c>
       <c r="S43">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T43">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="V43">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z43">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB43">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG43">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P44">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="Q44">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="R44">
         <v>2</v>
       </c>
       <c r="S44">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AA44">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC44">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AD44">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
         <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="V50">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="AA50">
+        <v>1.36</v>
+      </c>
+      <c r="AB50">
+        <v>2.7</v>
+      </c>
+      <c r="AC50">
+        <v>2.01</v>
+      </c>
+      <c r="AD50">
+        <v>1.79</v>
+      </c>
+      <c r="AE50">
+        <v>1.34</v>
+      </c>
+      <c r="AF50">
+        <v>1.4</v>
+      </c>
+      <c r="AG50">
+        <v>2.75</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.22</v>
+      </c>
+      <c r="AK50">
         <v>1.6</v>
-      </c>
-      <c r="AB50">
-        <v>2.36</v>
-      </c>
-      <c r="AC50">
-        <v>2.4</v>
-      </c>
-      <c r="AD50">
-        <v>1.54</v>
-      </c>
-      <c r="AE50">
-        <v>1.17</v>
-      </c>
-      <c r="AF50">
-        <v>1.7</v>
-      </c>
-      <c r="AG50">
-        <v>2.04</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.19</v>
-      </c>
-      <c r="AK50">
-        <v>2.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U51">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="V51">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="W51">
+        <v>1.12</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.14</v>
+      </c>
+      <c r="Z51">
+        <v>4.45</v>
+      </c>
+      <c r="AA51">
+        <v>1.6</v>
+      </c>
+      <c r="AB51">
+        <v>2.36</v>
+      </c>
+      <c r="AC51">
+        <v>2.4</v>
+      </c>
+      <c r="AD51">
+        <v>1.54</v>
+      </c>
+      <c r="AE51">
         <v>1.17</v>
       </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
-        <v>1.07</v>
-      </c>
-      <c r="Z51">
-        <v>5.95</v>
-      </c>
-      <c r="AA51">
-        <v>1.36</v>
-      </c>
-      <c r="AB51">
-        <v>2.7</v>
-      </c>
-      <c r="AC51">
-        <v>2.01</v>
-      </c>
-      <c r="AD51">
-        <v>1.79</v>
-      </c>
-      <c r="AE51">
-        <v>1.34</v>
-      </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8797,13 +8797,13 @@
         <v>1.56</v>
       </c>
       <c r="R52">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="S52">
         <v>1.2</v>
       </c>
       <c r="T52">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U52">
         <v>2</v>
@@ -8815,7 +8815,7 @@
         <v>1.18</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.13</v>
@@ -8827,7 +8827,7 @@
         <v>1.43</v>
       </c>
       <c r="AB52">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AC52">
         <v>2.06</v>
@@ -8839,10 +8839,10 @@
         <v>1.26</v>
       </c>
       <c r="AF52">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG52">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.05</v>
       </c>
       <c r="AK52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9929,10 +9929,10 @@
         <v>2.66</v>
       </c>
       <c r="O59">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10415,37 +10415,37 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P62">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q62">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="R62">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T62">
         <v>3.34</v>
       </c>
       <c r="U62">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
         <v>1.12</v>
@@ -10454,19 +10454,19 @@
         <v>4.7</v>
       </c>
       <c r="AA62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC62">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AD62">
         <v>1.54</v>
       </c>
       <c r="AE62">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
         <v>1.53</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O63">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P63">
         <v>1.93</v>
@@ -10596,46 +10596,46 @@
         <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U63">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V63">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA63">
         <v>1.57</v>
       </c>
       <c r="AB63">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC63">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AD63">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF63">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG63">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10744,61 +10744,61 @@
         <v>2.8</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q64">
-        <v>3.02</v>
+        <v>4.06</v>
       </c>
       <c r="R64">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S64">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W64">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA64">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB64">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC64">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AD64">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE64">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF64">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG64">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK64">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q65">
-        <v>2.56</v>
+        <v>2.01</v>
       </c>
       <c r="R65">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="S65">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T65">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U65">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="V65">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>5.3</v>
+        <v>4.95</v>
       </c>
       <c r="AA65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AC65">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="AD65">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AG65">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="O66">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>4.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="R66">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T66">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="U66">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA66">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB66">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AC66">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE66">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF66">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AG66">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P70">
         <v>3</v>
       </c>
       <c r="Q70">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="R70">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T70">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="U70">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="V70">
         <v>1.37</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA70">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB70">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC70">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD70">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG70">
         <v>1.93</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK70">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11888,7 +11888,7 @@
         <v>3.4</v>
       </c>
       <c r="P71">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -14167,55 +14167,55 @@
         <v>2.2</v>
       </c>
       <c r="O85">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="Q85">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S85">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T85">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U85">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V85">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W85">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
         <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z85">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA85">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB85">
         <v>1.65</v>
       </c>
       <c r="AC85">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AD85">
         <v>1.2</v>
       </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF85">
         <v>1.84</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O95">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q95">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="R95">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S95">
         <v>1.31</v>
@@ -15815,43 +15815,43 @@
         <v>3.1</v>
       </c>
       <c r="U95">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W95">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>4.56</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB95">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC95">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="AD95">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG95">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,19 +15957,19 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q96">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="R96">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S96">
         <v>1.31</v>
@@ -15978,43 +15978,43 @@
         <v>3.1</v>
       </c>
       <c r="U96">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V96">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z96">
-        <v>4.25</v>
+        <v>4.56</v>
       </c>
       <c r="AA96">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB96">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC96">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="AD96">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE96">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK96">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O102">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P102">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q102">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R102">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S102">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T102">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U102">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V102">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA102">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB102">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AC102">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD102">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG102">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK102">
-        <v>3.24</v>
+        <v>4.2</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17427,10 +17427,10 @@
         <v>1.9</v>
       </c>
       <c r="O105">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P105">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="Q105">
         <v>2.5</v>
@@ -17439,22 +17439,22 @@
         <v>1.95</v>
       </c>
       <c r="S105">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="T105">
         <v>2.53</v>
       </c>
       <c r="U105">
-        <v>3.16</v>
+        <v>2.88</v>
       </c>
       <c r="V105">
         <v>1.35</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
         <v>1.35</v>
@@ -17463,10 +17463,10 @@
         <v>3.3</v>
       </c>
       <c r="AA105">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB105">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC105">
         <v>3.6</v>
@@ -17475,13 +17475,13 @@
         <v>1.24</v>
       </c>
       <c r="AE105">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
         <v>1.93</v>
       </c>
       <c r="AG105">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="O106">
         <v>3.4</v>
@@ -17611,7 +17611,7 @@
         <v>2.25</v>
       </c>
       <c r="V106">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
         <v>1.14</v>
@@ -17620,13 +17620,13 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
         <v>4.45</v>
       </c>
       <c r="AA106">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB106">
         <v>2.27</v>
@@ -17635,7 +17635,7 @@
         <v>2.35</v>
       </c>
       <c r="AD106">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE106">
         <v>1.16</v>
@@ -17753,13 +17753,13 @@
         <v>2.11</v>
       </c>
       <c r="O107">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P107">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q107">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R107">
         <v>2.19</v>
@@ -17771,10 +17771,10 @@
         <v>3.15</v>
       </c>
       <c r="U107">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V107">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W107">
         <v>1.1</v>
@@ -17792,7 +17792,7 @@
         <v>1.72</v>
       </c>
       <c r="AB107">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC107">
         <v>2.66</v>
@@ -17807,7 +17807,7 @@
         <v>1.56</v>
       </c>
       <c r="AG107">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O108">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P108">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="Q108">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R108">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S108">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U108">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="V108">
         <v>1.5</v>
       </c>
       <c r="W108">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X108">
         <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="AA108">
         <v>1.67</v>
       </c>
       <c r="AB108">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC108">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AD108">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG108">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>1.2</v>
       </c>
       <c r="AK108">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18239,34 +18239,34 @@
         </is>
       </c>
       <c r="N110">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O110">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P110">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q110">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R110">
         <v>2.28</v>
       </c>
       <c r="S110">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T110">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="U110">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="V110">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
         <v>1.01</v>
@@ -18275,13 +18275,13 @@
         <v>1.17</v>
       </c>
       <c r="Z110">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA110">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB110">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AC110">
         <v>2.53</v>
@@ -18293,10 +18293,10 @@
         <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG110">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="AK110">
         <v>1.34</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O111">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
         <v>2.25</v>
       </c>
       <c r="Q111">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="R111">
         <v>2.5</v>
       </c>
       <c r="S111">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="U111">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V111">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W111">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X111">
         <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z111">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA111">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB111">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC111">
         <v>2.1</v>
       </c>
       <c r="AD111">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE111">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF111">
         <v>1.36</v>
       </c>
       <c r="AG111">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK111">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="O112">
-        <v>4.94</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="Q112">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="R112">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S112">
         <v>1.22</v>
       </c>
       <c r="T112">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="U112">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="V112">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="W112">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z112">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA112">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB112">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC112">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="AD112">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AE112">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AF112">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG112">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK112">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,65 +18728,65 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="O113">
-        <v>3.51</v>
+        <v>4.8</v>
       </c>
       <c r="P113">
-        <v>3.51</v>
+        <v>6</v>
       </c>
       <c r="Q113">
+        <v>1.87</v>
+      </c>
+      <c r="R113">
+        <v>2.64</v>
+      </c>
+      <c r="S113">
+        <v>1.22</v>
+      </c>
+      <c r="T113">
+        <v>4.05</v>
+      </c>
+      <c r="U113">
+        <v>2.09</v>
+      </c>
+      <c r="V113">
+        <v>1.77</v>
+      </c>
+      <c r="W113">
+        <v>1.2</v>
+      </c>
+      <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.08</v>
+      </c>
+      <c r="Z113">
+        <v>6</v>
+      </c>
+      <c r="AA113">
+        <v>1.4</v>
+      </c>
+      <c r="AB113">
+        <v>2.64</v>
+      </c>
+      <c r="AC113">
+        <v>2.05</v>
+      </c>
+      <c r="AD113">
+        <v>1.84</v>
+      </c>
+      <c r="AE113">
+        <v>1.29</v>
+      </c>
+      <c r="AF113">
+        <v>1.55</v>
+      </c>
+      <c r="AG113">
         <v>2.32</v>
       </c>
-      <c r="R113">
-        <v>2.32</v>
-      </c>
-      <c r="S113">
-        <v>1.28</v>
-      </c>
-      <c r="T113">
-        <v>3.48</v>
-      </c>
-      <c r="U113">
-        <v>2.39</v>
-      </c>
-      <c r="V113">
-        <v>1.6</v>
-      </c>
-      <c r="W113">
-        <v>1.13</v>
-      </c>
-      <c r="X113">
-        <v>1.01</v>
-      </c>
-      <c r="Y113">
-        <v>1.2</v>
-      </c>
-      <c r="Z113">
-        <v>4.7</v>
-      </c>
-      <c r="AA113">
-        <v>1.6</v>
-      </c>
-      <c r="AB113">
-        <v>2.37</v>
-      </c>
-      <c r="AC113">
-        <v>2.38</v>
-      </c>
-      <c r="AD113">
-        <v>1.5</v>
-      </c>
-      <c r="AE113">
-        <v>1.16</v>
-      </c>
-      <c r="AF113">
-        <v>1.54</v>
-      </c>
-      <c r="AG113">
-        <v>2.35</v>
-      </c>
       <c r="AH113" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK113">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18897,28 +18897,28 @@
         <v>3.9</v>
       </c>
       <c r="P114">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q114">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="R114">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S114">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T114">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="U114">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="V114">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="W114">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X114">
         <v>1.02</v>
@@ -18927,28 +18927,28 @@
         <v>1.1</v>
       </c>
       <c r="Z114">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA114">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB114">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC114">
         <v>2.2</v>
       </c>
       <c r="AD114">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE114">
         <v>1.25</v>
       </c>
       <c r="AF114">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG114">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="O120">
-        <v>7.3</v>
+        <v>3.5</v>
       </c>
       <c r="P120">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="Q120">
-        <v>1.48</v>
+        <v>3.04</v>
       </c>
       <c r="R120">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="S120">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="U120">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="V120">
-        <v>1.79</v>
+        <v>1.42</v>
       </c>
       <c r="W120">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA120">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
-        <v>1.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD120">
-        <v>1.97</v>
+        <v>1.3</v>
       </c>
       <c r="AE120">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AG120">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AK120">
-        <v>5.4</v>
+        <v>1.59</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,37 +20195,37 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O122">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P122">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q122">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="R122">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="U122">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V122">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
         <v>1.26</v>
@@ -20237,22 +20237,22 @@
         <v>1.9</v>
       </c>
       <c r="AB122">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC122">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE122">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK122">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.25</v>
+        <v>1.16</v>
       </c>
       <c r="O123">
-        <v>3.22</v>
+        <v>7.3</v>
       </c>
       <c r="P123">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="Q123">
-        <v>3.07</v>
+        <v>1.48</v>
       </c>
       <c r="R123">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="S123">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="T123">
-        <v>2.89</v>
+        <v>4.75</v>
       </c>
       <c r="U123">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="V123">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="W123">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X123">
         <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Z123">
+        <v>6.5</v>
+      </c>
+      <c r="AA123">
+        <v>1.33</v>
+      </c>
+      <c r="AB123">
         <v>3.4</v>
       </c>
-      <c r="AA123">
-        <v>1.9</v>
-      </c>
-      <c r="AB123">
-        <v>2.01</v>
-      </c>
       <c r="AC123">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="AD123">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AF123">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AG123">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AK123">
-        <v>1.65</v>
+        <v>5.4</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
+        <v>2.86</v>
+      </c>
+      <c r="R124">
+        <v>2.07</v>
+      </c>
+      <c r="S124">
+        <v>1.38</v>
+      </c>
+      <c r="T124">
+        <v>2.77</v>
+      </c>
+      <c r="U124">
         <v>2.88</v>
-      </c>
-      <c r="R124">
-        <v>2.05</v>
-      </c>
-      <c r="S124">
-        <v>1.41</v>
-      </c>
-      <c r="T124">
-        <v>2.69</v>
-      </c>
-      <c r="U124">
-        <v>3</v>
       </c>
       <c r="V124">
         <v>1.36</v>
       </c>
       <c r="W124">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z124">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="AA124">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB124">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC124">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="AD124">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE124">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF124">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG124">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK124">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O139">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P139">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q139">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="R139">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S139">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T139">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="U139">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="V139">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X139">
+        <v>1.02</v>
+      </c>
+      <c r="Y139">
+        <v>1.27</v>
+      </c>
+      <c r="Z139">
+        <v>3.14</v>
+      </c>
+      <c r="AA139">
+        <v>1.98</v>
+      </c>
+      <c r="AB139">
+        <v>1.78</v>
+      </c>
+      <c r="AC139">
+        <v>3.46</v>
+      </c>
+      <c r="AD139">
+        <v>1.24</v>
+      </c>
+      <c r="AE139">
         <v>1.04</v>
       </c>
-      <c r="Y139">
-        <v>1.18</v>
-      </c>
-      <c r="Z139">
-        <v>3.88</v>
-      </c>
-      <c r="AA139">
-        <v>1.73</v>
-      </c>
-      <c r="AB139">
-        <v>2.05</v>
-      </c>
-      <c r="AC139">
-        <v>2.66</v>
-      </c>
-      <c r="AD139">
-        <v>1.36</v>
-      </c>
-      <c r="AE139">
-        <v>1.1</v>
-      </c>
       <c r="AF139">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AG139">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK139">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O140">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P140">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q140">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="R140">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="S140">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T140">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="U140">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="V140">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W140">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X140">
         <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z140">
-        <v>3.14</v>
+        <v>4.01</v>
       </c>
       <c r="AA140">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB140">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="AC140">
-        <v>3.46</v>
+        <v>2.74</v>
       </c>
       <c r="AD140">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE140">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF140">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK140">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,80 +23292,80 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="O141">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P141">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q141">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="R141">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S141">
+        <v>1.39</v>
+      </c>
+      <c r="T141">
+        <v>2.73</v>
+      </c>
+      <c r="U141">
+        <v>2.95</v>
+      </c>
+      <c r="V141">
+        <v>1.36</v>
+      </c>
+      <c r="W141">
+        <v>1.03</v>
+      </c>
+      <c r="X141">
+        <v>1</v>
+      </c>
+      <c r="Y141">
+        <v>1.27</v>
+      </c>
+      <c r="Z141">
+        <v>3.14</v>
+      </c>
+      <c r="AA141">
+        <v>1.98</v>
+      </c>
+      <c r="AB141">
+        <v>1.78</v>
+      </c>
+      <c r="AC141">
+        <v>3.34</v>
+      </c>
+      <c r="AD141">
+        <v>1.24</v>
+      </c>
+      <c r="AE141">
+        <v>1.04</v>
+      </c>
+      <c r="AF141">
+        <v>1.74</v>
+      </c>
+      <c r="AG141">
+        <v>1.98</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
+        <v>1.3</v>
+      </c>
+      <c r="AK141">
         <v>1.34</v>
-      </c>
-      <c r="T141">
-        <v>2.95</v>
-      </c>
-      <c r="U141">
-        <v>2.56</v>
-      </c>
-      <c r="V141">
-        <v>1.44</v>
-      </c>
-      <c r="W141">
-        <v>1.07</v>
-      </c>
-      <c r="X141">
-        <v>1.01</v>
-      </c>
-      <c r="Y141">
-        <v>1.28</v>
-      </c>
-      <c r="Z141">
-        <v>3.58</v>
-      </c>
-      <c r="AA141">
-        <v>1.79</v>
-      </c>
-      <c r="AB141">
-        <v>1.93</v>
-      </c>
-      <c r="AC141">
-        <v>3.5</v>
-      </c>
-      <c r="AD141">
-        <v>1.25</v>
-      </c>
-      <c r="AE141">
-        <v>1.06</v>
-      </c>
-      <c r="AF141">
-        <v>1.61</v>
-      </c>
-      <c r="AG141">
-        <v>2.18</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>1.43</v>
-      </c>
-      <c r="AK141">
-        <v>1.44</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O142">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q142">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="R142">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="S142">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T142">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="U142">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V142">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W142">
+        <v>1.07</v>
+      </c>
+      <c r="X142">
+        <v>1.01</v>
+      </c>
+      <c r="Y142">
+        <v>1.28</v>
+      </c>
+      <c r="Z142">
+        <v>3.58</v>
+      </c>
+      <c r="AA142">
+        <v>1.79</v>
+      </c>
+      <c r="AB142">
+        <v>1.93</v>
+      </c>
+      <c r="AC142">
+        <v>3.5</v>
+      </c>
+      <c r="AD142">
+        <v>1.25</v>
+      </c>
+      <c r="AE142">
         <v>1.06</v>
       </c>
-      <c r="X142">
-        <v>1.02</v>
-      </c>
-      <c r="Y142">
-        <v>1.18</v>
-      </c>
-      <c r="Z142">
-        <v>4.01</v>
-      </c>
-      <c r="AA142">
-        <v>1.73</v>
-      </c>
-      <c r="AB142">
-        <v>2.06</v>
-      </c>
-      <c r="AC142">
-        <v>2.74</v>
-      </c>
-      <c r="AD142">
-        <v>1.4</v>
-      </c>
-      <c r="AE142">
-        <v>1.1</v>
-      </c>
       <c r="AF142">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG142">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AK142">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="O145">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P145">
+        <v>3.3</v>
+      </c>
+      <c r="Q145">
+        <v>2.53</v>
+      </c>
+      <c r="R145">
         <v>2.15</v>
       </c>
-      <c r="Q145">
-        <v>3.3</v>
-      </c>
-      <c r="R145">
-        <v>2.1</v>
-      </c>
       <c r="S145">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T145">
-        <v>2.73</v>
+        <v>3.21</v>
       </c>
       <c r="U145">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="V145">
+        <v>1.46</v>
+      </c>
+      <c r="W145">
+        <v>1.07</v>
+      </c>
+      <c r="X145">
+        <v>1.04</v>
+      </c>
+      <c r="Y145">
+        <v>1.18</v>
+      </c>
+      <c r="Z145">
+        <v>3.88</v>
+      </c>
+      <c r="AA145">
+        <v>1.73</v>
+      </c>
+      <c r="AB145">
+        <v>2.05</v>
+      </c>
+      <c r="AC145">
+        <v>2.66</v>
+      </c>
+      <c r="AD145">
         <v>1.36</v>
       </c>
-      <c r="W145">
-        <v>1.03</v>
-      </c>
-      <c r="X145">
-        <v>1</v>
-      </c>
-      <c r="Y145">
-        <v>1.27</v>
-      </c>
-      <c r="Z145">
-        <v>3.14</v>
-      </c>
-      <c r="AA145">
-        <v>1.98</v>
-      </c>
-      <c r="AB145">
-        <v>1.78</v>
-      </c>
-      <c r="AC145">
-        <v>3.34</v>
-      </c>
-      <c r="AD145">
-        <v>1.24</v>
-      </c>
       <c r="AE145">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AG145">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK145">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.35</v>
+        <v>3.21</v>
       </c>
       <c r="O154">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="P154">
-        <v>8.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q154">
-        <v>1.82</v>
+        <v>4.16</v>
       </c>
       <c r="R154">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="S154">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T154">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="U154">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V154">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
         <v>1.07</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z154">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="AA154">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB154">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AC154">
-        <v>2.64</v>
+        <v>2.99</v>
       </c>
       <c r="AD154">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE154">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF154">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="AG154">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK154">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
+        <v>1.35</v>
+      </c>
+      <c r="O155">
+        <v>4.9</v>
+      </c>
+      <c r="P155">
+        <v>8.15</v>
+      </c>
+      <c r="Q155">
+        <v>1.82</v>
+      </c>
+      <c r="R155">
+        <v>2.43</v>
+      </c>
+      <c r="S155">
+        <v>1.31</v>
+      </c>
+      <c r="T155">
         <v>3.21</v>
       </c>
-      <c r="O155">
-        <v>3.55</v>
-      </c>
-      <c r="P155">
-        <v>2.13</v>
-      </c>
-      <c r="Q155">
-        <v>4.16</v>
-      </c>
-      <c r="R155">
-        <v>2.09</v>
-      </c>
-      <c r="S155">
-        <v>1.36</v>
-      </c>
-      <c r="T155">
-        <v>2.9</v>
-      </c>
       <c r="U155">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W155">
         <v>1.07</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="AA155">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AB155">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC155">
-        <v>2.99</v>
+        <v>2.64</v>
       </c>
       <c r="AD155">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF155">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="AG155">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK155">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="O158">
-        <v>3.71</v>
+        <v>4.54</v>
       </c>
       <c r="P158">
-        <v>3.77</v>
+        <v>6.54</v>
       </c>
       <c r="Q158">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="R158">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="S158">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U158">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="V158">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W158">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X158">
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA158">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB158">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC158">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AD158">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AE158">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF158">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG158">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK158">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="O159">
-        <v>4.54</v>
+        <v>3.71</v>
       </c>
       <c r="P159">
-        <v>6.54</v>
+        <v>3.77</v>
       </c>
       <c r="Q159">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="R159">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="S159">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T159">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U159">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="V159">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W159">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA159">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB159">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC159">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD159">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AE159">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF159">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG159">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK159">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O164">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P164">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="Q164">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R164">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S164">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T164">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="U164">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="V164">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W164">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X164">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y164">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z164">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="AA164">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AB164">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="AC164">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="AD164">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE164">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF164">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG164">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK164">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,64 +27204,64 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O165">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P165">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q165">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="R165">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S165">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T165">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U165">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="V165">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W165">
+        <v>1.06</v>
+      </c>
+      <c r="X165">
+        <v>1.02</v>
+      </c>
+      <c r="Y165">
+        <v>1.19</v>
+      </c>
+      <c r="Z165">
+        <v>3.82</v>
+      </c>
+      <c r="AA165">
+        <v>1.76</v>
+      </c>
+      <c r="AB165">
+        <v>2.03</v>
+      </c>
+      <c r="AC165">
+        <v>2.76</v>
+      </c>
+      <c r="AD165">
+        <v>1.35</v>
+      </c>
+      <c r="AE165">
         <v>1.09</v>
       </c>
-      <c r="X165">
-        <v>1.03</v>
-      </c>
-      <c r="Y165">
-        <v>1.14</v>
-      </c>
-      <c r="Z165">
-        <v>4.35</v>
-      </c>
-      <c r="AA165">
-        <v>1.61</v>
-      </c>
-      <c r="AB165">
-        <v>2.27</v>
-      </c>
-      <c r="AC165">
-        <v>2.36</v>
-      </c>
-      <c r="AD165">
-        <v>1.47</v>
-      </c>
-      <c r="AE165">
-        <v>1.16</v>
-      </c>
       <c r="AF165">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG165">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AK165">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="O166">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P166">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q166">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="R166">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S166">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T166">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="U166">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V166">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W166">
         <v>1.06</v>
       </c>
       <c r="X166">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y166">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z166">
-        <v>3.82</v>
+        <v>3.52</v>
       </c>
       <c r="AA166">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB166">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC166">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AD166">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE166">
         <v>1.09</v>
       </c>
       <c r="AF166">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG166">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK166">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O167">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P167">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="Q167">
         <v>2.2</v>
       </c>
       <c r="R167">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S167">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T167">
+        <v>3.23</v>
+      </c>
+      <c r="U167">
+        <v>2.44</v>
+      </c>
+      <c r="V167">
+        <v>1.45</v>
+      </c>
+      <c r="W167">
+        <v>1.08</v>
+      </c>
+      <c r="X167">
+        <v>1.02</v>
+      </c>
+      <c r="Y167">
+        <v>1.24</v>
+      </c>
+      <c r="Z167">
+        <v>3.7</v>
+      </c>
+      <c r="AA167">
+        <v>1.71</v>
+      </c>
+      <c r="AB167">
+        <v>2.04</v>
+      </c>
+      <c r="AC167">
         <v>2.94</v>
       </c>
-      <c r="U167">
-        <v>2.7</v>
-      </c>
-      <c r="V167">
-        <v>1.43</v>
-      </c>
-      <c r="W167">
-        <v>1.06</v>
-      </c>
-      <c r="X167">
-        <v>1.01</v>
-      </c>
-      <c r="Y167">
-        <v>1.22</v>
-      </c>
-      <c r="Z167">
-        <v>3.52</v>
-      </c>
-      <c r="AA167">
-        <v>1.82</v>
-      </c>
-      <c r="AB167">
-        <v>1.95</v>
-      </c>
-      <c r="AC167">
-        <v>2.82</v>
-      </c>
       <c r="AD167">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE167">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF167">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG167">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
         <v>1.23</v>
       </c>
       <c r="AK167">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,65 +28997,65 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA176">
+        <v>1.82</v>
+      </c>
+      <c r="AB176">
+        <v>1.87</v>
+      </c>
+      <c r="AC176">
+        <v>3.04</v>
+      </c>
+      <c r="AD176">
+        <v>1.29</v>
+      </c>
+      <c r="AE176">
+        <v>1.07</v>
+      </c>
+      <c r="AF176">
+        <v>1.65</v>
+      </c>
+      <c r="AG176">
         <v>2.07</v>
       </c>
-      <c r="AB176">
-        <v>1.72</v>
-      </c>
-      <c r="AC176">
-        <v>0</v>
-      </c>
-      <c r="AD176">
-        <v>0</v>
-      </c>
-      <c r="AE176">
-        <v>0</v>
-      </c>
-      <c r="AF176">
-        <v>0</v>
-      </c>
-      <c r="AG176">
-        <v>0</v>
-      </c>
       <c r="AH176" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O184">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P184">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30470,19 +30470,19 @@
         <v>3.2</v>
       </c>
       <c r="P185">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="Q185">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R185">
         <v>2.05</v>
       </c>
       <c r="S185">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T185">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U185">
         <v>2.75</v>
@@ -30491,34 +30491,34 @@
         <v>1.4</v>
       </c>
       <c r="W185">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X185">
         <v>1</v>
       </c>
       <c r="Y185">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z185">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="AA185">
         <v>2.04</v>
       </c>
       <c r="AB185">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC185">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AD185">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE185">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF185">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG185">
         <v>2.05</v>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AK185">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30962,55 +30962,55 @@
         <v>0</v>
       </c>
       <c r="Q188">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R188">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S188">
         <v>1.4</v>
       </c>
       <c r="T188">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U188">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V188">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W188">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X188">
         <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z188">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA188">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AB188">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC188">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AD188">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE188">
         <v>1.04</v>
       </c>
       <c r="AF188">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG188">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK188">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31611,25 +31611,25 @@
         <v>4.3</v>
       </c>
       <c r="P192">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q192">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R192">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S192">
         <v>1.17</v>
       </c>
       <c r="T192">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="U192">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V192">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W192">
         <v>1.13</v>
@@ -31644,13 +31644,13 @@
         <v>5.25</v>
       </c>
       <c r="AA192">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB192">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC192">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD192">
         <v>1.61</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK192">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31940,10 +31940,10 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="R194">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="S194">
         <v>1.38</v>
@@ -31955,7 +31955,7 @@
         <v>2.75</v>
       </c>
       <c r="V194">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W194">
         <v>1.05</v>
@@ -31967,16 +31967,16 @@
         <v>1.26</v>
       </c>
       <c r="Z194">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA194">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB194">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC194">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AD194">
         <v>1.28</v>
@@ -31985,7 +31985,7 @@
         <v>1.07</v>
       </c>
       <c r="AF194">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG194">
         <v>1.8</v>
@@ -32094,34 +32094,34 @@
         </is>
       </c>
       <c r="N195">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="O195">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="P195">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q195">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="R195">
         <v>2.56</v>
       </c>
       <c r="S195">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="T195">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="U195">
         <v>1.85</v>
       </c>
       <c r="V195">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W195">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X195">
         <v>1.01</v>
@@ -32133,25 +32133,25 @@
         <v>6.45</v>
       </c>
       <c r="AA195">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB195">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC195">
         <v>1.86</v>
       </c>
       <c r="AD195">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AE195">
         <v>1.42</v>
       </c>
       <c r="AF195">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AG195">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,28 +32257,28 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O196">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P196">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Q196">
         <v>2.62</v>
       </c>
       <c r="R196">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S196">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T196">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U196">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V196">
         <v>1.68</v>
@@ -32290,16 +32290,16 @@
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z196">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA196">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB196">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC196">
         <v>2.06</v>
@@ -32311,10 +32311,10 @@
         <v>1.26</v>
       </c>
       <c r="AF196">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG196">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK196">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -34059,55 +34059,55 @@
         <v>0</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA207">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB207">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="O208">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P208">
         <v>2.59</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA208">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB208">
+        <v>1.71</v>
+      </c>
+      <c r="AC208">
+        <v>3.34</v>
+      </c>
+      <c r="AD208">
+        <v>1.24</v>
+      </c>
+      <c r="AE208">
+        <v>1.05</v>
+      </c>
+      <c r="AF208">
         <v>1.75</v>
       </c>
-      <c r="AC208">
-        <v>0</v>
-      </c>
-      <c r="AD208">
-        <v>0</v>
-      </c>
-      <c r="AE208">
-        <v>0</v>
-      </c>
-      <c r="AF208">
-        <v>0</v>
-      </c>
       <c r="AG208">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34714,16 +34714,16 @@
         <v>2.75</v>
       </c>
       <c r="R211">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S211">
         <v>1.4</v>
       </c>
       <c r="T211">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U211">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="V211">
         <v>1.36</v>
@@ -34741,22 +34741,22 @@
         <v>3.24</v>
       </c>
       <c r="AA211">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB211">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC211">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="AD211">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE211">
         <v>1.05</v>
       </c>
       <c r="AF211">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG211">
         <v>2.01</v>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK211">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O221">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P221">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36495,25 +36495,25 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O222">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="P222">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="Q222">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R222">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S222">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T222">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="U222">
         <v>2.4</v>
@@ -36528,16 +36528,16 @@
         <v>1.02</v>
       </c>
       <c r="Y222">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z222">
-        <v>3.98</v>
+        <v>4.9</v>
       </c>
       <c r="AA222">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB222">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC222">
         <v>2.52</v>
@@ -36546,10 +36546,10 @@
         <v>1.41</v>
       </c>
       <c r="AE222">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF222">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG222">
         <v>2.15</v>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK222">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36830,7 +36830,7 @@
         <v>2.8</v>
       </c>
       <c r="Q224">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R224">
         <v>1.93</v>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK224">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>2.66</v>
       </c>
       <c r="AA225">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB225">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC225">
         <v>4.1</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="O234">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P234">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Q234">
         <v>9</v>
@@ -38472,19 +38472,19 @@
         <v>3.28</v>
       </c>
       <c r="U234">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="V234">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W234">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X234">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z234">
         <v>4.05</v>
@@ -38493,22 +38493,22 @@
         <v>1.66</v>
       </c>
       <c r="AB234">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC234">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AD234">
         <v>1.42</v>
       </c>
       <c r="AE234">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF234">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AG234">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK234">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38777,31 +38777,31 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O236">
         <v>3.1</v>
       </c>
       <c r="P236">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q236">
+        <v>2.99</v>
+      </c>
+      <c r="R236">
+        <v>2</v>
+      </c>
+      <c r="S236">
+        <v>1.42</v>
+      </c>
+      <c r="T236">
+        <v>2.53</v>
+      </c>
+      <c r="U236">
         <v>3.04</v>
       </c>
-      <c r="R236">
-        <v>1.95</v>
-      </c>
-      <c r="S236">
-        <v>1.41</v>
-      </c>
-      <c r="T236">
-        <v>2.56</v>
-      </c>
-      <c r="U236">
-        <v>2.88</v>
-      </c>
       <c r="V236">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W236">
         <v>1.02</v>
@@ -38810,31 +38810,31 @@
         <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z236">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA236">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AB236">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC236">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="AD236">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE236">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF236">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG236">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38850,7 +38850,7 @@
         <v>1.28</v>
       </c>
       <c r="AK236">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -39432,31 +39432,31 @@
         <v>1.5</v>
       </c>
       <c r="O240">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P240">
         <v>4.6</v>
       </c>
       <c r="Q240">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="R240">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S240">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T240">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U240">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="V240">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="W240">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X240">
         <v>1.02</v>
@@ -39465,22 +39465,22 @@
         <v>1.12</v>
       </c>
       <c r="Z240">
-        <v>5.65</v>
+        <v>5.9</v>
       </c>
       <c r="AA240">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB240">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AC240">
         <v>2.1</v>
       </c>
       <c r="AD240">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AE240">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF240">
         <v>1.49</v>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK240">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39613,10 +39613,10 @@
         <v>2.83</v>
       </c>
       <c r="U241">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V241">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -39646,7 +39646,7 @@
         <v>1.07</v>
       </c>
       <c r="AF241">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG241">
         <v>2.07</v>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK241">
         <v>1.42</v>
@@ -39755,19 +39755,19 @@
         </is>
       </c>
       <c r="N242">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O242">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P242">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q242">
         <v>5.5</v>
       </c>
       <c r="R242">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S242">
         <v>1.32</v>
@@ -39776,13 +39776,13 @@
         <v>2.9</v>
       </c>
       <c r="U242">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="V242">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W242">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X242">
         <v>1</v>
@@ -39794,19 +39794,19 @@
         <v>3.42</v>
       </c>
       <c r="AA242">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB242">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC242">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD242">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE242">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF242">
         <v>1.85</v>
@@ -39825,7 +39825,7 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK242">
         <v>1.12</v>
@@ -40102,7 +40102,7 @@
         <v>2.95</v>
       </c>
       <c r="U244">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V244">
         <v>1.44</v>
@@ -40129,16 +40129,16 @@
         <v>2.81</v>
       </c>
       <c r="AD244">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE244">
         <v>1.1</v>
       </c>
       <c r="AF244">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG244">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>1.2</v>
       </c>
       <c r="AK244">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40244,31 +40244,31 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="O245">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P245">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q245">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="R245">
         <v>2.15</v>
       </c>
       <c r="S245">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T245">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="U245">
         <v>3</v>
       </c>
       <c r="V245">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W245">
         <v>1.05</v>
@@ -40277,16 +40277,16 @@
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z245">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="AA245">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB245">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC245">
         <v>3.44</v>
@@ -40298,10 +40298,10 @@
         <v>1.05</v>
       </c>
       <c r="AF245">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG245">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40579,28 +40579,28 @@
         <v>3.3</v>
       </c>
       <c r="Q247">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R247">
         <v>2.02</v>
       </c>
       <c r="S247">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T247">
-        <v>2.82</v>
+        <v>3.4</v>
       </c>
       <c r="U247">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V247">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W247">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X247">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y247">
         <v>1.15</v>
@@ -40612,7 +40612,7 @@
         <v>1.6</v>
       </c>
       <c r="AB247">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC247">
         <v>2.28</v>
@@ -40621,7 +40621,7 @@
         <v>1.5</v>
       </c>
       <c r="AE247">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF247">
         <v>1.47</v>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK247">
         <v>1.57</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB249">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O253">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P253">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41723,43 +41723,43 @@
         <v>2.5</v>
       </c>
       <c r="R254">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S254">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T254">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="U254">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V254">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W254">
         <v>1.07</v>
       </c>
       <c r="X254">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y254">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z254">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AA254">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB254">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC254">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="AD254">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE254">
         <v>1.14</v>
@@ -41768,7 +41768,7 @@
         <v>1.6</v>
       </c>
       <c r="AG254">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -42363,34 +42363,34 @@
         </is>
       </c>
       <c r="N258">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O258">
-        <v>8.550000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="P258">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Q258">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R258">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="S258">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T258">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U258">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="V258">
         <v>2.09</v>
       </c>
       <c r="W258">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X258">
         <v>1</v>
@@ -42408,16 +42408,16 @@
         <v>4</v>
       </c>
       <c r="AC258">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AD258">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AE258">
         <v>1.55</v>
       </c>
       <c r="AF258">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG258">
         <v>2</v>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK258">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42547,10 +42547,10 @@
         <v>2.62</v>
       </c>
       <c r="U259">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V259">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W259">
         <v>1.02</v>
@@ -42580,7 +42580,7 @@
         <v>1.03</v>
       </c>
       <c r="AF259">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG259">
         <v>1.75</v>
@@ -42698,7 +42698,7 @@
         <v>0</v>
       </c>
       <c r="Q260">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="R260">
         <v>1.98</v>
@@ -42746,7 +42746,7 @@
         <v>1.85</v>
       </c>
       <c r="AG260">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42870,7 +42870,7 @@
         <v>1.42</v>
       </c>
       <c r="T261">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U261">
         <v>3.08</v>
@@ -42891,10 +42891,10 @@
         <v>2.88</v>
       </c>
       <c r="AA261">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AB261">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC261">
         <v>3.8</v>
@@ -43341,19 +43341,19 @@
         </is>
       </c>
       <c r="N264">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O264">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="P264">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="Q264">
         <v>2.5</v>
       </c>
       <c r="R264">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="S264">
         <v>1.26</v>
@@ -43374,22 +43374,22 @@
         <v>1.02</v>
       </c>
       <c r="Y264">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z264">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA264">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB264">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC264">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD264">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE264">
         <v>1.2</v>
@@ -43398,7 +43398,7 @@
         <v>1.44</v>
       </c>
       <c r="AG264">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK264">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43507,61 +43507,61 @@
         <v>1.8</v>
       </c>
       <c r="O265">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="P265">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="Q265">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="R265">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S265">
         <v>1.31</v>
       </c>
       <c r="T265">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="U265">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V265">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W265">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X265">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y265">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z265">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="AA265">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB265">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC265">
         <v>2.81</v>
       </c>
       <c r="AD265">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE265">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF265">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG265">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK265">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43830,7 +43830,7 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O267">
         <v>3.5</v>
@@ -43839,25 +43839,25 @@
         <v>3.9</v>
       </c>
       <c r="Q267">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R267">
         <v>2.1</v>
       </c>
       <c r="S267">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T267">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="U267">
         <v>2.96</v>
       </c>
       <c r="V267">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W267">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X267">
         <v>1.02</v>
@@ -43869,19 +43869,19 @@
         <v>3.05</v>
       </c>
       <c r="AA267">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB267">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC267">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AD267">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE267">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF267">
         <v>1.89</v>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK267">
         <v>1.95</v>
@@ -43993,10 +43993,10 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O268">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P268">
         <v>2.87</v>
@@ -44011,10 +44011,10 @@
         <v>1.35</v>
       </c>
       <c r="T268">
-        <v>2.82</v>
+        <v>3.07</v>
       </c>
       <c r="U268">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V268">
         <v>1.39</v>
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O273">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P273">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA273">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB273">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44971,43 +44971,43 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O274">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P274">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA274">
         <v>1.8</v>
@@ -45016,19 +45016,19 @@
         <v>2</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45460,16 +45460,16 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O277">
+        <v>3.05</v>
+      </c>
+      <c r="P277">
         <v>3</v>
       </c>
-      <c r="P277">
-        <v>2.87</v>
-      </c>
       <c r="Q277">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="R277">
         <v>2</v>
@@ -45481,7 +45481,7 @@
         <v>2.62</v>
       </c>
       <c r="U277">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="V277">
         <v>1.33</v>
@@ -45493,31 +45493,31 @@
         <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z277">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA277">
         <v>2.1</v>
       </c>
       <c r="AB277">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC277">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AD277">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE277">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF277">
         <v>1.79</v>
       </c>
       <c r="AG277">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK277">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -46112,7 +46112,7 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O281">
         <v>3.22</v>
@@ -46275,19 +46275,19 @@
         </is>
       </c>
       <c r="N282">
-        <v>5.03</v>
+        <v>5.25</v>
       </c>
       <c r="O282">
-        <v>4.72</v>
+        <v>4.4</v>
       </c>
       <c r="P282">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q282">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="R282">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="S282">
         <v>1.16</v>
@@ -46296,10 +46296,10 @@
         <v>4.05</v>
       </c>
       <c r="U282">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V282">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W282">
         <v>1.18</v>
@@ -46308,28 +46308,28 @@
         <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z282">
-        <v>5.8</v>
+        <v>6.12</v>
       </c>
       <c r="AA282">
         <v>1.4</v>
       </c>
       <c r="AB282">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AC282">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD282">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE282">
         <v>1.3</v>
       </c>
       <c r="AF282">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG282">
         <v>2.63</v>
@@ -46438,7 +46438,7 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O283">
         <v>2.9</v>
@@ -46456,7 +46456,7 @@
         <v>1.5</v>
       </c>
       <c r="T283">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="U283">
         <v>3.38</v>
@@ -46471,13 +46471,13 @@
         <v>1.05</v>
       </c>
       <c r="Y283">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z283">
         <v>2.46</v>
       </c>
       <c r="AA283">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB283">
         <v>1.51</v>
@@ -47579,19 +47579,19 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O290">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P290">
-        <v>7.5</v>
+        <v>7.85</v>
       </c>
       <c r="Q290">
         <v>1.83</v>
       </c>
       <c r="R290">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="S290">
         <v>1.32</v>
@@ -47600,34 +47600,34 @@
         <v>3.25</v>
       </c>
       <c r="U290">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V290">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W290">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X290">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y290">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z290">
-        <v>3.78</v>
+        <v>3.93</v>
       </c>
       <c r="AA290">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB290">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC290">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AD290">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE290">
         <v>1.1</v>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK290">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O293">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P293">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q293">
         <v>2.33</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q294">
         <v>2.3</v>
@@ -48394,7 +48394,7 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O295">
         <v>4</v>
@@ -48406,7 +48406,7 @@
         <v>3.04</v>
       </c>
       <c r="R295">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="S295">
         <v>1.14</v>
@@ -48415,25 +48415,25 @@
         <v>4.8</v>
       </c>
       <c r="U295">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V295">
         <v>1.8</v>
       </c>
       <c r="W295">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X295">
         <v>1.01</v>
       </c>
       <c r="Y295">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z295">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA295">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB295">
         <v>3.4</v>
@@ -48442,16 +48442,16 @@
         <v>1.86</v>
       </c>
       <c r="AD295">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AE295">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AF295">
         <v>1.3</v>
       </c>
       <c r="AG295">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK295">
         <v>1.45</v>
@@ -49209,22 +49209,22 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O300">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="P300">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q300">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R300">
         <v>2.25</v>
       </c>
       <c r="S300">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T300">
         <v>2.77</v>
@@ -49233,40 +49233,40 @@
         <v>2.75</v>
       </c>
       <c r="V300">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W300">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X300">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y300">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z300">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA300">
         <v>1.9</v>
       </c>
       <c r="AB300">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC300">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD300">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE300">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF300">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG300">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK300">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -50682,49 +50682,49 @@
         <v>3.85</v>
       </c>
       <c r="P309">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q309">
         <v>2.3</v>
       </c>
       <c r="R309">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S309">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T309">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="U309">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="V309">
         <v>1.42</v>
       </c>
       <c r="W309">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X309">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y309">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z309">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="AA309">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB309">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC309">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AD309">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE309">
         <v>1.08</v>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK309">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O310">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P310">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -51340,7 +51340,7 @@
         <v>2.81</v>
       </c>
       <c r="R313">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S313">
         <v>1.42</v>
@@ -51349,7 +51349,7 @@
         <v>2.53</v>
       </c>
       <c r="U313">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V313">
         <v>1.29</v>
@@ -51980,7 +51980,7 @@
         </is>
       </c>
       <c r="N317">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="O317">
         <v>3.2</v>
@@ -52001,28 +52001,28 @@
         <v>2.91</v>
       </c>
       <c r="U317">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="V317">
         <v>1.38</v>
       </c>
       <c r="W317">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X317">
         <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z317">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AA317">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB317">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC317">
         <v>3.18</v>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK317">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O320">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P320">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52632,31 +52632,31 @@
         </is>
       </c>
       <c r="N321">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O321">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P321">
         <v>3.2</v>
       </c>
       <c r="Q321">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="R321">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S321">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T321">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U321">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="V321">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W321">
         <v>1.02</v>
@@ -52665,31 +52665,31 @@
         <v>1.02</v>
       </c>
       <c r="Y321">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z321">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA321">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB321">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC321">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD321">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE321">
         <v>1.03</v>
       </c>
       <c r="AF321">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG321">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK321">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="O322">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P322">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q322">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R322">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S322">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T322">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U322">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V322">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W322">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X322">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA322">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB322">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC322">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD322">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE322">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF322">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG322">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK322">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL322">
         <v>0